--- a/outputs/TAS_historical_prices.xlsx
+++ b/outputs/TAS_historical_prices.xlsx
@@ -528,16 +528,16 @@
         </is>
       </c>
       <c r="B5" s="5" t="n">
-        <v>90.53</v>
+        <v>89.92</v>
       </c>
       <c r="C5" s="5" t="n">
-        <v>103.26</v>
+        <v>102.15</v>
       </c>
       <c r="D5" s="5" t="n">
-        <v>92.29000000000001</v>
+        <v>91.38</v>
       </c>
       <c r="E5" s="5" t="n">
-        <v>105.42</v>
+        <v>103.97</v>
       </c>
     </row>
     <row r="6">
@@ -547,16 +547,16 @@
         </is>
       </c>
       <c r="B6" s="5" t="n">
-        <v>99.8</v>
+        <v>97.93000000000001</v>
       </c>
       <c r="C6" s="5" t="n">
-        <v>110.5</v>
+        <v>108.6</v>
       </c>
       <c r="D6" s="5" t="n">
-        <v>103.43</v>
+        <v>101.21</v>
       </c>
       <c r="E6" s="5" t="n">
-        <v>114.56</v>
+        <v>112.3</v>
       </c>
     </row>
     <row r="7">
@@ -566,16 +566,16 @@
         </is>
       </c>
       <c r="B7" s="5" t="n">
-        <v>84.16</v>
+        <v>84.48999999999999</v>
       </c>
       <c r="C7" s="5" t="n">
-        <v>92.41</v>
+        <v>92.78</v>
       </c>
       <c r="D7" s="5" t="n">
-        <v>87.95999999999999</v>
+        <v>88.06</v>
       </c>
       <c r="E7" s="5" t="n">
-        <v>96.59</v>
+        <v>96.73</v>
       </c>
     </row>
     <row r="8">
@@ -585,16 +585,16 @@
         </is>
       </c>
       <c r="B8" s="5" t="n">
-        <v>89.62</v>
+        <v>90.53</v>
       </c>
       <c r="C8" s="5" t="n">
-        <v>99</v>
+        <v>99.92</v>
       </c>
       <c r="D8" s="5" t="n">
-        <v>98.08</v>
+        <v>98.84</v>
       </c>
       <c r="E8" s="5" t="n">
-        <v>108.45</v>
+        <v>109.19</v>
       </c>
     </row>
     <row r="9">
@@ -604,22 +604,22 @@
         </is>
       </c>
       <c r="B9" s="5" t="n">
-        <v>80.01000000000001</v>
+        <v>80.43000000000001</v>
       </c>
       <c r="C9" s="5" t="n">
-        <v>87.7</v>
+        <v>88.06</v>
       </c>
       <c r="D9" s="5" t="n">
-        <v>94.65000000000001</v>
+        <v>94.94</v>
       </c>
       <c r="E9" s="5" t="n">
-        <v>103.76</v>
+        <v>103.95</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="6" t="inlineStr">
         <is>
-          <t>Data through: Apr 2026</t>
+          <t>Data through: May 2026</t>
         </is>
       </c>
     </row>
@@ -634,7 +634,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F253"/>
+  <dimension ref="A1:F254"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -5813,6 +5813,26 @@
       </c>
       <c r="F253" s="7" t="inlineStr"/>
     </row>
+    <row r="254">
+      <c r="A254" s="4" t="inlineStr">
+        <is>
+          <t>May 2026</t>
+        </is>
+      </c>
+      <c r="B254" s="5" t="n">
+        <v>96.14</v>
+      </c>
+      <c r="C254" s="5" t="n">
+        <v>100.08</v>
+      </c>
+      <c r="D254" s="5" t="n">
+        <v>96.14</v>
+      </c>
+      <c r="E254" s="5" t="n">
+        <v>100.08</v>
+      </c>
+      <c r="F254" s="7" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -5824,7 +5844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E253"/>
+  <dimension ref="A1:E254"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -10649,8 +10669,27 @@
         <v>87.34</v>
       </c>
     </row>
+    <row r="254">
+      <c r="A254" s="4" t="inlineStr">
+        <is>
+          <t>May 2026</t>
+        </is>
+      </c>
+      <c r="B254" s="5" t="n">
+        <v>96.14</v>
+      </c>
+      <c r="C254" s="5" t="n">
+        <v>100.08</v>
+      </c>
+      <c r="D254" s="5" t="n">
+        <v>96.14</v>
+      </c>
+      <c r="E254" s="5" t="n">
+        <v>100.08</v>
+      </c>
+    </row>
   </sheetData>
-  <conditionalFormatting sqref="B2:B253">
+  <conditionalFormatting sqref="B2:B254">
     <cfRule type="colorScale" priority="1">
       <colorScale>
         <cfvo type="min"/>
@@ -10662,7 +10701,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C2:C253">
+  <conditionalFormatting sqref="C2:C254">
     <cfRule type="colorScale" priority="2">
       <colorScale>
         <cfvo type="min"/>
@@ -10674,7 +10713,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D2:D253">
+  <conditionalFormatting sqref="D2:D254">
     <cfRule type="colorScale" priority="3">
       <colorScale>
         <cfvo type="min"/>
@@ -10686,7 +10725,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E2:E253">
+  <conditionalFormatting sqref="E2:E254">
     <cfRule type="colorScale" priority="4">
       <colorScale>
         <cfvo type="min"/>

--- a/outputs/TAS_historical_prices.xlsx
+++ b/outputs/TAS_historical_prices.xlsx
@@ -528,16 +528,16 @@
         </is>
       </c>
       <c r="B5" s="5" t="n">
-        <v>89.92</v>
+        <v>78.05</v>
       </c>
       <c r="C5" s="5" t="n">
-        <v>102.15</v>
+        <v>81.63</v>
       </c>
       <c r="D5" s="5" t="n">
-        <v>91.38</v>
+        <v>78.90000000000001</v>
       </c>
       <c r="E5" s="5" t="n">
-        <v>103.97</v>
+        <v>82.54000000000001</v>
       </c>
     </row>
     <row r="6">
@@ -547,16 +547,16 @@
         </is>
       </c>
       <c r="B6" s="5" t="n">
-        <v>97.93000000000001</v>
+        <v>93.7</v>
       </c>
       <c r="C6" s="5" t="n">
-        <v>108.6</v>
+        <v>103.13</v>
       </c>
       <c r="D6" s="5" t="n">
-        <v>101.21</v>
+        <v>96.58</v>
       </c>
       <c r="E6" s="5" t="n">
-        <v>112.3</v>
+        <v>106.35</v>
       </c>
     </row>
     <row r="7">
@@ -566,16 +566,16 @@
         </is>
       </c>
       <c r="B7" s="5" t="n">
-        <v>84.48999999999999</v>
+        <v>85.56999999999999</v>
       </c>
       <c r="C7" s="5" t="n">
-        <v>92.78</v>
+        <v>93.59999999999999</v>
       </c>
       <c r="D7" s="5" t="n">
-        <v>88.06</v>
+        <v>89.04000000000001</v>
       </c>
       <c r="E7" s="5" t="n">
-        <v>96.73</v>
+        <v>97.40000000000001</v>
       </c>
     </row>
     <row r="8">
@@ -585,16 +585,16 @@
         </is>
       </c>
       <c r="B8" s="5" t="n">
-        <v>90.53</v>
+        <v>90.66</v>
       </c>
       <c r="C8" s="5" t="n">
-        <v>99.92</v>
+        <v>99.98</v>
       </c>
       <c r="D8" s="5" t="n">
-        <v>98.84</v>
+        <v>98.7</v>
       </c>
       <c r="E8" s="5" t="n">
-        <v>109.19</v>
+        <v>108.96</v>
       </c>
     </row>
     <row r="9">
@@ -604,22 +604,22 @@
         </is>
       </c>
       <c r="B9" s="5" t="n">
-        <v>80.43000000000001</v>
+        <v>80.47</v>
       </c>
       <c r="C9" s="5" t="n">
-        <v>88.06</v>
+        <v>87.91</v>
       </c>
       <c r="D9" s="5" t="n">
-        <v>94.94</v>
+        <v>94.77</v>
       </c>
       <c r="E9" s="5" t="n">
-        <v>103.95</v>
+        <v>103.51</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="6" t="inlineStr">
         <is>
-          <t>Data through: May 2026</t>
+          <t>Data through: Jun 2026</t>
         </is>
       </c>
     </row>
@@ -634,7 +634,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F254"/>
+  <dimension ref="A1:F255"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -5833,6 +5833,26 @@
       </c>
       <c r="F254" s="7" t="inlineStr"/>
     </row>
+    <row r="255">
+      <c r="A255" s="4" t="inlineStr">
+        <is>
+          <t>Jun 2026</t>
+        </is>
+      </c>
+      <c r="B255" s="5" t="n">
+        <v>76.83</v>
+      </c>
+      <c r="C255" s="5" t="n">
+        <v>81.73</v>
+      </c>
+      <c r="D255" s="5" t="n">
+        <v>76.83</v>
+      </c>
+      <c r="E255" s="5" t="n">
+        <v>81.73</v>
+      </c>
+      <c r="F255" s="7" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -5844,7 +5864,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E254"/>
+  <dimension ref="A1:E255"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -10688,8 +10708,27 @@
         <v>100.08</v>
       </c>
     </row>
+    <row r="255">
+      <c r="A255" s="4" t="inlineStr">
+        <is>
+          <t>Jun 2026</t>
+        </is>
+      </c>
+      <c r="B255" s="5" t="n">
+        <v>76.83</v>
+      </c>
+      <c r="C255" s="5" t="n">
+        <v>81.73</v>
+      </c>
+      <c r="D255" s="5" t="n">
+        <v>76.83</v>
+      </c>
+      <c r="E255" s="5" t="n">
+        <v>81.73</v>
+      </c>
+    </row>
   </sheetData>
-  <conditionalFormatting sqref="B2:B254">
+  <conditionalFormatting sqref="B2:B255">
     <cfRule type="colorScale" priority="1">
       <colorScale>
         <cfvo type="min"/>
@@ -10701,7 +10740,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C2:C254">
+  <conditionalFormatting sqref="C2:C255">
     <cfRule type="colorScale" priority="2">
       <colorScale>
         <cfvo type="min"/>
@@ -10713,7 +10752,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D2:D254">
+  <conditionalFormatting sqref="D2:D255">
     <cfRule type="colorScale" priority="3">
       <colorScale>
         <cfvo type="min"/>
@@ -10725,7 +10764,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E2:E254">
+  <conditionalFormatting sqref="E2:E255">
     <cfRule type="colorScale" priority="4">
       <colorScale>
         <cfvo type="min"/>

--- a/outputs/TAS_historical_prices.xlsx
+++ b/outputs/TAS_historical_prices.xlsx
@@ -528,16 +528,16 @@
         </is>
       </c>
       <c r="B5" s="5" t="n">
-        <v>78.05</v>
+        <v>74.15000000000001</v>
       </c>
       <c r="C5" s="5" t="n">
-        <v>81.63</v>
+        <v>78.58</v>
       </c>
       <c r="D5" s="5" t="n">
-        <v>78.90000000000001</v>
+        <v>75.04000000000001</v>
       </c>
       <c r="E5" s="5" t="n">
-        <v>82.54000000000001</v>
+        <v>79.52</v>
       </c>
     </row>
     <row r="6">
@@ -547,16 +547,16 @@
         </is>
       </c>
       <c r="B6" s="5" t="n">
-        <v>93.7</v>
+        <v>89.13</v>
       </c>
       <c r="C6" s="5" t="n">
-        <v>103.13</v>
+        <v>98.06</v>
       </c>
       <c r="D6" s="5" t="n">
-        <v>96.58</v>
+        <v>92.09</v>
       </c>
       <c r="E6" s="5" t="n">
-        <v>106.35</v>
+        <v>101.33</v>
       </c>
     </row>
     <row r="7">
@@ -566,16 +566,16 @@
         </is>
       </c>
       <c r="B7" s="5" t="n">
-        <v>85.56999999999999</v>
+        <v>86.90000000000001</v>
       </c>
       <c r="C7" s="5" t="n">
-        <v>93.59999999999999</v>
+        <v>95.3</v>
       </c>
       <c r="D7" s="5" t="n">
-        <v>89.04000000000001</v>
+        <v>90.81</v>
       </c>
       <c r="E7" s="5" t="n">
-        <v>97.40000000000001</v>
+        <v>99.56999999999999</v>
       </c>
     </row>
     <row r="8">
@@ -585,16 +585,16 @@
         </is>
       </c>
       <c r="B8" s="5" t="n">
-        <v>90.66</v>
+        <v>91.20999999999999</v>
       </c>
       <c r="C8" s="5" t="n">
-        <v>99.98</v>
+        <v>100.83</v>
       </c>
       <c r="D8" s="5" t="n">
-        <v>98.7</v>
+        <v>99.67</v>
       </c>
       <c r="E8" s="5" t="n">
-        <v>108.96</v>
+        <v>110.27</v>
       </c>
     </row>
     <row r="9">
@@ -604,22 +604,22 @@
         </is>
       </c>
       <c r="B9" s="5" t="n">
-        <v>80.47</v>
+        <v>80.5</v>
       </c>
       <c r="C9" s="5" t="n">
-        <v>87.91</v>
+        <v>87.88</v>
       </c>
       <c r="D9" s="5" t="n">
-        <v>94.77</v>
+        <v>95.15000000000001</v>
       </c>
       <c r="E9" s="5" t="n">
-        <v>103.51</v>
+        <v>103.81</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="6" t="inlineStr">
         <is>
-          <t>Data through: Jun 2026</t>
+          <t>Data through: Jul 2026</t>
         </is>
       </c>
     </row>
@@ -634,7 +634,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F255"/>
+  <dimension ref="A1:F256"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -690,10 +690,10 @@
         <v>392.08</v>
       </c>
       <c r="D2" s="5" t="n">
-        <v>545.26</v>
+        <v>548.53</v>
       </c>
       <c r="E2" s="5" t="n">
-        <v>696.66</v>
+        <v>700.84</v>
       </c>
       <c r="F2" s="7" t="inlineStr"/>
     </row>
@@ -710,10 +710,10 @@
         <v>86.38</v>
       </c>
       <c r="D3" s="5" t="n">
-        <v>139.44</v>
+        <v>140.27</v>
       </c>
       <c r="E3" s="5" t="n">
-        <v>153.18</v>
+        <v>154.1</v>
       </c>
       <c r="F3" s="7" t="inlineStr"/>
     </row>
@@ -730,10 +730,10 @@
         <v>115.44</v>
       </c>
       <c r="D4" s="5" t="n">
-        <v>198.56</v>
+        <v>199.75</v>
       </c>
       <c r="E4" s="5" t="n">
-        <v>204.04</v>
+        <v>205.26</v>
       </c>
       <c r="F4" s="7" t="inlineStr"/>
     </row>
@@ -750,10 +750,10 @@
         <v>141.07</v>
       </c>
       <c r="D5" s="5" t="n">
-        <v>188.85</v>
+        <v>189.98</v>
       </c>
       <c r="E5" s="5" t="n">
-        <v>248.52</v>
+        <v>250.01</v>
       </c>
       <c r="F5" s="7" t="inlineStr"/>
     </row>
@@ -770,10 +770,10 @@
         <v>78.06</v>
       </c>
       <c r="D6" s="5" t="n">
-        <v>121.77</v>
+        <v>122.5</v>
       </c>
       <c r="E6" s="5" t="n">
-        <v>137.06</v>
+        <v>137.89</v>
       </c>
       <c r="F6" s="7" t="inlineStr"/>
     </row>
@@ -790,10 +790,10 @@
         <v>102.26</v>
       </c>
       <c r="D7" s="5" t="n">
-        <v>144.4</v>
+        <v>145.27</v>
       </c>
       <c r="E7" s="5" t="n">
-        <v>179.25</v>
+        <v>180.32</v>
       </c>
       <c r="F7" s="7" t="inlineStr"/>
     </row>
@@ -810,10 +810,10 @@
         <v>59.27</v>
       </c>
       <c r="D8" s="5" t="n">
-        <v>100.86</v>
+        <v>101.47</v>
       </c>
       <c r="E8" s="5" t="n">
-        <v>103.71</v>
+        <v>104.33</v>
       </c>
       <c r="F8" s="7" t="inlineStr"/>
     </row>
@@ -830,10 +830,10 @@
         <v>47</v>
       </c>
       <c r="D9" s="5" t="n">
-        <v>74.8</v>
+        <v>75.25</v>
       </c>
       <c r="E9" s="5" t="n">
-        <v>82.09999999999999</v>
+        <v>82.59</v>
       </c>
       <c r="F9" s="7" t="inlineStr"/>
     </row>
@@ -850,10 +850,10 @@
         <v>40.37</v>
       </c>
       <c r="D10" s="5" t="n">
-        <v>64.27</v>
+        <v>64.66</v>
       </c>
       <c r="E10" s="5" t="n">
-        <v>70.31999999999999</v>
+        <v>70.73999999999999</v>
       </c>
       <c r="F10" s="7" t="inlineStr"/>
     </row>
@@ -870,10 +870,10 @@
         <v>35.76</v>
       </c>
       <c r="D11" s="5" t="n">
-        <v>56.34</v>
+        <v>56.68</v>
       </c>
       <c r="E11" s="5" t="n">
-        <v>62.11</v>
+        <v>62.48</v>
       </c>
       <c r="F11" s="7" t="inlineStr"/>
     </row>
@@ -890,10 +890,10 @@
         <v>32.55</v>
       </c>
       <c r="D12" s="5" t="n">
-        <v>49.19</v>
+        <v>49.48</v>
       </c>
       <c r="E12" s="5" t="n">
-        <v>56.37</v>
+        <v>56.71</v>
       </c>
       <c r="F12" s="7" t="inlineStr"/>
     </row>
@@ -910,10 +910,10 @@
         <v>33.84</v>
       </c>
       <c r="D13" s="5" t="n">
-        <v>57.47</v>
+        <v>57.82</v>
       </c>
       <c r="E13" s="5" t="n">
-        <v>58.3</v>
+        <v>58.65</v>
       </c>
       <c r="F13" s="7" t="inlineStr"/>
     </row>
@@ -930,10 +930,10 @@
         <v>47.58</v>
       </c>
       <c r="D14" s="5" t="n">
-        <v>57.86</v>
+        <v>58.21</v>
       </c>
       <c r="E14" s="5" t="n">
-        <v>81.55</v>
+        <v>82.03</v>
       </c>
       <c r="F14" s="7" t="inlineStr"/>
     </row>
@@ -950,10 +950,10 @@
         <v>51.97</v>
       </c>
       <c r="D15" s="5" t="n">
-        <v>70.56999999999999</v>
+        <v>70.98999999999999</v>
       </c>
       <c r="E15" s="5" t="n">
-        <v>88.61</v>
+        <v>89.14</v>
       </c>
       <c r="F15" s="7" t="inlineStr"/>
     </row>
@@ -970,10 +970,10 @@
         <v>68.81</v>
       </c>
       <c r="D16" s="5" t="n">
-        <v>82</v>
+        <v>82.5</v>
       </c>
       <c r="E16" s="5" t="n">
-        <v>116.97</v>
+        <v>117.67</v>
       </c>
       <c r="F16" s="7" t="inlineStr"/>
     </row>
@@ -990,10 +990,10 @@
         <v>39.83</v>
       </c>
       <c r="D17" s="5" t="n">
-        <v>59.61</v>
+        <v>59.97</v>
       </c>
       <c r="E17" s="5" t="n">
-        <v>67.51000000000001</v>
+        <v>67.91</v>
       </c>
       <c r="F17" s="7" t="inlineStr"/>
     </row>
@@ -1010,10 +1010,10 @@
         <v>41.53</v>
       </c>
       <c r="D18" s="5" t="n">
-        <v>64.64</v>
+        <v>65.03</v>
       </c>
       <c r="E18" s="5" t="n">
-        <v>70.18000000000001</v>
+        <v>70.59999999999999</v>
       </c>
       <c r="F18" s="7" t="inlineStr"/>
     </row>
@@ -1030,10 +1030,10 @@
         <v>36.83</v>
       </c>
       <c r="D19" s="5" t="n">
-        <v>57.87</v>
+        <v>58.22</v>
       </c>
       <c r="E19" s="5" t="n">
-        <v>62.26</v>
+        <v>62.64</v>
       </c>
       <c r="F19" s="7" t="inlineStr"/>
     </row>
@@ -1050,10 +1050,10 @@
         <v>44.85</v>
       </c>
       <c r="D20" s="5" t="n">
-        <v>67.31</v>
+        <v>67.72</v>
       </c>
       <c r="E20" s="5" t="n">
-        <v>75.84999999999999</v>
+        <v>76.31</v>
       </c>
       <c r="F20" s="7" t="inlineStr"/>
     </row>
@@ -1070,10 +1070,10 @@
         <v>41.08</v>
       </c>
       <c r="D21" s="5" t="n">
-        <v>59.5</v>
+        <v>59.86</v>
       </c>
       <c r="E21" s="5" t="n">
-        <v>69.5</v>
+        <v>69.92</v>
       </c>
       <c r="F21" s="7" t="inlineStr"/>
     </row>
@@ -1090,10 +1090,10 @@
         <v>47.25</v>
       </c>
       <c r="D22" s="5" t="n">
-        <v>74.93000000000001</v>
+        <v>75.38</v>
       </c>
       <c r="E22" s="5" t="n">
-        <v>79.92</v>
+        <v>80.40000000000001</v>
       </c>
       <c r="F22" s="7" t="inlineStr"/>
     </row>
@@ -1110,10 +1110,10 @@
         <v>67.59999999999999</v>
       </c>
       <c r="D23" s="5" t="n">
-        <v>89.54000000000001</v>
+        <v>90.06999999999999</v>
       </c>
       <c r="E23" s="5" t="n">
-        <v>114.31</v>
+        <v>114.99</v>
       </c>
       <c r="F23" s="7" t="inlineStr"/>
     </row>
@@ -1130,10 +1130,10 @@
         <v>53.83</v>
       </c>
       <c r="D24" s="5" t="n">
-        <v>85.79000000000001</v>
+        <v>86.31</v>
       </c>
       <c r="E24" s="5" t="n">
-        <v>91</v>
+        <v>91.55</v>
       </c>
       <c r="F24" s="7" t="inlineStr"/>
     </row>
@@ -1150,10 +1150,10 @@
         <v>82.19</v>
       </c>
       <c r="D25" s="5" t="n">
-        <v>123.04</v>
+        <v>123.77</v>
       </c>
       <c r="E25" s="5" t="n">
-        <v>138.37</v>
+        <v>139.2</v>
       </c>
       <c r="F25" s="7" t="inlineStr"/>
     </row>
@@ -1170,10 +1170,10 @@
         <v>72.31</v>
       </c>
       <c r="D26" s="5" t="n">
-        <v>111.24</v>
+        <v>111.9</v>
       </c>
       <c r="E26" s="5" t="n">
-        <v>121.25</v>
+        <v>121.97</v>
       </c>
       <c r="F26" s="7" t="inlineStr"/>
     </row>
@@ -1190,10 +1190,10 @@
         <v>79.93000000000001</v>
       </c>
       <c r="D27" s="5" t="n">
-        <v>129.94</v>
+        <v>130.72</v>
       </c>
       <c r="E27" s="5" t="n">
-        <v>133.48</v>
+        <v>134.28</v>
       </c>
       <c r="F27" s="7" t="inlineStr"/>
     </row>
@@ -1210,10 +1210,10 @@
         <v>115.5</v>
       </c>
       <c r="D28" s="5" t="n">
-        <v>165.7</v>
+        <v>166.69</v>
       </c>
       <c r="E28" s="5" t="n">
-        <v>192.44</v>
+        <v>193.59</v>
       </c>
       <c r="F28" s="7" t="inlineStr"/>
     </row>
@@ -1230,10 +1230,10 @@
         <v>48.82</v>
       </c>
       <c r="D29" s="5" t="n">
-        <v>67.66</v>
+        <v>68.06</v>
       </c>
       <c r="E29" s="5" t="n">
-        <v>81.15000000000001</v>
+        <v>81.64</v>
       </c>
       <c r="F29" s="7" t="inlineStr"/>
     </row>
@@ -1250,10 +1250,10 @@
         <v>50.3</v>
       </c>
       <c r="D30" s="5" t="n">
-        <v>78.34999999999999</v>
+        <v>78.81999999999999</v>
       </c>
       <c r="E30" s="5" t="n">
-        <v>83.42</v>
+        <v>83.92</v>
       </c>
       <c r="F30" s="7" t="inlineStr"/>
     </row>
@@ -1270,10 +1270,10 @@
         <v>38.54</v>
       </c>
       <c r="D31" s="5" t="n">
-        <v>56.26</v>
+        <v>56.6</v>
       </c>
       <c r="E31" s="5" t="n">
-        <v>63.72</v>
+        <v>64.09999999999999</v>
       </c>
       <c r="F31" s="7" t="inlineStr"/>
     </row>
@@ -1290,10 +1290,10 @@
         <v>49.43</v>
       </c>
       <c r="D32" s="5" t="n">
-        <v>73.73999999999999</v>
+        <v>74.19</v>
       </c>
       <c r="E32" s="5" t="n">
-        <v>81.48</v>
+        <v>81.95999999999999</v>
       </c>
       <c r="F32" s="7" t="inlineStr"/>
     </row>
@@ -1310,10 +1310,10 @@
         <v>60.54</v>
       </c>
       <c r="D33" s="5" t="n">
-        <v>83.73999999999999</v>
+        <v>84.23999999999999</v>
       </c>
       <c r="E33" s="5" t="n">
-        <v>99.48</v>
+        <v>100.08</v>
       </c>
       <c r="F33" s="7" t="inlineStr"/>
     </row>
@@ -1330,10 +1330,10 @@
         <v>59.06</v>
       </c>
       <c r="D34" s="5" t="n">
-        <v>77.43000000000001</v>
+        <v>77.89</v>
       </c>
       <c r="E34" s="5" t="n">
-        <v>96.62</v>
+        <v>97.2</v>
       </c>
       <c r="F34" s="7" t="inlineStr"/>
     </row>
@@ -1350,10 +1350,10 @@
         <v>67.75</v>
       </c>
       <c r="D35" s="5" t="n">
-        <v>91.95999999999999</v>
+        <v>92.51000000000001</v>
       </c>
       <c r="E35" s="5" t="n">
-        <v>110.34</v>
+        <v>111</v>
       </c>
       <c r="F35" s="7" t="inlineStr"/>
     </row>
@@ -1370,10 +1370,10 @@
         <v>68.79000000000001</v>
       </c>
       <c r="D36" s="5" t="n">
-        <v>91.08</v>
+        <v>91.63</v>
       </c>
       <c r="E36" s="5" t="n">
-        <v>111.54</v>
+        <v>112.21</v>
       </c>
       <c r="F36" s="7" t="inlineStr"/>
     </row>
@@ -1390,10 +1390,10 @@
         <v>63.84</v>
       </c>
       <c r="D37" s="5" t="n">
-        <v>88.64</v>
+        <v>89.17</v>
       </c>
       <c r="E37" s="5" t="n">
-        <v>103.02</v>
+        <v>103.64</v>
       </c>
       <c r="F37" s="7" t="inlineStr"/>
     </row>
@@ -1410,10 +1410,10 @@
         <v>69.72</v>
       </c>
       <c r="D38" s="5" t="n">
-        <v>108.79</v>
+        <v>109.44</v>
       </c>
       <c r="E38" s="5" t="n">
-        <v>111.97</v>
+        <v>112.64</v>
       </c>
       <c r="F38" s="7" t="inlineStr"/>
     </row>
@@ -1430,10 +1430,10 @@
         <v>63.27</v>
       </c>
       <c r="D39" s="5" t="n">
-        <v>89.44</v>
+        <v>89.98</v>
       </c>
       <c r="E39" s="5" t="n">
-        <v>101.12</v>
+        <v>101.73</v>
       </c>
       <c r="F39" s="7" t="inlineStr"/>
     </row>
@@ -1450,10 +1450,10 @@
         <v>30.26</v>
       </c>
       <c r="D40" s="5" t="n">
-        <v>48.34</v>
+        <v>48.63</v>
       </c>
       <c r="E40" s="5" t="n">
-        <v>48.18</v>
+        <v>48.47</v>
       </c>
       <c r="F40" s="7" t="inlineStr"/>
     </row>
@@ -1470,10 +1470,10 @@
         <v>60.94</v>
       </c>
       <c r="D41" s="5" t="n">
-        <v>87.17</v>
+        <v>87.69</v>
       </c>
       <c r="E41" s="5" t="n">
-        <v>96.65000000000001</v>
+        <v>97.23</v>
       </c>
       <c r="F41" s="7" t="inlineStr"/>
     </row>
@@ -1490,10 +1490,10 @@
         <v>53.5</v>
       </c>
       <c r="D42" s="5" t="n">
-        <v>69.42</v>
+        <v>69.84</v>
       </c>
       <c r="E42" s="5" t="n">
-        <v>84.53</v>
+        <v>85.03</v>
       </c>
       <c r="F42" s="7" t="inlineStr"/>
     </row>
@@ -1510,10 +1510,10 @@
         <v>56.32</v>
       </c>
       <c r="D43" s="5" t="n">
-        <v>72.63</v>
+        <v>73.06</v>
       </c>
       <c r="E43" s="5" t="n">
-        <v>89.08</v>
+        <v>89.61</v>
       </c>
       <c r="F43" s="7" t="inlineStr"/>
     </row>
@@ -1530,10 +1530,10 @@
         <v>61.31</v>
       </c>
       <c r="D44" s="5" t="n">
-        <v>80.28</v>
+        <v>80.76000000000001</v>
       </c>
       <c r="E44" s="5" t="n">
-        <v>97.08</v>
+        <v>97.66</v>
       </c>
       <c r="F44" s="7" t="inlineStr"/>
     </row>
@@ -1550,10 +1550,10 @@
         <v>38.3</v>
       </c>
       <c r="D45" s="5" t="n">
-        <v>52.17</v>
+        <v>52.48</v>
       </c>
       <c r="E45" s="5" t="n">
-        <v>60.71</v>
+        <v>61.07</v>
       </c>
       <c r="F45" s="7" t="inlineStr"/>
     </row>
@@ -1570,10 +1570,10 @@
         <v>119.63</v>
       </c>
       <c r="D46" s="5" t="n">
-        <v>124.99</v>
+        <v>125.74</v>
       </c>
       <c r="E46" s="5" t="n">
-        <v>189.56</v>
+        <v>190.69</v>
       </c>
       <c r="F46" s="7" t="inlineStr"/>
     </row>
@@ -1590,10 +1590,10 @@
         <v>63.91</v>
       </c>
       <c r="D47" s="5" t="n">
-        <v>61.9</v>
+        <v>62.27</v>
       </c>
       <c r="E47" s="5" t="n">
-        <v>101.23</v>
+        <v>101.84</v>
       </c>
       <c r="F47" s="7" t="inlineStr"/>
     </row>
@@ -1610,10 +1610,10 @@
         <v>43.73</v>
       </c>
       <c r="D48" s="5" t="n">
-        <v>57.76</v>
+        <v>58.11</v>
       </c>
       <c r="E48" s="5" t="n">
-        <v>69.23999999999999</v>
+        <v>69.66</v>
       </c>
       <c r="F48" s="7" t="inlineStr"/>
     </row>
@@ -1630,10 +1630,10 @@
         <v>63.23</v>
       </c>
       <c r="D49" s="5" t="n">
-        <v>109.56</v>
+        <v>110.22</v>
       </c>
       <c r="E49" s="5" t="n">
-        <v>99.95</v>
+        <v>100.55</v>
       </c>
       <c r="F49" s="7" t="inlineStr"/>
     </row>
@@ -1650,10 +1650,10 @@
         <v>50.07</v>
       </c>
       <c r="D50" s="5" t="n">
-        <v>73.92</v>
+        <v>74.36</v>
       </c>
       <c r="E50" s="5" t="n">
-        <v>79.02</v>
+        <v>79.48999999999999</v>
       </c>
       <c r="F50" s="7" t="inlineStr"/>
     </row>
@@ -1670,10 +1670,10 @@
         <v>292.02</v>
       </c>
       <c r="D51" s="5" t="n">
-        <v>273.83</v>
+        <v>275.47</v>
       </c>
       <c r="E51" s="5" t="n">
-        <v>460.08</v>
+        <v>462.84</v>
       </c>
       <c r="F51" s="7" t="inlineStr"/>
     </row>
@@ -1690,10 +1690,10 @@
         <v>31.68</v>
       </c>
       <c r="D52" s="5" t="n">
-        <v>40.66</v>
+        <v>40.91</v>
       </c>
       <c r="E52" s="5" t="n">
-        <v>49.76</v>
+        <v>50.05</v>
       </c>
       <c r="F52" s="7" t="inlineStr"/>
     </row>
@@ -1710,10 +1710,10 @@
         <v>28.03</v>
       </c>
       <c r="D53" s="5" t="n">
-        <v>33.33</v>
+        <v>33.53</v>
       </c>
       <c r="E53" s="5" t="n">
-        <v>43.89</v>
+        <v>44.15</v>
       </c>
       <c r="F53" s="7" t="inlineStr"/>
     </row>
@@ -1730,10 +1730,10 @@
         <v>27.51</v>
       </c>
       <c r="D54" s="5" t="n">
-        <v>33.59</v>
+        <v>33.79</v>
       </c>
       <c r="E54" s="5" t="n">
-        <v>42.94</v>
+        <v>43.19</v>
       </c>
       <c r="F54" s="7" t="inlineStr"/>
     </row>
@@ -1750,10 +1750,10 @@
         <v>30.14</v>
       </c>
       <c r="D55" s="5" t="n">
-        <v>40.16</v>
+        <v>40.41</v>
       </c>
       <c r="E55" s="5" t="n">
-        <v>46.96</v>
+        <v>47.24</v>
       </c>
       <c r="F55" s="7" t="inlineStr"/>
     </row>
@@ -1770,10 +1770,10 @@
         <v>38.11</v>
       </c>
       <c r="D56" s="5" t="n">
-        <v>52.41</v>
+        <v>52.72</v>
       </c>
       <c r="E56" s="5" t="n">
-        <v>59.27</v>
+        <v>59.62</v>
       </c>
       <c r="F56" s="7" t="inlineStr"/>
     </row>
@@ -1790,10 +1790,10 @@
         <v>31.86</v>
       </c>
       <c r="D57" s="5" t="n">
-        <v>49.46</v>
+        <v>49.76</v>
       </c>
       <c r="E57" s="5" t="n">
-        <v>49.46</v>
+        <v>49.76</v>
       </c>
       <c r="F57" s="7" t="inlineStr"/>
     </row>
@@ -1810,10 +1810,10 @@
         <v>32.52</v>
       </c>
       <c r="D58" s="5" t="n">
-        <v>45.24</v>
+        <v>45.51</v>
       </c>
       <c r="E58" s="5" t="n">
-        <v>50.33</v>
+        <v>50.63</v>
       </c>
       <c r="F58" s="7" t="inlineStr"/>
     </row>
@@ -1830,10 +1830,10 @@
         <v>20.61</v>
       </c>
       <c r="D59" s="5" t="n">
-        <v>36.97</v>
+        <v>37.19</v>
       </c>
       <c r="E59" s="5" t="n">
-        <v>31.8</v>
+        <v>31.99</v>
       </c>
       <c r="F59" s="7" t="inlineStr"/>
     </row>
@@ -1850,10 +1850,10 @@
         <v>28.67</v>
       </c>
       <c r="D60" s="5" t="n">
-        <v>40.3</v>
+        <v>40.54</v>
       </c>
       <c r="E60" s="5" t="n">
-        <v>44.1</v>
+        <v>44.36</v>
       </c>
       <c r="F60" s="7" t="inlineStr"/>
     </row>
@@ -1870,10 +1870,10 @@
         <v>26.2</v>
       </c>
       <c r="D61" s="5" t="n">
-        <v>37.49</v>
+        <v>37.71</v>
       </c>
       <c r="E61" s="5" t="n">
-        <v>40.22</v>
+        <v>40.46</v>
       </c>
       <c r="F61" s="7" t="inlineStr"/>
     </row>
@@ -1890,10 +1890,10 @@
         <v>40.53</v>
       </c>
       <c r="D62" s="5" t="n">
-        <v>87.27</v>
+        <v>87.8</v>
       </c>
       <c r="E62" s="5" t="n">
-        <v>62.09</v>
+        <v>62.46</v>
       </c>
       <c r="F62" s="7" t="inlineStr"/>
     </row>
@@ -1910,10 +1910,10 @@
         <v>34.48</v>
       </c>
       <c r="D63" s="5" t="n">
-        <v>47.23</v>
+        <v>47.51</v>
       </c>
       <c r="E63" s="5" t="n">
-        <v>52.72</v>
+        <v>53.03</v>
       </c>
       <c r="F63" s="7" t="inlineStr"/>
     </row>
@@ -1930,10 +1930,10 @@
         <v>33.99</v>
       </c>
       <c r="D64" s="5" t="n">
-        <v>46.06</v>
+        <v>46.34</v>
       </c>
       <c r="E64" s="5" t="n">
-        <v>51.84</v>
+        <v>52.15</v>
       </c>
       <c r="F64" s="7" t="inlineStr"/>
     </row>
@@ -1950,10 +1950,10 @@
         <v>27.77</v>
       </c>
       <c r="D65" s="5" t="n">
-        <v>98.59999999999999</v>
+        <v>99.19</v>
       </c>
       <c r="E65" s="5" t="n">
-        <v>42.25</v>
+        <v>42.51</v>
       </c>
       <c r="F65" s="7" t="inlineStr"/>
     </row>
@@ -1970,10 +1970,10 @@
         <v>23.94</v>
       </c>
       <c r="D66" s="5" t="n">
-        <v>31.51</v>
+        <v>31.7</v>
       </c>
       <c r="E66" s="5" t="n">
-        <v>36.34</v>
+        <v>36.56</v>
       </c>
       <c r="F66" s="7" t="inlineStr"/>
     </row>
@@ -1990,10 +1990,10 @@
         <v>18.56</v>
       </c>
       <c r="D67" s="5" t="n">
-        <v>27.5</v>
+        <v>27.66</v>
       </c>
       <c r="E67" s="5" t="n">
-        <v>28.14</v>
+        <v>28.3</v>
       </c>
       <c r="F67" s="7" t="inlineStr"/>
     </row>
@@ -2010,10 +2010,10 @@
         <v>38.48</v>
       </c>
       <c r="D68" s="5" t="n">
-        <v>41.03</v>
+        <v>41.28</v>
       </c>
       <c r="E68" s="5" t="n">
-        <v>58.26</v>
+        <v>58.61</v>
       </c>
       <c r="F68" s="7" t="inlineStr"/>
     </row>
@@ -2030,10 +2030,10 @@
         <v>17.8</v>
       </c>
       <c r="D69" s="5" t="n">
-        <v>25.25</v>
+        <v>25.4</v>
       </c>
       <c r="E69" s="5" t="n">
-        <v>26.91</v>
+        <v>27.08</v>
       </c>
       <c r="F69" s="7" t="inlineStr"/>
     </row>
@@ -2050,10 +2050,10 @@
         <v>28.36</v>
       </c>
       <c r="D70" s="5" t="n">
-        <v>39.04</v>
+        <v>39.27</v>
       </c>
       <c r="E70" s="5" t="n">
-        <v>42.66</v>
+        <v>42.92</v>
       </c>
       <c r="F70" s="7" t="inlineStr"/>
     </row>
@@ -2070,10 +2070,10 @@
         <v>31.48</v>
       </c>
       <c r="D71" s="5" t="n">
-        <v>42.98</v>
+        <v>43.24</v>
       </c>
       <c r="E71" s="5" t="n">
-        <v>47.11</v>
+        <v>47.4</v>
       </c>
       <c r="F71" s="7" t="inlineStr"/>
     </row>
@@ -2090,10 +2090,10 @@
         <v>27.22</v>
       </c>
       <c r="D72" s="5" t="n">
-        <v>38.46</v>
+        <v>38.69</v>
       </c>
       <c r="E72" s="5" t="n">
-        <v>40.53</v>
+        <v>40.77</v>
       </c>
       <c r="F72" s="7" t="inlineStr"/>
     </row>
@@ -2110,10 +2110,10 @@
         <v>27.79</v>
       </c>
       <c r="D73" s="5" t="n">
-        <v>39.78</v>
+        <v>40.02</v>
       </c>
       <c r="E73" s="5" t="n">
-        <v>41.25</v>
+        <v>41.5</v>
       </c>
       <c r="F73" s="7" t="inlineStr"/>
     </row>
@@ -2130,10 +2130,10 @@
         <v>40.73</v>
       </c>
       <c r="D74" s="5" t="n">
-        <v>57.23</v>
+        <v>57.57</v>
       </c>
       <c r="E74" s="5" t="n">
-        <v>60.28</v>
+        <v>60.64</v>
       </c>
       <c r="F74" s="7" t="inlineStr"/>
     </row>
@@ -2150,10 +2150,10 @@
         <v>32.31</v>
       </c>
       <c r="D75" s="5" t="n">
-        <v>43.02</v>
+        <v>43.28</v>
       </c>
       <c r="E75" s="5" t="n">
-        <v>47.67</v>
+        <v>47.96</v>
       </c>
       <c r="F75" s="7" t="inlineStr"/>
     </row>
@@ -2170,10 +2170,10 @@
         <v>49.12</v>
       </c>
       <c r="D76" s="5" t="n">
-        <v>47.99</v>
+        <v>48.28</v>
       </c>
       <c r="E76" s="5" t="n">
-        <v>72.33</v>
+        <v>72.76000000000001</v>
       </c>
       <c r="F76" s="7" t="inlineStr"/>
     </row>
@@ -2190,10 +2190,10 @@
         <v>34.69</v>
       </c>
       <c r="D77" s="5" t="n">
-        <v>39.91</v>
+        <v>40.15</v>
       </c>
       <c r="E77" s="5" t="n">
-        <v>50.98</v>
+        <v>51.29</v>
       </c>
       <c r="F77" s="7" t="inlineStr"/>
     </row>
@@ -2210,10 +2210,10 @@
         <v>29.9</v>
       </c>
       <c r="D78" s="5" t="n">
-        <v>38.72</v>
+        <v>38.95</v>
       </c>
       <c r="E78" s="5" t="n">
-        <v>43.85</v>
+        <v>44.12</v>
       </c>
       <c r="F78" s="7" t="inlineStr"/>
     </row>
@@ -2230,10 +2230,10 @@
         <v>31.6</v>
       </c>
       <c r="D79" s="5" t="n">
-        <v>47.78</v>
+        <v>48.07</v>
       </c>
       <c r="E79" s="5" t="n">
-        <v>46.35</v>
+        <v>46.63</v>
       </c>
       <c r="F79" s="7" t="inlineStr"/>
     </row>
@@ -2250,10 +2250,10 @@
         <v>30.44</v>
       </c>
       <c r="D80" s="5" t="n">
-        <v>45.1</v>
+        <v>45.37</v>
       </c>
       <c r="E80" s="5" t="n">
-        <v>44.65</v>
+        <v>44.91</v>
       </c>
       <c r="F80" s="7" t="inlineStr"/>
     </row>
@@ -2270,10 +2270,10 @@
         <v>26.57</v>
       </c>
       <c r="D81" s="5" t="n">
-        <v>37.91</v>
+        <v>38.14</v>
       </c>
       <c r="E81" s="5" t="n">
-        <v>38.97</v>
+        <v>39.2</v>
       </c>
       <c r="F81" s="7" t="inlineStr"/>
     </row>
@@ -2290,10 +2290,10 @@
         <v>34.13</v>
       </c>
       <c r="D82" s="5" t="n">
-        <v>57.66</v>
+        <v>58</v>
       </c>
       <c r="E82" s="5" t="n">
-        <v>50.05</v>
+        <v>50.35</v>
       </c>
       <c r="F82" s="7" t="inlineStr"/>
     </row>
@@ -2310,10 +2310,10 @@
         <v>29.92</v>
       </c>
       <c r="D83" s="5" t="n">
-        <v>54.79</v>
+        <v>55.12</v>
       </c>
       <c r="E83" s="5" t="n">
-        <v>43.87</v>
+        <v>44.13</v>
       </c>
       <c r="F83" s="7" t="inlineStr"/>
     </row>
@@ -2330,10 +2330,10 @@
         <v>29.84</v>
       </c>
       <c r="D84" s="5" t="n">
-        <v>52.65</v>
+        <v>52.97</v>
       </c>
       <c r="E84" s="5" t="n">
-        <v>43.74</v>
+        <v>44</v>
       </c>
       <c r="F84" s="7" t="inlineStr"/>
     </row>
@@ -2350,10 +2350,10 @@
         <v>42.04</v>
       </c>
       <c r="D85" s="5" t="n">
-        <v>52.62</v>
+        <v>52.94</v>
       </c>
       <c r="E85" s="5" t="n">
-        <v>61.52</v>
+        <v>61.89</v>
       </c>
       <c r="F85" s="7" t="inlineStr"/>
     </row>
@@ -2370,10 +2370,10 @@
         <v>29.9</v>
       </c>
       <c r="D86" s="5" t="n">
-        <v>48.06</v>
+        <v>48.35</v>
       </c>
       <c r="E86" s="5" t="n">
-        <v>43.68</v>
+        <v>43.94</v>
       </c>
       <c r="F86" s="7" t="inlineStr"/>
     </row>
@@ -2390,10 +2390,10 @@
         <v>38.55</v>
       </c>
       <c r="D87" s="5" t="n">
-        <v>50.22</v>
+        <v>50.52</v>
       </c>
       <c r="E87" s="5" t="n">
-        <v>56.22</v>
+        <v>56.55</v>
       </c>
       <c r="F87" s="7" t="inlineStr"/>
     </row>
@@ -2410,10 +2410,10 @@
         <v>67.45</v>
       </c>
       <c r="D88" s="9" t="n">
-        <v>85.98</v>
+        <v>86.5</v>
       </c>
       <c r="E88" s="9" t="n">
-        <v>97.92</v>
+        <v>98.5</v>
       </c>
       <c r="F88" s="10" t="inlineStr">
         <is>
@@ -2434,10 +2434,10 @@
         <v>48.6</v>
       </c>
       <c r="D89" s="9" t="n">
-        <v>68.23999999999999</v>
+        <v>68.65000000000001</v>
       </c>
       <c r="E89" s="9" t="n">
-        <v>70.23</v>
+        <v>70.66</v>
       </c>
       <c r="F89" s="10" t="inlineStr">
         <is>
@@ -2458,10 +2458,10 @@
         <v>41.42</v>
       </c>
       <c r="D90" s="9" t="n">
-        <v>56.77</v>
+        <v>57.11</v>
       </c>
       <c r="E90" s="9" t="n">
-        <v>59.59</v>
+        <v>59.95</v>
       </c>
       <c r="F90" s="10" t="inlineStr">
         <is>
@@ -2482,10 +2482,10 @@
         <v>44.97</v>
       </c>
       <c r="D91" s="9" t="n">
-        <v>62.7</v>
+        <v>63.08</v>
       </c>
       <c r="E91" s="9" t="n">
-        <v>64.64</v>
+        <v>65.03</v>
       </c>
       <c r="F91" s="10" t="inlineStr">
         <is>
@@ -2506,10 +2506,10 @@
         <v>51.39</v>
       </c>
       <c r="D92" s="9" t="n">
-        <v>72.64</v>
+        <v>73.08</v>
       </c>
       <c r="E92" s="9" t="n">
-        <v>73.81</v>
+        <v>74.25</v>
       </c>
       <c r="F92" s="10" t="inlineStr">
         <is>
@@ -2530,10 +2530,10 @@
         <v>46.41</v>
       </c>
       <c r="D93" s="9" t="n">
-        <v>67.02</v>
+        <v>67.42</v>
       </c>
       <c r="E93" s="9" t="n">
-        <v>66.59999999999999</v>
+        <v>67</v>
       </c>
       <c r="F93" s="10" t="inlineStr">
         <is>
@@ -2554,10 +2554,10 @@
         <v>46.53</v>
       </c>
       <c r="D94" s="9" t="n">
-        <v>81.65000000000001</v>
+        <v>82.14</v>
       </c>
       <c r="E94" s="9" t="n">
-        <v>66.7</v>
+        <v>67.09999999999999</v>
       </c>
       <c r="F94" s="10" t="inlineStr">
         <is>
@@ -2578,10 +2578,10 @@
         <v>46.11</v>
       </c>
       <c r="D95" s="9" t="n">
-        <v>65.56</v>
+        <v>65.95</v>
       </c>
       <c r="E95" s="9" t="n">
-        <v>66.02</v>
+        <v>66.42</v>
       </c>
       <c r="F95" s="10" t="inlineStr">
         <is>
@@ -2602,10 +2602,10 @@
         <v>50.82</v>
       </c>
       <c r="D96" s="9" t="n">
-        <v>71.23999999999999</v>
+        <v>71.66</v>
       </c>
       <c r="E96" s="9" t="n">
-        <v>72.68000000000001</v>
+        <v>73.12</v>
       </c>
       <c r="F96" s="10" t="inlineStr">
         <is>
@@ -2626,10 +2626,10 @@
         <v>46.73</v>
       </c>
       <c r="D97" s="9" t="n">
-        <v>64.45</v>
+        <v>64.83</v>
       </c>
       <c r="E97" s="9" t="n">
-        <v>66.75</v>
+        <v>67.15000000000001</v>
       </c>
       <c r="F97" s="10" t="inlineStr">
         <is>
@@ -2650,10 +2650,10 @@
         <v>49.68</v>
       </c>
       <c r="D98" s="9" t="n">
-        <v>63.72</v>
+        <v>64.11</v>
       </c>
       <c r="E98" s="9" t="n">
-        <v>70.87</v>
+        <v>71.3</v>
       </c>
       <c r="F98" s="10" t="inlineStr">
         <is>
@@ -2674,10 +2674,10 @@
         <v>51.77</v>
       </c>
       <c r="D99" s="9" t="n">
-        <v>71.08</v>
+        <v>71.51000000000001</v>
       </c>
       <c r="E99" s="9" t="n">
-        <v>73.76000000000001</v>
+        <v>74.2</v>
       </c>
       <c r="F99" s="10" t="inlineStr">
         <is>
@@ -2698,10 +2698,10 @@
         <v>50.69</v>
       </c>
       <c r="D100" s="9" t="n">
-        <v>73.08</v>
+        <v>73.52</v>
       </c>
       <c r="E100" s="9" t="n">
-        <v>71.93000000000001</v>
+        <v>72.36</v>
       </c>
       <c r="F100" s="10" t="inlineStr">
         <is>
@@ -2722,10 +2722,10 @@
         <v>49.44</v>
       </c>
       <c r="D101" s="9" t="n">
-        <v>64.83</v>
+        <v>65.22</v>
       </c>
       <c r="E101" s="9" t="n">
-        <v>69.87</v>
+        <v>70.29000000000001</v>
       </c>
       <c r="F101" s="10" t="inlineStr">
         <is>
@@ -2746,10 +2746,10 @@
         <v>44.8</v>
       </c>
       <c r="D102" s="9" t="n">
-        <v>59.72</v>
+        <v>60.08</v>
       </c>
       <c r="E102" s="9" t="n">
-        <v>63.06</v>
+        <v>63.44</v>
       </c>
       <c r="F102" s="10" t="inlineStr">
         <is>
@@ -2770,10 +2770,10 @@
         <v>41.47</v>
       </c>
       <c r="D103" s="9" t="n">
-        <v>54.2</v>
+        <v>54.53</v>
       </c>
       <c r="E103" s="9" t="n">
-        <v>58.23</v>
+        <v>58.58</v>
       </c>
       <c r="F103" s="10" t="inlineStr">
         <is>
@@ -2794,10 +2794,10 @@
         <v>52.99</v>
       </c>
       <c r="D104" s="9" t="n">
-        <v>65.97</v>
+        <v>66.36</v>
       </c>
       <c r="E104" s="9" t="n">
-        <v>74.23</v>
+        <v>74.68000000000001</v>
       </c>
       <c r="F104" s="10" t="inlineStr">
         <is>
@@ -2818,10 +2818,10 @@
         <v>37.58</v>
       </c>
       <c r="D105" s="9" t="n">
-        <v>52.55</v>
+        <v>52.86</v>
       </c>
       <c r="E105" s="9" t="n">
-        <v>52.52</v>
+        <v>52.84</v>
       </c>
       <c r="F105" s="10" t="inlineStr">
         <is>
@@ -2842,10 +2842,10 @@
         <v>29.48</v>
       </c>
       <c r="D106" s="9" t="n">
-        <v>48.65</v>
+        <v>48.94</v>
       </c>
       <c r="E106" s="9" t="n">
-        <v>41.12</v>
+        <v>41.37</v>
       </c>
       <c r="F106" s="10" t="inlineStr">
         <is>
@@ -2866,10 +2866,10 @@
         <v>43.27</v>
       </c>
       <c r="D107" s="9" t="n">
-        <v>61.1</v>
+        <v>61.46</v>
       </c>
       <c r="E107" s="9" t="n">
-        <v>60.23</v>
+        <v>60.6</v>
       </c>
       <c r="F107" s="10" t="inlineStr">
         <is>
@@ -2890,10 +2890,10 @@
         <v>45.47</v>
       </c>
       <c r="D108" s="9" t="n">
-        <v>62.21</v>
+        <v>62.59</v>
       </c>
       <c r="E108" s="9" t="n">
-        <v>63.17</v>
+        <v>63.55</v>
       </c>
       <c r="F108" s="10" t="inlineStr">
         <is>
@@ -2914,10 +2914,10 @@
         <v>38.57</v>
       </c>
       <c r="D109" s="9" t="n">
-        <v>52.26</v>
+        <v>52.58</v>
       </c>
       <c r="E109" s="9" t="n">
-        <v>53.5</v>
+        <v>53.82</v>
       </c>
       <c r="F109" s="10" t="inlineStr">
         <is>
@@ -2938,10 +2938,10 @@
         <v>40.99</v>
       </c>
       <c r="D110" s="9" t="n">
-        <v>50.57</v>
+        <v>50.87</v>
       </c>
       <c r="E110" s="9" t="n">
-        <v>56.76</v>
+        <v>57.1</v>
       </c>
       <c r="F110" s="10" t="inlineStr">
         <is>
@@ -2962,10 +2962,10 @@
         <v>44.06</v>
       </c>
       <c r="D111" s="9" t="n">
-        <v>59.65</v>
+        <v>60.01</v>
       </c>
       <c r="E111" s="9" t="n">
-        <v>60.91</v>
+        <v>61.27</v>
       </c>
       <c r="F111" s="10" t="inlineStr">
         <is>
@@ -2986,10 +2986,10 @@
         <v>37.29</v>
       </c>
       <c r="D112" s="5" t="n">
-        <v>46.7</v>
+        <v>46.98</v>
       </c>
       <c r="E112" s="5" t="n">
-        <v>51.48</v>
+        <v>51.78</v>
       </c>
       <c r="F112" s="7" t="inlineStr"/>
     </row>
@@ -3006,10 +3006,10 @@
         <v>41.88</v>
       </c>
       <c r="D113" s="5" t="n">
-        <v>50.09</v>
+        <v>50.39</v>
       </c>
       <c r="E113" s="5" t="n">
-        <v>57.73</v>
+        <v>58.08</v>
       </c>
       <c r="F113" s="7" t="inlineStr"/>
     </row>
@@ -3026,10 +3026,10 @@
         <v>40.3</v>
       </c>
       <c r="D114" s="5" t="n">
-        <v>51.83</v>
+        <v>52.14</v>
       </c>
       <c r="E114" s="5" t="n">
-        <v>55.48</v>
+        <v>55.81</v>
       </c>
       <c r="F114" s="7" t="inlineStr"/>
     </row>
@@ -3046,10 +3046,10 @@
         <v>32.91</v>
       </c>
       <c r="D115" s="5" t="n">
-        <v>48.03</v>
+        <v>48.31</v>
       </c>
       <c r="E115" s="5" t="n">
-        <v>45.27</v>
+        <v>45.55</v>
       </c>
       <c r="F115" s="7" t="inlineStr"/>
     </row>
@@ -3066,10 +3066,10 @@
         <v>37.03</v>
       </c>
       <c r="D116" s="5" t="n">
-        <v>54.91</v>
+        <v>55.24</v>
       </c>
       <c r="E116" s="5" t="n">
-        <v>50.91</v>
+        <v>51.21</v>
       </c>
       <c r="F116" s="7" t="inlineStr"/>
     </row>
@@ -3086,10 +3086,10 @@
         <v>44.4</v>
       </c>
       <c r="D117" s="5" t="n">
-        <v>62.19</v>
+        <v>62.56</v>
       </c>
       <c r="E117" s="5" t="n">
-        <v>61</v>
+        <v>61.37</v>
       </c>
       <c r="F117" s="7" t="inlineStr"/>
     </row>
@@ -3106,10 +3106,10 @@
         <v>36.8</v>
       </c>
       <c r="D118" s="5" t="n">
-        <v>48.17</v>
+        <v>48.46</v>
       </c>
       <c r="E118" s="5" t="n">
-        <v>50.53</v>
+        <v>50.83</v>
       </c>
       <c r="F118" s="7" t="inlineStr"/>
     </row>
@@ -3126,10 +3126,10 @@
         <v>41.1</v>
       </c>
       <c r="D119" s="5" t="n">
-        <v>58.37</v>
+        <v>58.72</v>
       </c>
       <c r="E119" s="5" t="n">
-        <v>56.4</v>
+        <v>56.74</v>
       </c>
       <c r="F119" s="7" t="inlineStr"/>
     </row>
@@ -3146,10 +3146,10 @@
         <v>39.98</v>
       </c>
       <c r="D120" s="5" t="n">
-        <v>54.54</v>
+        <v>54.87</v>
       </c>
       <c r="E120" s="5" t="n">
-        <v>54.83</v>
+        <v>55.16</v>
       </c>
       <c r="F120" s="7" t="inlineStr"/>
     </row>
@@ -3166,10 +3166,10 @@
         <v>38.37</v>
       </c>
       <c r="D121" s="5" t="n">
-        <v>55.6</v>
+        <v>55.93</v>
       </c>
       <c r="E121" s="5" t="n">
-        <v>52.49</v>
+        <v>52.81</v>
       </c>
       <c r="F121" s="7" t="inlineStr"/>
     </row>
@@ -3186,10 +3186,10 @@
         <v>37.02</v>
       </c>
       <c r="D122" s="5" t="n">
-        <v>38.63</v>
+        <v>38.86</v>
       </c>
       <c r="E122" s="5" t="n">
-        <v>50.53</v>
+        <v>50.83</v>
       </c>
       <c r="F122" s="7" t="inlineStr"/>
     </row>
@@ -3206,10 +3206,10 @@
         <v>37.68</v>
       </c>
       <c r="D123" s="5" t="n">
-        <v>43.91</v>
+        <v>44.18</v>
       </c>
       <c r="E123" s="5" t="n">
-        <v>51.31</v>
+        <v>51.61</v>
       </c>
       <c r="F123" s="7" t="inlineStr"/>
     </row>
@@ -3226,10 +3226,10 @@
         <v>39.11</v>
       </c>
       <c r="D124" s="5" t="n">
-        <v>47.46</v>
+        <v>47.74</v>
       </c>
       <c r="E124" s="5" t="n">
-        <v>53.18</v>
+        <v>53.5</v>
       </c>
       <c r="F124" s="7" t="inlineStr"/>
     </row>
@@ -3246,10 +3246,10 @@
         <v>38.28</v>
       </c>
       <c r="D125" s="5" t="n">
-        <v>43.31</v>
+        <v>43.57</v>
       </c>
       <c r="E125" s="5" t="n">
-        <v>51.99</v>
+        <v>52.3</v>
       </c>
       <c r="F125" s="7" t="inlineStr"/>
     </row>
@@ -3266,10 +3266,10 @@
         <v>48.78</v>
       </c>
       <c r="D126" s="5" t="n">
-        <v>62.42</v>
+        <v>62.79</v>
       </c>
       <c r="E126" s="5" t="n">
-        <v>66.16</v>
+        <v>66.56</v>
       </c>
       <c r="F126" s="7" t="inlineStr"/>
     </row>
@@ -3286,10 +3286,10 @@
         <v>60.34</v>
       </c>
       <c r="D127" s="5" t="n">
-        <v>80.22</v>
+        <v>80.7</v>
       </c>
       <c r="E127" s="5" t="n">
-        <v>81.73999999999999</v>
+        <v>82.23</v>
       </c>
       <c r="F127" s="7" t="inlineStr"/>
     </row>
@@ -3306,10 +3306,10 @@
         <v>85.88</v>
       </c>
       <c r="D128" s="5" t="n">
-        <v>113.28</v>
+        <v>113.96</v>
       </c>
       <c r="E128" s="5" t="n">
-        <v>116.18</v>
+        <v>116.88</v>
       </c>
       <c r="F128" s="7" t="inlineStr"/>
     </row>
@@ -3326,10 +3326,10 @@
         <v>97.17</v>
       </c>
       <c r="D129" s="5" t="n">
-        <v>129.84</v>
+        <v>130.62</v>
       </c>
       <c r="E129" s="5" t="n">
-        <v>131.29</v>
+        <v>132.08</v>
       </c>
       <c r="F129" s="7" t="inlineStr"/>
     </row>
@@ -3346,10 +3346,10 @@
         <v>114.3</v>
       </c>
       <c r="D130" s="5" t="n">
-        <v>152.41</v>
+        <v>153.33</v>
       </c>
       <c r="E130" s="5" t="n">
-        <v>154.54</v>
+        <v>155.46</v>
       </c>
       <c r="F130" s="7" t="inlineStr"/>
     </row>
@@ -3366,10 +3366,10 @@
         <v>164</v>
       </c>
       <c r="D131" s="5" t="n">
-        <v>224.14</v>
+        <v>225.48</v>
       </c>
       <c r="E131" s="5" t="n">
-        <v>221.88</v>
+        <v>223.21</v>
       </c>
       <c r="F131" s="7" t="inlineStr"/>
     </row>
@@ -3386,10 +3386,10 @@
         <v>256.22</v>
       </c>
       <c r="D132" s="5" t="n">
-        <v>341.67</v>
+        <v>343.72</v>
       </c>
       <c r="E132" s="5" t="n">
-        <v>346.88</v>
+        <v>348.96</v>
       </c>
       <c r="F132" s="7" t="inlineStr"/>
     </row>
@@ -3406,10 +3406,10 @@
         <v>236.68</v>
       </c>
       <c r="D133" s="5" t="n">
-        <v>320.19</v>
+        <v>322.11</v>
       </c>
       <c r="E133" s="5" t="n">
-        <v>319.96</v>
+        <v>321.88</v>
       </c>
       <c r="F133" s="7" t="inlineStr"/>
     </row>
@@ -3426,10 +3426,10 @@
         <v>57.34</v>
       </c>
       <c r="D134" s="5" t="n">
-        <v>61.35</v>
+        <v>61.72</v>
       </c>
       <c r="E134" s="5" t="n">
-        <v>77.40000000000001</v>
+        <v>77.87</v>
       </c>
       <c r="F134" s="7" t="inlineStr"/>
     </row>
@@ -3446,10 +3446,10 @@
         <v>100.06</v>
       </c>
       <c r="D135" s="5" t="n">
-        <v>97.72</v>
+        <v>98.31</v>
       </c>
       <c r="E135" s="5" t="n">
-        <v>134.87</v>
+        <v>135.68</v>
       </c>
       <c r="F135" s="7" t="inlineStr"/>
     </row>
@@ -3466,10 +3466,10 @@
         <v>97.12</v>
       </c>
       <c r="D136" s="5" t="n">
-        <v>91.34</v>
+        <v>91.88</v>
       </c>
       <c r="E136" s="5" t="n">
-        <v>130.6</v>
+        <v>131.39</v>
       </c>
       <c r="F136" s="7" t="inlineStr"/>
     </row>
@@ -3486,10 +3486,10 @@
         <v>58.34</v>
       </c>
       <c r="D137" s="5" t="n">
-        <v>58.6</v>
+        <v>58.95</v>
       </c>
       <c r="E137" s="5" t="n">
-        <v>78.27</v>
+        <v>78.73999999999999</v>
       </c>
       <c r="F137" s="7" t="inlineStr"/>
     </row>
@@ -3506,10 +3506,10 @@
         <v>52.77</v>
       </c>
       <c r="D138" s="5" t="n">
-        <v>61.81</v>
+        <v>62.18</v>
       </c>
       <c r="E138" s="5" t="n">
-        <v>70.63</v>
+        <v>71.06</v>
       </c>
       <c r="F138" s="7" t="inlineStr"/>
     </row>
@@ -3526,10 +3526,10 @@
         <v>42.16</v>
       </c>
       <c r="D139" s="5" t="n">
-        <v>44.39</v>
+        <v>44.65</v>
       </c>
       <c r="E139" s="5" t="n">
-        <v>56.33</v>
+        <v>56.67</v>
       </c>
       <c r="F139" s="7" t="inlineStr"/>
     </row>
@@ -3546,10 +3546,10 @@
         <v>52.68</v>
       </c>
       <c r="D140" s="5" t="n">
-        <v>50.13</v>
+        <v>50.43</v>
       </c>
       <c r="E140" s="5" t="n">
-        <v>70.27</v>
+        <v>70.69</v>
       </c>
       <c r="F140" s="7" t="inlineStr"/>
     </row>
@@ -3566,10 +3566,10 @@
         <v>46.61</v>
       </c>
       <c r="D141" s="5" t="n">
-        <v>54.99</v>
+        <v>55.32</v>
       </c>
       <c r="E141" s="5" t="n">
-        <v>62.06</v>
+        <v>62.43</v>
       </c>
       <c r="F141" s="7" t="inlineStr"/>
     </row>
@@ -3586,10 +3586,10 @@
         <v>91.34999999999999</v>
       </c>
       <c r="D142" s="5" t="n">
-        <v>114.48</v>
+        <v>115.17</v>
       </c>
       <c r="E142" s="5" t="n">
-        <v>121.45</v>
+        <v>122.18</v>
       </c>
       <c r="F142" s="7" t="inlineStr"/>
     </row>
@@ -3606,10 +3606,10 @@
         <v>104.02</v>
       </c>
       <c r="D143" s="5" t="n">
-        <v>125.28</v>
+        <v>126.04</v>
       </c>
       <c r="E143" s="5" t="n">
-        <v>138.08</v>
+        <v>138.91</v>
       </c>
       <c r="F143" s="7" t="inlineStr"/>
     </row>
@@ -3626,10 +3626,10 @@
         <v>117.62</v>
       </c>
       <c r="D144" s="5" t="n">
-        <v>150.85</v>
+        <v>151.75</v>
       </c>
       <c r="E144" s="5" t="n">
-        <v>155.9</v>
+        <v>156.83</v>
       </c>
       <c r="F144" s="7" t="inlineStr"/>
     </row>
@@ -3646,10 +3646,10 @@
         <v>128.93</v>
       </c>
       <c r="D145" s="5" t="n">
-        <v>173.85</v>
+        <v>174.89</v>
       </c>
       <c r="E145" s="5" t="n">
-        <v>170.78</v>
+        <v>171.8</v>
       </c>
       <c r="F145" s="7" t="inlineStr"/>
     </row>
@@ -3666,10 +3666,10 @@
         <v>118.62</v>
       </c>
       <c r="D146" s="5" t="n">
-        <v>142.88</v>
+        <v>143.74</v>
       </c>
       <c r="E146" s="5" t="n">
-        <v>157.02</v>
+        <v>157.96</v>
       </c>
       <c r="F146" s="7" t="inlineStr"/>
     </row>
@@ -3686,10 +3686,10 @@
         <v>109.77</v>
       </c>
       <c r="D147" s="5" t="n">
-        <v>137.36</v>
+        <v>138.19</v>
       </c>
       <c r="E147" s="5" t="n">
-        <v>145.21</v>
+        <v>146.08</v>
       </c>
       <c r="F147" s="7" t="inlineStr"/>
     </row>
@@ -3706,10 +3706,10 @@
         <v>126.14</v>
       </c>
       <c r="D148" s="5" t="n">
-        <v>153.18</v>
+        <v>154.1</v>
       </c>
       <c r="E148" s="5" t="n">
-        <v>166.52</v>
+        <v>167.52</v>
       </c>
       <c r="F148" s="7" t="inlineStr"/>
     </row>
@@ -3726,10 +3726,10 @@
         <v>110.94</v>
       </c>
       <c r="D149" s="5" t="n">
-        <v>128.07</v>
+        <v>128.84</v>
       </c>
       <c r="E149" s="5" t="n">
-        <v>146.16</v>
+        <v>147.04</v>
       </c>
       <c r="F149" s="7" t="inlineStr"/>
     </row>
@@ -3746,10 +3746,10 @@
         <v>82.05</v>
       </c>
       <c r="D150" s="5" t="n">
-        <v>96.73999999999999</v>
+        <v>97.31999999999999</v>
       </c>
       <c r="E150" s="5" t="n">
-        <v>107.88</v>
+        <v>108.53</v>
       </c>
       <c r="F150" s="7" t="inlineStr"/>
     </row>
@@ -3766,10 +3766,10 @@
         <v>75.56</v>
       </c>
       <c r="D151" s="5" t="n">
-        <v>90.06999999999999</v>
+        <v>90.61</v>
       </c>
       <c r="E151" s="5" t="n">
-        <v>99.12</v>
+        <v>99.72</v>
       </c>
       <c r="F151" s="7" t="inlineStr"/>
     </row>
@@ -3786,10 +3786,10 @@
         <v>105.59</v>
       </c>
       <c r="D152" s="5" t="n">
-        <v>123.08</v>
+        <v>123.82</v>
       </c>
       <c r="E152" s="5" t="n">
-        <v>138.21</v>
+        <v>139.04</v>
       </c>
       <c r="F152" s="7" t="inlineStr"/>
     </row>
@@ -3806,10 +3806,10 @@
         <v>106.82</v>
       </c>
       <c r="D153" s="5" t="n">
-        <v>118.8</v>
+        <v>119.51</v>
       </c>
       <c r="E153" s="5" t="n">
-        <v>139.51</v>
+        <v>140.35</v>
       </c>
       <c r="F153" s="7" t="inlineStr"/>
     </row>
@@ -3826,10 +3826,10 @@
         <v>95.51000000000001</v>
       </c>
       <c r="D154" s="5" t="n">
-        <v>129.07</v>
+        <v>129.84</v>
       </c>
       <c r="E154" s="5" t="n">
-        <v>124.56</v>
+        <v>125.3</v>
       </c>
       <c r="F154" s="7" t="inlineStr"/>
     </row>
@@ -3846,10 +3846,10 @@
         <v>89.34999999999999</v>
       </c>
       <c r="D155" s="5" t="n">
-        <v>116.25</v>
+        <v>116.95</v>
       </c>
       <c r="E155" s="5" t="n">
-        <v>116.35</v>
+        <v>117.05</v>
       </c>
       <c r="F155" s="7" t="inlineStr"/>
     </row>
@@ -3866,10 +3866,10 @@
         <v>86.02</v>
       </c>
       <c r="D156" s="5" t="n">
-        <v>108.6</v>
+        <v>109.26</v>
       </c>
       <c r="E156" s="5" t="n">
-        <v>111.86</v>
+        <v>112.53</v>
       </c>
       <c r="F156" s="7" t="inlineStr"/>
     </row>
@@ -3886,10 +3886,10 @@
         <v>80.12</v>
       </c>
       <c r="D157" s="5" t="n">
-        <v>104.83</v>
+        <v>105.45</v>
       </c>
       <c r="E157" s="5" t="n">
-        <v>104.06</v>
+        <v>104.68</v>
       </c>
       <c r="F157" s="7" t="inlineStr"/>
     </row>
@@ -3906,10 +3906,10 @@
         <v>79.66</v>
       </c>
       <c r="D158" s="5" t="n">
-        <v>99.31999999999999</v>
+        <v>99.91</v>
       </c>
       <c r="E158" s="5" t="n">
-        <v>103.34</v>
+        <v>103.96</v>
       </c>
       <c r="F158" s="7" t="inlineStr"/>
     </row>
@@ -3926,10 +3926,10 @@
         <v>81.06</v>
       </c>
       <c r="D159" s="5" t="n">
-        <v>95.34999999999999</v>
+        <v>95.92</v>
       </c>
       <c r="E159" s="5" t="n">
-        <v>105.03</v>
+        <v>105.66</v>
       </c>
       <c r="F159" s="7" t="inlineStr"/>
     </row>
@@ -3946,10 +3946,10 @@
         <v>50.01</v>
       </c>
       <c r="D160" s="5" t="n">
-        <v>58.03</v>
+        <v>58.38</v>
       </c>
       <c r="E160" s="5" t="n">
-        <v>64.7</v>
+        <v>65.09</v>
       </c>
       <c r="F160" s="7" t="inlineStr"/>
     </row>
@@ -3966,10 +3966,10 @@
         <v>31.66</v>
       </c>
       <c r="D161" s="5" t="n">
-        <v>32.34</v>
+        <v>32.53</v>
       </c>
       <c r="E161" s="5" t="n">
-        <v>40.9</v>
+        <v>41.15</v>
       </c>
       <c r="F161" s="7" t="inlineStr"/>
     </row>
@@ -3986,10 +3986,10 @@
         <v>75.48</v>
       </c>
       <c r="D162" s="5" t="n">
-        <v>78.52</v>
+        <v>78.98999999999999</v>
       </c>
       <c r="E162" s="5" t="n">
-        <v>97.38</v>
+        <v>97.95999999999999</v>
       </c>
       <c r="F162" s="7" t="inlineStr"/>
     </row>
@@ -4006,10 +4006,10 @@
         <v>102.32</v>
       </c>
       <c r="D163" s="5" t="n">
-        <v>122.83</v>
+        <v>123.56</v>
       </c>
       <c r="E163" s="5" t="n">
-        <v>131.78</v>
+        <v>132.57</v>
       </c>
       <c r="F163" s="7" t="inlineStr"/>
     </row>
@@ -4026,10 +4026,10 @@
         <v>88.54000000000001</v>
       </c>
       <c r="D164" s="5" t="n">
-        <v>110.05</v>
+        <v>110.71</v>
       </c>
       <c r="E164" s="5" t="n">
-        <v>113.83</v>
+        <v>114.52</v>
       </c>
       <c r="F164" s="7" t="inlineStr"/>
     </row>
@@ -4046,10 +4046,10 @@
         <v>71.18000000000001</v>
       </c>
       <c r="D165" s="5" t="n">
-        <v>92.56999999999999</v>
+        <v>93.13</v>
       </c>
       <c r="E165" s="5" t="n">
-        <v>91.36</v>
+        <v>91.90000000000001</v>
       </c>
       <c r="F165" s="7" t="inlineStr"/>
     </row>
@@ -4066,10 +4066,10 @@
         <v>163.88</v>
       </c>
       <c r="D166" s="5" t="n">
-        <v>189.84</v>
+        <v>190.98</v>
       </c>
       <c r="E166" s="5" t="n">
-        <v>210.34</v>
+        <v>211.6</v>
       </c>
       <c r="F166" s="7" t="inlineStr"/>
     </row>
@@ -4086,10 +4086,10 @@
         <v>133.69</v>
       </c>
       <c r="D167" s="5" t="n">
-        <v>173.01</v>
+        <v>174.05</v>
       </c>
       <c r="E167" s="5" t="n">
-        <v>171.6</v>
+        <v>172.63</v>
       </c>
       <c r="F167" s="7" t="inlineStr"/>
     </row>
@@ -4106,10 +4106,10 @@
         <v>115.58</v>
       </c>
       <c r="D168" s="5" t="n">
-        <v>158.44</v>
+        <v>159.39</v>
       </c>
       <c r="E168" s="5" t="n">
-        <v>148.36</v>
+        <v>149.25</v>
       </c>
       <c r="F168" s="7" t="inlineStr"/>
     </row>
@@ -4126,10 +4126,10 @@
         <v>109.29</v>
       </c>
       <c r="D169" s="5" t="n">
-        <v>134.15</v>
+        <v>134.96</v>
       </c>
       <c r="E169" s="5" t="n">
-        <v>140.01</v>
+        <v>140.85</v>
       </c>
       <c r="F169" s="7" t="inlineStr"/>
     </row>
@@ -4146,10 +4146,10 @@
         <v>102.33</v>
       </c>
       <c r="D170" s="5" t="n">
-        <v>118.33</v>
+        <v>119.04</v>
       </c>
       <c r="E170" s="5" t="n">
-        <v>130.83</v>
+        <v>131.62</v>
       </c>
       <c r="F170" s="7" t="inlineStr"/>
     </row>
@@ -4166,10 +4166,10 @@
         <v>109.49</v>
       </c>
       <c r="D171" s="5" t="n">
-        <v>123.52</v>
+        <v>124.26</v>
       </c>
       <c r="E171" s="5" t="n">
-        <v>139.71</v>
+        <v>140.55</v>
       </c>
       <c r="F171" s="7" t="inlineStr"/>
     </row>
@@ -4186,10 +4186,10 @@
         <v>89.78</v>
       </c>
       <c r="D172" s="5" t="n">
-        <v>95.23</v>
+        <v>95.8</v>
       </c>
       <c r="E172" s="5" t="n">
-        <v>114.35</v>
+        <v>115.03</v>
       </c>
       <c r="F172" s="7" t="inlineStr"/>
     </row>
@@ -4206,10 +4206,10 @@
         <v>81.81</v>
       </c>
       <c r="D173" s="5" t="n">
-        <v>89.04000000000001</v>
+        <v>89.56999999999999</v>
       </c>
       <c r="E173" s="5" t="n">
-        <v>104</v>
+        <v>104.62</v>
       </c>
       <c r="F173" s="7" t="inlineStr"/>
     </row>
@@ -4226,10 +4226,10 @@
         <v>63.98</v>
       </c>
       <c r="D174" s="5" t="n">
-        <v>73.11</v>
+        <v>73.55</v>
       </c>
       <c r="E174" s="5" t="n">
-        <v>81.18000000000001</v>
+        <v>81.67</v>
       </c>
       <c r="F174" s="7" t="inlineStr"/>
     </row>
@@ -4246,10 +4246,10 @@
         <v>106.88</v>
       </c>
       <c r="D175" s="5" t="n">
-        <v>136.32</v>
+        <v>137.14</v>
       </c>
       <c r="E175" s="5" t="n">
-        <v>135.31</v>
+        <v>136.12</v>
       </c>
       <c r="F175" s="7" t="inlineStr"/>
     </row>
@@ -4266,10 +4266,10 @@
         <v>77.56</v>
       </c>
       <c r="D176" s="5" t="n">
-        <v>86.26000000000001</v>
+        <v>86.77</v>
       </c>
       <c r="E176" s="5" t="n">
-        <v>97.97</v>
+        <v>98.55</v>
       </c>
       <c r="F176" s="7" t="inlineStr"/>
     </row>
@@ -4286,10 +4286,10 @@
         <v>50.23</v>
       </c>
       <c r="D177" s="5" t="n">
-        <v>65.76000000000001</v>
+        <v>66.15000000000001</v>
       </c>
       <c r="E177" s="5" t="n">
-        <v>63.3</v>
+        <v>63.68</v>
       </c>
       <c r="F177" s="7" t="inlineStr"/>
     </row>
@@ -4306,10 +4306,10 @@
         <v>49.85</v>
       </c>
       <c r="D178" s="5" t="n">
-        <v>71.54000000000001</v>
+        <v>71.97</v>
       </c>
       <c r="E178" s="5" t="n">
-        <v>62.74</v>
+        <v>63.12</v>
       </c>
       <c r="F178" s="7" t="inlineStr"/>
     </row>
@@ -4326,10 +4326,10 @@
         <v>38.9</v>
       </c>
       <c r="D179" s="5" t="n">
-        <v>49.15</v>
+        <v>49.45</v>
       </c>
       <c r="E179" s="5" t="n">
-        <v>48.9</v>
+        <v>49.19</v>
       </c>
       <c r="F179" s="7" t="inlineStr"/>
     </row>
@@ -4346,10 +4346,10 @@
         <v>35.52</v>
       </c>
       <c r="D180" s="5" t="n">
-        <v>46.92</v>
+        <v>47.2</v>
       </c>
       <c r="E180" s="5" t="n">
-        <v>44.6</v>
+        <v>44.86</v>
       </c>
       <c r="F180" s="7" t="inlineStr"/>
     </row>
@@ -4366,10 +4366,10 @@
         <v>24.48</v>
       </c>
       <c r="D181" s="5" t="n">
-        <v>29.53</v>
+        <v>29.71</v>
       </c>
       <c r="E181" s="5" t="n">
-        <v>30.93</v>
+        <v>31.12</v>
       </c>
       <c r="F181" s="7" t="inlineStr"/>
     </row>
@@ -4386,10 +4386,10 @@
         <v>41.19</v>
       </c>
       <c r="D182" s="5" t="n">
-        <v>44.22</v>
+        <v>44.49</v>
       </c>
       <c r="E182" s="5" t="n">
-        <v>52.39</v>
+        <v>52.7</v>
       </c>
       <c r="F182" s="7" t="inlineStr"/>
     </row>
@@ -4406,10 +4406,10 @@
         <v>39.42</v>
       </c>
       <c r="D183" s="5" t="n">
-        <v>46.61</v>
+        <v>46.89</v>
       </c>
       <c r="E183" s="5" t="n">
-        <v>50.47</v>
+        <v>50.77</v>
       </c>
       <c r="F183" s="7" t="inlineStr"/>
     </row>
@@ -4426,10 +4426,10 @@
         <v>57.55</v>
       </c>
       <c r="D184" s="5" t="n">
-        <v>72.09</v>
+        <v>72.52</v>
       </c>
       <c r="E184" s="5" t="n">
-        <v>73.3</v>
+        <v>73.73999999999999</v>
       </c>
       <c r="F184" s="7" t="inlineStr"/>
     </row>
@@ -4446,10 +4446,10 @@
         <v>56.78</v>
       </c>
       <c r="D185" s="5" t="n">
-        <v>70.64</v>
+        <v>71.06999999999999</v>
       </c>
       <c r="E185" s="5" t="n">
-        <v>71.95</v>
+        <v>72.38</v>
       </c>
       <c r="F185" s="7" t="inlineStr"/>
     </row>
@@ -4466,10 +4466,10 @@
         <v>39.19</v>
       </c>
       <c r="D186" s="5" t="n">
-        <v>47.3</v>
+        <v>47.58</v>
       </c>
       <c r="E186" s="5" t="n">
-        <v>49.41</v>
+        <v>49.7</v>
       </c>
       <c r="F186" s="7" t="inlineStr"/>
     </row>
@@ -4486,10 +4486,10 @@
         <v>42.32</v>
       </c>
       <c r="D187" s="5" t="n">
-        <v>52.17</v>
+        <v>52.49</v>
       </c>
       <c r="E187" s="5" t="n">
-        <v>53.19</v>
+        <v>53.51</v>
       </c>
       <c r="F187" s="7" t="inlineStr"/>
     </row>
@@ -4506,10 +4506,10 @@
         <v>57.44</v>
       </c>
       <c r="D188" s="5" t="n">
-        <v>74.40000000000001</v>
+        <v>74.84</v>
       </c>
       <c r="E188" s="5" t="n">
-        <v>71.98</v>
+        <v>72.41</v>
       </c>
       <c r="F188" s="7" t="inlineStr"/>
     </row>
@@ -4526,10 +4526,10 @@
         <v>43.49</v>
       </c>
       <c r="D189" s="5" t="n">
-        <v>46.05</v>
+        <v>46.33</v>
       </c>
       <c r="E189" s="5" t="n">
-        <v>54.34</v>
+        <v>54.66</v>
       </c>
       <c r="F189" s="7" t="inlineStr"/>
     </row>
@@ -4546,10 +4546,10 @@
         <v>40.16</v>
       </c>
       <c r="D190" s="5" t="n">
-        <v>47.15</v>
+        <v>47.43</v>
       </c>
       <c r="E190" s="5" t="n">
-        <v>50.08</v>
+        <v>50.38</v>
       </c>
       <c r="F190" s="7" t="inlineStr"/>
     </row>
@@ -4566,10 +4566,10 @@
         <v>36.94</v>
       </c>
       <c r="D191" s="5" t="n">
-        <v>39.81</v>
+        <v>40.05</v>
       </c>
       <c r="E191" s="5" t="n">
-        <v>45.98</v>
+        <v>46.25</v>
       </c>
       <c r="F191" s="7" t="inlineStr"/>
     </row>
@@ -4586,10 +4586,10 @@
         <v>31.99</v>
       </c>
       <c r="D192" s="5" t="n">
-        <v>38.24</v>
+        <v>38.46</v>
       </c>
       <c r="E192" s="5" t="n">
-        <v>39.74</v>
+        <v>39.98</v>
       </c>
       <c r="F192" s="7" t="inlineStr"/>
     </row>
@@ -4606,10 +4606,10 @@
         <v>28.96</v>
       </c>
       <c r="D193" s="5" t="n">
-        <v>31.4</v>
+        <v>31.59</v>
       </c>
       <c r="E193" s="5" t="n">
-        <v>35.89</v>
+        <v>36.1</v>
       </c>
       <c r="F193" s="7" t="inlineStr"/>
     </row>
@@ -4626,10 +4626,10 @@
         <v>45.01</v>
       </c>
       <c r="D194" s="5" t="n">
-        <v>50.99</v>
+        <v>51.3</v>
       </c>
       <c r="E194" s="5" t="n">
-        <v>55.64</v>
+        <v>55.97</v>
       </c>
       <c r="F194" s="7" t="inlineStr"/>
     </row>
@@ -4646,10 +4646,10 @@
         <v>77.88</v>
       </c>
       <c r="D195" s="5" t="n">
-        <v>84.94</v>
+        <v>85.45</v>
       </c>
       <c r="E195" s="5" t="n">
-        <v>96.04000000000001</v>
+        <v>96.62</v>
       </c>
       <c r="F195" s="7" t="inlineStr"/>
     </row>
@@ -4666,10 +4666,10 @@
         <v>43.06</v>
       </c>
       <c r="D196" s="5" t="n">
-        <v>46.91</v>
+        <v>47.19</v>
       </c>
       <c r="E196" s="5" t="n">
-        <v>52.95</v>
+        <v>53.27</v>
       </c>
       <c r="F196" s="7" t="inlineStr"/>
     </row>
@@ -4686,10 +4686,10 @@
         <v>25.45</v>
       </c>
       <c r="D197" s="5" t="n">
-        <v>26.32</v>
+        <v>26.47</v>
       </c>
       <c r="E197" s="5" t="n">
-        <v>31.21</v>
+        <v>31.39</v>
       </c>
       <c r="F197" s="7" t="inlineStr"/>
     </row>
@@ -4706,10 +4706,10 @@
         <v>22.15</v>
       </c>
       <c r="D198" s="5" t="n">
-        <v>20.2</v>
+        <v>20.32</v>
       </c>
       <c r="E198" s="5" t="n">
-        <v>27.08</v>
+        <v>27.25</v>
       </c>
       <c r="F198" s="7" t="inlineStr"/>
     </row>
@@ -4726,10 +4726,10 @@
         <v>9.77</v>
       </c>
       <c r="D199" s="5" t="n">
-        <v>11.42</v>
+        <v>11.49</v>
       </c>
       <c r="E199" s="5" t="n">
-        <v>11.9</v>
+        <v>11.97</v>
       </c>
       <c r="F199" s="7" t="inlineStr"/>
     </row>
@@ -4746,10 +4746,10 @@
         <v>33.57</v>
       </c>
       <c r="D200" s="5" t="n">
-        <v>38.51</v>
+        <v>38.74</v>
       </c>
       <c r="E200" s="5" t="n">
-        <v>40.7</v>
+        <v>40.95</v>
       </c>
       <c r="F200" s="7" t="inlineStr"/>
     </row>
@@ -4766,10 +4766,10 @@
         <v>50.76</v>
       </c>
       <c r="D201" s="5" t="n">
-        <v>60.19</v>
+        <v>60.55</v>
       </c>
       <c r="E201" s="5" t="n">
-        <v>61.29</v>
+        <v>61.66</v>
       </c>
       <c r="F201" s="7" t="inlineStr"/>
     </row>
@@ -4786,10 +4786,10 @@
         <v>66.84999999999999</v>
       </c>
       <c r="D202" s="5" t="n">
-        <v>74.97</v>
+        <v>75.42</v>
       </c>
       <c r="E202" s="5" t="n">
-        <v>80.14</v>
+        <v>80.62</v>
       </c>
       <c r="F202" s="7" t="inlineStr"/>
     </row>
@@ -4806,10 +4806,10 @@
         <v>78.13</v>
       </c>
       <c r="D203" s="5" t="n">
-        <v>85.95</v>
+        <v>86.45999999999999</v>
       </c>
       <c r="E203" s="5" t="n">
-        <v>93</v>
+        <v>93.55</v>
       </c>
       <c r="F203" s="7" t="inlineStr"/>
     </row>
@@ -4826,10 +4826,10 @@
         <v>78.79000000000001</v>
       </c>
       <c r="D204" s="5" t="n">
-        <v>88.44</v>
+        <v>88.97</v>
       </c>
       <c r="E204" s="5" t="n">
-        <v>93.12</v>
+        <v>93.68000000000001</v>
       </c>
       <c r="F204" s="7" t="inlineStr"/>
     </row>
@@ -4846,10 +4846,10 @@
         <v>165</v>
       </c>
       <c r="D205" s="5" t="n">
-        <v>165.97</v>
+        <v>166.97</v>
       </c>
       <c r="E205" s="5" t="n">
-        <v>193.85</v>
+        <v>195.02</v>
       </c>
       <c r="F205" s="7" t="inlineStr"/>
     </row>
@@ -4866,10 +4866,10 @@
         <v>241.96</v>
       </c>
       <c r="D206" s="5" t="n">
-        <v>253.66</v>
+        <v>255.19</v>
       </c>
       <c r="E206" s="5" t="n">
-        <v>282.59</v>
+        <v>284.29</v>
       </c>
       <c r="F206" s="7" t="inlineStr"/>
     </row>
@@ -4886,10 +4886,10 @@
         <v>382.49</v>
       </c>
       <c r="D207" s="5" t="n">
-        <v>332.94</v>
+        <v>334.94</v>
       </c>
       <c r="E207" s="5" t="n">
-        <v>444.11</v>
+        <v>446.77</v>
       </c>
       <c r="F207" s="7" t="inlineStr"/>
     </row>
@@ -4906,10 +4906,10 @@
         <v>366.3</v>
       </c>
       <c r="D208" s="5" t="n">
-        <v>372.56</v>
+        <v>374.8</v>
       </c>
       <c r="E208" s="5" t="n">
-        <v>422.72</v>
+        <v>425.25</v>
       </c>
       <c r="F208" s="7" t="inlineStr"/>
     </row>
@@ -4926,10 +4926,10 @@
         <v>169.69</v>
       </c>
       <c r="D209" s="5" t="n">
-        <v>171.49</v>
+        <v>172.52</v>
       </c>
       <c r="E209" s="5" t="n">
-        <v>194.64</v>
+        <v>195.81</v>
       </c>
       <c r="F209" s="7" t="inlineStr"/>
     </row>
@@ -4946,10 +4946,10 @@
         <v>150.78</v>
       </c>
       <c r="D210" s="5" t="n">
-        <v>151.34</v>
+        <v>152.25</v>
       </c>
       <c r="E210" s="5" t="n">
-        <v>171.91</v>
+        <v>172.94</v>
       </c>
       <c r="F210" s="7" t="inlineStr"/>
     </row>
@@ -4966,10 +4966,10 @@
         <v>126.75</v>
       </c>
       <c r="D211" s="5" t="n">
-        <v>138.24</v>
+        <v>139.07</v>
       </c>
       <c r="E211" s="5" t="n">
-        <v>143.63</v>
+        <v>144.49</v>
       </c>
       <c r="F211" s="7" t="inlineStr"/>
     </row>
@@ -4986,10 +4986,10 @@
         <v>114.81</v>
       </c>
       <c r="D212" s="5" t="n">
-        <v>113.73</v>
+        <v>114.41</v>
       </c>
       <c r="E212" s="5" t="n">
-        <v>129.3</v>
+        <v>130.08</v>
       </c>
       <c r="F212" s="7" t="inlineStr"/>
     </row>
@@ -5006,10 +5006,10 @@
         <v>67.38</v>
       </c>
       <c r="D213" s="5" t="n">
-        <v>85.48</v>
+        <v>85.98999999999999</v>
       </c>
       <c r="E213" s="5" t="n">
-        <v>75.43000000000001</v>
+        <v>75.88</v>
       </c>
       <c r="F213" s="7" t="inlineStr"/>
     </row>
@@ -5026,10 +5026,10 @@
         <v>81.12</v>
       </c>
       <c r="D214" s="5" t="n">
-        <v>96.8</v>
+        <v>97.38</v>
       </c>
       <c r="E214" s="5" t="n">
-        <v>90.40000000000001</v>
+        <v>90.94</v>
       </c>
       <c r="F214" s="7" t="inlineStr"/>
     </row>
@@ -5046,10 +5046,10 @@
         <v>76.66</v>
       </c>
       <c r="D215" s="5" t="n">
-        <v>90.45</v>
+        <v>90.98999999999999</v>
       </c>
       <c r="E215" s="5" t="n">
-        <v>85.05</v>
+        <v>85.56</v>
       </c>
       <c r="F215" s="7" t="inlineStr"/>
     </row>
@@ -5066,10 +5066,10 @@
         <v>68.13</v>
       </c>
       <c r="D216" s="5" t="n">
-        <v>79.91</v>
+        <v>80.39</v>
       </c>
       <c r="E216" s="5" t="n">
-        <v>75.25</v>
+        <v>75.7</v>
       </c>
       <c r="F216" s="7" t="inlineStr"/>
     </row>
@@ -5086,10 +5086,10 @@
         <v>70.95</v>
       </c>
       <c r="D217" s="5" t="n">
-        <v>77.13</v>
+        <v>77.59</v>
       </c>
       <c r="E217" s="5" t="n">
-        <v>78.14</v>
+        <v>78.61</v>
       </c>
       <c r="F217" s="7" t="inlineStr"/>
     </row>
@@ -5106,10 +5106,10 @@
         <v>86.54000000000001</v>
       </c>
       <c r="D218" s="5" t="n">
-        <v>92.42</v>
+        <v>92.98</v>
       </c>
       <c r="E218" s="5" t="n">
-        <v>95.04000000000001</v>
+        <v>95.61</v>
       </c>
       <c r="F218" s="7" t="inlineStr"/>
     </row>
@@ -5126,10 +5126,10 @@
         <v>52.33</v>
       </c>
       <c r="D219" s="5" t="n">
-        <v>41.66</v>
+        <v>41.91</v>
       </c>
       <c r="E219" s="5" t="n">
-        <v>57.31</v>
+        <v>57.65</v>
       </c>
       <c r="F219" s="7" t="inlineStr"/>
     </row>
@@ -5146,10 +5146,10 @@
         <v>32.72</v>
       </c>
       <c r="D220" s="5" t="n">
-        <v>25.44</v>
+        <v>25.59</v>
       </c>
       <c r="E220" s="5" t="n">
-        <v>35.69</v>
+        <v>35.91</v>
       </c>
       <c r="F220" s="7" t="inlineStr"/>
     </row>
@@ -5166,10 +5166,10 @@
         <v>37.93</v>
       </c>
       <c r="D221" s="5" t="n">
-        <v>40.92</v>
+        <v>41.16</v>
       </c>
       <c r="E221" s="5" t="n">
-        <v>41.22</v>
+        <v>41.47</v>
       </c>
       <c r="F221" s="7" t="inlineStr"/>
     </row>
@@ -5186,10 +5186,10 @@
         <v>24.88</v>
       </c>
       <c r="D222" s="5" t="n">
-        <v>28.92</v>
+        <v>29.09</v>
       </c>
       <c r="E222" s="5" t="n">
-        <v>26.94</v>
+        <v>27.1</v>
       </c>
       <c r="F222" s="7" t="inlineStr"/>
     </row>
@@ -5206,10 +5206,10 @@
         <v>36.02</v>
       </c>
       <c r="D223" s="5" t="n">
-        <v>40.69</v>
+        <v>40.93</v>
       </c>
       <c r="E223" s="5" t="n">
-        <v>38.91</v>
+        <v>39.15</v>
       </c>
       <c r="F223" s="7" t="inlineStr"/>
     </row>
@@ -5226,10 +5226,10 @@
         <v>57.48</v>
       </c>
       <c r="D224" s="5" t="n">
-        <v>64.65000000000001</v>
+        <v>65.04000000000001</v>
       </c>
       <c r="E224" s="5" t="n">
-        <v>61.97</v>
+        <v>62.34</v>
       </c>
       <c r="F224" s="7" t="inlineStr"/>
     </row>
@@ -5246,10 +5246,10 @@
         <v>49.05</v>
       </c>
       <c r="D225" s="5" t="n">
-        <v>56.04</v>
+        <v>56.38</v>
       </c>
       <c r="E225" s="5" t="n">
-        <v>52.77</v>
+        <v>53.09</v>
       </c>
       <c r="F225" s="7" t="inlineStr"/>
     </row>
@@ -5266,10 +5266,10 @@
         <v>49.55</v>
       </c>
       <c r="D226" s="5" t="n">
-        <v>53.75</v>
+        <v>54.08</v>
       </c>
       <c r="E226" s="5" t="n">
-        <v>53.14</v>
+        <v>53.46</v>
       </c>
       <c r="F226" s="7" t="inlineStr"/>
     </row>
@@ -5286,10 +5286,10 @@
         <v>110.19</v>
       </c>
       <c r="D227" s="5" t="n">
-        <v>87.53</v>
+        <v>88.05</v>
       </c>
       <c r="E227" s="5" t="n">
-        <v>117.82</v>
+        <v>118.52</v>
       </c>
       <c r="F227" s="7" t="inlineStr"/>
     </row>
@@ -5306,10 +5306,10 @@
         <v>67.51000000000001</v>
       </c>
       <c r="D228" s="5" t="n">
-        <v>74.23999999999999</v>
+        <v>74.69</v>
       </c>
       <c r="E228" s="5" t="n">
-        <v>71.95999999999999</v>
+        <v>72.39</v>
       </c>
       <c r="F228" s="7" t="inlineStr"/>
     </row>
@@ -5326,10 +5326,10 @@
         <v>70.58</v>
       </c>
       <c r="D229" s="5" t="n">
-        <v>77.91</v>
+        <v>78.38</v>
       </c>
       <c r="E229" s="5" t="n">
-        <v>74.97</v>
+        <v>75.42</v>
       </c>
       <c r="F229" s="7" t="inlineStr"/>
     </row>
@@ -5346,10 +5346,10 @@
         <v>145.64</v>
       </c>
       <c r="D230" s="5" t="n">
-        <v>149.28</v>
+        <v>150.18</v>
       </c>
       <c r="E230" s="5" t="n">
-        <v>154.16</v>
+        <v>155.09</v>
       </c>
       <c r="F230" s="7" t="inlineStr"/>
     </row>
@@ -5366,10 +5366,10 @@
         <v>212.93</v>
       </c>
       <c r="D231" s="5" t="n">
-        <v>188.03</v>
+        <v>189.16</v>
       </c>
       <c r="E231" s="5" t="n">
-        <v>224.61</v>
+        <v>225.96</v>
       </c>
       <c r="F231" s="7" t="inlineStr"/>
     </row>
@@ -5386,10 +5386,10 @@
         <v>215.63</v>
       </c>
       <c r="D232" s="5" t="n">
-        <v>190.54</v>
+        <v>191.68</v>
       </c>
       <c r="E232" s="5" t="n">
-        <v>227.3</v>
+        <v>228.66</v>
       </c>
       <c r="F232" s="7" t="inlineStr"/>
     </row>
@@ -5406,10 +5406,10 @@
         <v>156.24</v>
       </c>
       <c r="D233" s="5" t="n">
-        <v>135.55</v>
+        <v>136.37</v>
       </c>
       <c r="E233" s="5" t="n">
-        <v>164.57</v>
+        <v>165.56</v>
       </c>
       <c r="F233" s="7" t="inlineStr"/>
     </row>
@@ -5426,10 +5426,10 @@
         <v>31.25</v>
       </c>
       <c r="D234" s="5" t="n">
-        <v>23.69</v>
+        <v>23.84</v>
       </c>
       <c r="E234" s="5" t="n">
-        <v>32.89</v>
+        <v>33.09</v>
       </c>
       <c r="F234" s="7" t="inlineStr"/>
     </row>
@@ -5446,10 +5446,10 @@
         <v>52.52</v>
       </c>
       <c r="D235" s="5" t="n">
-        <v>52.38</v>
+        <v>52.7</v>
       </c>
       <c r="E235" s="5" t="n">
-        <v>55.25</v>
+        <v>55.58</v>
       </c>
       <c r="F235" s="7" t="inlineStr"/>
     </row>
@@ -5466,10 +5466,10 @@
         <v>96.58</v>
       </c>
       <c r="D236" s="5" t="n">
-        <v>100.77</v>
+        <v>101.37</v>
       </c>
       <c r="E236" s="5" t="n">
-        <v>101.52</v>
+        <v>102.13</v>
       </c>
       <c r="F236" s="7" t="inlineStr"/>
     </row>
@@ -5486,10 +5486,10 @@
         <v>68.48</v>
       </c>
       <c r="D237" s="5" t="n">
-        <v>79.95</v>
+        <v>80.43000000000001</v>
       </c>
       <c r="E237" s="5" t="n">
-        <v>71.94</v>
+        <v>72.37</v>
       </c>
       <c r="F237" s="7" t="inlineStr"/>
     </row>
@@ -5506,10 +5506,10 @@
         <v>109.08</v>
       </c>
       <c r="D238" s="5" t="n">
-        <v>119</v>
+        <v>119.72</v>
       </c>
       <c r="E238" s="5" t="n">
-        <v>114.24</v>
+        <v>114.92</v>
       </c>
       <c r="F238" s="7" t="inlineStr"/>
     </row>
@@ -5526,10 +5526,10 @@
         <v>125.01</v>
       </c>
       <c r="D239" s="5" t="n">
-        <v>127.06</v>
+        <v>127.82</v>
       </c>
       <c r="E239" s="5" t="n">
-        <v>130.52</v>
+        <v>131.31</v>
       </c>
       <c r="F239" s="7" t="inlineStr"/>
     </row>
@@ -5546,10 +5546,10 @@
         <v>100.83</v>
       </c>
       <c r="D240" s="5" t="n">
-        <v>104.14</v>
+        <v>104.76</v>
       </c>
       <c r="E240" s="5" t="n">
-        <v>104.96</v>
+        <v>105.59</v>
       </c>
       <c r="F240" s="7" t="inlineStr"/>
     </row>
@@ -5566,10 +5566,10 @@
         <v>98.58</v>
       </c>
       <c r="D241" s="5" t="n">
-        <v>104.39</v>
+        <v>105.01</v>
       </c>
       <c r="E241" s="5" t="n">
-        <v>102.36</v>
+        <v>102.98</v>
       </c>
       <c r="F241" s="7" t="inlineStr"/>
     </row>
@@ -5586,10 +5586,10 @@
         <v>113.37</v>
       </c>
       <c r="D242" s="5" t="n">
-        <v>107.09</v>
+        <v>107.73</v>
       </c>
       <c r="E242" s="5" t="n">
-        <v>117.43</v>
+        <v>118.13</v>
       </c>
       <c r="F242" s="7" t="inlineStr"/>
     </row>
@@ -5606,10 +5606,10 @@
         <v>327.99</v>
       </c>
       <c r="D243" s="5" t="n">
-        <v>226.63</v>
+        <v>227.99</v>
       </c>
       <c r="E243" s="5" t="n">
-        <v>338.89</v>
+        <v>340.92</v>
       </c>
       <c r="F243" s="7" t="inlineStr"/>
     </row>
@@ -5626,10 +5626,10 @@
         <v>130.45</v>
       </c>
       <c r="D244" s="5" t="n">
-        <v>121.23</v>
+        <v>121.96</v>
       </c>
       <c r="E244" s="5" t="n">
-        <v>134.19</v>
+        <v>135</v>
       </c>
       <c r="F244" s="7" t="inlineStr"/>
     </row>
@@ -5646,10 +5646,10 @@
         <v>133.56</v>
       </c>
       <c r="D245" s="5" t="n">
-        <v>128.25</v>
+        <v>129.02</v>
       </c>
       <c r="E245" s="5" t="n">
-        <v>136.79</v>
+        <v>137.61</v>
       </c>
       <c r="F245" s="7" t="inlineStr"/>
     </row>
@@ -5666,10 +5666,10 @@
         <v>36.24</v>
       </c>
       <c r="D246" s="5" t="n">
-        <v>29.2</v>
+        <v>29.37</v>
       </c>
       <c r="E246" s="5" t="n">
-        <v>36.96</v>
+        <v>37.18</v>
       </c>
       <c r="F246" s="7" t="inlineStr"/>
     </row>
@@ -5686,10 +5686,10 @@
         <v>26.88</v>
       </c>
       <c r="D247" s="5" t="n">
-        <v>24.99</v>
+        <v>25.14</v>
       </c>
       <c r="E247" s="5" t="n">
-        <v>27.36</v>
+        <v>27.52</v>
       </c>
       <c r="F247" s="7" t="inlineStr"/>
     </row>
@@ -5706,10 +5706,10 @@
         <v>34.34</v>
       </c>
       <c r="D248" s="5" t="n">
-        <v>41.15</v>
+        <v>41.39</v>
       </c>
       <c r="E248" s="5" t="n">
-        <v>34.88</v>
+        <v>35.09</v>
       </c>
       <c r="F248" s="7" t="inlineStr"/>
     </row>
@@ -5726,10 +5726,10 @@
         <v>55.6</v>
       </c>
       <c r="D249" s="5" t="n">
-        <v>60.16</v>
+        <v>60.52</v>
       </c>
       <c r="E249" s="5" t="n">
-        <v>56.36</v>
+        <v>56.7</v>
       </c>
       <c r="F249" s="7" t="inlineStr"/>
     </row>
@@ -5746,10 +5746,10 @@
         <v>114.88</v>
       </c>
       <c r="D250" s="5" t="n">
-        <v>101.85</v>
+        <v>102.46</v>
       </c>
       <c r="E250" s="5" t="n">
-        <v>115.93</v>
+        <v>116.62</v>
       </c>
       <c r="F250" s="7" t="inlineStr"/>
     </row>
@@ -5766,10 +5766,10 @@
         <v>87.56</v>
       </c>
       <c r="D251" s="5" t="n">
-        <v>90.69</v>
+        <v>91.23</v>
       </c>
       <c r="E251" s="5" t="n">
-        <v>87.95999999999999</v>
+        <v>88.48999999999999</v>
       </c>
       <c r="F251" s="7" t="inlineStr"/>
     </row>
@@ -5786,10 +5786,10 @@
         <v>90.94</v>
       </c>
       <c r="D252" s="5" t="n">
-        <v>91.04000000000001</v>
+        <v>91.59</v>
       </c>
       <c r="E252" s="5" t="n">
-        <v>90.94</v>
+        <v>91.48999999999999</v>
       </c>
       <c r="F252" s="7" t="inlineStr"/>
     </row>
@@ -5806,10 +5806,10 @@
         <v>87.34</v>
       </c>
       <c r="D253" s="5" t="n">
-        <v>85.23999999999999</v>
+        <v>85.58</v>
       </c>
       <c r="E253" s="5" t="n">
-        <v>87.34</v>
+        <v>87.69</v>
       </c>
       <c r="F253" s="7" t="inlineStr"/>
     </row>
@@ -5826,10 +5826,10 @@
         <v>100.08</v>
       </c>
       <c r="D254" s="5" t="n">
-        <v>96.14</v>
+        <v>96.33</v>
       </c>
       <c r="E254" s="5" t="n">
-        <v>100.08</v>
+        <v>100.28</v>
       </c>
       <c r="F254" s="7" t="inlineStr"/>
     </row>
@@ -5852,6 +5852,26 @@
         <v>81.73</v>
       </c>
       <c r="F255" s="7" t="inlineStr"/>
+    </row>
+    <row r="256">
+      <c r="A256" s="4" t="inlineStr">
+        <is>
+          <t>Jul 2026</t>
+        </is>
+      </c>
+      <c r="B256" s="5" t="n">
+        <v>71.04000000000001</v>
+      </c>
+      <c r="C256" s="5" t="n">
+        <v>93.83</v>
+      </c>
+      <c r="D256" s="5" t="n">
+        <v>71.04000000000001</v>
+      </c>
+      <c r="E256" s="5" t="n">
+        <v>93.83</v>
+      </c>
+      <c r="F256" s="7" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -5864,7 +5884,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E255"/>
+  <dimension ref="A1:E256"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -5914,10 +5934,10 @@
         <v>392.08</v>
       </c>
       <c r="D2" s="5" t="n">
-        <v>545.26</v>
+        <v>548.53</v>
       </c>
       <c r="E2" s="5" t="n">
-        <v>696.66</v>
+        <v>700.84</v>
       </c>
     </row>
     <row r="3">
@@ -5933,10 +5953,10 @@
         <v>86.38</v>
       </c>
       <c r="D3" s="5" t="n">
-        <v>139.44</v>
+        <v>140.27</v>
       </c>
       <c r="E3" s="5" t="n">
-        <v>153.18</v>
+        <v>154.1</v>
       </c>
     </row>
     <row r="4">
@@ -5952,10 +5972,10 @@
         <v>115.44</v>
       </c>
       <c r="D4" s="5" t="n">
-        <v>198.56</v>
+        <v>199.75</v>
       </c>
       <c r="E4" s="5" t="n">
-        <v>204.04</v>
+        <v>205.26</v>
       </c>
     </row>
     <row r="5">
@@ -5971,10 +5991,10 @@
         <v>141.07</v>
       </c>
       <c r="D5" s="5" t="n">
-        <v>188.85</v>
+        <v>189.98</v>
       </c>
       <c r="E5" s="5" t="n">
-        <v>248.52</v>
+        <v>250.01</v>
       </c>
     </row>
     <row r="6">
@@ -5990,10 +6010,10 @@
         <v>78.06</v>
       </c>
       <c r="D6" s="5" t="n">
-        <v>121.77</v>
+        <v>122.5</v>
       </c>
       <c r="E6" s="5" t="n">
-        <v>137.06</v>
+        <v>137.89</v>
       </c>
     </row>
     <row r="7">
@@ -6009,10 +6029,10 @@
         <v>102.26</v>
       </c>
       <c r="D7" s="5" t="n">
-        <v>144.4</v>
+        <v>145.27</v>
       </c>
       <c r="E7" s="5" t="n">
-        <v>179.25</v>
+        <v>180.32</v>
       </c>
     </row>
     <row r="8">
@@ -6028,10 +6048,10 @@
         <v>59.27</v>
       </c>
       <c r="D8" s="5" t="n">
-        <v>100.86</v>
+        <v>101.47</v>
       </c>
       <c r="E8" s="5" t="n">
-        <v>103.71</v>
+        <v>104.33</v>
       </c>
     </row>
     <row r="9">
@@ -6047,10 +6067,10 @@
         <v>47</v>
       </c>
       <c r="D9" s="5" t="n">
-        <v>74.8</v>
+        <v>75.25</v>
       </c>
       <c r="E9" s="5" t="n">
-        <v>82.09999999999999</v>
+        <v>82.59</v>
       </c>
     </row>
     <row r="10">
@@ -6066,10 +6086,10 @@
         <v>40.37</v>
       </c>
       <c r="D10" s="5" t="n">
-        <v>64.27</v>
+        <v>64.66</v>
       </c>
       <c r="E10" s="5" t="n">
-        <v>70.31999999999999</v>
+        <v>70.73999999999999</v>
       </c>
     </row>
     <row r="11">
@@ -6085,10 +6105,10 @@
         <v>35.76</v>
       </c>
       <c r="D11" s="5" t="n">
-        <v>56.34</v>
+        <v>56.68</v>
       </c>
       <c r="E11" s="5" t="n">
-        <v>62.11</v>
+        <v>62.48</v>
       </c>
     </row>
     <row r="12">
@@ -6104,10 +6124,10 @@
         <v>32.55</v>
       </c>
       <c r="D12" s="5" t="n">
-        <v>49.19</v>
+        <v>49.48</v>
       </c>
       <c r="E12" s="5" t="n">
-        <v>56.37</v>
+        <v>56.71</v>
       </c>
     </row>
     <row r="13">
@@ -6123,10 +6143,10 @@
         <v>33.84</v>
       </c>
       <c r="D13" s="5" t="n">
-        <v>57.47</v>
+        <v>57.82</v>
       </c>
       <c r="E13" s="5" t="n">
-        <v>58.3</v>
+        <v>58.65</v>
       </c>
     </row>
     <row r="14">
@@ -6142,10 +6162,10 @@
         <v>47.58</v>
       </c>
       <c r="D14" s="5" t="n">
-        <v>57.86</v>
+        <v>58.21</v>
       </c>
       <c r="E14" s="5" t="n">
-        <v>81.55</v>
+        <v>82.03</v>
       </c>
     </row>
     <row r="15">
@@ -6161,10 +6181,10 @@
         <v>51.97</v>
       </c>
       <c r="D15" s="5" t="n">
-        <v>70.56999999999999</v>
+        <v>70.98999999999999</v>
       </c>
       <c r="E15" s="5" t="n">
-        <v>88.61</v>
+        <v>89.14</v>
       </c>
     </row>
     <row r="16">
@@ -6180,10 +6200,10 @@
         <v>68.81</v>
       </c>
       <c r="D16" s="5" t="n">
-        <v>82</v>
+        <v>82.5</v>
       </c>
       <c r="E16" s="5" t="n">
-        <v>116.97</v>
+        <v>117.67</v>
       </c>
     </row>
     <row r="17">
@@ -6199,10 +6219,10 @@
         <v>39.83</v>
       </c>
       <c r="D17" s="5" t="n">
-        <v>59.61</v>
+        <v>59.97</v>
       </c>
       <c r="E17" s="5" t="n">
-        <v>67.51000000000001</v>
+        <v>67.91</v>
       </c>
     </row>
     <row r="18">
@@ -6218,10 +6238,10 @@
         <v>41.53</v>
       </c>
       <c r="D18" s="5" t="n">
-        <v>64.64</v>
+        <v>65.03</v>
       </c>
       <c r="E18" s="5" t="n">
-        <v>70.18000000000001</v>
+        <v>70.59999999999999</v>
       </c>
     </row>
     <row r="19">
@@ -6237,10 +6257,10 @@
         <v>36.83</v>
       </c>
       <c r="D19" s="5" t="n">
-        <v>57.87</v>
+        <v>58.22</v>
       </c>
       <c r="E19" s="5" t="n">
-        <v>62.26</v>
+        <v>62.64</v>
       </c>
     </row>
     <row r="20">
@@ -6256,10 +6276,10 @@
         <v>44.85</v>
       </c>
       <c r="D20" s="5" t="n">
-        <v>67.31</v>
+        <v>67.72</v>
       </c>
       <c r="E20" s="5" t="n">
-        <v>75.84999999999999</v>
+        <v>76.31</v>
       </c>
     </row>
     <row r="21">
@@ -6275,10 +6295,10 @@
         <v>41.08</v>
       </c>
       <c r="D21" s="5" t="n">
-        <v>59.5</v>
+        <v>59.86</v>
       </c>
       <c r="E21" s="5" t="n">
-        <v>69.5</v>
+        <v>69.92</v>
       </c>
     </row>
     <row r="22">
@@ -6294,10 +6314,10 @@
         <v>47.25</v>
       </c>
       <c r="D22" s="5" t="n">
-        <v>74.93000000000001</v>
+        <v>75.38</v>
       </c>
       <c r="E22" s="5" t="n">
-        <v>79.92</v>
+        <v>80.40000000000001</v>
       </c>
     </row>
     <row r="23">
@@ -6313,10 +6333,10 @@
         <v>67.59999999999999</v>
       </c>
       <c r="D23" s="5" t="n">
-        <v>89.54000000000001</v>
+        <v>90.06999999999999</v>
       </c>
       <c r="E23" s="5" t="n">
-        <v>114.31</v>
+        <v>114.99</v>
       </c>
     </row>
     <row r="24">
@@ -6332,10 +6352,10 @@
         <v>53.83</v>
       </c>
       <c r="D24" s="5" t="n">
-        <v>85.79000000000001</v>
+        <v>86.31</v>
       </c>
       <c r="E24" s="5" t="n">
-        <v>91</v>
+        <v>91.55</v>
       </c>
     </row>
     <row r="25">
@@ -6351,10 +6371,10 @@
         <v>82.19</v>
       </c>
       <c r="D25" s="5" t="n">
-        <v>123.04</v>
+        <v>123.77</v>
       </c>
       <c r="E25" s="5" t="n">
-        <v>138.37</v>
+        <v>139.2</v>
       </c>
     </row>
     <row r="26">
@@ -6370,10 +6390,10 @@
         <v>72.31</v>
       </c>
       <c r="D26" s="5" t="n">
-        <v>111.24</v>
+        <v>111.9</v>
       </c>
       <c r="E26" s="5" t="n">
-        <v>121.25</v>
+        <v>121.97</v>
       </c>
     </row>
     <row r="27">
@@ -6389,10 +6409,10 @@
         <v>79.93000000000001</v>
       </c>
       <c r="D27" s="5" t="n">
-        <v>129.94</v>
+        <v>130.72</v>
       </c>
       <c r="E27" s="5" t="n">
-        <v>133.48</v>
+        <v>134.28</v>
       </c>
     </row>
     <row r="28">
@@ -6408,10 +6428,10 @@
         <v>115.5</v>
       </c>
       <c r="D28" s="5" t="n">
-        <v>165.7</v>
+        <v>166.69</v>
       </c>
       <c r="E28" s="5" t="n">
-        <v>192.44</v>
+        <v>193.59</v>
       </c>
     </row>
     <row r="29">
@@ -6427,10 +6447,10 @@
         <v>48.82</v>
       </c>
       <c r="D29" s="5" t="n">
-        <v>67.66</v>
+        <v>68.06</v>
       </c>
       <c r="E29" s="5" t="n">
-        <v>81.15000000000001</v>
+        <v>81.64</v>
       </c>
     </row>
     <row r="30">
@@ -6446,10 +6466,10 @@
         <v>50.3</v>
       </c>
       <c r="D30" s="5" t="n">
-        <v>78.34999999999999</v>
+        <v>78.81999999999999</v>
       </c>
       <c r="E30" s="5" t="n">
-        <v>83.42</v>
+        <v>83.92</v>
       </c>
     </row>
     <row r="31">
@@ -6465,10 +6485,10 @@
         <v>38.54</v>
       </c>
       <c r="D31" s="5" t="n">
-        <v>56.26</v>
+        <v>56.6</v>
       </c>
       <c r="E31" s="5" t="n">
-        <v>63.72</v>
+        <v>64.09999999999999</v>
       </c>
     </row>
     <row r="32">
@@ -6484,10 +6504,10 @@
         <v>49.43</v>
       </c>
       <c r="D32" s="5" t="n">
-        <v>73.73999999999999</v>
+        <v>74.19</v>
       </c>
       <c r="E32" s="5" t="n">
-        <v>81.48</v>
+        <v>81.95999999999999</v>
       </c>
     </row>
     <row r="33">
@@ -6503,10 +6523,10 @@
         <v>60.54</v>
       </c>
       <c r="D33" s="5" t="n">
-        <v>83.73999999999999</v>
+        <v>84.23999999999999</v>
       </c>
       <c r="E33" s="5" t="n">
-        <v>99.48</v>
+        <v>100.08</v>
       </c>
     </row>
     <row r="34">
@@ -6522,10 +6542,10 @@
         <v>59.06</v>
       </c>
       <c r="D34" s="5" t="n">
-        <v>77.43000000000001</v>
+        <v>77.89</v>
       </c>
       <c r="E34" s="5" t="n">
-        <v>96.62</v>
+        <v>97.2</v>
       </c>
     </row>
     <row r="35">
@@ -6541,10 +6561,10 @@
         <v>67.75</v>
       </c>
       <c r="D35" s="5" t="n">
-        <v>91.95999999999999</v>
+        <v>92.51000000000001</v>
       </c>
       <c r="E35" s="5" t="n">
-        <v>110.34</v>
+        <v>111</v>
       </c>
     </row>
     <row r="36">
@@ -6560,10 +6580,10 @@
         <v>68.79000000000001</v>
       </c>
       <c r="D36" s="5" t="n">
-        <v>91.08</v>
+        <v>91.63</v>
       </c>
       <c r="E36" s="5" t="n">
-        <v>111.54</v>
+        <v>112.21</v>
       </c>
     </row>
     <row r="37">
@@ -6579,10 +6599,10 @@
         <v>63.84</v>
       </c>
       <c r="D37" s="5" t="n">
-        <v>88.64</v>
+        <v>89.17</v>
       </c>
       <c r="E37" s="5" t="n">
-        <v>103.02</v>
+        <v>103.64</v>
       </c>
     </row>
     <row r="38">
@@ -6598,10 +6618,10 @@
         <v>69.72</v>
       </c>
       <c r="D38" s="5" t="n">
-        <v>108.79</v>
+        <v>109.44</v>
       </c>
       <c r="E38" s="5" t="n">
-        <v>111.97</v>
+        <v>112.64</v>
       </c>
     </row>
     <row r="39">
@@ -6617,10 +6637,10 @@
         <v>63.27</v>
       </c>
       <c r="D39" s="5" t="n">
-        <v>89.44</v>
+        <v>89.98</v>
       </c>
       <c r="E39" s="5" t="n">
-        <v>101.12</v>
+        <v>101.73</v>
       </c>
     </row>
     <row r="40">
@@ -6636,10 +6656,10 @@
         <v>30.26</v>
       </c>
       <c r="D40" s="5" t="n">
-        <v>48.34</v>
+        <v>48.63</v>
       </c>
       <c r="E40" s="5" t="n">
-        <v>48.18</v>
+        <v>48.47</v>
       </c>
     </row>
     <row r="41">
@@ -6655,10 +6675,10 @@
         <v>60.94</v>
       </c>
       <c r="D41" s="5" t="n">
-        <v>87.17</v>
+        <v>87.69</v>
       </c>
       <c r="E41" s="5" t="n">
-        <v>96.65000000000001</v>
+        <v>97.23</v>
       </c>
     </row>
     <row r="42">
@@ -6674,10 +6694,10 @@
         <v>53.5</v>
       </c>
       <c r="D42" s="5" t="n">
-        <v>69.42</v>
+        <v>69.84</v>
       </c>
       <c r="E42" s="5" t="n">
-        <v>84.53</v>
+        <v>85.03</v>
       </c>
     </row>
     <row r="43">
@@ -6693,10 +6713,10 @@
         <v>56.32</v>
       </c>
       <c r="D43" s="5" t="n">
-        <v>72.63</v>
+        <v>73.06</v>
       </c>
       <c r="E43" s="5" t="n">
-        <v>89.08</v>
+        <v>89.61</v>
       </c>
     </row>
     <row r="44">
@@ -6712,10 +6732,10 @@
         <v>61.31</v>
       </c>
       <c r="D44" s="5" t="n">
-        <v>80.28</v>
+        <v>80.76000000000001</v>
       </c>
       <c r="E44" s="5" t="n">
-        <v>97.08</v>
+        <v>97.66</v>
       </c>
     </row>
     <row r="45">
@@ -6731,10 +6751,10 @@
         <v>38.3</v>
       </c>
       <c r="D45" s="5" t="n">
-        <v>52.17</v>
+        <v>52.48</v>
       </c>
       <c r="E45" s="5" t="n">
-        <v>60.71</v>
+        <v>61.07</v>
       </c>
     </row>
     <row r="46">
@@ -6750,10 +6770,10 @@
         <v>119.63</v>
       </c>
       <c r="D46" s="5" t="n">
-        <v>124.99</v>
+        <v>125.74</v>
       </c>
       <c r="E46" s="5" t="n">
-        <v>189.56</v>
+        <v>190.69</v>
       </c>
     </row>
     <row r="47">
@@ -6769,10 +6789,10 @@
         <v>63.91</v>
       </c>
       <c r="D47" s="5" t="n">
-        <v>61.9</v>
+        <v>62.27</v>
       </c>
       <c r="E47" s="5" t="n">
-        <v>101.23</v>
+        <v>101.84</v>
       </c>
     </row>
     <row r="48">
@@ -6788,10 +6808,10 @@
         <v>43.73</v>
       </c>
       <c r="D48" s="5" t="n">
-        <v>57.76</v>
+        <v>58.11</v>
       </c>
       <c r="E48" s="5" t="n">
-        <v>69.23999999999999</v>
+        <v>69.66</v>
       </c>
     </row>
     <row r="49">
@@ -6807,10 +6827,10 @@
         <v>63.23</v>
       </c>
       <c r="D49" s="5" t="n">
-        <v>109.56</v>
+        <v>110.22</v>
       </c>
       <c r="E49" s="5" t="n">
-        <v>99.95</v>
+        <v>100.55</v>
       </c>
     </row>
     <row r="50">
@@ -6826,10 +6846,10 @@
         <v>50.07</v>
       </c>
       <c r="D50" s="5" t="n">
-        <v>73.92</v>
+        <v>74.36</v>
       </c>
       <c r="E50" s="5" t="n">
-        <v>79.02</v>
+        <v>79.48999999999999</v>
       </c>
     </row>
     <row r="51">
@@ -6845,10 +6865,10 @@
         <v>292.02</v>
       </c>
       <c r="D51" s="5" t="n">
-        <v>273.83</v>
+        <v>275.47</v>
       </c>
       <c r="E51" s="5" t="n">
-        <v>460.08</v>
+        <v>462.84</v>
       </c>
     </row>
     <row r="52">
@@ -6864,10 +6884,10 @@
         <v>31.68</v>
       </c>
       <c r="D52" s="5" t="n">
-        <v>40.66</v>
+        <v>40.91</v>
       </c>
       <c r="E52" s="5" t="n">
-        <v>49.76</v>
+        <v>50.05</v>
       </c>
     </row>
     <row r="53">
@@ -6883,10 +6903,10 @@
         <v>28.03</v>
       </c>
       <c r="D53" s="5" t="n">
-        <v>33.33</v>
+        <v>33.53</v>
       </c>
       <c r="E53" s="5" t="n">
-        <v>43.89</v>
+        <v>44.15</v>
       </c>
     </row>
     <row r="54">
@@ -6902,10 +6922,10 @@
         <v>27.51</v>
       </c>
       <c r="D54" s="5" t="n">
-        <v>33.59</v>
+        <v>33.79</v>
       </c>
       <c r="E54" s="5" t="n">
-        <v>42.94</v>
+        <v>43.19</v>
       </c>
     </row>
     <row r="55">
@@ -6921,10 +6941,10 @@
         <v>30.14</v>
       </c>
       <c r="D55" s="5" t="n">
-        <v>40.16</v>
+        <v>40.41</v>
       </c>
       <c r="E55" s="5" t="n">
-        <v>46.96</v>
+        <v>47.24</v>
       </c>
     </row>
     <row r="56">
@@ -6940,10 +6960,10 @@
         <v>38.11</v>
       </c>
       <c r="D56" s="5" t="n">
-        <v>52.41</v>
+        <v>52.72</v>
       </c>
       <c r="E56" s="5" t="n">
-        <v>59.27</v>
+        <v>59.62</v>
       </c>
     </row>
     <row r="57">
@@ -6959,10 +6979,10 @@
         <v>31.86</v>
       </c>
       <c r="D57" s="5" t="n">
-        <v>49.46</v>
+        <v>49.76</v>
       </c>
       <c r="E57" s="5" t="n">
-        <v>49.46</v>
+        <v>49.76</v>
       </c>
     </row>
     <row r="58">
@@ -6978,10 +6998,10 @@
         <v>32.52</v>
       </c>
       <c r="D58" s="5" t="n">
-        <v>45.24</v>
+        <v>45.51</v>
       </c>
       <c r="E58" s="5" t="n">
-        <v>50.33</v>
+        <v>50.63</v>
       </c>
     </row>
     <row r="59">
@@ -6997,10 +7017,10 @@
         <v>20.61</v>
       </c>
       <c r="D59" s="5" t="n">
-        <v>36.97</v>
+        <v>37.19</v>
       </c>
       <c r="E59" s="5" t="n">
-        <v>31.8</v>
+        <v>31.99</v>
       </c>
     </row>
     <row r="60">
@@ -7016,10 +7036,10 @@
         <v>28.67</v>
       </c>
       <c r="D60" s="5" t="n">
-        <v>40.3</v>
+        <v>40.54</v>
       </c>
       <c r="E60" s="5" t="n">
-        <v>44.1</v>
+        <v>44.36</v>
       </c>
     </row>
     <row r="61">
@@ -7035,10 +7055,10 @@
         <v>26.2</v>
       </c>
       <c r="D61" s="5" t="n">
-        <v>37.49</v>
+        <v>37.71</v>
       </c>
       <c r="E61" s="5" t="n">
-        <v>40.22</v>
+        <v>40.46</v>
       </c>
     </row>
     <row r="62">
@@ -7054,10 +7074,10 @@
         <v>40.53</v>
       </c>
       <c r="D62" s="5" t="n">
-        <v>87.27</v>
+        <v>87.8</v>
       </c>
       <c r="E62" s="5" t="n">
-        <v>62.09</v>
+        <v>62.46</v>
       </c>
     </row>
     <row r="63">
@@ -7073,10 +7093,10 @@
         <v>34.48</v>
       </c>
       <c r="D63" s="5" t="n">
-        <v>47.23</v>
+        <v>47.51</v>
       </c>
       <c r="E63" s="5" t="n">
-        <v>52.72</v>
+        <v>53.03</v>
       </c>
     </row>
     <row r="64">
@@ -7092,10 +7112,10 @@
         <v>33.99</v>
       </c>
       <c r="D64" s="5" t="n">
-        <v>46.06</v>
+        <v>46.34</v>
       </c>
       <c r="E64" s="5" t="n">
-        <v>51.84</v>
+        <v>52.15</v>
       </c>
     </row>
     <row r="65">
@@ -7111,10 +7131,10 @@
         <v>27.77</v>
       </c>
       <c r="D65" s="5" t="n">
-        <v>98.59999999999999</v>
+        <v>99.19</v>
       </c>
       <c r="E65" s="5" t="n">
-        <v>42.25</v>
+        <v>42.51</v>
       </c>
     </row>
     <row r="66">
@@ -7130,10 +7150,10 @@
         <v>23.94</v>
       </c>
       <c r="D66" s="5" t="n">
-        <v>31.51</v>
+        <v>31.7</v>
       </c>
       <c r="E66" s="5" t="n">
-        <v>36.34</v>
+        <v>36.56</v>
       </c>
     </row>
     <row r="67">
@@ -7149,10 +7169,10 @@
         <v>18.56</v>
       </c>
       <c r="D67" s="5" t="n">
-        <v>27.5</v>
+        <v>27.66</v>
       </c>
       <c r="E67" s="5" t="n">
-        <v>28.14</v>
+        <v>28.3</v>
       </c>
     </row>
     <row r="68">
@@ -7168,10 +7188,10 @@
         <v>38.48</v>
       </c>
       <c r="D68" s="5" t="n">
-        <v>41.03</v>
+        <v>41.28</v>
       </c>
       <c r="E68" s="5" t="n">
-        <v>58.26</v>
+        <v>58.61</v>
       </c>
     </row>
     <row r="69">
@@ -7187,10 +7207,10 @@
         <v>17.8</v>
       </c>
       <c r="D69" s="5" t="n">
-        <v>25.25</v>
+        <v>25.4</v>
       </c>
       <c r="E69" s="5" t="n">
-        <v>26.91</v>
+        <v>27.08</v>
       </c>
     </row>
     <row r="70">
@@ -7206,10 +7226,10 @@
         <v>28.36</v>
       </c>
       <c r="D70" s="5" t="n">
-        <v>39.04</v>
+        <v>39.27</v>
       </c>
       <c r="E70" s="5" t="n">
-        <v>42.66</v>
+        <v>42.92</v>
       </c>
     </row>
     <row r="71">
@@ -7225,10 +7245,10 @@
         <v>31.48</v>
       </c>
       <c r="D71" s="5" t="n">
-        <v>42.98</v>
+        <v>43.24</v>
       </c>
       <c r="E71" s="5" t="n">
-        <v>47.11</v>
+        <v>47.4</v>
       </c>
     </row>
     <row r="72">
@@ -7244,10 +7264,10 @@
         <v>27.22</v>
       </c>
       <c r="D72" s="5" t="n">
-        <v>38.46</v>
+        <v>38.69</v>
       </c>
       <c r="E72" s="5" t="n">
-        <v>40.53</v>
+        <v>40.77</v>
       </c>
     </row>
     <row r="73">
@@ -7263,10 +7283,10 @@
         <v>27.79</v>
       </c>
       <c r="D73" s="5" t="n">
-        <v>39.78</v>
+        <v>40.02</v>
       </c>
       <c r="E73" s="5" t="n">
-        <v>41.25</v>
+        <v>41.5</v>
       </c>
     </row>
     <row r="74">
@@ -7282,10 +7302,10 @@
         <v>40.73</v>
       </c>
       <c r="D74" s="5" t="n">
-        <v>57.23</v>
+        <v>57.57</v>
       </c>
       <c r="E74" s="5" t="n">
-        <v>60.28</v>
+        <v>60.64</v>
       </c>
     </row>
     <row r="75">
@@ -7301,10 +7321,10 @@
         <v>32.31</v>
       </c>
       <c r="D75" s="5" t="n">
-        <v>43.02</v>
+        <v>43.28</v>
       </c>
       <c r="E75" s="5" t="n">
-        <v>47.67</v>
+        <v>47.96</v>
       </c>
     </row>
     <row r="76">
@@ -7320,10 +7340,10 @@
         <v>49.12</v>
       </c>
       <c r="D76" s="5" t="n">
-        <v>47.99</v>
+        <v>48.28</v>
       </c>
       <c r="E76" s="5" t="n">
-        <v>72.33</v>
+        <v>72.76000000000001</v>
       </c>
     </row>
     <row r="77">
@@ -7339,10 +7359,10 @@
         <v>34.69</v>
       </c>
       <c r="D77" s="5" t="n">
-        <v>39.91</v>
+        <v>40.15</v>
       </c>
       <c r="E77" s="5" t="n">
-        <v>50.98</v>
+        <v>51.29</v>
       </c>
     </row>
     <row r="78">
@@ -7358,10 +7378,10 @@
         <v>29.9</v>
       </c>
       <c r="D78" s="5" t="n">
-        <v>38.72</v>
+        <v>38.95</v>
       </c>
       <c r="E78" s="5" t="n">
-        <v>43.85</v>
+        <v>44.12</v>
       </c>
     </row>
     <row r="79">
@@ -7377,10 +7397,10 @@
         <v>31.6</v>
       </c>
       <c r="D79" s="5" t="n">
-        <v>47.78</v>
+        <v>48.07</v>
       </c>
       <c r="E79" s="5" t="n">
-        <v>46.35</v>
+        <v>46.63</v>
       </c>
     </row>
     <row r="80">
@@ -7396,10 +7416,10 @@
         <v>30.44</v>
       </c>
       <c r="D80" s="5" t="n">
-        <v>45.1</v>
+        <v>45.37</v>
       </c>
       <c r="E80" s="5" t="n">
-        <v>44.65</v>
+        <v>44.91</v>
       </c>
     </row>
     <row r="81">
@@ -7415,10 +7435,10 @@
         <v>26.57</v>
       </c>
       <c r="D81" s="5" t="n">
-        <v>37.91</v>
+        <v>38.14</v>
       </c>
       <c r="E81" s="5" t="n">
-        <v>38.97</v>
+        <v>39.2</v>
       </c>
     </row>
     <row r="82">
@@ -7434,10 +7454,10 @@
         <v>34.13</v>
       </c>
       <c r="D82" s="5" t="n">
-        <v>57.66</v>
+        <v>58</v>
       </c>
       <c r="E82" s="5" t="n">
-        <v>50.05</v>
+        <v>50.35</v>
       </c>
     </row>
     <row r="83">
@@ -7453,10 +7473,10 @@
         <v>29.92</v>
       </c>
       <c r="D83" s="5" t="n">
-        <v>54.79</v>
+        <v>55.12</v>
       </c>
       <c r="E83" s="5" t="n">
-        <v>43.87</v>
+        <v>44.13</v>
       </c>
     </row>
     <row r="84">
@@ -7472,10 +7492,10 @@
         <v>29.84</v>
       </c>
       <c r="D84" s="5" t="n">
-        <v>52.65</v>
+        <v>52.97</v>
       </c>
       <c r="E84" s="5" t="n">
-        <v>43.74</v>
+        <v>44</v>
       </c>
     </row>
     <row r="85">
@@ -7491,10 +7511,10 @@
         <v>42.04</v>
       </c>
       <c r="D85" s="5" t="n">
-        <v>52.62</v>
+        <v>52.94</v>
       </c>
       <c r="E85" s="5" t="n">
-        <v>61.52</v>
+        <v>61.89</v>
       </c>
     </row>
     <row r="86">
@@ -7510,10 +7530,10 @@
         <v>29.9</v>
       </c>
       <c r="D86" s="5" t="n">
-        <v>48.06</v>
+        <v>48.35</v>
       </c>
       <c r="E86" s="5" t="n">
-        <v>43.68</v>
+        <v>43.94</v>
       </c>
     </row>
     <row r="87">
@@ -7529,10 +7549,10 @@
         <v>38.55</v>
       </c>
       <c r="D87" s="5" t="n">
-        <v>50.22</v>
+        <v>50.52</v>
       </c>
       <c r="E87" s="5" t="n">
-        <v>56.22</v>
+        <v>56.55</v>
       </c>
     </row>
     <row r="88">
@@ -7548,10 +7568,10 @@
         <v>67.45</v>
       </c>
       <c r="D88" s="5" t="n">
-        <v>85.98</v>
+        <v>86.5</v>
       </c>
       <c r="E88" s="5" t="n">
-        <v>97.92</v>
+        <v>98.5</v>
       </c>
     </row>
     <row r="89">
@@ -7567,10 +7587,10 @@
         <v>48.6</v>
       </c>
       <c r="D89" s="5" t="n">
-        <v>68.23999999999999</v>
+        <v>68.65000000000001</v>
       </c>
       <c r="E89" s="5" t="n">
-        <v>70.23</v>
+        <v>70.66</v>
       </c>
     </row>
     <row r="90">
@@ -7586,10 +7606,10 @@
         <v>41.42</v>
       </c>
       <c r="D90" s="5" t="n">
-        <v>56.77</v>
+        <v>57.11</v>
       </c>
       <c r="E90" s="5" t="n">
-        <v>59.59</v>
+        <v>59.95</v>
       </c>
     </row>
     <row r="91">
@@ -7605,10 +7625,10 @@
         <v>44.97</v>
       </c>
       <c r="D91" s="5" t="n">
-        <v>62.7</v>
+        <v>63.08</v>
       </c>
       <c r="E91" s="5" t="n">
-        <v>64.64</v>
+        <v>65.03</v>
       </c>
     </row>
     <row r="92">
@@ -7624,10 +7644,10 @@
         <v>51.39</v>
       </c>
       <c r="D92" s="5" t="n">
-        <v>72.64</v>
+        <v>73.08</v>
       </c>
       <c r="E92" s="5" t="n">
-        <v>73.81</v>
+        <v>74.25</v>
       </c>
     </row>
     <row r="93">
@@ -7643,10 +7663,10 @@
         <v>46.41</v>
       </c>
       <c r="D93" s="5" t="n">
-        <v>67.02</v>
+        <v>67.42</v>
       </c>
       <c r="E93" s="5" t="n">
-        <v>66.59999999999999</v>
+        <v>67</v>
       </c>
     </row>
     <row r="94">
@@ -7662,10 +7682,10 @@
         <v>46.53</v>
       </c>
       <c r="D94" s="5" t="n">
-        <v>81.65000000000001</v>
+        <v>82.14</v>
       </c>
       <c r="E94" s="5" t="n">
-        <v>66.7</v>
+        <v>67.09999999999999</v>
       </c>
     </row>
     <row r="95">
@@ -7681,10 +7701,10 @@
         <v>46.11</v>
       </c>
       <c r="D95" s="5" t="n">
-        <v>65.56</v>
+        <v>65.95</v>
       </c>
       <c r="E95" s="5" t="n">
-        <v>66.02</v>
+        <v>66.42</v>
       </c>
     </row>
     <row r="96">
@@ -7700,10 +7720,10 @@
         <v>50.82</v>
       </c>
       <c r="D96" s="5" t="n">
-        <v>71.23999999999999</v>
+        <v>71.66</v>
       </c>
       <c r="E96" s="5" t="n">
-        <v>72.68000000000001</v>
+        <v>73.12</v>
       </c>
     </row>
     <row r="97">
@@ -7719,10 +7739,10 @@
         <v>46.73</v>
       </c>
       <c r="D97" s="5" t="n">
-        <v>64.45</v>
+        <v>64.83</v>
       </c>
       <c r="E97" s="5" t="n">
-        <v>66.75</v>
+        <v>67.15000000000001</v>
       </c>
     </row>
     <row r="98">
@@ -7738,10 +7758,10 @@
         <v>49.68</v>
       </c>
       <c r="D98" s="5" t="n">
-        <v>63.72</v>
+        <v>64.11</v>
       </c>
       <c r="E98" s="5" t="n">
-        <v>70.87</v>
+        <v>71.3</v>
       </c>
     </row>
     <row r="99">
@@ -7757,10 +7777,10 @@
         <v>51.77</v>
       </c>
       <c r="D99" s="5" t="n">
-        <v>71.08</v>
+        <v>71.51000000000001</v>
       </c>
       <c r="E99" s="5" t="n">
-        <v>73.76000000000001</v>
+        <v>74.2</v>
       </c>
     </row>
     <row r="100">
@@ -7776,10 +7796,10 @@
         <v>50.69</v>
       </c>
       <c r="D100" s="5" t="n">
-        <v>73.08</v>
+        <v>73.52</v>
       </c>
       <c r="E100" s="5" t="n">
-        <v>71.93000000000001</v>
+        <v>72.36</v>
       </c>
     </row>
     <row r="101">
@@ -7795,10 +7815,10 @@
         <v>49.44</v>
       </c>
       <c r="D101" s="5" t="n">
-        <v>64.83</v>
+        <v>65.22</v>
       </c>
       <c r="E101" s="5" t="n">
-        <v>69.87</v>
+        <v>70.29000000000001</v>
       </c>
     </row>
     <row r="102">
@@ -7814,10 +7834,10 @@
         <v>44.8</v>
       </c>
       <c r="D102" s="5" t="n">
-        <v>59.72</v>
+        <v>60.08</v>
       </c>
       <c r="E102" s="5" t="n">
-        <v>63.06</v>
+        <v>63.44</v>
       </c>
     </row>
     <row r="103">
@@ -7833,10 +7853,10 @@
         <v>41.47</v>
       </c>
       <c r="D103" s="5" t="n">
-        <v>54.2</v>
+        <v>54.53</v>
       </c>
       <c r="E103" s="5" t="n">
-        <v>58.23</v>
+        <v>58.58</v>
       </c>
     </row>
     <row r="104">
@@ -7852,10 +7872,10 @@
         <v>52.99</v>
       </c>
       <c r="D104" s="5" t="n">
-        <v>65.97</v>
+        <v>66.36</v>
       </c>
       <c r="E104" s="5" t="n">
-        <v>74.23</v>
+        <v>74.68000000000001</v>
       </c>
     </row>
     <row r="105">
@@ -7871,10 +7891,10 @@
         <v>37.58</v>
       </c>
       <c r="D105" s="5" t="n">
-        <v>52.55</v>
+        <v>52.86</v>
       </c>
       <c r="E105" s="5" t="n">
-        <v>52.52</v>
+        <v>52.84</v>
       </c>
     </row>
     <row r="106">
@@ -7890,10 +7910,10 @@
         <v>29.48</v>
       </c>
       <c r="D106" s="5" t="n">
-        <v>48.65</v>
+        <v>48.94</v>
       </c>
       <c r="E106" s="5" t="n">
-        <v>41.12</v>
+        <v>41.37</v>
       </c>
     </row>
     <row r="107">
@@ -7909,10 +7929,10 @@
         <v>43.27</v>
       </c>
       <c r="D107" s="5" t="n">
-        <v>61.1</v>
+        <v>61.46</v>
       </c>
       <c r="E107" s="5" t="n">
-        <v>60.23</v>
+        <v>60.6</v>
       </c>
     </row>
     <row r="108">
@@ -7928,10 +7948,10 @@
         <v>45.47</v>
       </c>
       <c r="D108" s="5" t="n">
-        <v>62.21</v>
+        <v>62.59</v>
       </c>
       <c r="E108" s="5" t="n">
-        <v>63.17</v>
+        <v>63.55</v>
       </c>
     </row>
     <row r="109">
@@ -7947,10 +7967,10 @@
         <v>38.57</v>
       </c>
       <c r="D109" s="5" t="n">
-        <v>52.26</v>
+        <v>52.58</v>
       </c>
       <c r="E109" s="5" t="n">
-        <v>53.5</v>
+        <v>53.82</v>
       </c>
     </row>
     <row r="110">
@@ -7966,10 +7986,10 @@
         <v>40.99</v>
       </c>
       <c r="D110" s="5" t="n">
-        <v>50.57</v>
+        <v>50.87</v>
       </c>
       <c r="E110" s="5" t="n">
-        <v>56.76</v>
+        <v>57.1</v>
       </c>
     </row>
     <row r="111">
@@ -7985,10 +8005,10 @@
         <v>44.06</v>
       </c>
       <c r="D111" s="5" t="n">
-        <v>59.65</v>
+        <v>60.01</v>
       </c>
       <c r="E111" s="5" t="n">
-        <v>60.91</v>
+        <v>61.27</v>
       </c>
     </row>
     <row r="112">
@@ -8004,10 +8024,10 @@
         <v>37.29</v>
       </c>
       <c r="D112" s="5" t="n">
-        <v>46.7</v>
+        <v>46.98</v>
       </c>
       <c r="E112" s="5" t="n">
-        <v>51.48</v>
+        <v>51.78</v>
       </c>
     </row>
     <row r="113">
@@ -8023,10 +8043,10 @@
         <v>41.88</v>
       </c>
       <c r="D113" s="5" t="n">
-        <v>50.09</v>
+        <v>50.39</v>
       </c>
       <c r="E113" s="5" t="n">
-        <v>57.73</v>
+        <v>58.08</v>
       </c>
     </row>
     <row r="114">
@@ -8042,10 +8062,10 @@
         <v>40.3</v>
       </c>
       <c r="D114" s="5" t="n">
-        <v>51.83</v>
+        <v>52.14</v>
       </c>
       <c r="E114" s="5" t="n">
-        <v>55.48</v>
+        <v>55.81</v>
       </c>
     </row>
     <row r="115">
@@ -8061,10 +8081,10 @@
         <v>32.91</v>
       </c>
       <c r="D115" s="5" t="n">
-        <v>48.03</v>
+        <v>48.31</v>
       </c>
       <c r="E115" s="5" t="n">
-        <v>45.27</v>
+        <v>45.55</v>
       </c>
     </row>
     <row r="116">
@@ -8080,10 +8100,10 @@
         <v>37.03</v>
       </c>
       <c r="D116" s="5" t="n">
-        <v>54.91</v>
+        <v>55.24</v>
       </c>
       <c r="E116" s="5" t="n">
-        <v>50.91</v>
+        <v>51.21</v>
       </c>
     </row>
     <row r="117">
@@ -8099,10 +8119,10 @@
         <v>44.4</v>
       </c>
       <c r="D117" s="5" t="n">
-        <v>62.19</v>
+        <v>62.56</v>
       </c>
       <c r="E117" s="5" t="n">
-        <v>61</v>
+        <v>61.37</v>
       </c>
     </row>
     <row r="118">
@@ -8118,10 +8138,10 @@
         <v>36.8</v>
       </c>
       <c r="D118" s="5" t="n">
-        <v>48.17</v>
+        <v>48.46</v>
       </c>
       <c r="E118" s="5" t="n">
-        <v>50.53</v>
+        <v>50.83</v>
       </c>
     </row>
     <row r="119">
@@ -8137,10 +8157,10 @@
         <v>41.1</v>
       </c>
       <c r="D119" s="5" t="n">
-        <v>58.37</v>
+        <v>58.72</v>
       </c>
       <c r="E119" s="5" t="n">
-        <v>56.4</v>
+        <v>56.74</v>
       </c>
     </row>
     <row r="120">
@@ -8156,10 +8176,10 @@
         <v>39.98</v>
       </c>
       <c r="D120" s="5" t="n">
-        <v>54.54</v>
+        <v>54.87</v>
       </c>
       <c r="E120" s="5" t="n">
-        <v>54.83</v>
+        <v>55.16</v>
       </c>
     </row>
     <row r="121">
@@ -8175,10 +8195,10 @@
         <v>38.37</v>
       </c>
       <c r="D121" s="5" t="n">
-        <v>55.6</v>
+        <v>55.93</v>
       </c>
       <c r="E121" s="5" t="n">
-        <v>52.49</v>
+        <v>52.81</v>
       </c>
     </row>
     <row r="122">
@@ -8194,10 +8214,10 @@
         <v>37.02</v>
       </c>
       <c r="D122" s="5" t="n">
-        <v>38.63</v>
+        <v>38.86</v>
       </c>
       <c r="E122" s="5" t="n">
-        <v>50.53</v>
+        <v>50.83</v>
       </c>
     </row>
     <row r="123">
@@ -8213,10 +8233,10 @@
         <v>37.68</v>
       </c>
       <c r="D123" s="5" t="n">
-        <v>43.91</v>
+        <v>44.18</v>
       </c>
       <c r="E123" s="5" t="n">
-        <v>51.31</v>
+        <v>51.61</v>
       </c>
     </row>
     <row r="124">
@@ -8232,10 +8252,10 @@
         <v>39.11</v>
       </c>
       <c r="D124" s="5" t="n">
-        <v>47.46</v>
+        <v>47.74</v>
       </c>
       <c r="E124" s="5" t="n">
-        <v>53.18</v>
+        <v>53.5</v>
       </c>
     </row>
     <row r="125">
@@ -8251,10 +8271,10 @@
         <v>38.28</v>
       </c>
       <c r="D125" s="5" t="n">
-        <v>43.31</v>
+        <v>43.57</v>
       </c>
       <c r="E125" s="5" t="n">
-        <v>51.99</v>
+        <v>52.3</v>
       </c>
     </row>
     <row r="126">
@@ -8270,10 +8290,10 @@
         <v>48.78</v>
       </c>
       <c r="D126" s="5" t="n">
-        <v>62.42</v>
+        <v>62.79</v>
       </c>
       <c r="E126" s="5" t="n">
-        <v>66.16</v>
+        <v>66.56</v>
       </c>
     </row>
     <row r="127">
@@ -8289,10 +8309,10 @@
         <v>60.34</v>
       </c>
       <c r="D127" s="5" t="n">
-        <v>80.22</v>
+        <v>80.7</v>
       </c>
       <c r="E127" s="5" t="n">
-        <v>81.73999999999999</v>
+        <v>82.23</v>
       </c>
     </row>
     <row r="128">
@@ -8308,10 +8328,10 @@
         <v>85.88</v>
       </c>
       <c r="D128" s="5" t="n">
-        <v>113.28</v>
+        <v>113.96</v>
       </c>
       <c r="E128" s="5" t="n">
-        <v>116.18</v>
+        <v>116.88</v>
       </c>
     </row>
     <row r="129">
@@ -8327,10 +8347,10 @@
         <v>97.17</v>
       </c>
       <c r="D129" s="5" t="n">
-        <v>129.84</v>
+        <v>130.62</v>
       </c>
       <c r="E129" s="5" t="n">
-        <v>131.29</v>
+        <v>132.08</v>
       </c>
     </row>
     <row r="130">
@@ -8346,10 +8366,10 @@
         <v>114.3</v>
       </c>
       <c r="D130" s="5" t="n">
-        <v>152.41</v>
+        <v>153.33</v>
       </c>
       <c r="E130" s="5" t="n">
-        <v>154.54</v>
+        <v>155.46</v>
       </c>
     </row>
     <row r="131">
@@ -8365,10 +8385,10 @@
         <v>164</v>
       </c>
       <c r="D131" s="5" t="n">
-        <v>224.14</v>
+        <v>225.48</v>
       </c>
       <c r="E131" s="5" t="n">
-        <v>221.88</v>
+        <v>223.21</v>
       </c>
     </row>
     <row r="132">
@@ -8384,10 +8404,10 @@
         <v>256.22</v>
       </c>
       <c r="D132" s="5" t="n">
-        <v>341.67</v>
+        <v>343.72</v>
       </c>
       <c r="E132" s="5" t="n">
-        <v>346.88</v>
+        <v>348.96</v>
       </c>
     </row>
     <row r="133">
@@ -8403,10 +8423,10 @@
         <v>236.68</v>
       </c>
       <c r="D133" s="5" t="n">
-        <v>320.19</v>
+        <v>322.11</v>
       </c>
       <c r="E133" s="5" t="n">
-        <v>319.96</v>
+        <v>321.88</v>
       </c>
     </row>
     <row r="134">
@@ -8422,10 +8442,10 @@
         <v>57.34</v>
       </c>
       <c r="D134" s="5" t="n">
-        <v>61.35</v>
+        <v>61.72</v>
       </c>
       <c r="E134" s="5" t="n">
-        <v>77.40000000000001</v>
+        <v>77.87</v>
       </c>
     </row>
     <row r="135">
@@ -8441,10 +8461,10 @@
         <v>100.06</v>
       </c>
       <c r="D135" s="5" t="n">
-        <v>97.72</v>
+        <v>98.31</v>
       </c>
       <c r="E135" s="5" t="n">
-        <v>134.87</v>
+        <v>135.68</v>
       </c>
     </row>
     <row r="136">
@@ -8460,10 +8480,10 @@
         <v>97.12</v>
       </c>
       <c r="D136" s="5" t="n">
-        <v>91.34</v>
+        <v>91.88</v>
       </c>
       <c r="E136" s="5" t="n">
-        <v>130.6</v>
+        <v>131.39</v>
       </c>
     </row>
     <row r="137">
@@ -8479,10 +8499,10 @@
         <v>58.34</v>
       </c>
       <c r="D137" s="5" t="n">
-        <v>58.6</v>
+        <v>58.95</v>
       </c>
       <c r="E137" s="5" t="n">
-        <v>78.27</v>
+        <v>78.73999999999999</v>
       </c>
     </row>
     <row r="138">
@@ -8498,10 +8518,10 @@
         <v>52.77</v>
       </c>
       <c r="D138" s="5" t="n">
-        <v>61.81</v>
+        <v>62.18</v>
       </c>
       <c r="E138" s="5" t="n">
-        <v>70.63</v>
+        <v>71.06</v>
       </c>
     </row>
     <row r="139">
@@ -8517,10 +8537,10 @@
         <v>42.16</v>
       </c>
       <c r="D139" s="5" t="n">
-        <v>44.39</v>
+        <v>44.65</v>
       </c>
       <c r="E139" s="5" t="n">
-        <v>56.33</v>
+        <v>56.67</v>
       </c>
     </row>
     <row r="140">
@@ -8536,10 +8556,10 @@
         <v>52.68</v>
       </c>
       <c r="D140" s="5" t="n">
-        <v>50.13</v>
+        <v>50.43</v>
       </c>
       <c r="E140" s="5" t="n">
-        <v>70.27</v>
+        <v>70.69</v>
       </c>
     </row>
     <row r="141">
@@ -8555,10 +8575,10 @@
         <v>46.61</v>
       </c>
       <c r="D141" s="5" t="n">
-        <v>54.99</v>
+        <v>55.32</v>
       </c>
       <c r="E141" s="5" t="n">
-        <v>62.06</v>
+        <v>62.43</v>
       </c>
     </row>
     <row r="142">
@@ -8574,10 +8594,10 @@
         <v>91.34999999999999</v>
       </c>
       <c r="D142" s="5" t="n">
-        <v>114.48</v>
+        <v>115.17</v>
       </c>
       <c r="E142" s="5" t="n">
-        <v>121.45</v>
+        <v>122.18</v>
       </c>
     </row>
     <row r="143">
@@ -8593,10 +8613,10 @@
         <v>104.02</v>
       </c>
       <c r="D143" s="5" t="n">
-        <v>125.28</v>
+        <v>126.04</v>
       </c>
       <c r="E143" s="5" t="n">
-        <v>138.08</v>
+        <v>138.91</v>
       </c>
     </row>
     <row r="144">
@@ -8612,10 +8632,10 @@
         <v>117.62</v>
       </c>
       <c r="D144" s="5" t="n">
-        <v>150.85</v>
+        <v>151.75</v>
       </c>
       <c r="E144" s="5" t="n">
-        <v>155.9</v>
+        <v>156.83</v>
       </c>
     </row>
     <row r="145">
@@ -8631,10 +8651,10 @@
         <v>128.93</v>
       </c>
       <c r="D145" s="5" t="n">
-        <v>173.85</v>
+        <v>174.89</v>
       </c>
       <c r="E145" s="5" t="n">
-        <v>170.78</v>
+        <v>171.8</v>
       </c>
     </row>
     <row r="146">
@@ -8650,10 +8670,10 @@
         <v>118.62</v>
       </c>
       <c r="D146" s="5" t="n">
-        <v>142.88</v>
+        <v>143.74</v>
       </c>
       <c r="E146" s="5" t="n">
-        <v>157.02</v>
+        <v>157.96</v>
       </c>
     </row>
     <row r="147">
@@ -8669,10 +8689,10 @@
         <v>109.77</v>
       </c>
       <c r="D147" s="5" t="n">
-        <v>137.36</v>
+        <v>138.19</v>
       </c>
       <c r="E147" s="5" t="n">
-        <v>145.21</v>
+        <v>146.08</v>
       </c>
     </row>
     <row r="148">
@@ -8688,10 +8708,10 @@
         <v>126.14</v>
       </c>
       <c r="D148" s="5" t="n">
-        <v>153.18</v>
+        <v>154.1</v>
       </c>
       <c r="E148" s="5" t="n">
-        <v>166.52</v>
+        <v>167.52</v>
       </c>
     </row>
     <row r="149">
@@ -8707,10 +8727,10 @@
         <v>110.94</v>
       </c>
       <c r="D149" s="5" t="n">
-        <v>128.07</v>
+        <v>128.84</v>
       </c>
       <c r="E149" s="5" t="n">
-        <v>146.16</v>
+        <v>147.04</v>
       </c>
     </row>
     <row r="150">
@@ -8726,10 +8746,10 @@
         <v>82.05</v>
       </c>
       <c r="D150" s="5" t="n">
-        <v>96.73999999999999</v>
+        <v>97.31999999999999</v>
       </c>
       <c r="E150" s="5" t="n">
-        <v>107.88</v>
+        <v>108.53</v>
       </c>
     </row>
     <row r="151">
@@ -8745,10 +8765,10 @@
         <v>75.56</v>
       </c>
       <c r="D151" s="5" t="n">
-        <v>90.06999999999999</v>
+        <v>90.61</v>
       </c>
       <c r="E151" s="5" t="n">
-        <v>99.12</v>
+        <v>99.72</v>
       </c>
     </row>
     <row r="152">
@@ -8764,10 +8784,10 @@
         <v>105.59</v>
       </c>
       <c r="D152" s="5" t="n">
-        <v>123.08</v>
+        <v>123.82</v>
       </c>
       <c r="E152" s="5" t="n">
-        <v>138.21</v>
+        <v>139.04</v>
       </c>
     </row>
     <row r="153">
@@ -8783,10 +8803,10 @@
         <v>106.82</v>
       </c>
       <c r="D153" s="5" t="n">
-        <v>118.8</v>
+        <v>119.51</v>
       </c>
       <c r="E153" s="5" t="n">
-        <v>139.51</v>
+        <v>140.35</v>
       </c>
     </row>
     <row r="154">
@@ -8802,10 +8822,10 @@
         <v>95.51000000000001</v>
       </c>
       <c r="D154" s="5" t="n">
-        <v>129.07</v>
+        <v>129.84</v>
       </c>
       <c r="E154" s="5" t="n">
-        <v>124.56</v>
+        <v>125.3</v>
       </c>
     </row>
     <row r="155">
@@ -8821,10 +8841,10 @@
         <v>89.34999999999999</v>
       </c>
       <c r="D155" s="5" t="n">
-        <v>116.25</v>
+        <v>116.95</v>
       </c>
       <c r="E155" s="5" t="n">
-        <v>116.35</v>
+        <v>117.05</v>
       </c>
     </row>
     <row r="156">
@@ -8840,10 +8860,10 @@
         <v>86.02</v>
       </c>
       <c r="D156" s="5" t="n">
-        <v>108.6</v>
+        <v>109.26</v>
       </c>
       <c r="E156" s="5" t="n">
-        <v>111.86</v>
+        <v>112.53</v>
       </c>
     </row>
     <row r="157">
@@ -8859,10 +8879,10 @@
         <v>80.12</v>
       </c>
       <c r="D157" s="5" t="n">
-        <v>104.83</v>
+        <v>105.45</v>
       </c>
       <c r="E157" s="5" t="n">
-        <v>104.06</v>
+        <v>104.68</v>
       </c>
     </row>
     <row r="158">
@@ -8878,10 +8898,10 @@
         <v>79.66</v>
       </c>
       <c r="D158" s="5" t="n">
-        <v>99.31999999999999</v>
+        <v>99.91</v>
       </c>
       <c r="E158" s="5" t="n">
-        <v>103.34</v>
+        <v>103.96</v>
       </c>
     </row>
     <row r="159">
@@ -8897,10 +8917,10 @@
         <v>81.06</v>
       </c>
       <c r="D159" s="5" t="n">
-        <v>95.34999999999999</v>
+        <v>95.92</v>
       </c>
       <c r="E159" s="5" t="n">
-        <v>105.03</v>
+        <v>105.66</v>
       </c>
     </row>
     <row r="160">
@@ -8916,10 +8936,10 @@
         <v>50.01</v>
       </c>
       <c r="D160" s="5" t="n">
-        <v>58.03</v>
+        <v>58.38</v>
       </c>
       <c r="E160" s="5" t="n">
-        <v>64.7</v>
+        <v>65.09</v>
       </c>
     </row>
     <row r="161">
@@ -8935,10 +8955,10 @@
         <v>31.66</v>
       </c>
       <c r="D161" s="5" t="n">
-        <v>32.34</v>
+        <v>32.53</v>
       </c>
       <c r="E161" s="5" t="n">
-        <v>40.9</v>
+        <v>41.15</v>
       </c>
     </row>
     <row r="162">
@@ -8954,10 +8974,10 @@
         <v>75.48</v>
       </c>
       <c r="D162" s="5" t="n">
-        <v>78.52</v>
+        <v>78.98999999999999</v>
       </c>
       <c r="E162" s="5" t="n">
-        <v>97.38</v>
+        <v>97.95999999999999</v>
       </c>
     </row>
     <row r="163">
@@ -8973,10 +8993,10 @@
         <v>102.32</v>
       </c>
       <c r="D163" s="5" t="n">
-        <v>122.83</v>
+        <v>123.56</v>
       </c>
       <c r="E163" s="5" t="n">
-        <v>131.78</v>
+        <v>132.57</v>
       </c>
     </row>
     <row r="164">
@@ -8992,10 +9012,10 @@
         <v>88.54000000000001</v>
       </c>
       <c r="D164" s="5" t="n">
-        <v>110.05</v>
+        <v>110.71</v>
       </c>
       <c r="E164" s="5" t="n">
-        <v>113.83</v>
+        <v>114.52</v>
       </c>
     </row>
     <row r="165">
@@ -9011,10 +9031,10 @@
         <v>71.18000000000001</v>
       </c>
       <c r="D165" s="5" t="n">
-        <v>92.56999999999999</v>
+        <v>93.13</v>
       </c>
       <c r="E165" s="5" t="n">
-        <v>91.36</v>
+        <v>91.90000000000001</v>
       </c>
     </row>
     <row r="166">
@@ -9030,10 +9050,10 @@
         <v>163.88</v>
       </c>
       <c r="D166" s="5" t="n">
-        <v>189.84</v>
+        <v>190.98</v>
       </c>
       <c r="E166" s="5" t="n">
-        <v>210.34</v>
+        <v>211.6</v>
       </c>
     </row>
     <row r="167">
@@ -9049,10 +9069,10 @@
         <v>133.69</v>
       </c>
       <c r="D167" s="5" t="n">
-        <v>173.01</v>
+        <v>174.05</v>
       </c>
       <c r="E167" s="5" t="n">
-        <v>171.6</v>
+        <v>172.63</v>
       </c>
     </row>
     <row r="168">
@@ -9068,10 +9088,10 @@
         <v>115.58</v>
       </c>
       <c r="D168" s="5" t="n">
-        <v>158.44</v>
+        <v>159.39</v>
       </c>
       <c r="E168" s="5" t="n">
-        <v>148.36</v>
+        <v>149.25</v>
       </c>
     </row>
     <row r="169">
@@ -9087,10 +9107,10 @@
         <v>109.29</v>
       </c>
       <c r="D169" s="5" t="n">
-        <v>134.15</v>
+        <v>134.96</v>
       </c>
       <c r="E169" s="5" t="n">
-        <v>140.01</v>
+        <v>140.85</v>
       </c>
     </row>
     <row r="170">
@@ -9106,10 +9126,10 @@
         <v>102.33</v>
       </c>
       <c r="D170" s="5" t="n">
-        <v>118.33</v>
+        <v>119.04</v>
       </c>
       <c r="E170" s="5" t="n">
-        <v>130.83</v>
+        <v>131.62</v>
       </c>
     </row>
     <row r="171">
@@ -9125,10 +9145,10 @@
         <v>109.49</v>
       </c>
       <c r="D171" s="5" t="n">
-        <v>123.52</v>
+        <v>124.26</v>
       </c>
       <c r="E171" s="5" t="n">
-        <v>139.71</v>
+        <v>140.55</v>
       </c>
     </row>
     <row r="172">
@@ -9144,10 +9164,10 @@
         <v>89.78</v>
       </c>
       <c r="D172" s="5" t="n">
-        <v>95.23</v>
+        <v>95.8</v>
       </c>
       <c r="E172" s="5" t="n">
-        <v>114.35</v>
+        <v>115.03</v>
       </c>
     </row>
     <row r="173">
@@ -9163,10 +9183,10 @@
         <v>81.81</v>
       </c>
       <c r="D173" s="5" t="n">
-        <v>89.04000000000001</v>
+        <v>89.56999999999999</v>
       </c>
       <c r="E173" s="5" t="n">
-        <v>104</v>
+        <v>104.62</v>
       </c>
     </row>
     <row r="174">
@@ -9182,10 +9202,10 @@
         <v>63.98</v>
       </c>
       <c r="D174" s="5" t="n">
-        <v>73.11</v>
+        <v>73.55</v>
       </c>
       <c r="E174" s="5" t="n">
-        <v>81.18000000000001</v>
+        <v>81.67</v>
       </c>
     </row>
     <row r="175">
@@ -9201,10 +9221,10 @@
         <v>106.88</v>
       </c>
       <c r="D175" s="5" t="n">
-        <v>136.32</v>
+        <v>137.14</v>
       </c>
       <c r="E175" s="5" t="n">
-        <v>135.31</v>
+        <v>136.12</v>
       </c>
     </row>
     <row r="176">
@@ -9220,10 +9240,10 @@
         <v>77.56</v>
       </c>
       <c r="D176" s="5" t="n">
-        <v>86.26000000000001</v>
+        <v>86.77</v>
       </c>
       <c r="E176" s="5" t="n">
-        <v>97.97</v>
+        <v>98.55</v>
       </c>
     </row>
     <row r="177">
@@ -9239,10 +9259,10 @@
         <v>50.23</v>
       </c>
       <c r="D177" s="5" t="n">
-        <v>65.76000000000001</v>
+        <v>66.15000000000001</v>
       </c>
       <c r="E177" s="5" t="n">
-        <v>63.3</v>
+        <v>63.68</v>
       </c>
     </row>
     <row r="178">
@@ -9258,10 +9278,10 @@
         <v>49.85</v>
       </c>
       <c r="D178" s="5" t="n">
-        <v>71.54000000000001</v>
+        <v>71.97</v>
       </c>
       <c r="E178" s="5" t="n">
-        <v>62.74</v>
+        <v>63.12</v>
       </c>
     </row>
     <row r="179">
@@ -9277,10 +9297,10 @@
         <v>38.9</v>
       </c>
       <c r="D179" s="5" t="n">
-        <v>49.15</v>
+        <v>49.45</v>
       </c>
       <c r="E179" s="5" t="n">
-        <v>48.9</v>
+        <v>49.19</v>
       </c>
     </row>
     <row r="180">
@@ -9296,10 +9316,10 @@
         <v>35.52</v>
       </c>
       <c r="D180" s="5" t="n">
-        <v>46.92</v>
+        <v>47.2</v>
       </c>
       <c r="E180" s="5" t="n">
-        <v>44.6</v>
+        <v>44.86</v>
       </c>
     </row>
     <row r="181">
@@ -9315,10 +9335,10 @@
         <v>24.48</v>
       </c>
       <c r="D181" s="5" t="n">
-        <v>29.53</v>
+        <v>29.71</v>
       </c>
       <c r="E181" s="5" t="n">
-        <v>30.93</v>
+        <v>31.12</v>
       </c>
     </row>
     <row r="182">
@@ -9334,10 +9354,10 @@
         <v>41.19</v>
       </c>
       <c r="D182" s="5" t="n">
-        <v>44.22</v>
+        <v>44.49</v>
       </c>
       <c r="E182" s="5" t="n">
-        <v>52.39</v>
+        <v>52.7</v>
       </c>
     </row>
     <row r="183">
@@ -9353,10 +9373,10 @@
         <v>39.42</v>
       </c>
       <c r="D183" s="5" t="n">
-        <v>46.61</v>
+        <v>46.89</v>
       </c>
       <c r="E183" s="5" t="n">
-        <v>50.47</v>
+        <v>50.77</v>
       </c>
     </row>
     <row r="184">
@@ -9372,10 +9392,10 @@
         <v>57.55</v>
       </c>
       <c r="D184" s="5" t="n">
-        <v>72.09</v>
+        <v>72.52</v>
       </c>
       <c r="E184" s="5" t="n">
-        <v>73.3</v>
+        <v>73.73999999999999</v>
       </c>
     </row>
     <row r="185">
@@ -9391,10 +9411,10 @@
         <v>56.78</v>
       </c>
       <c r="D185" s="5" t="n">
-        <v>70.64</v>
+        <v>71.06999999999999</v>
       </c>
       <c r="E185" s="5" t="n">
-        <v>71.95</v>
+        <v>72.38</v>
       </c>
     </row>
     <row r="186">
@@ -9410,10 +9430,10 @@
         <v>39.19</v>
       </c>
       <c r="D186" s="5" t="n">
-        <v>47.3</v>
+        <v>47.58</v>
       </c>
       <c r="E186" s="5" t="n">
-        <v>49.41</v>
+        <v>49.7</v>
       </c>
     </row>
     <row r="187">
@@ -9429,10 +9449,10 @@
         <v>42.32</v>
       </c>
       <c r="D187" s="5" t="n">
-        <v>52.17</v>
+        <v>52.49</v>
       </c>
       <c r="E187" s="5" t="n">
-        <v>53.19</v>
+        <v>53.51</v>
       </c>
     </row>
     <row r="188">
@@ -9448,10 +9468,10 @@
         <v>57.44</v>
       </c>
       <c r="D188" s="5" t="n">
-        <v>74.40000000000001</v>
+        <v>74.84</v>
       </c>
       <c r="E188" s="5" t="n">
-        <v>71.98</v>
+        <v>72.41</v>
       </c>
     </row>
     <row r="189">
@@ -9467,10 +9487,10 @@
         <v>43.49</v>
       </c>
       <c r="D189" s="5" t="n">
-        <v>46.05</v>
+        <v>46.33</v>
       </c>
       <c r="E189" s="5" t="n">
-        <v>54.34</v>
+        <v>54.66</v>
       </c>
     </row>
     <row r="190">
@@ -9486,10 +9506,10 @@
         <v>40.16</v>
       </c>
       <c r="D190" s="5" t="n">
-        <v>47.15</v>
+        <v>47.43</v>
       </c>
       <c r="E190" s="5" t="n">
-        <v>50.08</v>
+        <v>50.38</v>
       </c>
     </row>
     <row r="191">
@@ -9505,10 +9525,10 @@
         <v>36.94</v>
       </c>
       <c r="D191" s="5" t="n">
-        <v>39.81</v>
+        <v>40.05</v>
       </c>
       <c r="E191" s="5" t="n">
-        <v>45.98</v>
+        <v>46.25</v>
       </c>
     </row>
     <row r="192">
@@ -9524,10 +9544,10 @@
         <v>31.99</v>
       </c>
       <c r="D192" s="5" t="n">
-        <v>38.24</v>
+        <v>38.46</v>
       </c>
       <c r="E192" s="5" t="n">
-        <v>39.74</v>
+        <v>39.98</v>
       </c>
     </row>
     <row r="193">
@@ -9543,10 +9563,10 @@
         <v>28.96</v>
       </c>
       <c r="D193" s="5" t="n">
-        <v>31.4</v>
+        <v>31.59</v>
       </c>
       <c r="E193" s="5" t="n">
-        <v>35.89</v>
+        <v>36.1</v>
       </c>
     </row>
     <row r="194">
@@ -9562,10 +9582,10 @@
         <v>45.01</v>
       </c>
       <c r="D194" s="5" t="n">
-        <v>50.99</v>
+        <v>51.3</v>
       </c>
       <c r="E194" s="5" t="n">
-        <v>55.64</v>
+        <v>55.97</v>
       </c>
     </row>
     <row r="195">
@@ -9581,10 +9601,10 @@
         <v>77.88</v>
       </c>
       <c r="D195" s="5" t="n">
-        <v>84.94</v>
+        <v>85.45</v>
       </c>
       <c r="E195" s="5" t="n">
-        <v>96.04000000000001</v>
+        <v>96.62</v>
       </c>
     </row>
     <row r="196">
@@ -9600,10 +9620,10 @@
         <v>43.06</v>
       </c>
       <c r="D196" s="5" t="n">
-        <v>46.91</v>
+        <v>47.19</v>
       </c>
       <c r="E196" s="5" t="n">
-        <v>52.95</v>
+        <v>53.27</v>
       </c>
     </row>
     <row r="197">
@@ -9619,10 +9639,10 @@
         <v>25.45</v>
       </c>
       <c r="D197" s="5" t="n">
-        <v>26.32</v>
+        <v>26.47</v>
       </c>
       <c r="E197" s="5" t="n">
-        <v>31.21</v>
+        <v>31.39</v>
       </c>
     </row>
     <row r="198">
@@ -9638,10 +9658,10 @@
         <v>22.15</v>
       </c>
       <c r="D198" s="5" t="n">
-        <v>20.2</v>
+        <v>20.32</v>
       </c>
       <c r="E198" s="5" t="n">
-        <v>27.08</v>
+        <v>27.25</v>
       </c>
     </row>
     <row r="199">
@@ -9657,10 +9677,10 @@
         <v>9.77</v>
       </c>
       <c r="D199" s="5" t="n">
-        <v>11.42</v>
+        <v>11.49</v>
       </c>
       <c r="E199" s="5" t="n">
-        <v>11.9</v>
+        <v>11.97</v>
       </c>
     </row>
     <row r="200">
@@ -9676,10 +9696,10 @@
         <v>33.57</v>
       </c>
       <c r="D200" s="5" t="n">
-        <v>38.51</v>
+        <v>38.74</v>
       </c>
       <c r="E200" s="5" t="n">
-        <v>40.7</v>
+        <v>40.95</v>
       </c>
     </row>
     <row r="201">
@@ -9695,10 +9715,10 @@
         <v>50.76</v>
       </c>
       <c r="D201" s="5" t="n">
-        <v>60.19</v>
+        <v>60.55</v>
       </c>
       <c r="E201" s="5" t="n">
-        <v>61.29</v>
+        <v>61.66</v>
       </c>
     </row>
     <row r="202">
@@ -9714,10 +9734,10 @@
         <v>66.84999999999999</v>
       </c>
       <c r="D202" s="5" t="n">
-        <v>74.97</v>
+        <v>75.42</v>
       </c>
       <c r="E202" s="5" t="n">
-        <v>80.14</v>
+        <v>80.62</v>
       </c>
     </row>
     <row r="203">
@@ -9733,10 +9753,10 @@
         <v>78.13</v>
       </c>
       <c r="D203" s="5" t="n">
-        <v>85.95</v>
+        <v>86.45999999999999</v>
       </c>
       <c r="E203" s="5" t="n">
-        <v>93</v>
+        <v>93.55</v>
       </c>
     </row>
     <row r="204">
@@ -9752,10 +9772,10 @@
         <v>78.79000000000001</v>
       </c>
       <c r="D204" s="5" t="n">
-        <v>88.44</v>
+        <v>88.97</v>
       </c>
       <c r="E204" s="5" t="n">
-        <v>93.12</v>
+        <v>93.68000000000001</v>
       </c>
     </row>
     <row r="205">
@@ -9771,10 +9791,10 @@
         <v>165</v>
       </c>
       <c r="D205" s="5" t="n">
-        <v>165.97</v>
+        <v>166.97</v>
       </c>
       <c r="E205" s="5" t="n">
-        <v>193.85</v>
+        <v>195.02</v>
       </c>
     </row>
     <row r="206">
@@ -9790,10 +9810,10 @@
         <v>241.96</v>
       </c>
       <c r="D206" s="5" t="n">
-        <v>253.66</v>
+        <v>255.19</v>
       </c>
       <c r="E206" s="5" t="n">
-        <v>282.59</v>
+        <v>284.29</v>
       </c>
     </row>
     <row r="207">
@@ -9809,10 +9829,10 @@
         <v>382.49</v>
       </c>
       <c r="D207" s="5" t="n">
-        <v>332.94</v>
+        <v>334.94</v>
       </c>
       <c r="E207" s="5" t="n">
-        <v>444.11</v>
+        <v>446.77</v>
       </c>
     </row>
     <row r="208">
@@ -9828,10 +9848,10 @@
         <v>366.3</v>
       </c>
       <c r="D208" s="5" t="n">
-        <v>372.56</v>
+        <v>374.8</v>
       </c>
       <c r="E208" s="5" t="n">
-        <v>422.72</v>
+        <v>425.25</v>
       </c>
     </row>
     <row r="209">
@@ -9847,10 +9867,10 @@
         <v>169.69</v>
       </c>
       <c r="D209" s="5" t="n">
-        <v>171.49</v>
+        <v>172.52</v>
       </c>
       <c r="E209" s="5" t="n">
-        <v>194.64</v>
+        <v>195.81</v>
       </c>
     </row>
     <row r="210">
@@ -9866,10 +9886,10 @@
         <v>150.78</v>
       </c>
       <c r="D210" s="5" t="n">
-        <v>151.34</v>
+        <v>152.25</v>
       </c>
       <c r="E210" s="5" t="n">
-        <v>171.91</v>
+        <v>172.94</v>
       </c>
     </row>
     <row r="211">
@@ -9885,10 +9905,10 @@
         <v>126.75</v>
       </c>
       <c r="D211" s="5" t="n">
-        <v>138.24</v>
+        <v>139.07</v>
       </c>
       <c r="E211" s="5" t="n">
-        <v>143.63</v>
+        <v>144.49</v>
       </c>
     </row>
     <row r="212">
@@ -9904,10 +9924,10 @@
         <v>114.81</v>
       </c>
       <c r="D212" s="5" t="n">
-        <v>113.73</v>
+        <v>114.41</v>
       </c>
       <c r="E212" s="5" t="n">
-        <v>129.3</v>
+        <v>130.08</v>
       </c>
     </row>
     <row r="213">
@@ -9923,10 +9943,10 @@
         <v>67.38</v>
       </c>
       <c r="D213" s="5" t="n">
-        <v>85.48</v>
+        <v>85.98999999999999</v>
       </c>
       <c r="E213" s="5" t="n">
-        <v>75.43000000000001</v>
+        <v>75.88</v>
       </c>
     </row>
     <row r="214">
@@ -9942,10 +9962,10 @@
         <v>81.12</v>
       </c>
       <c r="D214" s="5" t="n">
-        <v>96.8</v>
+        <v>97.38</v>
       </c>
       <c r="E214" s="5" t="n">
-        <v>90.40000000000001</v>
+        <v>90.94</v>
       </c>
     </row>
     <row r="215">
@@ -9961,10 +9981,10 @@
         <v>76.66</v>
       </c>
       <c r="D215" s="5" t="n">
-        <v>90.45</v>
+        <v>90.98999999999999</v>
       </c>
       <c r="E215" s="5" t="n">
-        <v>85.05</v>
+        <v>85.56</v>
       </c>
     </row>
     <row r="216">
@@ -9980,10 +10000,10 @@
         <v>68.13</v>
       </c>
       <c r="D216" s="5" t="n">
-        <v>79.91</v>
+        <v>80.39</v>
       </c>
       <c r="E216" s="5" t="n">
-        <v>75.25</v>
+        <v>75.7</v>
       </c>
     </row>
     <row r="217">
@@ -9999,10 +10019,10 @@
         <v>70.95</v>
       </c>
       <c r="D217" s="5" t="n">
-        <v>77.13</v>
+        <v>77.59</v>
       </c>
       <c r="E217" s="5" t="n">
-        <v>78.14</v>
+        <v>78.61</v>
       </c>
     </row>
     <row r="218">
@@ -10018,10 +10038,10 @@
         <v>86.54000000000001</v>
       </c>
       <c r="D218" s="5" t="n">
-        <v>92.42</v>
+        <v>92.98</v>
       </c>
       <c r="E218" s="5" t="n">
-        <v>95.04000000000001</v>
+        <v>95.61</v>
       </c>
     </row>
     <row r="219">
@@ -10037,10 +10057,10 @@
         <v>52.33</v>
       </c>
       <c r="D219" s="5" t="n">
-        <v>41.66</v>
+        <v>41.91</v>
       </c>
       <c r="E219" s="5" t="n">
-        <v>57.31</v>
+        <v>57.65</v>
       </c>
     </row>
     <row r="220">
@@ -10056,10 +10076,10 @@
         <v>32.72</v>
       </c>
       <c r="D220" s="5" t="n">
-        <v>25.44</v>
+        <v>25.59</v>
       </c>
       <c r="E220" s="5" t="n">
-        <v>35.69</v>
+        <v>35.91</v>
       </c>
     </row>
     <row r="221">
@@ -10075,10 +10095,10 @@
         <v>37.93</v>
       </c>
       <c r="D221" s="5" t="n">
-        <v>40.92</v>
+        <v>41.16</v>
       </c>
       <c r="E221" s="5" t="n">
-        <v>41.22</v>
+        <v>41.47</v>
       </c>
     </row>
     <row r="222">
@@ -10094,10 +10114,10 @@
         <v>24.88</v>
       </c>
       <c r="D222" s="5" t="n">
-        <v>28.92</v>
+        <v>29.09</v>
       </c>
       <c r="E222" s="5" t="n">
-        <v>26.94</v>
+        <v>27.1</v>
       </c>
     </row>
     <row r="223">
@@ -10113,10 +10133,10 @@
         <v>36.02</v>
       </c>
       <c r="D223" s="5" t="n">
-        <v>40.69</v>
+        <v>40.93</v>
       </c>
       <c r="E223" s="5" t="n">
-        <v>38.91</v>
+        <v>39.15</v>
       </c>
     </row>
     <row r="224">
@@ -10132,10 +10152,10 @@
         <v>57.48</v>
       </c>
       <c r="D224" s="5" t="n">
-        <v>64.65000000000001</v>
+        <v>65.04000000000001</v>
       </c>
       <c r="E224" s="5" t="n">
-        <v>61.97</v>
+        <v>62.34</v>
       </c>
     </row>
     <row r="225">
@@ -10151,10 +10171,10 @@
         <v>49.05</v>
       </c>
       <c r="D225" s="5" t="n">
-        <v>56.04</v>
+        <v>56.38</v>
       </c>
       <c r="E225" s="5" t="n">
-        <v>52.77</v>
+        <v>53.09</v>
       </c>
     </row>
     <row r="226">
@@ -10170,10 +10190,10 @@
         <v>49.55</v>
       </c>
       <c r="D226" s="5" t="n">
-        <v>53.75</v>
+        <v>54.08</v>
       </c>
       <c r="E226" s="5" t="n">
-        <v>53.14</v>
+        <v>53.46</v>
       </c>
     </row>
     <row r="227">
@@ -10189,10 +10209,10 @@
         <v>110.19</v>
       </c>
       <c r="D227" s="5" t="n">
-        <v>87.53</v>
+        <v>88.05</v>
       </c>
       <c r="E227" s="5" t="n">
-        <v>117.82</v>
+        <v>118.52</v>
       </c>
     </row>
     <row r="228">
@@ -10208,10 +10228,10 @@
         <v>67.51000000000001</v>
       </c>
       <c r="D228" s="5" t="n">
-        <v>74.23999999999999</v>
+        <v>74.69</v>
       </c>
       <c r="E228" s="5" t="n">
-        <v>71.95999999999999</v>
+        <v>72.39</v>
       </c>
     </row>
     <row r="229">
@@ -10227,10 +10247,10 @@
         <v>70.58</v>
       </c>
       <c r="D229" s="5" t="n">
-        <v>77.91</v>
+        <v>78.38</v>
       </c>
       <c r="E229" s="5" t="n">
-        <v>74.97</v>
+        <v>75.42</v>
       </c>
     </row>
     <row r="230">
@@ -10246,10 +10266,10 @@
         <v>145.64</v>
       </c>
       <c r="D230" s="5" t="n">
-        <v>149.28</v>
+        <v>150.18</v>
       </c>
       <c r="E230" s="5" t="n">
-        <v>154.16</v>
+        <v>155.09</v>
       </c>
     </row>
     <row r="231">
@@ -10265,10 +10285,10 @@
         <v>212.93</v>
       </c>
       <c r="D231" s="5" t="n">
-        <v>188.03</v>
+        <v>189.16</v>
       </c>
       <c r="E231" s="5" t="n">
-        <v>224.61</v>
+        <v>225.96</v>
       </c>
     </row>
     <row r="232">
@@ -10284,10 +10304,10 @@
         <v>215.63</v>
       </c>
       <c r="D232" s="5" t="n">
-        <v>190.54</v>
+        <v>191.68</v>
       </c>
       <c r="E232" s="5" t="n">
-        <v>227.3</v>
+        <v>228.66</v>
       </c>
     </row>
     <row r="233">
@@ -10303,10 +10323,10 @@
         <v>156.24</v>
       </c>
       <c r="D233" s="5" t="n">
-        <v>135.55</v>
+        <v>136.37</v>
       </c>
       <c r="E233" s="5" t="n">
-        <v>164.57</v>
+        <v>165.56</v>
       </c>
     </row>
     <row r="234">
@@ -10322,10 +10342,10 @@
         <v>31.25</v>
       </c>
       <c r="D234" s="5" t="n">
-        <v>23.69</v>
+        <v>23.84</v>
       </c>
       <c r="E234" s="5" t="n">
-        <v>32.89</v>
+        <v>33.09</v>
       </c>
     </row>
     <row r="235">
@@ -10341,10 +10361,10 @@
         <v>52.52</v>
       </c>
       <c r="D235" s="5" t="n">
-        <v>52.38</v>
+        <v>52.7</v>
       </c>
       <c r="E235" s="5" t="n">
-        <v>55.25</v>
+        <v>55.58</v>
       </c>
     </row>
     <row r="236">
@@ -10360,10 +10380,10 @@
         <v>96.58</v>
       </c>
       <c r="D236" s="5" t="n">
-        <v>100.77</v>
+        <v>101.37</v>
       </c>
       <c r="E236" s="5" t="n">
-        <v>101.52</v>
+        <v>102.13</v>
       </c>
     </row>
     <row r="237">
@@ -10379,10 +10399,10 @@
         <v>68.48</v>
       </c>
       <c r="D237" s="5" t="n">
-        <v>79.95</v>
+        <v>80.43000000000001</v>
       </c>
       <c r="E237" s="5" t="n">
-        <v>71.94</v>
+        <v>72.37</v>
       </c>
     </row>
     <row r="238">
@@ -10398,10 +10418,10 @@
         <v>109.08</v>
       </c>
       <c r="D238" s="5" t="n">
-        <v>119</v>
+        <v>119.72</v>
       </c>
       <c r="E238" s="5" t="n">
-        <v>114.24</v>
+        <v>114.92</v>
       </c>
     </row>
     <row r="239">
@@ -10417,10 +10437,10 @@
         <v>125.01</v>
       </c>
       <c r="D239" s="5" t="n">
-        <v>127.06</v>
+        <v>127.82</v>
       </c>
       <c r="E239" s="5" t="n">
-        <v>130.52</v>
+        <v>131.31</v>
       </c>
     </row>
     <row r="240">
@@ -10436,10 +10456,10 @@
         <v>100.83</v>
       </c>
       <c r="D240" s="5" t="n">
-        <v>104.14</v>
+        <v>104.76</v>
       </c>
       <c r="E240" s="5" t="n">
-        <v>104.96</v>
+        <v>105.59</v>
       </c>
     </row>
     <row r="241">
@@ -10455,10 +10475,10 @@
         <v>98.58</v>
       </c>
       <c r="D241" s="5" t="n">
-        <v>104.39</v>
+        <v>105.01</v>
       </c>
       <c r="E241" s="5" t="n">
-        <v>102.36</v>
+        <v>102.98</v>
       </c>
     </row>
     <row r="242">
@@ -10474,10 +10494,10 @@
         <v>113.37</v>
       </c>
       <c r="D242" s="5" t="n">
-        <v>107.09</v>
+        <v>107.73</v>
       </c>
       <c r="E242" s="5" t="n">
-        <v>117.43</v>
+        <v>118.13</v>
       </c>
     </row>
     <row r="243">
@@ -10493,10 +10513,10 @@
         <v>327.99</v>
       </c>
       <c r="D243" s="5" t="n">
-        <v>226.63</v>
+        <v>227.99</v>
       </c>
       <c r="E243" s="5" t="n">
-        <v>338.89</v>
+        <v>340.92</v>
       </c>
     </row>
     <row r="244">
@@ -10512,10 +10532,10 @@
         <v>130.45</v>
       </c>
       <c r="D244" s="5" t="n">
-        <v>121.23</v>
+        <v>121.96</v>
       </c>
       <c r="E244" s="5" t="n">
-        <v>134.19</v>
+        <v>135</v>
       </c>
     </row>
     <row r="245">
@@ -10531,10 +10551,10 @@
         <v>133.56</v>
       </c>
       <c r="D245" s="5" t="n">
-        <v>128.25</v>
+        <v>129.02</v>
       </c>
       <c r="E245" s="5" t="n">
-        <v>136.79</v>
+        <v>137.61</v>
       </c>
     </row>
     <row r="246">
@@ -10550,10 +10570,10 @@
         <v>36.24</v>
       </c>
       <c r="D246" s="5" t="n">
-        <v>29.2</v>
+        <v>29.37</v>
       </c>
       <c r="E246" s="5" t="n">
-        <v>36.96</v>
+        <v>37.18</v>
       </c>
     </row>
     <row r="247">
@@ -10569,10 +10589,10 @@
         <v>26.88</v>
       </c>
       <c r="D247" s="5" t="n">
-        <v>24.99</v>
+        <v>25.14</v>
       </c>
       <c r="E247" s="5" t="n">
-        <v>27.36</v>
+        <v>27.52</v>
       </c>
     </row>
     <row r="248">
@@ -10588,10 +10608,10 @@
         <v>34.34</v>
       </c>
       <c r="D248" s="5" t="n">
-        <v>41.15</v>
+        <v>41.39</v>
       </c>
       <c r="E248" s="5" t="n">
-        <v>34.88</v>
+        <v>35.09</v>
       </c>
     </row>
     <row r="249">
@@ -10607,10 +10627,10 @@
         <v>55.6</v>
       </c>
       <c r="D249" s="5" t="n">
-        <v>60.16</v>
+        <v>60.52</v>
       </c>
       <c r="E249" s="5" t="n">
-        <v>56.36</v>
+        <v>56.7</v>
       </c>
     </row>
     <row r="250">
@@ -10626,10 +10646,10 @@
         <v>114.88</v>
       </c>
       <c r="D250" s="5" t="n">
-        <v>101.85</v>
+        <v>102.46</v>
       </c>
       <c r="E250" s="5" t="n">
-        <v>115.93</v>
+        <v>116.62</v>
       </c>
     </row>
     <row r="251">
@@ -10645,10 +10665,10 @@
         <v>87.56</v>
       </c>
       <c r="D251" s="5" t="n">
-        <v>90.69</v>
+        <v>91.23</v>
       </c>
       <c r="E251" s="5" t="n">
-        <v>87.95999999999999</v>
+        <v>88.48999999999999</v>
       </c>
     </row>
     <row r="252">
@@ -10664,10 +10684,10 @@
         <v>90.94</v>
       </c>
       <c r="D252" s="5" t="n">
-        <v>91.04000000000001</v>
+        <v>91.59</v>
       </c>
       <c r="E252" s="5" t="n">
-        <v>90.94</v>
+        <v>91.48999999999999</v>
       </c>
     </row>
     <row r="253">
@@ -10683,10 +10703,10 @@
         <v>87.34</v>
       </c>
       <c r="D253" s="5" t="n">
-        <v>85.23999999999999</v>
+        <v>85.58</v>
       </c>
       <c r="E253" s="5" t="n">
-        <v>87.34</v>
+        <v>87.69</v>
       </c>
     </row>
     <row r="254">
@@ -10702,10 +10722,10 @@
         <v>100.08</v>
       </c>
       <c r="D254" s="5" t="n">
-        <v>96.14</v>
+        <v>96.33</v>
       </c>
       <c r="E254" s="5" t="n">
-        <v>100.08</v>
+        <v>100.28</v>
       </c>
     </row>
     <row r="255">
@@ -10727,8 +10747,27 @@
         <v>81.73</v>
       </c>
     </row>
+    <row r="256">
+      <c r="A256" s="4" t="inlineStr">
+        <is>
+          <t>Jul 2026</t>
+        </is>
+      </c>
+      <c r="B256" s="5" t="n">
+        <v>71.04000000000001</v>
+      </c>
+      <c r="C256" s="5" t="n">
+        <v>93.83</v>
+      </c>
+      <c r="D256" s="5" t="n">
+        <v>71.04000000000001</v>
+      </c>
+      <c r="E256" s="5" t="n">
+        <v>93.83</v>
+      </c>
+    </row>
   </sheetData>
-  <conditionalFormatting sqref="B2:B255">
+  <conditionalFormatting sqref="B2:B256">
     <cfRule type="colorScale" priority="1">
       <colorScale>
         <cfvo type="min"/>
@@ -10740,7 +10779,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C2:C255">
+  <conditionalFormatting sqref="C2:C256">
     <cfRule type="colorScale" priority="2">
       <colorScale>
         <cfvo type="min"/>
@@ -10752,7 +10791,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D2:D255">
+  <conditionalFormatting sqref="D2:D256">
     <cfRule type="colorScale" priority="3">
       <colorScale>
         <cfvo type="min"/>
@@ -10764,7 +10803,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E2:E255">
+  <conditionalFormatting sqref="E2:E256">
     <cfRule type="colorScale" priority="4">
       <colorScale>
         <cfvo type="min"/>

--- a/outputs/TAS_historical_prices.xlsx
+++ b/outputs/TAS_historical_prices.xlsx
@@ -528,16 +528,16 @@
         </is>
       </c>
       <c r="B5" s="5" t="n">
-        <v>74.15000000000001</v>
+        <v>68.54000000000001</v>
       </c>
       <c r="C5" s="5" t="n">
-        <v>78.58</v>
+        <v>72.94</v>
       </c>
       <c r="D5" s="5" t="n">
-        <v>75.04000000000001</v>
+        <v>69.12</v>
       </c>
       <c r="E5" s="5" t="n">
-        <v>79.52</v>
+        <v>73.54000000000001</v>
       </c>
     </row>
     <row r="6">
@@ -547,16 +547,16 @@
         </is>
       </c>
       <c r="B6" s="5" t="n">
-        <v>89.13</v>
+        <v>86.19</v>
       </c>
       <c r="C6" s="5" t="n">
-        <v>98.06</v>
+        <v>94.29000000000001</v>
       </c>
       <c r="D6" s="5" t="n">
-        <v>92.09</v>
+        <v>88.81999999999999</v>
       </c>
       <c r="E6" s="5" t="n">
-        <v>101.33</v>
+        <v>97.17</v>
       </c>
     </row>
     <row r="7">
@@ -566,16 +566,16 @@
         </is>
       </c>
       <c r="B7" s="5" t="n">
-        <v>86.90000000000001</v>
+        <v>87.45999999999999</v>
       </c>
       <c r="C7" s="5" t="n">
-        <v>95.3</v>
+        <v>96.06999999999999</v>
       </c>
       <c r="D7" s="5" t="n">
-        <v>90.81</v>
+        <v>91.27</v>
       </c>
       <c r="E7" s="5" t="n">
-        <v>99.56999999999999</v>
+        <v>100.24</v>
       </c>
     </row>
     <row r="8">
@@ -585,16 +585,16 @@
         </is>
       </c>
       <c r="B8" s="5" t="n">
-        <v>91.20999999999999</v>
+        <v>91.81999999999999</v>
       </c>
       <c r="C8" s="5" t="n">
-        <v>100.83</v>
+        <v>101.5</v>
       </c>
       <c r="D8" s="5" t="n">
-        <v>99.67</v>
+        <v>100.2</v>
       </c>
       <c r="E8" s="5" t="n">
-        <v>110.27</v>
+        <v>110.84</v>
       </c>
     </row>
     <row r="9">
@@ -604,22 +604,22 @@
         </is>
       </c>
       <c r="B9" s="5" t="n">
-        <v>80.5</v>
+        <v>80.61</v>
       </c>
       <c r="C9" s="5" t="n">
-        <v>87.88</v>
+        <v>87.94</v>
       </c>
       <c r="D9" s="5" t="n">
-        <v>95.15000000000001</v>
+        <v>95.14</v>
       </c>
       <c r="E9" s="5" t="n">
-        <v>103.81</v>
+        <v>103.7</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="6" t="inlineStr">
         <is>
-          <t>Data through: Jul 2026</t>
+          <t>Data through: Aug 2026</t>
         </is>
       </c>
     </row>
@@ -634,7 +634,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F256"/>
+  <dimension ref="A1:F257"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -5873,6 +5873,26 @@
       </c>
       <c r="F256" s="7" t="inlineStr"/>
     </row>
+    <row r="257">
+      <c r="A257" s="4" t="inlineStr">
+        <is>
+          <t>Aug 2026</t>
+        </is>
+      </c>
+      <c r="B257" s="5" t="n">
+        <v>57.95</v>
+      </c>
+      <c r="C257" s="5" t="n">
+        <v>65.81</v>
+      </c>
+      <c r="D257" s="5" t="n">
+        <v>57.95</v>
+      </c>
+      <c r="E257" s="5" t="n">
+        <v>65.81</v>
+      </c>
+      <c r="F257" s="7" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -5884,7 +5904,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E256"/>
+  <dimension ref="A1:E257"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -10766,8 +10786,27 @@
         <v>93.83</v>
       </c>
     </row>
+    <row r="257">
+      <c r="A257" s="4" t="inlineStr">
+        <is>
+          <t>Aug 2026</t>
+        </is>
+      </c>
+      <c r="B257" s="5" t="n">
+        <v>57.95</v>
+      </c>
+      <c r="C257" s="5" t="n">
+        <v>65.81</v>
+      </c>
+      <c r="D257" s="5" t="n">
+        <v>57.95</v>
+      </c>
+      <c r="E257" s="5" t="n">
+        <v>65.81</v>
+      </c>
+    </row>
   </sheetData>
-  <conditionalFormatting sqref="B2:B256">
+  <conditionalFormatting sqref="B2:B257">
     <cfRule type="colorScale" priority="1">
       <colorScale>
         <cfvo type="min"/>
@@ -10779,7 +10818,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C2:C256">
+  <conditionalFormatting sqref="C2:C257">
     <cfRule type="colorScale" priority="2">
       <colorScale>
         <cfvo type="min"/>
@@ -10791,7 +10830,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D2:D256">
+  <conditionalFormatting sqref="D2:D257">
     <cfRule type="colorScale" priority="3">
       <colorScale>
         <cfvo type="min"/>
@@ -10803,7 +10842,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E2:E256">
+  <conditionalFormatting sqref="E2:E257">
     <cfRule type="colorScale" priority="4">
       <colorScale>
         <cfvo type="min"/>

--- a/outputs/TAS_historical_prices.xlsx
+++ b/outputs/TAS_historical_prices.xlsx
@@ -528,16 +528,16 @@
         </is>
       </c>
       <c r="B5" s="5" t="n">
-        <v>68.54000000000001</v>
+        <v>69.39</v>
       </c>
       <c r="C5" s="5" t="n">
-        <v>72.94</v>
+        <v>73.06999999999999</v>
       </c>
       <c r="D5" s="5" t="n">
-        <v>69.12</v>
+        <v>69.91</v>
       </c>
       <c r="E5" s="5" t="n">
-        <v>73.54000000000001</v>
+        <v>73.59</v>
       </c>
     </row>
     <row r="6">
@@ -547,16 +547,16 @@
         </is>
       </c>
       <c r="B6" s="5" t="n">
-        <v>86.19</v>
+        <v>86.87</v>
       </c>
       <c r="C6" s="5" t="n">
-        <v>94.29000000000001</v>
+        <v>94.56</v>
       </c>
       <c r="D6" s="5" t="n">
-        <v>88.81999999999999</v>
+        <v>89.45</v>
       </c>
       <c r="E6" s="5" t="n">
-        <v>97.17</v>
+        <v>97.37</v>
       </c>
     </row>
     <row r="7">
@@ -566,16 +566,16 @@
         </is>
       </c>
       <c r="B7" s="5" t="n">
-        <v>87.45999999999999</v>
+        <v>87.8</v>
       </c>
       <c r="C7" s="5" t="n">
-        <v>96.06999999999999</v>
+        <v>96.43000000000001</v>
       </c>
       <c r="D7" s="5" t="n">
-        <v>91.27</v>
+        <v>91.54000000000001</v>
       </c>
       <c r="E7" s="5" t="n">
-        <v>100.24</v>
+        <v>100.54</v>
       </c>
     </row>
     <row r="8">
@@ -585,16 +585,16 @@
         </is>
       </c>
       <c r="B8" s="5" t="n">
-        <v>91.81999999999999</v>
+        <v>92.19</v>
       </c>
       <c r="C8" s="5" t="n">
-        <v>101.5</v>
+        <v>101.76</v>
       </c>
       <c r="D8" s="5" t="n">
-        <v>100.2</v>
+        <v>100.51</v>
       </c>
       <c r="E8" s="5" t="n">
-        <v>110.84</v>
+        <v>111.02</v>
       </c>
     </row>
     <row r="9">
@@ -604,22 +604,22 @@
         </is>
       </c>
       <c r="B9" s="5" t="n">
-        <v>80.61</v>
+        <v>80.55</v>
       </c>
       <c r="C9" s="5" t="n">
-        <v>87.94</v>
+        <v>87.81999999999999</v>
       </c>
       <c r="D9" s="5" t="n">
-        <v>95.14</v>
+        <v>94.95</v>
       </c>
       <c r="E9" s="5" t="n">
-        <v>103.7</v>
+        <v>103.42</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="6" t="inlineStr">
         <is>
-          <t>Data through: Aug 2026</t>
+          <t>Data through: Sep 2026</t>
         </is>
       </c>
     </row>
@@ -634,7 +634,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F257"/>
+  <dimension ref="A1:F258"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -5893,6 +5893,26 @@
       </c>
       <c r="F257" s="7" t="inlineStr"/>
     </row>
+    <row r="258">
+      <c r="A258" s="4" t="inlineStr">
+        <is>
+          <t>Sep 2026</t>
+        </is>
+      </c>
+      <c r="B258" s="5" t="n">
+        <v>38.86</v>
+      </c>
+      <c r="C258" s="5" t="n">
+        <v>37.8</v>
+      </c>
+      <c r="D258" s="5" t="n">
+        <v>38.86</v>
+      </c>
+      <c r="E258" s="5" t="n">
+        <v>37.8</v>
+      </c>
+      <c r="F258" s="7" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -5904,7 +5924,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E257"/>
+  <dimension ref="A1:E258"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -10805,8 +10825,27 @@
         <v>65.81</v>
       </c>
     </row>
+    <row r="258">
+      <c r="A258" s="4" t="inlineStr">
+        <is>
+          <t>Sep 2026</t>
+        </is>
+      </c>
+      <c r="B258" s="5" t="n">
+        <v>38.86</v>
+      </c>
+      <c r="C258" s="5" t="n">
+        <v>37.8</v>
+      </c>
+      <c r="D258" s="5" t="n">
+        <v>38.86</v>
+      </c>
+      <c r="E258" s="5" t="n">
+        <v>37.8</v>
+      </c>
+    </row>
   </sheetData>
-  <conditionalFormatting sqref="B2:B257">
+  <conditionalFormatting sqref="B2:B258">
     <cfRule type="colorScale" priority="1">
       <colorScale>
         <cfvo type="min"/>
@@ -10818,7 +10857,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C2:C257">
+  <conditionalFormatting sqref="C2:C258">
     <cfRule type="colorScale" priority="2">
       <colorScale>
         <cfvo type="min"/>
@@ -10830,7 +10869,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D2:D257">
+  <conditionalFormatting sqref="D2:D258">
     <cfRule type="colorScale" priority="3">
       <colorScale>
         <cfvo type="min"/>
@@ -10842,7 +10881,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E2:E257">
+  <conditionalFormatting sqref="E2:E258">
     <cfRule type="colorScale" priority="4">
       <colorScale>
         <cfvo type="min"/>

--- a/outputs/TAS_historical_prices.xlsx
+++ b/outputs/TAS_historical_prices.xlsx
@@ -531,13 +531,13 @@
         <v>69.39</v>
       </c>
       <c r="C5" s="5" t="n">
-        <v>73.06999999999999</v>
+        <v>73.04000000000001</v>
       </c>
       <c r="D5" s="5" t="n">
         <v>69.91</v>
       </c>
       <c r="E5" s="5" t="n">
-        <v>73.59</v>
+        <v>73.56</v>
       </c>
     </row>
     <row r="6">
@@ -550,13 +550,13 @@
         <v>86.87</v>
       </c>
       <c r="C6" s="5" t="n">
-        <v>94.56</v>
+        <v>94.51000000000001</v>
       </c>
       <c r="D6" s="5" t="n">
         <v>89.45</v>
       </c>
       <c r="E6" s="5" t="n">
-        <v>97.37</v>
+        <v>97.31999999999999</v>
       </c>
     </row>
     <row r="7">
@@ -569,13 +569,13 @@
         <v>87.8</v>
       </c>
       <c r="C7" s="5" t="n">
-        <v>96.43000000000001</v>
+        <v>96.36</v>
       </c>
       <c r="D7" s="5" t="n">
         <v>91.54000000000001</v>
       </c>
       <c r="E7" s="5" t="n">
-        <v>100.54</v>
+        <v>100.47</v>
       </c>
     </row>
     <row r="8">
@@ -588,13 +588,13 @@
         <v>92.19</v>
       </c>
       <c r="C8" s="5" t="n">
-        <v>101.76</v>
+        <v>101.62</v>
       </c>
       <c r="D8" s="5" t="n">
         <v>100.51</v>
       </c>
       <c r="E8" s="5" t="n">
-        <v>111.02</v>
+        <v>110.86</v>
       </c>
     </row>
     <row r="9">
@@ -607,13 +607,13 @@
         <v>80.55</v>
       </c>
       <c r="C9" s="5" t="n">
-        <v>87.81999999999999</v>
+        <v>87.36</v>
       </c>
       <c r="D9" s="5" t="n">
         <v>94.95</v>
       </c>
       <c r="E9" s="5" t="n">
-        <v>103.42</v>
+        <v>102.84</v>
       </c>
     </row>
     <row r="11">
@@ -687,13 +687,13 @@
         <v>306.87</v>
       </c>
       <c r="C2" s="5" t="n">
-        <v>392.08</v>
+        <v>361.77</v>
       </c>
       <c r="D2" s="5" t="n">
         <v>548.53</v>
       </c>
       <c r="E2" s="5" t="n">
-        <v>700.84</v>
+        <v>646.66</v>
       </c>
       <c r="F2" s="7" t="inlineStr"/>
     </row>
@@ -727,13 +727,13 @@
         <v>112.34</v>
       </c>
       <c r="C4" s="5" t="n">
-        <v>115.44</v>
+        <v>115.77</v>
       </c>
       <c r="D4" s="5" t="n">
         <v>199.75</v>
       </c>
       <c r="E4" s="5" t="n">
-        <v>205.26</v>
+        <v>205.85</v>
       </c>
       <c r="F4" s="7" t="inlineStr"/>
     </row>
@@ -747,13 +747,13 @@
         <v>107.2</v>
       </c>
       <c r="C5" s="5" t="n">
-        <v>141.07</v>
+        <v>141.34</v>
       </c>
       <c r="D5" s="5" t="n">
         <v>189.98</v>
       </c>
       <c r="E5" s="5" t="n">
-        <v>250.01</v>
+        <v>250.48</v>
       </c>
       <c r="F5" s="7" t="inlineStr"/>
     </row>
@@ -767,13 +767,13 @@
         <v>69.34999999999999</v>
       </c>
       <c r="C6" s="5" t="n">
-        <v>78.06</v>
+        <v>77.7</v>
       </c>
       <c r="D6" s="5" t="n">
         <v>122.5</v>
       </c>
       <c r="E6" s="5" t="n">
-        <v>137.89</v>
+        <v>137.25</v>
       </c>
       <c r="F6" s="7" t="inlineStr"/>
     </row>
@@ -787,13 +787,13 @@
         <v>82.38</v>
       </c>
       <c r="C7" s="5" t="n">
-        <v>102.26</v>
+        <v>102.17</v>
       </c>
       <c r="D7" s="5" t="n">
         <v>145.27</v>
       </c>
       <c r="E7" s="5" t="n">
-        <v>180.32</v>
+        <v>180.16</v>
       </c>
       <c r="F7" s="7" t="inlineStr"/>
     </row>
@@ -807,13 +807,13 @@
         <v>57.64</v>
       </c>
       <c r="C8" s="5" t="n">
-        <v>59.27</v>
+        <v>59.19</v>
       </c>
       <c r="D8" s="5" t="n">
         <v>101.47</v>
       </c>
       <c r="E8" s="5" t="n">
-        <v>104.33</v>
+        <v>104.19</v>
       </c>
       <c r="F8" s="7" t="inlineStr"/>
     </row>
@@ -827,13 +827,13 @@
         <v>42.82</v>
       </c>
       <c r="C9" s="5" t="n">
-        <v>47</v>
+        <v>46.71</v>
       </c>
       <c r="D9" s="5" t="n">
         <v>75.25</v>
       </c>
       <c r="E9" s="5" t="n">
-        <v>82.59</v>
+        <v>82.08</v>
       </c>
       <c r="F9" s="7" t="inlineStr"/>
     </row>
@@ -847,13 +847,13 @@
         <v>36.9</v>
       </c>
       <c r="C10" s="5" t="n">
-        <v>40.37</v>
+        <v>40.3</v>
       </c>
       <c r="D10" s="5" t="n">
         <v>64.66</v>
       </c>
       <c r="E10" s="5" t="n">
-        <v>70.73999999999999</v>
+        <v>70.62</v>
       </c>
       <c r="F10" s="7" t="inlineStr"/>
     </row>
@@ -867,13 +867,13 @@
         <v>32.44</v>
       </c>
       <c r="C11" s="5" t="n">
-        <v>35.76</v>
+        <v>35.57</v>
       </c>
       <c r="D11" s="5" t="n">
         <v>56.68</v>
       </c>
       <c r="E11" s="5" t="n">
-        <v>62.48</v>
+        <v>62.15</v>
       </c>
       <c r="F11" s="7" t="inlineStr"/>
     </row>
@@ -887,13 +887,13 @@
         <v>28.4</v>
       </c>
       <c r="C12" s="5" t="n">
-        <v>32.55</v>
+        <v>32.53</v>
       </c>
       <c r="D12" s="5" t="n">
         <v>49.48</v>
       </c>
       <c r="E12" s="5" t="n">
-        <v>56.71</v>
+        <v>56.68</v>
       </c>
       <c r="F12" s="7" t="inlineStr"/>
     </row>
@@ -907,13 +907,13 @@
         <v>33.36</v>
       </c>
       <c r="C13" s="5" t="n">
-        <v>33.84</v>
+        <v>33.75</v>
       </c>
       <c r="D13" s="5" t="n">
         <v>57.82</v>
       </c>
       <c r="E13" s="5" t="n">
-        <v>58.65</v>
+        <v>58.5</v>
       </c>
       <c r="F13" s="7" t="inlineStr"/>
     </row>
@@ -927,13 +927,13 @@
         <v>33.76</v>
       </c>
       <c r="C14" s="5" t="n">
-        <v>47.58</v>
+        <v>47.59</v>
       </c>
       <c r="D14" s="5" t="n">
         <v>58.21</v>
       </c>
       <c r="E14" s="5" t="n">
-        <v>82.03</v>
+        <v>82.05</v>
       </c>
       <c r="F14" s="7" t="inlineStr"/>
     </row>
@@ -947,13 +947,13 @@
         <v>41.39</v>
       </c>
       <c r="C15" s="5" t="n">
-        <v>51.97</v>
+        <v>52.3</v>
       </c>
       <c r="D15" s="5" t="n">
         <v>70.98999999999999</v>
       </c>
       <c r="E15" s="5" t="n">
-        <v>89.14</v>
+        <v>89.7</v>
       </c>
       <c r="F15" s="7" t="inlineStr"/>
     </row>
@@ -967,13 +967,13 @@
         <v>48.24</v>
       </c>
       <c r="C16" s="5" t="n">
-        <v>68.81</v>
+        <v>69.09999999999999</v>
       </c>
       <c r="D16" s="5" t="n">
         <v>82.5</v>
       </c>
       <c r="E16" s="5" t="n">
-        <v>117.67</v>
+        <v>118.17</v>
       </c>
       <c r="F16" s="7" t="inlineStr"/>
     </row>
@@ -987,13 +987,13 @@
         <v>35.17</v>
       </c>
       <c r="C17" s="5" t="n">
-        <v>39.83</v>
+        <v>39.9</v>
       </c>
       <c r="D17" s="5" t="n">
         <v>59.97</v>
       </c>
       <c r="E17" s="5" t="n">
-        <v>67.91</v>
+        <v>68.03</v>
       </c>
       <c r="F17" s="7" t="inlineStr"/>
     </row>
@@ -1007,13 +1007,13 @@
         <v>38.25</v>
       </c>
       <c r="C18" s="5" t="n">
-        <v>41.53</v>
+        <v>41.6</v>
       </c>
       <c r="D18" s="5" t="n">
         <v>65.03</v>
       </c>
       <c r="E18" s="5" t="n">
-        <v>70.59999999999999</v>
+        <v>70.72</v>
       </c>
       <c r="F18" s="7" t="inlineStr"/>
     </row>
@@ -1027,13 +1027,13 @@
         <v>34.23</v>
       </c>
       <c r="C19" s="5" t="n">
-        <v>36.83</v>
+        <v>36.71</v>
       </c>
       <c r="D19" s="5" t="n">
         <v>58.22</v>
       </c>
       <c r="E19" s="5" t="n">
-        <v>62.64</v>
+        <v>62.43</v>
       </c>
       <c r="F19" s="7" t="inlineStr"/>
     </row>
@@ -1047,13 +1047,13 @@
         <v>39.8</v>
       </c>
       <c r="C20" s="5" t="n">
-        <v>44.85</v>
+        <v>44.53</v>
       </c>
       <c r="D20" s="5" t="n">
         <v>67.72</v>
       </c>
       <c r="E20" s="5" t="n">
-        <v>76.31</v>
+        <v>75.76000000000001</v>
       </c>
       <c r="F20" s="7" t="inlineStr"/>
     </row>
@@ -1067,13 +1067,13 @@
         <v>35.17</v>
       </c>
       <c r="C21" s="5" t="n">
-        <v>41.08</v>
+        <v>40.79</v>
       </c>
       <c r="D21" s="5" t="n">
         <v>59.86</v>
       </c>
       <c r="E21" s="5" t="n">
-        <v>69.92</v>
+        <v>69.43000000000001</v>
       </c>
       <c r="F21" s="7" t="inlineStr"/>
     </row>
@@ -1087,13 +1087,13 @@
         <v>44.3</v>
       </c>
       <c r="C22" s="5" t="n">
-        <v>47.25</v>
+        <v>47.2</v>
       </c>
       <c r="D22" s="5" t="n">
         <v>75.38</v>
       </c>
       <c r="E22" s="5" t="n">
-        <v>80.40000000000001</v>
+        <v>80.31</v>
       </c>
       <c r="F22" s="7" t="inlineStr"/>
     </row>
@@ -1107,13 +1107,13 @@
         <v>52.95</v>
       </c>
       <c r="C23" s="5" t="n">
-        <v>67.59999999999999</v>
+        <v>67.45</v>
       </c>
       <c r="D23" s="5" t="n">
         <v>90.06999999999999</v>
       </c>
       <c r="E23" s="5" t="n">
-        <v>114.99</v>
+        <v>114.74</v>
       </c>
       <c r="F23" s="7" t="inlineStr"/>
     </row>
@@ -1127,13 +1127,13 @@
         <v>50.75</v>
       </c>
       <c r="C24" s="5" t="n">
-        <v>53.83</v>
+        <v>53.78</v>
       </c>
       <c r="D24" s="5" t="n">
         <v>86.31</v>
       </c>
       <c r="E24" s="5" t="n">
-        <v>91.55</v>
+        <v>91.45999999999999</v>
       </c>
       <c r="F24" s="7" t="inlineStr"/>
     </row>
@@ -1147,13 +1147,13 @@
         <v>73.08</v>
       </c>
       <c r="C25" s="5" t="n">
-        <v>82.19</v>
+        <v>81.98999999999999</v>
       </c>
       <c r="D25" s="5" t="n">
         <v>123.77</v>
       </c>
       <c r="E25" s="5" t="n">
-        <v>139.2</v>
+        <v>138.87</v>
       </c>
       <c r="F25" s="7" t="inlineStr"/>
     </row>
@@ -1167,13 +1167,13 @@
         <v>66.34</v>
       </c>
       <c r="C26" s="5" t="n">
-        <v>72.31</v>
+        <v>72.01000000000001</v>
       </c>
       <c r="D26" s="5" t="n">
         <v>111.9</v>
       </c>
       <c r="E26" s="5" t="n">
-        <v>121.97</v>
+        <v>121.47</v>
       </c>
       <c r="F26" s="7" t="inlineStr"/>
     </row>
@@ -1187,13 +1187,13 @@
         <v>77.81</v>
       </c>
       <c r="C27" s="5" t="n">
-        <v>79.93000000000001</v>
+        <v>79.87</v>
       </c>
       <c r="D27" s="5" t="n">
         <v>130.72</v>
       </c>
       <c r="E27" s="5" t="n">
-        <v>134.28</v>
+        <v>134.18</v>
       </c>
       <c r="F27" s="7" t="inlineStr"/>
     </row>
@@ -1207,13 +1207,13 @@
         <v>99.45</v>
       </c>
       <c r="C28" s="5" t="n">
-        <v>115.5</v>
+        <v>115.14</v>
       </c>
       <c r="D28" s="5" t="n">
         <v>166.69</v>
       </c>
       <c r="E28" s="5" t="n">
-        <v>193.59</v>
+        <v>192.99</v>
       </c>
       <c r="F28" s="7" t="inlineStr"/>
     </row>
@@ -1227,13 +1227,13 @@
         <v>40.7</v>
       </c>
       <c r="C29" s="5" t="n">
-        <v>48.82</v>
+        <v>48.48</v>
       </c>
       <c r="D29" s="5" t="n">
         <v>68.06</v>
       </c>
       <c r="E29" s="5" t="n">
-        <v>81.64</v>
+        <v>81.06999999999999</v>
       </c>
       <c r="F29" s="7" t="inlineStr"/>
     </row>
@@ -1247,13 +1247,13 @@
         <v>47.24</v>
       </c>
       <c r="C30" s="5" t="n">
-        <v>50.3</v>
+        <v>49.1</v>
       </c>
       <c r="D30" s="5" t="n">
         <v>78.81999999999999</v>
       </c>
       <c r="E30" s="5" t="n">
-        <v>83.92</v>
+        <v>81.92</v>
       </c>
       <c r="F30" s="7" t="inlineStr"/>
     </row>
@@ -1267,13 +1267,13 @@
         <v>34.03</v>
       </c>
       <c r="C31" s="5" t="n">
-        <v>38.54</v>
+        <v>32.4</v>
       </c>
       <c r="D31" s="5" t="n">
         <v>56.6</v>
       </c>
       <c r="E31" s="5" t="n">
-        <v>64.09999999999999</v>
+        <v>53.89</v>
       </c>
       <c r="F31" s="7" t="inlineStr"/>
     </row>
@@ -1287,13 +1287,13 @@
         <v>44.74</v>
       </c>
       <c r="C32" s="5" t="n">
-        <v>49.43</v>
+        <v>49.25</v>
       </c>
       <c r="D32" s="5" t="n">
         <v>74.19</v>
       </c>
       <c r="E32" s="5" t="n">
-        <v>81.95999999999999</v>
+        <v>81.67</v>
       </c>
       <c r="F32" s="7" t="inlineStr"/>
     </row>
@@ -1307,13 +1307,13 @@
         <v>50.96</v>
       </c>
       <c r="C33" s="5" t="n">
-        <v>60.54</v>
+        <v>60.6</v>
       </c>
       <c r="D33" s="5" t="n">
         <v>84.23999999999999</v>
       </c>
       <c r="E33" s="5" t="n">
-        <v>100.08</v>
+        <v>100.18</v>
       </c>
       <c r="F33" s="7" t="inlineStr"/>
     </row>
@@ -1327,13 +1327,13 @@
         <v>47.33</v>
       </c>
       <c r="C34" s="5" t="n">
-        <v>59.06</v>
+        <v>59.02</v>
       </c>
       <c r="D34" s="5" t="n">
         <v>77.89</v>
       </c>
       <c r="E34" s="5" t="n">
-        <v>97.2</v>
+        <v>97.13</v>
       </c>
       <c r="F34" s="7" t="inlineStr"/>
     </row>
@@ -1347,13 +1347,13 @@
         <v>56.46</v>
       </c>
       <c r="C35" s="5" t="n">
-        <v>67.75</v>
+        <v>67.68000000000001</v>
       </c>
       <c r="D35" s="5" t="n">
         <v>92.51000000000001</v>
       </c>
       <c r="E35" s="5" t="n">
-        <v>111</v>
+        <v>110.89</v>
       </c>
       <c r="F35" s="7" t="inlineStr"/>
     </row>
@@ -1367,13 +1367,13 @@
         <v>56.17</v>
       </c>
       <c r="C36" s="5" t="n">
-        <v>68.79000000000001</v>
+        <v>68.55</v>
       </c>
       <c r="D36" s="5" t="n">
         <v>91.63</v>
       </c>
       <c r="E36" s="5" t="n">
-        <v>112.21</v>
+        <v>111.82</v>
       </c>
       <c r="F36" s="7" t="inlineStr"/>
     </row>
@@ -1387,13 +1387,13 @@
         <v>54.93</v>
       </c>
       <c r="C37" s="5" t="n">
-        <v>63.84</v>
+        <v>63.43</v>
       </c>
       <c r="D37" s="5" t="n">
         <v>89.17</v>
       </c>
       <c r="E37" s="5" t="n">
-        <v>103.64</v>
+        <v>102.97</v>
       </c>
       <c r="F37" s="7" t="inlineStr"/>
     </row>
@@ -1407,13 +1407,13 @@
         <v>67.73999999999999</v>
       </c>
       <c r="C38" s="5" t="n">
-        <v>69.72</v>
+        <v>69.15000000000001</v>
       </c>
       <c r="D38" s="5" t="n">
         <v>109.44</v>
       </c>
       <c r="E38" s="5" t="n">
-        <v>112.64</v>
+        <v>111.72</v>
       </c>
       <c r="F38" s="7" t="inlineStr"/>
     </row>
@@ -1427,13 +1427,13 @@
         <v>55.96</v>
       </c>
       <c r="C39" s="5" t="n">
-        <v>63.27</v>
+        <v>63.04</v>
       </c>
       <c r="D39" s="5" t="n">
         <v>89.98</v>
       </c>
       <c r="E39" s="5" t="n">
-        <v>101.73</v>
+        <v>101.36</v>
       </c>
       <c r="F39" s="7" t="inlineStr"/>
     </row>
@@ -1447,13 +1447,13 @@
         <v>30.36</v>
       </c>
       <c r="C40" s="5" t="n">
-        <v>30.26</v>
+        <v>31.08</v>
       </c>
       <c r="D40" s="5" t="n">
         <v>48.63</v>
       </c>
       <c r="E40" s="5" t="n">
-        <v>48.47</v>
+        <v>49.78</v>
       </c>
       <c r="F40" s="7" t="inlineStr"/>
     </row>
@@ -1467,13 +1467,13 @@
         <v>54.96</v>
       </c>
       <c r="C41" s="5" t="n">
-        <v>60.94</v>
+        <v>60.78</v>
       </c>
       <c r="D41" s="5" t="n">
         <v>87.69</v>
       </c>
       <c r="E41" s="5" t="n">
-        <v>97.23</v>
+        <v>96.98</v>
       </c>
       <c r="F41" s="7" t="inlineStr"/>
     </row>
@@ -1487,13 +1487,13 @@
         <v>43.94</v>
       </c>
       <c r="C42" s="5" t="n">
-        <v>53.5</v>
+        <v>53.01</v>
       </c>
       <c r="D42" s="5" t="n">
         <v>69.84</v>
       </c>
       <c r="E42" s="5" t="n">
-        <v>85.03</v>
+        <v>84.25</v>
       </c>
       <c r="F42" s="7" t="inlineStr"/>
     </row>
@@ -1507,13 +1507,13 @@
         <v>45.92</v>
       </c>
       <c r="C43" s="5" t="n">
-        <v>56.32</v>
+        <v>55.72</v>
       </c>
       <c r="D43" s="5" t="n">
         <v>73.06</v>
       </c>
       <c r="E43" s="5" t="n">
-        <v>89.61</v>
+        <v>88.66</v>
       </c>
       <c r="F43" s="7" t="inlineStr"/>
     </row>
@@ -1527,13 +1527,13 @@
         <v>50.7</v>
       </c>
       <c r="C44" s="5" t="n">
-        <v>61.31</v>
+        <v>60.73</v>
       </c>
       <c r="D44" s="5" t="n">
         <v>80.76000000000001</v>
       </c>
       <c r="E44" s="5" t="n">
-        <v>97.66</v>
+        <v>96.73</v>
       </c>
       <c r="F44" s="7" t="inlineStr"/>
     </row>
@@ -1547,13 +1547,13 @@
         <v>32.91</v>
       </c>
       <c r="C45" s="5" t="n">
-        <v>38.3</v>
+        <v>38.15</v>
       </c>
       <c r="D45" s="5" t="n">
         <v>52.48</v>
       </c>
       <c r="E45" s="5" t="n">
-        <v>61.07</v>
+        <v>60.83</v>
       </c>
       <c r="F45" s="7" t="inlineStr"/>
     </row>
@@ -1567,13 +1567,13 @@
         <v>78.88</v>
       </c>
       <c r="C46" s="5" t="n">
-        <v>119.63</v>
+        <v>119.54</v>
       </c>
       <c r="D46" s="5" t="n">
         <v>125.74</v>
       </c>
       <c r="E46" s="5" t="n">
-        <v>190.69</v>
+        <v>190.55</v>
       </c>
       <c r="F46" s="7" t="inlineStr"/>
     </row>
@@ -1587,13 +1587,13 @@
         <v>39.08</v>
       </c>
       <c r="C47" s="5" t="n">
-        <v>63.91</v>
+        <v>63.49</v>
       </c>
       <c r="D47" s="5" t="n">
         <v>62.27</v>
       </c>
       <c r="E47" s="5" t="n">
-        <v>101.84</v>
+        <v>101.17</v>
       </c>
       <c r="F47" s="7" t="inlineStr"/>
     </row>
@@ -1607,13 +1607,13 @@
         <v>36.48</v>
       </c>
       <c r="C48" s="5" t="n">
-        <v>43.73</v>
+        <v>43.09</v>
       </c>
       <c r="D48" s="5" t="n">
         <v>58.11</v>
       </c>
       <c r="E48" s="5" t="n">
-        <v>69.66</v>
+        <v>68.64</v>
       </c>
       <c r="F48" s="7" t="inlineStr"/>
     </row>
@@ -1627,13 +1627,13 @@
         <v>69.31</v>
       </c>
       <c r="C49" s="5" t="n">
-        <v>63.23</v>
+        <v>61.35</v>
       </c>
       <c r="D49" s="5" t="n">
         <v>110.22</v>
       </c>
       <c r="E49" s="5" t="n">
-        <v>100.55</v>
+        <v>97.56</v>
       </c>
       <c r="F49" s="7" t="inlineStr"/>
     </row>
@@ -1647,13 +1647,13 @@
         <v>46.84</v>
       </c>
       <c r="C50" s="5" t="n">
-        <v>50.07</v>
+        <v>48.31</v>
       </c>
       <c r="D50" s="5" t="n">
         <v>74.36</v>
       </c>
       <c r="E50" s="5" t="n">
-        <v>79.48999999999999</v>
+        <v>76.7</v>
       </c>
       <c r="F50" s="7" t="inlineStr"/>
     </row>
@@ -1667,13 +1667,13 @@
         <v>173.8</v>
       </c>
       <c r="C51" s="5" t="n">
-        <v>292.02</v>
+        <v>287.29</v>
       </c>
       <c r="D51" s="5" t="n">
         <v>275.47</v>
       </c>
       <c r="E51" s="5" t="n">
-        <v>462.84</v>
+        <v>455.35</v>
       </c>
       <c r="F51" s="7" t="inlineStr"/>
     </row>
@@ -1687,13 +1687,13 @@
         <v>25.89</v>
       </c>
       <c r="C52" s="5" t="n">
-        <v>31.68</v>
+        <v>31.56</v>
       </c>
       <c r="D52" s="5" t="n">
         <v>40.91</v>
       </c>
       <c r="E52" s="5" t="n">
-        <v>50.05</v>
+        <v>49.86</v>
       </c>
       <c r="F52" s="7" t="inlineStr"/>
     </row>
@@ -1707,13 +1707,13 @@
         <v>21.29</v>
       </c>
       <c r="C53" s="5" t="n">
-        <v>28.03</v>
+        <v>27.86</v>
       </c>
       <c r="D53" s="5" t="n">
         <v>33.53</v>
       </c>
       <c r="E53" s="5" t="n">
-        <v>44.15</v>
+        <v>43.88</v>
       </c>
       <c r="F53" s="7" t="inlineStr"/>
     </row>
@@ -1727,13 +1727,13 @@
         <v>21.52</v>
       </c>
       <c r="C54" s="5" t="n">
-        <v>27.51</v>
+        <v>27.5</v>
       </c>
       <c r="D54" s="5" t="n">
         <v>33.79</v>
       </c>
       <c r="E54" s="5" t="n">
-        <v>43.19</v>
+        <v>43.18</v>
       </c>
       <c r="F54" s="7" t="inlineStr"/>
     </row>
@@ -1747,13 +1747,13 @@
         <v>25.78</v>
       </c>
       <c r="C55" s="5" t="n">
-        <v>30.14</v>
+        <v>29.55</v>
       </c>
       <c r="D55" s="5" t="n">
         <v>40.41</v>
       </c>
       <c r="E55" s="5" t="n">
-        <v>47.24</v>
+        <v>46.31</v>
       </c>
       <c r="F55" s="7" t="inlineStr"/>
     </row>
@@ -1767,13 +1767,13 @@
         <v>33.7</v>
       </c>
       <c r="C56" s="5" t="n">
-        <v>38.11</v>
+        <v>37.68</v>
       </c>
       <c r="D56" s="5" t="n">
         <v>52.72</v>
       </c>
       <c r="E56" s="5" t="n">
-        <v>59.62</v>
+        <v>58.95</v>
       </c>
       <c r="F56" s="7" t="inlineStr"/>
     </row>
@@ -1787,13 +1787,13 @@
         <v>31.86</v>
       </c>
       <c r="C57" s="5" t="n">
-        <v>31.86</v>
+        <v>31.42</v>
       </c>
       <c r="D57" s="5" t="n">
         <v>49.76</v>
       </c>
       <c r="E57" s="5" t="n">
-        <v>49.76</v>
+        <v>49.07</v>
       </c>
       <c r="F57" s="7" t="inlineStr"/>
     </row>
@@ -1807,13 +1807,13 @@
         <v>29.23</v>
       </c>
       <c r="C58" s="5" t="n">
-        <v>32.52</v>
+        <v>32.51</v>
       </c>
       <c r="D58" s="5" t="n">
         <v>45.51</v>
       </c>
       <c r="E58" s="5" t="n">
-        <v>50.63</v>
+        <v>50.62</v>
       </c>
       <c r="F58" s="7" t="inlineStr"/>
     </row>
@@ -1827,13 +1827,13 @@
         <v>23.96</v>
       </c>
       <c r="C59" s="5" t="n">
-        <v>20.61</v>
+        <v>20.35</v>
       </c>
       <c r="D59" s="5" t="n">
         <v>37.19</v>
       </c>
       <c r="E59" s="5" t="n">
-        <v>31.99</v>
+        <v>31.59</v>
       </c>
       <c r="F59" s="7" t="inlineStr"/>
     </row>
@@ -1847,13 +1847,13 @@
         <v>26.2</v>
       </c>
       <c r="C60" s="5" t="n">
-        <v>28.67</v>
+        <v>28.45</v>
       </c>
       <c r="D60" s="5" t="n">
         <v>40.54</v>
       </c>
       <c r="E60" s="5" t="n">
-        <v>44.36</v>
+        <v>44.02</v>
       </c>
       <c r="F60" s="7" t="inlineStr"/>
     </row>
@@ -1867,13 +1867,13 @@
         <v>24.42</v>
       </c>
       <c r="C61" s="5" t="n">
-        <v>26.2</v>
+        <v>26.23</v>
       </c>
       <c r="D61" s="5" t="n">
         <v>37.71</v>
       </c>
       <c r="E61" s="5" t="n">
-        <v>40.46</v>
+        <v>40.51</v>
       </c>
       <c r="F61" s="7" t="inlineStr"/>
     </row>
@@ -1887,13 +1887,13 @@
         <v>56.97</v>
       </c>
       <c r="C62" s="5" t="n">
-        <v>40.53</v>
+        <v>36.98</v>
       </c>
       <c r="D62" s="5" t="n">
         <v>87.8</v>
       </c>
       <c r="E62" s="5" t="n">
-        <v>62.46</v>
+        <v>56.99</v>
       </c>
       <c r="F62" s="7" t="inlineStr"/>
     </row>
@@ -1907,13 +1907,13 @@
         <v>30.89</v>
       </c>
       <c r="C63" s="5" t="n">
-        <v>34.48</v>
+        <v>34.53</v>
       </c>
       <c r="D63" s="5" t="n">
         <v>47.51</v>
       </c>
       <c r="E63" s="5" t="n">
-        <v>53.03</v>
+        <v>53.11</v>
       </c>
       <c r="F63" s="7" t="inlineStr"/>
     </row>
@@ -1927,13 +1927,13 @@
         <v>30.2</v>
       </c>
       <c r="C64" s="5" t="n">
-        <v>33.99</v>
+        <v>27.43</v>
       </c>
       <c r="D64" s="5" t="n">
         <v>46.34</v>
       </c>
       <c r="E64" s="5" t="n">
-        <v>52.15</v>
+        <v>42.09</v>
       </c>
       <c r="F64" s="7" t="inlineStr"/>
     </row>
@@ -1947,13 +1947,13 @@
         <v>64.8</v>
       </c>
       <c r="C65" s="5" t="n">
-        <v>27.77</v>
+        <v>27.68</v>
       </c>
       <c r="D65" s="5" t="n">
         <v>99.19</v>
       </c>
       <c r="E65" s="5" t="n">
-        <v>42.51</v>
+        <v>42.37</v>
       </c>
       <c r="F65" s="7" t="inlineStr"/>
     </row>
@@ -1967,13 +1967,13 @@
         <v>20.76</v>
       </c>
       <c r="C66" s="5" t="n">
-        <v>23.94</v>
+        <v>23.49</v>
       </c>
       <c r="D66" s="5" t="n">
         <v>31.7</v>
       </c>
       <c r="E66" s="5" t="n">
-        <v>36.56</v>
+        <v>35.87</v>
       </c>
       <c r="F66" s="7" t="inlineStr"/>
     </row>
@@ -1987,13 +1987,13 @@
         <v>18.14</v>
       </c>
       <c r="C67" s="5" t="n">
-        <v>18.56</v>
+        <v>18.32</v>
       </c>
       <c r="D67" s="5" t="n">
         <v>27.66</v>
       </c>
       <c r="E67" s="5" t="n">
-        <v>28.3</v>
+        <v>27.94</v>
       </c>
       <c r="F67" s="7" t="inlineStr"/>
     </row>
@@ -2007,13 +2007,13 @@
         <v>27.1</v>
       </c>
       <c r="C68" s="5" t="n">
-        <v>38.48</v>
+        <v>19.55</v>
       </c>
       <c r="D68" s="5" t="n">
         <v>41.28</v>
       </c>
       <c r="E68" s="5" t="n">
-        <v>58.61</v>
+        <v>29.78</v>
       </c>
       <c r="F68" s="7" t="inlineStr"/>
     </row>
@@ -2027,13 +2027,13 @@
         <v>16.7</v>
       </c>
       <c r="C69" s="5" t="n">
-        <v>17.8</v>
+        <v>17.67</v>
       </c>
       <c r="D69" s="5" t="n">
         <v>25.4</v>
       </c>
       <c r="E69" s="5" t="n">
-        <v>27.08</v>
+        <v>26.88</v>
       </c>
       <c r="F69" s="7" t="inlineStr"/>
     </row>
@@ -2047,13 +2047,13 @@
         <v>25.95</v>
       </c>
       <c r="C70" s="5" t="n">
-        <v>28.36</v>
+        <v>28.13</v>
       </c>
       <c r="D70" s="5" t="n">
         <v>39.27</v>
       </c>
       <c r="E70" s="5" t="n">
-        <v>42.92</v>
+        <v>42.57</v>
       </c>
       <c r="F70" s="7" t="inlineStr"/>
     </row>
@@ -2067,13 +2067,13 @@
         <v>28.72</v>
       </c>
       <c r="C71" s="5" t="n">
-        <v>31.48</v>
+        <v>31.08</v>
       </c>
       <c r="D71" s="5" t="n">
         <v>43.24</v>
       </c>
       <c r="E71" s="5" t="n">
-        <v>47.4</v>
+        <v>46.79</v>
       </c>
       <c r="F71" s="7" t="inlineStr"/>
     </row>
@@ -2087,13 +2087,13 @@
         <v>25.83</v>
       </c>
       <c r="C72" s="5" t="n">
-        <v>27.22</v>
+        <v>27.04</v>
       </c>
       <c r="D72" s="5" t="n">
         <v>38.69</v>
       </c>
       <c r="E72" s="5" t="n">
-        <v>40.77</v>
+        <v>40.5</v>
       </c>
       <c r="F72" s="7" t="inlineStr"/>
     </row>
@@ -2107,13 +2107,13 @@
         <v>26.8</v>
       </c>
       <c r="C73" s="5" t="n">
-        <v>27.79</v>
+        <v>27.77</v>
       </c>
       <c r="D73" s="5" t="n">
         <v>40.02</v>
       </c>
       <c r="E73" s="5" t="n">
-        <v>41.5</v>
+        <v>41.47</v>
       </c>
       <c r="F73" s="7" t="inlineStr"/>
     </row>
@@ -2127,13 +2127,13 @@
         <v>38.67</v>
       </c>
       <c r="C74" s="5" t="n">
-        <v>40.73</v>
+        <v>40.49</v>
       </c>
       <c r="D74" s="5" t="n">
         <v>57.57</v>
       </c>
       <c r="E74" s="5" t="n">
-        <v>60.64</v>
+        <v>60.28</v>
       </c>
       <c r="F74" s="7" t="inlineStr"/>
     </row>
@@ -2147,13 +2147,13 @@
         <v>29.16</v>
       </c>
       <c r="C75" s="5" t="n">
-        <v>32.31</v>
+        <v>32.23</v>
       </c>
       <c r="D75" s="5" t="n">
         <v>43.28</v>
       </c>
       <c r="E75" s="5" t="n">
-        <v>47.96</v>
+        <v>47.84</v>
       </c>
       <c r="F75" s="7" t="inlineStr"/>
     </row>
@@ -2167,13 +2167,13 @@
         <v>32.59</v>
       </c>
       <c r="C76" s="5" t="n">
-        <v>49.12</v>
+        <v>49.09</v>
       </c>
       <c r="D76" s="5" t="n">
         <v>48.28</v>
       </c>
       <c r="E76" s="5" t="n">
-        <v>72.76000000000001</v>
+        <v>72.72</v>
       </c>
       <c r="F76" s="7" t="inlineStr"/>
     </row>
@@ -2187,13 +2187,13 @@
         <v>27.16</v>
       </c>
       <c r="C77" s="5" t="n">
-        <v>34.69</v>
+        <v>34.57</v>
       </c>
       <c r="D77" s="5" t="n">
         <v>40.15</v>
       </c>
       <c r="E77" s="5" t="n">
-        <v>51.29</v>
+        <v>51.11</v>
       </c>
       <c r="F77" s="7" t="inlineStr"/>
     </row>
@@ -2207,13 +2207,13 @@
         <v>26.4</v>
       </c>
       <c r="C78" s="5" t="n">
-        <v>29.9</v>
+        <v>29.91</v>
       </c>
       <c r="D78" s="5" t="n">
         <v>38.95</v>
       </c>
       <c r="E78" s="5" t="n">
-        <v>44.12</v>
+        <v>44.13</v>
       </c>
       <c r="F78" s="7" t="inlineStr"/>
     </row>
@@ -2227,13 +2227,13 @@
         <v>32.58</v>
       </c>
       <c r="C79" s="5" t="n">
-        <v>31.6</v>
+        <v>31.19</v>
       </c>
       <c r="D79" s="5" t="n">
         <v>48.07</v>
       </c>
       <c r="E79" s="5" t="n">
-        <v>46.63</v>
+        <v>46.02</v>
       </c>
       <c r="F79" s="7" t="inlineStr"/>
     </row>
@@ -2247,13 +2247,13 @@
         <v>30.75</v>
       </c>
       <c r="C80" s="5" t="n">
-        <v>30.44</v>
+        <v>29.77</v>
       </c>
       <c r="D80" s="5" t="n">
         <v>45.37</v>
       </c>
       <c r="E80" s="5" t="n">
-        <v>44.91</v>
+        <v>43.93</v>
       </c>
       <c r="F80" s="7" t="inlineStr"/>
     </row>
@@ -2267,13 +2267,13 @@
         <v>25.85</v>
       </c>
       <c r="C81" s="5" t="n">
-        <v>26.57</v>
+        <v>26.39</v>
       </c>
       <c r="D81" s="5" t="n">
         <v>38.14</v>
       </c>
       <c r="E81" s="5" t="n">
-        <v>39.2</v>
+        <v>38.94</v>
       </c>
       <c r="F81" s="7" t="inlineStr"/>
     </row>
@@ -2287,13 +2287,13 @@
         <v>39.32</v>
       </c>
       <c r="C82" s="5" t="n">
-        <v>34.13</v>
+        <v>34.3</v>
       </c>
       <c r="D82" s="5" t="n">
         <v>58</v>
       </c>
       <c r="E82" s="5" t="n">
-        <v>50.35</v>
+        <v>50.6</v>
       </c>
       <c r="F82" s="7" t="inlineStr"/>
     </row>
@@ -2307,13 +2307,13 @@
         <v>37.37</v>
       </c>
       <c r="C83" s="5" t="n">
-        <v>29.92</v>
+        <v>29.99</v>
       </c>
       <c r="D83" s="5" t="n">
         <v>55.12</v>
       </c>
       <c r="E83" s="5" t="n">
-        <v>44.13</v>
+        <v>44.23</v>
       </c>
       <c r="F83" s="7" t="inlineStr"/>
     </row>
@@ -2327,13 +2327,13 @@
         <v>35.92</v>
       </c>
       <c r="C84" s="5" t="n">
-        <v>29.84</v>
+        <v>29.57</v>
       </c>
       <c r="D84" s="5" t="n">
         <v>52.97</v>
       </c>
       <c r="E84" s="5" t="n">
-        <v>44</v>
+        <v>43.6</v>
       </c>
       <c r="F84" s="7" t="inlineStr"/>
     </row>
@@ -2347,13 +2347,13 @@
         <v>35.96</v>
       </c>
       <c r="C85" s="5" t="n">
-        <v>42.04</v>
+        <v>41.97</v>
       </c>
       <c r="D85" s="5" t="n">
         <v>52.94</v>
       </c>
       <c r="E85" s="5" t="n">
-        <v>61.89</v>
+        <v>61.78</v>
       </c>
       <c r="F85" s="7" t="inlineStr"/>
     </row>
@@ -2367,13 +2367,13 @@
         <v>32.9</v>
       </c>
       <c r="C86" s="5" t="n">
-        <v>29.9</v>
+        <v>29.93</v>
       </c>
       <c r="D86" s="5" t="n">
         <v>48.35</v>
       </c>
       <c r="E86" s="5" t="n">
-        <v>43.94</v>
+        <v>43.98</v>
       </c>
       <c r="F86" s="7" t="inlineStr"/>
     </row>
@@ -2387,13 +2387,13 @@
         <v>34.44</v>
       </c>
       <c r="C87" s="5" t="n">
-        <v>38.55</v>
+        <v>38.35</v>
       </c>
       <c r="D87" s="5" t="n">
         <v>50.52</v>
       </c>
       <c r="E87" s="5" t="n">
-        <v>56.55</v>
+        <v>56.26</v>
       </c>
       <c r="F87" s="7" t="inlineStr"/>
     </row>
@@ -2407,13 +2407,13 @@
         <v>59.23</v>
       </c>
       <c r="C88" s="9" t="n">
-        <v>67.45</v>
+        <v>67.09999999999999</v>
       </c>
       <c r="D88" s="9" t="n">
         <v>86.5</v>
       </c>
       <c r="E88" s="9" t="n">
-        <v>98.5</v>
+        <v>97.98999999999999</v>
       </c>
       <c r="F88" s="10" t="inlineStr">
         <is>
@@ -2431,13 +2431,13 @@
         <v>47.22</v>
       </c>
       <c r="C89" s="9" t="n">
-        <v>48.6</v>
+        <v>48.32</v>
       </c>
       <c r="D89" s="9" t="n">
         <v>68.65000000000001</v>
       </c>
       <c r="E89" s="9" t="n">
-        <v>70.66</v>
+        <v>70.25</v>
       </c>
       <c r="F89" s="10" t="inlineStr">
         <is>
@@ -2455,13 +2455,13 @@
         <v>39.46</v>
       </c>
       <c r="C90" s="9" t="n">
-        <v>41.42</v>
+        <v>41.39</v>
       </c>
       <c r="D90" s="9" t="n">
         <v>57.11</v>
       </c>
       <c r="E90" s="9" t="n">
-        <v>59.95</v>
+        <v>59.9</v>
       </c>
       <c r="F90" s="10" t="inlineStr">
         <is>
@@ -2479,13 +2479,13 @@
         <v>43.62</v>
       </c>
       <c r="C91" s="9" t="n">
-        <v>44.97</v>
+        <v>44.73</v>
       </c>
       <c r="D91" s="9" t="n">
         <v>63.08</v>
       </c>
       <c r="E91" s="9" t="n">
-        <v>65.03</v>
+        <v>64.68000000000001</v>
       </c>
       <c r="F91" s="10" t="inlineStr">
         <is>
@@ -2503,13 +2503,13 @@
         <v>50.58</v>
       </c>
       <c r="C92" s="9" t="n">
-        <v>51.39</v>
+        <v>51.23</v>
       </c>
       <c r="D92" s="9" t="n">
         <v>73.08</v>
       </c>
       <c r="E92" s="9" t="n">
-        <v>74.25</v>
+        <v>74.02</v>
       </c>
       <c r="F92" s="10" t="inlineStr">
         <is>
@@ -2527,13 +2527,13 @@
         <v>46.7</v>
       </c>
       <c r="C93" s="9" t="n">
-        <v>46.41</v>
+        <v>46.33</v>
       </c>
       <c r="D93" s="9" t="n">
         <v>67.42</v>
       </c>
       <c r="E93" s="9" t="n">
-        <v>67</v>
+        <v>66.88</v>
       </c>
       <c r="F93" s="10" t="inlineStr">
         <is>
@@ -2551,13 +2551,13 @@
         <v>56.96</v>
       </c>
       <c r="C94" s="9" t="n">
-        <v>46.53</v>
+        <v>46.27</v>
       </c>
       <c r="D94" s="9" t="n">
         <v>82.14</v>
       </c>
       <c r="E94" s="9" t="n">
-        <v>67.09999999999999</v>
+        <v>66.72</v>
       </c>
       <c r="F94" s="10" t="inlineStr">
         <is>
@@ -2575,13 +2575,13 @@
         <v>45.79</v>
       </c>
       <c r="C95" s="9" t="n">
-        <v>46.11</v>
+        <v>45.77</v>
       </c>
       <c r="D95" s="9" t="n">
         <v>65.95</v>
       </c>
       <c r="E95" s="9" t="n">
-        <v>66.42</v>
+        <v>65.93000000000001</v>
       </c>
       <c r="F95" s="10" t="inlineStr">
         <is>
@@ -2599,13 +2599,13 @@
         <v>49.81</v>
       </c>
       <c r="C96" s="9" t="n">
-        <v>50.82</v>
+        <v>50.56</v>
       </c>
       <c r="D96" s="9" t="n">
         <v>71.66</v>
       </c>
       <c r="E96" s="9" t="n">
-        <v>73.12</v>
+        <v>72.73999999999999</v>
       </c>
       <c r="F96" s="10" t="inlineStr">
         <is>
@@ -2623,13 +2623,13 @@
         <v>45.12</v>
       </c>
       <c r="C97" s="9" t="n">
-        <v>46.73</v>
+        <v>46.49</v>
       </c>
       <c r="D97" s="9" t="n">
         <v>64.83</v>
       </c>
       <c r="E97" s="9" t="n">
-        <v>67.15000000000001</v>
+        <v>66.8</v>
       </c>
       <c r="F97" s="10" t="inlineStr">
         <is>
@@ -2647,13 +2647,13 @@
         <v>44.67</v>
       </c>
       <c r="C98" s="9" t="n">
-        <v>49.68</v>
+        <v>49.59</v>
       </c>
       <c r="D98" s="9" t="n">
         <v>64.11</v>
       </c>
       <c r="E98" s="9" t="n">
-        <v>71.3</v>
+        <v>71.17</v>
       </c>
       <c r="F98" s="10" t="inlineStr">
         <is>
@@ -2671,13 +2671,13 @@
         <v>49.89</v>
       </c>
       <c r="C99" s="9" t="n">
-        <v>51.77</v>
+        <v>51.48</v>
       </c>
       <c r="D99" s="9" t="n">
         <v>71.51000000000001</v>
       </c>
       <c r="E99" s="9" t="n">
-        <v>74.2</v>
+        <v>73.79000000000001</v>
       </c>
       <c r="F99" s="10" t="inlineStr">
         <is>
@@ -2695,13 +2695,13 @@
         <v>51.5</v>
       </c>
       <c r="C100" s="9" t="n">
-        <v>50.69</v>
+        <v>53.74</v>
       </c>
       <c r="D100" s="9" t="n">
         <v>73.52</v>
       </c>
       <c r="E100" s="9" t="n">
-        <v>72.36</v>
+        <v>76.70999999999999</v>
       </c>
       <c r="F100" s="10" t="inlineStr">
         <is>
@@ -2719,13 +2719,13 @@
         <v>45.87</v>
       </c>
       <c r="C101" s="9" t="n">
-        <v>49.44</v>
+        <v>49.24</v>
       </c>
       <c r="D101" s="9" t="n">
         <v>65.22</v>
       </c>
       <c r="E101" s="9" t="n">
-        <v>70.29000000000001</v>
+        <v>70.01000000000001</v>
       </c>
       <c r="F101" s="10" t="inlineStr">
         <is>
@@ -2743,13 +2743,13 @@
         <v>42.43</v>
       </c>
       <c r="C102" s="9" t="n">
-        <v>44.8</v>
+        <v>44.67</v>
       </c>
       <c r="D102" s="9" t="n">
         <v>60.08</v>
       </c>
       <c r="E102" s="9" t="n">
-        <v>63.44</v>
+        <v>63.26</v>
       </c>
       <c r="F102" s="10" t="inlineStr">
         <is>
@@ -2767,13 +2767,13 @@
         <v>38.6</v>
       </c>
       <c r="C103" s="9" t="n">
-        <v>41.47</v>
+        <v>41.23</v>
       </c>
       <c r="D103" s="9" t="n">
         <v>54.53</v>
       </c>
       <c r="E103" s="9" t="n">
-        <v>58.58</v>
+        <v>58.24</v>
       </c>
       <c r="F103" s="10" t="inlineStr">
         <is>
@@ -2791,13 +2791,13 @@
         <v>47.09</v>
       </c>
       <c r="C104" s="9" t="n">
-        <v>52.99</v>
+        <v>52.96</v>
       </c>
       <c r="D104" s="9" t="n">
         <v>66.36</v>
       </c>
       <c r="E104" s="9" t="n">
-        <v>74.68000000000001</v>
+        <v>74.64</v>
       </c>
       <c r="F104" s="10" t="inlineStr">
         <is>
@@ -2815,13 +2815,13 @@
         <v>37.6</v>
       </c>
       <c r="C105" s="9" t="n">
-        <v>37.58</v>
+        <v>37.37</v>
       </c>
       <c r="D105" s="9" t="n">
         <v>52.86</v>
       </c>
       <c r="E105" s="9" t="n">
-        <v>52.84</v>
+        <v>52.54</v>
       </c>
       <c r="F105" s="10" t="inlineStr">
         <is>
@@ -2839,13 +2839,13 @@
         <v>34.88</v>
       </c>
       <c r="C106" s="9" t="n">
-        <v>29.48</v>
+        <v>29.27</v>
       </c>
       <c r="D106" s="9" t="n">
         <v>48.94</v>
       </c>
       <c r="E106" s="9" t="n">
-        <v>41.37</v>
+        <v>41.07</v>
       </c>
       <c r="F106" s="10" t="inlineStr">
         <is>
@@ -2863,13 +2863,13 @@
         <v>43.89</v>
       </c>
       <c r="C107" s="9" t="n">
-        <v>43.27</v>
+        <v>42.97</v>
       </c>
       <c r="D107" s="9" t="n">
         <v>61.46</v>
       </c>
       <c r="E107" s="9" t="n">
-        <v>60.6</v>
+        <v>60.18</v>
       </c>
       <c r="F107" s="10" t="inlineStr">
         <is>
@@ -2887,13 +2887,13 @@
         <v>44.78</v>
       </c>
       <c r="C108" s="9" t="n">
-        <v>45.47</v>
+        <v>45.1</v>
       </c>
       <c r="D108" s="9" t="n">
         <v>62.59</v>
       </c>
       <c r="E108" s="9" t="n">
-        <v>63.55</v>
+        <v>63.04</v>
       </c>
       <c r="F108" s="10" t="inlineStr">
         <is>
@@ -2911,13 +2911,13 @@
         <v>37.68</v>
       </c>
       <c r="C109" s="9" t="n">
-        <v>38.57</v>
+        <v>38.42</v>
       </c>
       <c r="D109" s="9" t="n">
         <v>52.58</v>
       </c>
       <c r="E109" s="9" t="n">
-        <v>53.82</v>
+        <v>53.61</v>
       </c>
       <c r="F109" s="10" t="inlineStr">
         <is>
@@ -2935,13 +2935,13 @@
         <v>36.52</v>
       </c>
       <c r="C110" s="9" t="n">
-        <v>40.99</v>
+        <v>40.85</v>
       </c>
       <c r="D110" s="9" t="n">
         <v>50.87</v>
       </c>
       <c r="E110" s="9" t="n">
-        <v>57.1</v>
+        <v>56.9</v>
       </c>
       <c r="F110" s="10" t="inlineStr">
         <is>
@@ -2959,13 +2959,13 @@
         <v>43.15</v>
       </c>
       <c r="C111" s="9" t="n">
-        <v>44.06</v>
+        <v>43.96</v>
       </c>
       <c r="D111" s="9" t="n">
         <v>60.01</v>
       </c>
       <c r="E111" s="9" t="n">
-        <v>61.27</v>
+        <v>61.13</v>
       </c>
       <c r="F111" s="10" t="inlineStr">
         <is>
@@ -2983,13 +2983,13 @@
         <v>33.83</v>
       </c>
       <c r="C112" s="5" t="n">
-        <v>37.29</v>
+        <v>37.17</v>
       </c>
       <c r="D112" s="5" t="n">
         <v>46.98</v>
       </c>
       <c r="E112" s="5" t="n">
-        <v>51.78</v>
+        <v>51.62</v>
       </c>
       <c r="F112" s="7" t="inlineStr"/>
     </row>
@@ -3003,13 +3003,13 @@
         <v>36.34</v>
       </c>
       <c r="C113" s="5" t="n">
-        <v>41.88</v>
+        <v>41.72</v>
       </c>
       <c r="D113" s="5" t="n">
         <v>50.39</v>
       </c>
       <c r="E113" s="5" t="n">
-        <v>58.08</v>
+        <v>57.86</v>
       </c>
       <c r="F113" s="7" t="inlineStr"/>
     </row>
@@ -3023,13 +3023,13 @@
         <v>37.65</v>
       </c>
       <c r="C114" s="5" t="n">
-        <v>40.3</v>
+        <v>39.82</v>
       </c>
       <c r="D114" s="5" t="n">
         <v>52.14</v>
       </c>
       <c r="E114" s="5" t="n">
-        <v>55.81</v>
+        <v>55.14</v>
       </c>
       <c r="F114" s="7" t="inlineStr"/>
     </row>
@@ -3043,13 +3043,13 @@
         <v>34.91</v>
       </c>
       <c r="C115" s="5" t="n">
-        <v>32.91</v>
+        <v>32.77</v>
       </c>
       <c r="D115" s="5" t="n">
         <v>48.31</v>
       </c>
       <c r="E115" s="5" t="n">
-        <v>45.55</v>
+        <v>45.35</v>
       </c>
       <c r="F115" s="7" t="inlineStr"/>
     </row>
@@ -3063,13 +3063,13 @@
         <v>39.94</v>
       </c>
       <c r="C116" s="5" t="n">
-        <v>37.03</v>
+        <v>37.02</v>
       </c>
       <c r="D116" s="5" t="n">
         <v>55.24</v>
       </c>
       <c r="E116" s="5" t="n">
-        <v>51.21</v>
+        <v>51.2</v>
       </c>
       <c r="F116" s="7" t="inlineStr"/>
     </row>
@@ -3083,13 +3083,13 @@
         <v>45.26</v>
       </c>
       <c r="C117" s="5" t="n">
-        <v>44.4</v>
+        <v>44.27</v>
       </c>
       <c r="D117" s="5" t="n">
         <v>62.56</v>
       </c>
       <c r="E117" s="5" t="n">
-        <v>61.37</v>
+        <v>61.19</v>
       </c>
       <c r="F117" s="7" t="inlineStr"/>
     </row>
@@ -3103,13 +3103,13 @@
         <v>35.08</v>
       </c>
       <c r="C118" s="5" t="n">
-        <v>36.8</v>
+        <v>36.59</v>
       </c>
       <c r="D118" s="5" t="n">
         <v>48.46</v>
       </c>
       <c r="E118" s="5" t="n">
-        <v>50.83</v>
+        <v>50.54</v>
       </c>
       <c r="F118" s="7" t="inlineStr"/>
     </row>
@@ -3123,13 +3123,13 @@
         <v>42.54</v>
       </c>
       <c r="C119" s="5" t="n">
-        <v>41.1</v>
+        <v>40.89</v>
       </c>
       <c r="D119" s="5" t="n">
         <v>58.72</v>
       </c>
       <c r="E119" s="5" t="n">
-        <v>56.74</v>
+        <v>56.45</v>
       </c>
       <c r="F119" s="7" t="inlineStr"/>
     </row>
@@ -3143,13 +3143,13 @@
         <v>39.77</v>
       </c>
       <c r="C120" s="5" t="n">
-        <v>39.98</v>
+        <v>39.56</v>
       </c>
       <c r="D120" s="5" t="n">
         <v>54.87</v>
       </c>
       <c r="E120" s="5" t="n">
-        <v>55.16</v>
+        <v>54.58</v>
       </c>
       <c r="F120" s="7" t="inlineStr"/>
     </row>
@@ -3163,13 +3163,13 @@
         <v>40.64</v>
       </c>
       <c r="C121" s="5" t="n">
-        <v>38.37</v>
+        <v>38.06</v>
       </c>
       <c r="D121" s="5" t="n">
         <v>55.93</v>
       </c>
       <c r="E121" s="5" t="n">
-        <v>52.81</v>
+        <v>52.38</v>
       </c>
       <c r="F121" s="7" t="inlineStr"/>
     </row>
@@ -3183,13 +3183,13 @@
         <v>28.3</v>
       </c>
       <c r="C122" s="5" t="n">
-        <v>37.02</v>
+        <v>33.76</v>
       </c>
       <c r="D122" s="5" t="n">
         <v>38.86</v>
       </c>
       <c r="E122" s="5" t="n">
-        <v>50.83</v>
+        <v>46.35</v>
       </c>
       <c r="F122" s="7" t="inlineStr"/>
     </row>
@@ -3203,13 +3203,13 @@
         <v>32.25</v>
       </c>
       <c r="C123" s="5" t="n">
-        <v>37.68</v>
+        <v>37.17</v>
       </c>
       <c r="D123" s="5" t="n">
         <v>44.18</v>
       </c>
       <c r="E123" s="5" t="n">
-        <v>51.61</v>
+        <v>50.92</v>
       </c>
       <c r="F123" s="7" t="inlineStr"/>
     </row>
@@ -3223,13 +3223,13 @@
         <v>34.9</v>
       </c>
       <c r="C124" s="5" t="n">
-        <v>39.11</v>
+        <v>38.8</v>
       </c>
       <c r="D124" s="5" t="n">
         <v>47.74</v>
       </c>
       <c r="E124" s="5" t="n">
-        <v>53.5</v>
+        <v>53.08</v>
       </c>
       <c r="F124" s="7" t="inlineStr"/>
     </row>
@@ -3243,13 +3243,13 @@
         <v>31.89</v>
       </c>
       <c r="C125" s="5" t="n">
-        <v>38.28</v>
+        <v>37.69</v>
       </c>
       <c r="D125" s="5" t="n">
         <v>43.57</v>
       </c>
       <c r="E125" s="5" t="n">
-        <v>52.3</v>
+        <v>51.49</v>
       </c>
       <c r="F125" s="7" t="inlineStr"/>
     </row>
@@ -3263,13 +3263,13 @@
         <v>46.02</v>
       </c>
       <c r="C126" s="5" t="n">
-        <v>48.78</v>
+        <v>48.67</v>
       </c>
       <c r="D126" s="5" t="n">
         <v>62.79</v>
       </c>
       <c r="E126" s="5" t="n">
-        <v>66.56</v>
+        <v>66.41</v>
       </c>
       <c r="F126" s="7" t="inlineStr"/>
     </row>
@@ -3283,13 +3283,13 @@
         <v>59.22</v>
       </c>
       <c r="C127" s="5" t="n">
-        <v>60.34</v>
+        <v>60.05</v>
       </c>
       <c r="D127" s="5" t="n">
         <v>80.7</v>
       </c>
       <c r="E127" s="5" t="n">
-        <v>82.23</v>
+        <v>81.83</v>
       </c>
       <c r="F127" s="7" t="inlineStr"/>
     </row>
@@ -3303,13 +3303,13 @@
         <v>83.73</v>
       </c>
       <c r="C128" s="5" t="n">
-        <v>85.88</v>
+        <v>85.7</v>
       </c>
       <c r="D128" s="5" t="n">
         <v>113.96</v>
       </c>
       <c r="E128" s="5" t="n">
-        <v>116.88</v>
+        <v>116.64</v>
       </c>
       <c r="F128" s="7" t="inlineStr"/>
     </row>
@@ -3323,13 +3323,13 @@
         <v>96.09999999999999</v>
       </c>
       <c r="C129" s="5" t="n">
-        <v>97.17</v>
+        <v>96.81999999999999</v>
       </c>
       <c r="D129" s="5" t="n">
         <v>130.62</v>
       </c>
       <c r="E129" s="5" t="n">
-        <v>132.08</v>
+        <v>131.6</v>
       </c>
       <c r="F129" s="7" t="inlineStr"/>
     </row>
@@ -3343,13 +3343,13 @@
         <v>112.73</v>
       </c>
       <c r="C130" s="5" t="n">
-        <v>114.3</v>
+        <v>112.56</v>
       </c>
       <c r="D130" s="5" t="n">
         <v>153.33</v>
       </c>
       <c r="E130" s="5" t="n">
-        <v>155.46</v>
+        <v>153.1</v>
       </c>
       <c r="F130" s="7" t="inlineStr"/>
     </row>
@@ -3363,13 +3363,13 @@
         <v>165.67</v>
       </c>
       <c r="C131" s="5" t="n">
-        <v>164</v>
+        <v>163.47</v>
       </c>
       <c r="D131" s="5" t="n">
         <v>225.48</v>
       </c>
       <c r="E131" s="5" t="n">
-        <v>223.21</v>
+        <v>222.49</v>
       </c>
       <c r="F131" s="7" t="inlineStr"/>
     </row>
@@ -3383,13 +3383,13 @@
         <v>252.37</v>
       </c>
       <c r="C132" s="5" t="n">
-        <v>256.22</v>
+        <v>255.9</v>
       </c>
       <c r="D132" s="5" t="n">
         <v>343.72</v>
       </c>
       <c r="E132" s="5" t="n">
-        <v>348.96</v>
+        <v>348.52</v>
       </c>
       <c r="F132" s="7" t="inlineStr"/>
     </row>
@@ -3403,13 +3403,13 @@
         <v>236.85</v>
       </c>
       <c r="C133" s="5" t="n">
-        <v>236.68</v>
+        <v>227.53</v>
       </c>
       <c r="D133" s="5" t="n">
         <v>322.11</v>
       </c>
       <c r="E133" s="5" t="n">
-        <v>321.88</v>
+        <v>309.43</v>
       </c>
       <c r="F133" s="7" t="inlineStr"/>
     </row>
@@ -3423,13 +3423,13 @@
         <v>45.45</v>
       </c>
       <c r="C134" s="5" t="n">
-        <v>57.34</v>
+        <v>57</v>
       </c>
       <c r="D134" s="5" t="n">
         <v>61.72</v>
       </c>
       <c r="E134" s="5" t="n">
-        <v>77.87</v>
+        <v>77.40000000000001</v>
       </c>
       <c r="F134" s="7" t="inlineStr"/>
     </row>
@@ -3443,13 +3443,13 @@
         <v>72.5</v>
       </c>
       <c r="C135" s="5" t="n">
-        <v>100.06</v>
+        <v>98.19</v>
       </c>
       <c r="D135" s="5" t="n">
         <v>98.31</v>
       </c>
       <c r="E135" s="5" t="n">
-        <v>135.68</v>
+        <v>133.15</v>
       </c>
       <c r="F135" s="7" t="inlineStr"/>
     </row>
@@ -3463,13 +3463,13 @@
         <v>67.92</v>
       </c>
       <c r="C136" s="5" t="n">
-        <v>97.12</v>
+        <v>95.26000000000001</v>
       </c>
       <c r="D136" s="5" t="n">
         <v>91.88</v>
       </c>
       <c r="E136" s="5" t="n">
-        <v>131.39</v>
+        <v>128.87</v>
       </c>
       <c r="F136" s="7" t="inlineStr"/>
     </row>
@@ -3483,13 +3483,13 @@
         <v>43.68</v>
       </c>
       <c r="C137" s="5" t="n">
-        <v>58.34</v>
+        <v>56.46</v>
       </c>
       <c r="D137" s="5" t="n">
         <v>58.95</v>
       </c>
       <c r="E137" s="5" t="n">
-        <v>78.73999999999999</v>
+        <v>76.2</v>
       </c>
       <c r="F137" s="7" t="inlineStr"/>
     </row>
@@ -3503,13 +3503,13 @@
         <v>46.18</v>
       </c>
       <c r="C138" s="5" t="n">
-        <v>52.77</v>
+        <v>52.02</v>
       </c>
       <c r="D138" s="5" t="n">
         <v>62.18</v>
       </c>
       <c r="E138" s="5" t="n">
-        <v>71.06</v>
+        <v>70.05</v>
       </c>
       <c r="F138" s="7" t="inlineStr"/>
     </row>
@@ -3523,13 +3523,13 @@
         <v>33.22</v>
       </c>
       <c r="C139" s="5" t="n">
-        <v>42.16</v>
+        <v>39.37</v>
       </c>
       <c r="D139" s="5" t="n">
         <v>44.65</v>
       </c>
       <c r="E139" s="5" t="n">
-        <v>56.67</v>
+        <v>52.92</v>
       </c>
       <c r="F139" s="7" t="inlineStr"/>
     </row>
@@ -3543,13 +3543,13 @@
         <v>37.58</v>
       </c>
       <c r="C140" s="5" t="n">
-        <v>52.68</v>
+        <v>50.91</v>
       </c>
       <c r="D140" s="5" t="n">
         <v>50.43</v>
       </c>
       <c r="E140" s="5" t="n">
-        <v>70.69</v>
+        <v>68.31</v>
       </c>
       <c r="F140" s="7" t="inlineStr"/>
     </row>
@@ -3563,13 +3563,13 @@
         <v>41.3</v>
       </c>
       <c r="C141" s="5" t="n">
-        <v>46.61</v>
+        <v>45.93</v>
       </c>
       <c r="D141" s="5" t="n">
         <v>55.32</v>
       </c>
       <c r="E141" s="5" t="n">
-        <v>62.43</v>
+        <v>61.52</v>
       </c>
       <c r="F141" s="7" t="inlineStr"/>
     </row>
@@ -3583,13 +3583,13 @@
         <v>86.11</v>
       </c>
       <c r="C142" s="5" t="n">
-        <v>91.34999999999999</v>
+        <v>90.94</v>
       </c>
       <c r="D142" s="5" t="n">
         <v>115.17</v>
       </c>
       <c r="E142" s="5" t="n">
-        <v>122.18</v>
+        <v>121.63</v>
       </c>
       <c r="F142" s="7" t="inlineStr"/>
     </row>
@@ -3603,13 +3603,13 @@
         <v>94.38</v>
       </c>
       <c r="C143" s="5" t="n">
-        <v>104.02</v>
+        <v>102.31</v>
       </c>
       <c r="D143" s="5" t="n">
         <v>126.04</v>
       </c>
       <c r="E143" s="5" t="n">
-        <v>138.91</v>
+        <v>136.63</v>
       </c>
       <c r="F143" s="7" t="inlineStr"/>
     </row>
@@ -3623,13 +3623,13 @@
         <v>113.81</v>
       </c>
       <c r="C144" s="5" t="n">
-        <v>117.62</v>
+        <v>116.54</v>
       </c>
       <c r="D144" s="5" t="n">
         <v>151.75</v>
       </c>
       <c r="E144" s="5" t="n">
-        <v>156.83</v>
+        <v>155.39</v>
       </c>
       <c r="F144" s="7" t="inlineStr"/>
     </row>
@@ -3643,13 +3643,13 @@
         <v>131.25</v>
       </c>
       <c r="C145" s="5" t="n">
-        <v>128.93</v>
+        <v>127.22</v>
       </c>
       <c r="D145" s="5" t="n">
         <v>174.89</v>
       </c>
       <c r="E145" s="5" t="n">
-        <v>171.8</v>
+        <v>169.52</v>
       </c>
       <c r="F145" s="7" t="inlineStr"/>
     </row>
@@ -3663,13 +3663,13 @@
         <v>107.94</v>
       </c>
       <c r="C146" s="5" t="n">
-        <v>118.62</v>
+        <v>117.37</v>
       </c>
       <c r="D146" s="5" t="n">
         <v>143.74</v>
       </c>
       <c r="E146" s="5" t="n">
-        <v>157.96</v>
+        <v>156.29</v>
       </c>
       <c r="F146" s="7" t="inlineStr"/>
     </row>
@@ -3683,13 +3683,13 @@
         <v>103.84</v>
       </c>
       <c r="C147" s="5" t="n">
-        <v>109.77</v>
+        <v>109.28</v>
       </c>
       <c r="D147" s="5" t="n">
         <v>138.19</v>
       </c>
       <c r="E147" s="5" t="n">
-        <v>146.08</v>
+        <v>145.43</v>
       </c>
       <c r="F147" s="7" t="inlineStr"/>
     </row>
@@ -3703,13 +3703,13 @@
         <v>116.03</v>
       </c>
       <c r="C148" s="5" t="n">
-        <v>126.14</v>
+        <v>125.08</v>
       </c>
       <c r="D148" s="5" t="n">
         <v>154.1</v>
       </c>
       <c r="E148" s="5" t="n">
-        <v>167.52</v>
+        <v>166.11</v>
       </c>
       <c r="F148" s="7" t="inlineStr"/>
     </row>
@@ -3723,13 +3723,13 @@
         <v>97.20999999999999</v>
       </c>
       <c r="C149" s="5" t="n">
-        <v>110.94</v>
+        <v>109.03</v>
       </c>
       <c r="D149" s="5" t="n">
         <v>128.84</v>
       </c>
       <c r="E149" s="5" t="n">
-        <v>147.04</v>
+        <v>144.51</v>
       </c>
       <c r="F149" s="7" t="inlineStr"/>
     </row>
@@ -3743,13 +3743,13 @@
         <v>73.58</v>
       </c>
       <c r="C150" s="5" t="n">
-        <v>82.05</v>
+        <v>81.7</v>
       </c>
       <c r="D150" s="5" t="n">
         <v>97.31999999999999</v>
       </c>
       <c r="E150" s="5" t="n">
-        <v>108.53</v>
+        <v>108.06</v>
       </c>
       <c r="F150" s="7" t="inlineStr"/>
     </row>
@@ -3763,13 +3763,13 @@
         <v>68.66</v>
       </c>
       <c r="C151" s="5" t="n">
-        <v>75.56</v>
+        <v>75.29000000000001</v>
       </c>
       <c r="D151" s="5" t="n">
         <v>90.61</v>
       </c>
       <c r="E151" s="5" t="n">
-        <v>99.72</v>
+        <v>99.36</v>
       </c>
       <c r="F151" s="7" t="inlineStr"/>
     </row>
@@ -3783,13 +3783,13 @@
         <v>94.03</v>
       </c>
       <c r="C152" s="5" t="n">
-        <v>105.59</v>
+        <v>105.28</v>
       </c>
       <c r="D152" s="5" t="n">
         <v>123.82</v>
       </c>
       <c r="E152" s="5" t="n">
-        <v>139.04</v>
+        <v>138.63</v>
       </c>
       <c r="F152" s="7" t="inlineStr"/>
     </row>
@@ -3803,13 +3803,13 @@
         <v>90.95999999999999</v>
       </c>
       <c r="C153" s="5" t="n">
-        <v>106.82</v>
+        <v>106.8</v>
       </c>
       <c r="D153" s="5" t="n">
         <v>119.51</v>
       </c>
       <c r="E153" s="5" t="n">
-        <v>140.35</v>
+        <v>140.32</v>
       </c>
       <c r="F153" s="7" t="inlineStr"/>
     </row>
@@ -3823,13 +3823,13 @@
         <v>98.97</v>
       </c>
       <c r="C154" s="5" t="n">
-        <v>95.51000000000001</v>
+        <v>96.02</v>
       </c>
       <c r="D154" s="5" t="n">
         <v>129.84</v>
       </c>
       <c r="E154" s="5" t="n">
-        <v>125.3</v>
+        <v>125.97</v>
       </c>
       <c r="F154" s="7" t="inlineStr"/>
     </row>
@@ -3843,13 +3843,13 @@
         <v>89.27</v>
       </c>
       <c r="C155" s="5" t="n">
-        <v>89.34999999999999</v>
+        <v>89.25</v>
       </c>
       <c r="D155" s="5" t="n">
         <v>116.95</v>
       </c>
       <c r="E155" s="5" t="n">
-        <v>117.05</v>
+        <v>116.92</v>
       </c>
       <c r="F155" s="7" t="inlineStr"/>
     </row>
@@ -3863,13 +3863,13 @@
         <v>83.52</v>
       </c>
       <c r="C156" s="5" t="n">
-        <v>86.02</v>
+        <v>85.43000000000001</v>
       </c>
       <c r="D156" s="5" t="n">
         <v>109.26</v>
       </c>
       <c r="E156" s="5" t="n">
-        <v>112.53</v>
+        <v>111.75</v>
       </c>
       <c r="F156" s="7" t="inlineStr"/>
     </row>
@@ -3883,13 +3883,13 @@
         <v>80.70999999999999</v>
       </c>
       <c r="C157" s="5" t="n">
-        <v>80.12</v>
+        <v>80.17</v>
       </c>
       <c r="D157" s="5" t="n">
         <v>105.45</v>
       </c>
       <c r="E157" s="5" t="n">
-        <v>104.68</v>
+        <v>104.75</v>
       </c>
       <c r="F157" s="7" t="inlineStr"/>
     </row>
@@ -3903,13 +3903,13 @@
         <v>76.56</v>
       </c>
       <c r="C158" s="5" t="n">
-        <v>79.66</v>
+        <v>79.65000000000001</v>
       </c>
       <c r="D158" s="5" t="n">
         <v>99.91</v>
       </c>
       <c r="E158" s="5" t="n">
-        <v>103.96</v>
+        <v>103.95</v>
       </c>
       <c r="F158" s="7" t="inlineStr"/>
     </row>
@@ -3923,13 +3923,13 @@
         <v>73.59</v>
       </c>
       <c r="C159" s="5" t="n">
-        <v>81.06</v>
+        <v>80.17</v>
       </c>
       <c r="D159" s="5" t="n">
         <v>95.92</v>
       </c>
       <c r="E159" s="5" t="n">
-        <v>105.66</v>
+        <v>104.5</v>
       </c>
       <c r="F159" s="7" t="inlineStr"/>
     </row>
@@ -3943,13 +3943,13 @@
         <v>44.85</v>
       </c>
       <c r="C160" s="5" t="n">
-        <v>50.01</v>
+        <v>49.51</v>
       </c>
       <c r="D160" s="5" t="n">
         <v>58.38</v>
       </c>
       <c r="E160" s="5" t="n">
-        <v>65.09</v>
+        <v>64.44</v>
       </c>
       <c r="F160" s="7" t="inlineStr"/>
     </row>
@@ -3963,13 +3963,13 @@
         <v>25.03</v>
       </c>
       <c r="C161" s="5" t="n">
-        <v>31.66</v>
+        <v>31.23</v>
       </c>
       <c r="D161" s="5" t="n">
         <v>32.53</v>
       </c>
       <c r="E161" s="5" t="n">
-        <v>41.15</v>
+        <v>40.59</v>
       </c>
       <c r="F161" s="7" t="inlineStr"/>
     </row>
@@ -3983,13 +3983,13 @@
         <v>60.86</v>
       </c>
       <c r="C162" s="5" t="n">
-        <v>75.48</v>
+        <v>70.7</v>
       </c>
       <c r="D162" s="5" t="n">
         <v>78.98999999999999</v>
       </c>
       <c r="E162" s="5" t="n">
-        <v>97.95999999999999</v>
+        <v>91.76000000000001</v>
       </c>
       <c r="F162" s="7" t="inlineStr"/>
     </row>
@@ -4003,13 +4003,13 @@
         <v>95.37</v>
       </c>
       <c r="C163" s="5" t="n">
-        <v>102.32</v>
+        <v>101.45</v>
       </c>
       <c r="D163" s="5" t="n">
         <v>123.56</v>
       </c>
       <c r="E163" s="5" t="n">
-        <v>132.57</v>
+        <v>131.44</v>
       </c>
       <c r="F163" s="7" t="inlineStr"/>
     </row>
@@ -4023,13 +4023,13 @@
         <v>85.59999999999999</v>
       </c>
       <c r="C164" s="5" t="n">
-        <v>88.54000000000001</v>
+        <v>88.25</v>
       </c>
       <c r="D164" s="5" t="n">
         <v>110.71</v>
       </c>
       <c r="E164" s="5" t="n">
-        <v>114.52</v>
+        <v>114.14</v>
       </c>
       <c r="F164" s="7" t="inlineStr"/>
     </row>
@@ -4043,13 +4043,13 @@
         <v>72.13</v>
       </c>
       <c r="C165" s="5" t="n">
-        <v>71.18000000000001</v>
+        <v>70.48</v>
       </c>
       <c r="D165" s="5" t="n">
         <v>93.13</v>
       </c>
       <c r="E165" s="5" t="n">
-        <v>91.90000000000001</v>
+        <v>91</v>
       </c>
       <c r="F165" s="7" t="inlineStr"/>
     </row>
@@ -4063,13 +4063,13 @@
         <v>147.91</v>
       </c>
       <c r="C166" s="5" t="n">
-        <v>163.88</v>
+        <v>163</v>
       </c>
       <c r="D166" s="5" t="n">
         <v>190.98</v>
       </c>
       <c r="E166" s="5" t="n">
-        <v>211.6</v>
+        <v>210.46</v>
       </c>
       <c r="F166" s="7" t="inlineStr"/>
     </row>
@@ -4083,13 +4083,13 @@
         <v>134.79</v>
       </c>
       <c r="C167" s="5" t="n">
-        <v>133.69</v>
+        <v>133.08</v>
       </c>
       <c r="D167" s="5" t="n">
         <v>174.05</v>
       </c>
       <c r="E167" s="5" t="n">
-        <v>172.63</v>
+        <v>171.84</v>
       </c>
       <c r="F167" s="7" t="inlineStr"/>
     </row>
@@ -4103,13 +4103,13 @@
         <v>123.43</v>
       </c>
       <c r="C168" s="5" t="n">
-        <v>115.58</v>
+        <v>114.79</v>
       </c>
       <c r="D168" s="5" t="n">
         <v>159.39</v>
       </c>
       <c r="E168" s="5" t="n">
-        <v>149.25</v>
+        <v>148.23</v>
       </c>
       <c r="F168" s="7" t="inlineStr"/>
     </row>
@@ -4123,13 +4123,13 @@
         <v>104.72</v>
       </c>
       <c r="C169" s="5" t="n">
-        <v>109.29</v>
+        <v>108.07</v>
       </c>
       <c r="D169" s="5" t="n">
         <v>134.96</v>
       </c>
       <c r="E169" s="5" t="n">
-        <v>140.85</v>
+        <v>139.28</v>
       </c>
       <c r="F169" s="7" t="inlineStr"/>
     </row>
@@ -4143,13 +4143,13 @@
         <v>92.55</v>
       </c>
       <c r="C170" s="5" t="n">
-        <v>102.33</v>
+        <v>101.97</v>
       </c>
       <c r="D170" s="5" t="n">
         <v>119.04</v>
       </c>
       <c r="E170" s="5" t="n">
-        <v>131.62</v>
+        <v>131.16</v>
       </c>
       <c r="F170" s="7" t="inlineStr"/>
     </row>
@@ -4163,13 +4163,13 @@
         <v>96.8</v>
       </c>
       <c r="C171" s="5" t="n">
-        <v>109.49</v>
+        <v>108.62</v>
       </c>
       <c r="D171" s="5" t="n">
         <v>124.26</v>
       </c>
       <c r="E171" s="5" t="n">
-        <v>140.55</v>
+        <v>139.43</v>
       </c>
       <c r="F171" s="7" t="inlineStr"/>
     </row>
@@ -4183,13 +4183,13 @@
         <v>74.77</v>
       </c>
       <c r="C172" s="5" t="n">
-        <v>89.78</v>
+        <v>89.16</v>
       </c>
       <c r="D172" s="5" t="n">
         <v>95.8</v>
       </c>
       <c r="E172" s="5" t="n">
-        <v>115.03</v>
+        <v>114.24</v>
       </c>
       <c r="F172" s="7" t="inlineStr"/>
     </row>
@@ -4203,13 +4203,13 @@
         <v>70.04000000000001</v>
       </c>
       <c r="C173" s="5" t="n">
-        <v>81.81</v>
+        <v>80.14</v>
       </c>
       <c r="D173" s="5" t="n">
         <v>89.56999999999999</v>
       </c>
       <c r="E173" s="5" t="n">
-        <v>104.62</v>
+        <v>102.49</v>
       </c>
       <c r="F173" s="7" t="inlineStr"/>
     </row>
@@ -4223,13 +4223,13 @@
         <v>57.62</v>
       </c>
       <c r="C174" s="5" t="n">
-        <v>63.98</v>
+        <v>63.58</v>
       </c>
       <c r="D174" s="5" t="n">
         <v>73.55</v>
       </c>
       <c r="E174" s="5" t="n">
-        <v>81.67</v>
+        <v>81.16</v>
       </c>
       <c r="F174" s="7" t="inlineStr"/>
     </row>
@@ -4243,13 +4243,13 @@
         <v>107.68</v>
       </c>
       <c r="C175" s="5" t="n">
-        <v>106.88</v>
+        <v>105.77</v>
       </c>
       <c r="D175" s="5" t="n">
         <v>137.14</v>
       </c>
       <c r="E175" s="5" t="n">
-        <v>136.12</v>
+        <v>134.71</v>
       </c>
       <c r="F175" s="7" t="inlineStr"/>
     </row>
@@ -4263,13 +4263,13 @@
         <v>68.29000000000001</v>
       </c>
       <c r="C176" s="5" t="n">
-        <v>77.56</v>
+        <v>76.48</v>
       </c>
       <c r="D176" s="5" t="n">
         <v>86.77</v>
       </c>
       <c r="E176" s="5" t="n">
-        <v>98.55</v>
+        <v>97.18000000000001</v>
       </c>
       <c r="F176" s="7" t="inlineStr"/>
     </row>
@@ -4283,13 +4283,13 @@
         <v>52.18</v>
       </c>
       <c r="C177" s="5" t="n">
-        <v>50.23</v>
+        <v>49.82</v>
       </c>
       <c r="D177" s="5" t="n">
         <v>66.15000000000001</v>
       </c>
       <c r="E177" s="5" t="n">
-        <v>63.68</v>
+        <v>63.16</v>
       </c>
       <c r="F177" s="7" t="inlineStr"/>
     </row>
@@ -4303,13 +4303,13 @@
         <v>56.84</v>
       </c>
       <c r="C178" s="5" t="n">
-        <v>49.85</v>
+        <v>49.53</v>
       </c>
       <c r="D178" s="5" t="n">
         <v>71.97</v>
       </c>
       <c r="E178" s="5" t="n">
-        <v>63.12</v>
+        <v>62.72</v>
       </c>
       <c r="F178" s="7" t="inlineStr"/>
     </row>
@@ -4323,13 +4323,13 @@
         <v>39.1</v>
       </c>
       <c r="C179" s="5" t="n">
-        <v>38.9</v>
+        <v>38.95</v>
       </c>
       <c r="D179" s="5" t="n">
         <v>49.45</v>
       </c>
       <c r="E179" s="5" t="n">
-        <v>49.19</v>
+        <v>49.26</v>
       </c>
       <c r="F179" s="7" t="inlineStr"/>
     </row>
@@ -4343,13 +4343,13 @@
         <v>37.37</v>
       </c>
       <c r="C180" s="5" t="n">
-        <v>35.52</v>
+        <v>34.97</v>
       </c>
       <c r="D180" s="5" t="n">
         <v>47.2</v>
       </c>
       <c r="E180" s="5" t="n">
-        <v>44.86</v>
+        <v>44.17</v>
       </c>
       <c r="F180" s="7" t="inlineStr"/>
     </row>
@@ -4363,13 +4363,13 @@
         <v>23.37</v>
       </c>
       <c r="C181" s="5" t="n">
-        <v>24.48</v>
+        <v>24.19</v>
       </c>
       <c r="D181" s="5" t="n">
         <v>29.71</v>
       </c>
       <c r="E181" s="5" t="n">
-        <v>31.12</v>
+        <v>30.75</v>
       </c>
       <c r="F181" s="7" t="inlineStr"/>
     </row>
@@ -4383,13 +4383,13 @@
         <v>34.77</v>
       </c>
       <c r="C182" s="5" t="n">
-        <v>41.19</v>
+        <v>40.61</v>
       </c>
       <c r="D182" s="5" t="n">
         <v>44.49</v>
       </c>
       <c r="E182" s="5" t="n">
-        <v>52.7</v>
+        <v>51.96</v>
       </c>
       <c r="F182" s="7" t="inlineStr"/>
     </row>
@@ -4403,13 +4403,13 @@
         <v>36.41</v>
       </c>
       <c r="C183" s="5" t="n">
-        <v>39.42</v>
+        <v>39.02</v>
       </c>
       <c r="D183" s="5" t="n">
         <v>46.89</v>
       </c>
       <c r="E183" s="5" t="n">
-        <v>50.77</v>
+        <v>50.25</v>
       </c>
       <c r="F183" s="7" t="inlineStr"/>
     </row>
@@ -4423,13 +4423,13 @@
         <v>56.6</v>
       </c>
       <c r="C184" s="5" t="n">
-        <v>57.55</v>
+        <v>57.29</v>
       </c>
       <c r="D184" s="5" t="n">
         <v>72.52</v>
       </c>
       <c r="E184" s="5" t="n">
-        <v>73.73999999999999</v>
+        <v>73.40000000000001</v>
       </c>
       <c r="F184" s="7" t="inlineStr"/>
     </row>
@@ -4443,13 +4443,13 @@
         <v>55.75</v>
       </c>
       <c r="C185" s="5" t="n">
-        <v>56.78</v>
+        <v>56.57</v>
       </c>
       <c r="D185" s="5" t="n">
         <v>71.06999999999999</v>
       </c>
       <c r="E185" s="5" t="n">
-        <v>72.38</v>
+        <v>72.11</v>
       </c>
       <c r="F185" s="7" t="inlineStr"/>
     </row>
@@ -4463,13 +4463,13 @@
         <v>37.52</v>
       </c>
       <c r="C186" s="5" t="n">
-        <v>39.19</v>
+        <v>38.94</v>
       </c>
       <c r="D186" s="5" t="n">
         <v>47.58</v>
       </c>
       <c r="E186" s="5" t="n">
-        <v>49.7</v>
+        <v>49.39</v>
       </c>
       <c r="F186" s="7" t="inlineStr"/>
     </row>
@@ -4483,13 +4483,13 @@
         <v>41.51</v>
       </c>
       <c r="C187" s="5" t="n">
-        <v>42.32</v>
+        <v>37.37</v>
       </c>
       <c r="D187" s="5" t="n">
         <v>52.49</v>
       </c>
       <c r="E187" s="5" t="n">
-        <v>53.51</v>
+        <v>47.25</v>
       </c>
       <c r="F187" s="7" t="inlineStr"/>
     </row>
@@ -4503,13 +4503,13 @@
         <v>59.37</v>
       </c>
       <c r="C188" s="5" t="n">
-        <v>57.44</v>
+        <v>57.08</v>
       </c>
       <c r="D188" s="5" t="n">
         <v>74.84</v>
       </c>
       <c r="E188" s="5" t="n">
-        <v>72.41</v>
+        <v>71.95999999999999</v>
       </c>
       <c r="F188" s="7" t="inlineStr"/>
     </row>
@@ -4523,13 +4523,13 @@
         <v>36.86</v>
       </c>
       <c r="C189" s="5" t="n">
-        <v>43.49</v>
+        <v>43.26</v>
       </c>
       <c r="D189" s="5" t="n">
         <v>46.33</v>
       </c>
       <c r="E189" s="5" t="n">
-        <v>54.66</v>
+        <v>54.37</v>
       </c>
       <c r="F189" s="7" t="inlineStr"/>
     </row>
@@ -4543,13 +4543,13 @@
         <v>37.81</v>
       </c>
       <c r="C190" s="5" t="n">
-        <v>40.16</v>
+        <v>40.03</v>
       </c>
       <c r="D190" s="5" t="n">
         <v>47.43</v>
       </c>
       <c r="E190" s="5" t="n">
-        <v>50.38</v>
+        <v>50.22</v>
       </c>
       <c r="F190" s="7" t="inlineStr"/>
     </row>
@@ -4563,13 +4563,13 @@
         <v>31.99</v>
       </c>
       <c r="C191" s="5" t="n">
-        <v>36.94</v>
+        <v>36.7</v>
       </c>
       <c r="D191" s="5" t="n">
         <v>40.05</v>
       </c>
       <c r="E191" s="5" t="n">
-        <v>46.25</v>
+        <v>45.95</v>
       </c>
       <c r="F191" s="7" t="inlineStr"/>
     </row>
@@ -4583,13 +4583,13 @@
         <v>30.78</v>
       </c>
       <c r="C192" s="5" t="n">
-        <v>31.99</v>
+        <v>31.5</v>
       </c>
       <c r="D192" s="5" t="n">
         <v>38.46</v>
       </c>
       <c r="E192" s="5" t="n">
-        <v>39.98</v>
+        <v>39.36</v>
       </c>
       <c r="F192" s="7" t="inlineStr"/>
     </row>
@@ -4603,13 +4603,13 @@
         <v>25.34</v>
       </c>
       <c r="C193" s="5" t="n">
-        <v>28.96</v>
+        <v>28.45</v>
       </c>
       <c r="D193" s="5" t="n">
         <v>31.59</v>
       </c>
       <c r="E193" s="5" t="n">
-        <v>36.1</v>
+        <v>35.47</v>
       </c>
       <c r="F193" s="7" t="inlineStr"/>
     </row>
@@ -4623,13 +4623,13 @@
         <v>41.25</v>
       </c>
       <c r="C194" s="5" t="n">
-        <v>45.01</v>
+        <v>44.32</v>
       </c>
       <c r="D194" s="5" t="n">
         <v>51.3</v>
       </c>
       <c r="E194" s="5" t="n">
-        <v>55.97</v>
+        <v>55.12</v>
       </c>
       <c r="F194" s="7" t="inlineStr"/>
     </row>
@@ -4643,13 +4643,13 @@
         <v>68.88</v>
       </c>
       <c r="C195" s="5" t="n">
-        <v>77.88</v>
+        <v>77.62</v>
       </c>
       <c r="D195" s="5" t="n">
         <v>85.45</v>
       </c>
       <c r="E195" s="5" t="n">
-        <v>96.62</v>
+        <v>96.29000000000001</v>
       </c>
       <c r="F195" s="7" t="inlineStr"/>
     </row>
@@ -4663,13 +4663,13 @@
         <v>38.15</v>
       </c>
       <c r="C196" s="5" t="n">
-        <v>43.06</v>
+        <v>42.75</v>
       </c>
       <c r="D196" s="5" t="n">
         <v>47.19</v>
       </c>
       <c r="E196" s="5" t="n">
-        <v>53.27</v>
+        <v>52.88</v>
       </c>
       <c r="F196" s="7" t="inlineStr"/>
     </row>
@@ -4683,13 +4683,13 @@
         <v>21.46</v>
       </c>
       <c r="C197" s="5" t="n">
-        <v>25.45</v>
+        <v>24.96</v>
       </c>
       <c r="D197" s="5" t="n">
         <v>26.47</v>
       </c>
       <c r="E197" s="5" t="n">
-        <v>31.39</v>
+        <v>30.79</v>
       </c>
       <c r="F197" s="7" t="inlineStr"/>
     </row>
@@ -4703,13 +4703,13 @@
         <v>16.52</v>
       </c>
       <c r="C198" s="5" t="n">
-        <v>22.15</v>
+        <v>21.88</v>
       </c>
       <c r="D198" s="5" t="n">
         <v>20.32</v>
       </c>
       <c r="E198" s="5" t="n">
-        <v>27.25</v>
+        <v>26.92</v>
       </c>
       <c r="F198" s="7" t="inlineStr"/>
     </row>
@@ -4723,13 +4723,13 @@
         <v>9.380000000000001</v>
       </c>
       <c r="C199" s="5" t="n">
-        <v>9.77</v>
+        <v>9.68</v>
       </c>
       <c r="D199" s="5" t="n">
         <v>11.49</v>
       </c>
       <c r="E199" s="5" t="n">
-        <v>11.97</v>
+        <v>11.86</v>
       </c>
       <c r="F199" s="7" t="inlineStr"/>
     </row>
@@ -4743,13 +4743,13 @@
         <v>31.76</v>
       </c>
       <c r="C200" s="5" t="n">
-        <v>33.57</v>
+        <v>33.48</v>
       </c>
       <c r="D200" s="5" t="n">
         <v>38.74</v>
       </c>
       <c r="E200" s="5" t="n">
-        <v>40.95</v>
+        <v>40.84</v>
       </c>
       <c r="F200" s="7" t="inlineStr"/>
     </row>
@@ -4763,13 +4763,13 @@
         <v>49.85</v>
       </c>
       <c r="C201" s="5" t="n">
-        <v>50.76</v>
+        <v>50.7</v>
       </c>
       <c r="D201" s="5" t="n">
         <v>60.55</v>
       </c>
       <c r="E201" s="5" t="n">
-        <v>61.66</v>
+        <v>61.58</v>
       </c>
       <c r="F201" s="7" t="inlineStr"/>
     </row>
@@ -4783,13 +4783,13 @@
         <v>62.54</v>
       </c>
       <c r="C202" s="5" t="n">
-        <v>66.84999999999999</v>
+        <v>66.73999999999999</v>
       </c>
       <c r="D202" s="5" t="n">
         <v>75.42</v>
       </c>
       <c r="E202" s="5" t="n">
-        <v>80.62</v>
+        <v>80.48999999999999</v>
       </c>
       <c r="F202" s="7" t="inlineStr"/>
     </row>
@@ -4803,13 +4803,13 @@
         <v>72.20999999999999</v>
       </c>
       <c r="C203" s="5" t="n">
-        <v>78.13</v>
+        <v>78.06999999999999</v>
       </c>
       <c r="D203" s="5" t="n">
         <v>86.45999999999999</v>
       </c>
       <c r="E203" s="5" t="n">
-        <v>93.55</v>
+        <v>93.48</v>
       </c>
       <c r="F203" s="7" t="inlineStr"/>
     </row>
@@ -4823,13 +4823,13 @@
         <v>74.83</v>
       </c>
       <c r="C204" s="5" t="n">
-        <v>78.79000000000001</v>
+        <v>78.65000000000001</v>
       </c>
       <c r="D204" s="5" t="n">
         <v>88.97</v>
       </c>
       <c r="E204" s="5" t="n">
-        <v>93.68000000000001</v>
+        <v>93.51000000000001</v>
       </c>
       <c r="F204" s="7" t="inlineStr"/>
     </row>
@@ -4843,13 +4843,13 @@
         <v>141.27</v>
       </c>
       <c r="C205" s="5" t="n">
-        <v>165</v>
+        <v>164.79</v>
       </c>
       <c r="D205" s="5" t="n">
         <v>166.97</v>
       </c>
       <c r="E205" s="5" t="n">
-        <v>195.02</v>
+        <v>194.77</v>
       </c>
       <c r="F205" s="7" t="inlineStr"/>
     </row>
@@ -4863,13 +4863,13 @@
         <v>217.19</v>
       </c>
       <c r="C206" s="5" t="n">
-        <v>241.96</v>
+        <v>241.85</v>
       </c>
       <c r="D206" s="5" t="n">
         <v>255.19</v>
       </c>
       <c r="E206" s="5" t="n">
-        <v>284.29</v>
+        <v>284.16</v>
       </c>
       <c r="F206" s="7" t="inlineStr"/>
     </row>
@@ -4883,13 +4883,13 @@
         <v>286.75</v>
       </c>
       <c r="C207" s="5" t="n">
-        <v>382.49</v>
+        <v>382.13</v>
       </c>
       <c r="D207" s="5" t="n">
         <v>334.94</v>
       </c>
       <c r="E207" s="5" t="n">
-        <v>446.77</v>
+        <v>446.35</v>
       </c>
       <c r="F207" s="7" t="inlineStr"/>
     </row>
@@ -4903,13 +4903,13 @@
         <v>322.84</v>
       </c>
       <c r="C208" s="5" t="n">
-        <v>366.3</v>
+        <v>366</v>
       </c>
       <c r="D208" s="5" t="n">
         <v>374.8</v>
       </c>
       <c r="E208" s="5" t="n">
-        <v>425.25</v>
+        <v>424.9</v>
       </c>
       <c r="F208" s="7" t="inlineStr"/>
     </row>
@@ -4923,13 +4923,13 @@
         <v>149.51</v>
       </c>
       <c r="C209" s="5" t="n">
-        <v>169.69</v>
+        <v>169.02</v>
       </c>
       <c r="D209" s="5" t="n">
         <v>172.52</v>
       </c>
       <c r="E209" s="5" t="n">
-        <v>195.81</v>
+        <v>195.03</v>
       </c>
       <c r="F209" s="7" t="inlineStr"/>
     </row>
@@ -4943,13 +4943,13 @@
         <v>132.74</v>
       </c>
       <c r="C210" s="5" t="n">
-        <v>150.78</v>
+        <v>150.51</v>
       </c>
       <c r="D210" s="5" t="n">
         <v>152.25</v>
       </c>
       <c r="E210" s="5" t="n">
-        <v>172.94</v>
+        <v>172.63</v>
       </c>
       <c r="F210" s="7" t="inlineStr"/>
     </row>
@@ -4963,13 +4963,13 @@
         <v>122</v>
       </c>
       <c r="C211" s="5" t="n">
-        <v>126.75</v>
+        <v>126.49</v>
       </c>
       <c r="D211" s="5" t="n">
         <v>139.07</v>
       </c>
       <c r="E211" s="5" t="n">
-        <v>144.49</v>
+        <v>144.19</v>
       </c>
       <c r="F211" s="7" t="inlineStr"/>
     </row>
@@ -4983,13 +4983,13 @@
         <v>100.98</v>
       </c>
       <c r="C212" s="5" t="n">
-        <v>114.81</v>
+        <v>112.35</v>
       </c>
       <c r="D212" s="5" t="n">
         <v>114.41</v>
       </c>
       <c r="E212" s="5" t="n">
-        <v>130.08</v>
+        <v>127.29</v>
       </c>
       <c r="F212" s="7" t="inlineStr"/>
     </row>
@@ -5023,13 +5023,13 @@
         <v>86.86</v>
       </c>
       <c r="C214" s="5" t="n">
-        <v>81.12</v>
+        <v>81.09</v>
       </c>
       <c r="D214" s="5" t="n">
         <v>97.38</v>
       </c>
       <c r="E214" s="5" t="n">
-        <v>90.94</v>
+        <v>90.91</v>
       </c>
       <c r="F214" s="7" t="inlineStr"/>
     </row>
@@ -5043,13 +5043,13 @@
         <v>81.53</v>
       </c>
       <c r="C215" s="5" t="n">
-        <v>76.66</v>
+        <v>76.56999999999999</v>
       </c>
       <c r="D215" s="5" t="n">
         <v>90.98999999999999</v>
       </c>
       <c r="E215" s="5" t="n">
-        <v>85.56</v>
+        <v>85.45999999999999</v>
       </c>
       <c r="F215" s="7" t="inlineStr"/>
     </row>
@@ -5063,13 +5063,13 @@
         <v>72.34999999999999</v>
       </c>
       <c r="C216" s="5" t="n">
-        <v>68.13</v>
+        <v>68.09999999999999</v>
       </c>
       <c r="D216" s="5" t="n">
         <v>80.39</v>
       </c>
       <c r="E216" s="5" t="n">
-        <v>75.7</v>
+        <v>75.67</v>
       </c>
       <c r="F216" s="7" t="inlineStr"/>
     </row>
@@ -5083,13 +5083,13 @@
         <v>70.03</v>
       </c>
       <c r="C217" s="5" t="n">
-        <v>70.95</v>
+        <v>70.91</v>
       </c>
       <c r="D217" s="5" t="n">
         <v>77.59</v>
       </c>
       <c r="E217" s="5" t="n">
-        <v>78.61</v>
+        <v>78.56</v>
       </c>
       <c r="F217" s="7" t="inlineStr"/>
     </row>
@@ -5103,13 +5103,13 @@
         <v>84.16</v>
       </c>
       <c r="C218" s="5" t="n">
-        <v>86.54000000000001</v>
+        <v>86.34999999999999</v>
       </c>
       <c r="D218" s="5" t="n">
         <v>92.98</v>
       </c>
       <c r="E218" s="5" t="n">
-        <v>95.61</v>
+        <v>95.40000000000001</v>
       </c>
       <c r="F218" s="7" t="inlineStr"/>
     </row>
@@ -5123,13 +5123,13 @@
         <v>38.04</v>
       </c>
       <c r="C219" s="5" t="n">
-        <v>52.33</v>
+        <v>52.09</v>
       </c>
       <c r="D219" s="5" t="n">
         <v>41.91</v>
       </c>
       <c r="E219" s="5" t="n">
-        <v>57.65</v>
+        <v>57.38</v>
       </c>
       <c r="F219" s="7" t="inlineStr"/>
     </row>
@@ -5143,13 +5143,13 @@
         <v>23.32</v>
       </c>
       <c r="C220" s="5" t="n">
-        <v>32.72</v>
+        <v>32.62</v>
       </c>
       <c r="D220" s="5" t="n">
         <v>25.59</v>
       </c>
       <c r="E220" s="5" t="n">
-        <v>35.91</v>
+        <v>35.8</v>
       </c>
       <c r="F220" s="7" t="inlineStr"/>
     </row>
@@ -5163,13 +5163,13 @@
         <v>37.65</v>
       </c>
       <c r="C221" s="5" t="n">
-        <v>37.93</v>
+        <v>37.77</v>
       </c>
       <c r="D221" s="5" t="n">
         <v>41.16</v>
       </c>
       <c r="E221" s="5" t="n">
-        <v>41.47</v>
+        <v>41.29</v>
       </c>
       <c r="F221" s="7" t="inlineStr"/>
     </row>
@@ -5183,13 +5183,13 @@
         <v>26.71</v>
       </c>
       <c r="C222" s="5" t="n">
-        <v>24.88</v>
+        <v>24.86</v>
       </c>
       <c r="D222" s="5" t="n">
         <v>29.09</v>
       </c>
       <c r="E222" s="5" t="n">
-        <v>27.1</v>
+        <v>27.08</v>
       </c>
       <c r="F222" s="7" t="inlineStr"/>
     </row>
@@ -5223,13 +5223,13 @@
         <v>59.97</v>
       </c>
       <c r="C224" s="5" t="n">
-        <v>57.48</v>
+        <v>57.49</v>
       </c>
       <c r="D224" s="5" t="n">
         <v>65.04000000000001</v>
       </c>
       <c r="E224" s="5" t="n">
-        <v>62.34</v>
+        <v>62.35</v>
       </c>
       <c r="F224" s="7" t="inlineStr"/>
     </row>
@@ -5243,13 +5243,13 @@
         <v>52.09</v>
       </c>
       <c r="C225" s="5" t="n">
-        <v>49.05</v>
+        <v>49.09</v>
       </c>
       <c r="D225" s="5" t="n">
         <v>56.38</v>
       </c>
       <c r="E225" s="5" t="n">
-        <v>53.09</v>
+        <v>53.13</v>
       </c>
       <c r="F225" s="7" t="inlineStr"/>
     </row>
@@ -5263,13 +5263,13 @@
         <v>50.12</v>
       </c>
       <c r="C226" s="5" t="n">
-        <v>49.55</v>
+        <v>49.62</v>
       </c>
       <c r="D226" s="5" t="n">
         <v>54.08</v>
       </c>
       <c r="E226" s="5" t="n">
-        <v>53.46</v>
+        <v>53.54</v>
       </c>
       <c r="F226" s="7" t="inlineStr"/>
     </row>
@@ -5283,13 +5283,13 @@
         <v>81.86</v>
       </c>
       <c r="C227" s="5" t="n">
-        <v>110.19</v>
+        <v>110.18</v>
       </c>
       <c r="D227" s="5" t="n">
         <v>88.05</v>
       </c>
       <c r="E227" s="5" t="n">
-        <v>118.52</v>
+        <v>118.51</v>
       </c>
       <c r="F227" s="7" t="inlineStr"/>
     </row>
@@ -5303,13 +5303,13 @@
         <v>69.65000000000001</v>
       </c>
       <c r="C228" s="5" t="n">
-        <v>67.51000000000001</v>
+        <v>67.43000000000001</v>
       </c>
       <c r="D228" s="5" t="n">
         <v>74.69</v>
       </c>
       <c r="E228" s="5" t="n">
-        <v>72.39</v>
+        <v>72.31</v>
       </c>
       <c r="F228" s="7" t="inlineStr"/>
     </row>
@@ -5323,13 +5323,13 @@
         <v>73.34999999999999</v>
       </c>
       <c r="C229" s="5" t="n">
-        <v>70.58</v>
+        <v>70.53</v>
       </c>
       <c r="D229" s="5" t="n">
         <v>78.38</v>
       </c>
       <c r="E229" s="5" t="n">
-        <v>75.42</v>
+        <v>75.37</v>
       </c>
       <c r="F229" s="7" t="inlineStr"/>
     </row>
@@ -5343,13 +5343,13 @@
         <v>141.03</v>
       </c>
       <c r="C230" s="5" t="n">
-        <v>145.64</v>
+        <v>145.36</v>
       </c>
       <c r="D230" s="5" t="n">
         <v>150.18</v>
       </c>
       <c r="E230" s="5" t="n">
-        <v>155.09</v>
+        <v>154.79</v>
       </c>
       <c r="F230" s="7" t="inlineStr"/>
     </row>
@@ -5363,13 +5363,13 @@
         <v>178.25</v>
       </c>
       <c r="C231" s="5" t="n">
-        <v>212.93</v>
+        <v>212.7</v>
       </c>
       <c r="D231" s="5" t="n">
         <v>189.16</v>
       </c>
       <c r="E231" s="5" t="n">
-        <v>225.96</v>
+        <v>225.72</v>
       </c>
       <c r="F231" s="7" t="inlineStr"/>
     </row>
@@ -5383,13 +5383,13 @@
         <v>180.76</v>
       </c>
       <c r="C232" s="5" t="n">
-        <v>215.63</v>
+        <v>215.33</v>
       </c>
       <c r="D232" s="5" t="n">
         <v>191.68</v>
       </c>
       <c r="E232" s="5" t="n">
-        <v>228.66</v>
+        <v>228.34</v>
       </c>
       <c r="F232" s="7" t="inlineStr"/>
     </row>
@@ -5403,13 +5403,13 @@
         <v>128.69</v>
       </c>
       <c r="C233" s="5" t="n">
-        <v>156.24</v>
+        <v>155.78</v>
       </c>
       <c r="D233" s="5" t="n">
         <v>136.37</v>
       </c>
       <c r="E233" s="5" t="n">
-        <v>165.56</v>
+        <v>165.07</v>
       </c>
       <c r="F233" s="7" t="inlineStr"/>
     </row>
@@ -5423,13 +5423,13 @@
         <v>22.51</v>
       </c>
       <c r="C234" s="5" t="n">
-        <v>31.25</v>
+        <v>31.21</v>
       </c>
       <c r="D234" s="5" t="n">
         <v>23.84</v>
       </c>
       <c r="E234" s="5" t="n">
-        <v>33.09</v>
+        <v>33.05</v>
       </c>
       <c r="F234" s="7" t="inlineStr"/>
     </row>
@@ -5443,13 +5443,13 @@
         <v>49.8</v>
       </c>
       <c r="C235" s="5" t="n">
-        <v>52.52</v>
+        <v>52.54</v>
       </c>
       <c r="D235" s="5" t="n">
         <v>52.7</v>
       </c>
       <c r="E235" s="5" t="n">
-        <v>55.58</v>
+        <v>55.6</v>
       </c>
       <c r="F235" s="7" t="inlineStr"/>
     </row>
@@ -5463,13 +5463,13 @@
         <v>95.86</v>
       </c>
       <c r="C236" s="5" t="n">
-        <v>96.58</v>
+        <v>96.67</v>
       </c>
       <c r="D236" s="5" t="n">
         <v>101.37</v>
       </c>
       <c r="E236" s="5" t="n">
-        <v>102.13</v>
+        <v>102.23</v>
       </c>
       <c r="F236" s="7" t="inlineStr"/>
     </row>
@@ -5483,13 +5483,13 @@
         <v>76.11</v>
       </c>
       <c r="C237" s="5" t="n">
-        <v>68.48</v>
+        <v>68.69</v>
       </c>
       <c r="D237" s="5" t="n">
         <v>80.43000000000001</v>
       </c>
       <c r="E237" s="5" t="n">
-        <v>72.37</v>
+        <v>72.59</v>
       </c>
       <c r="F237" s="7" t="inlineStr"/>
     </row>
@@ -5503,13 +5503,13 @@
         <v>113.63</v>
       </c>
       <c r="C238" s="5" t="n">
-        <v>109.08</v>
+        <v>109.16</v>
       </c>
       <c r="D238" s="5" t="n">
         <v>119.72</v>
       </c>
       <c r="E238" s="5" t="n">
-        <v>114.92</v>
+        <v>115.01</v>
       </c>
       <c r="F238" s="7" t="inlineStr"/>
     </row>
@@ -5523,13 +5523,13 @@
         <v>121.69</v>
       </c>
       <c r="C239" s="5" t="n">
-        <v>125.01</v>
+        <v>124.99</v>
       </c>
       <c r="D239" s="5" t="n">
         <v>127.82</v>
       </c>
       <c r="E239" s="5" t="n">
-        <v>131.31</v>
+        <v>131.29</v>
       </c>
       <c r="F239" s="7" t="inlineStr"/>
     </row>
@@ -5543,13 +5543,13 @@
         <v>100.04</v>
       </c>
       <c r="C240" s="5" t="n">
-        <v>100.83</v>
+        <v>100.72</v>
       </c>
       <c r="D240" s="5" t="n">
         <v>104.76</v>
       </c>
       <c r="E240" s="5" t="n">
-        <v>105.59</v>
+        <v>105.47</v>
       </c>
       <c r="F240" s="7" t="inlineStr"/>
     </row>
@@ -5563,13 +5563,13 @@
         <v>100.53</v>
       </c>
       <c r="C241" s="5" t="n">
-        <v>98.58</v>
+        <v>98.45999999999999</v>
       </c>
       <c r="D241" s="5" t="n">
         <v>105.01</v>
       </c>
       <c r="E241" s="5" t="n">
-        <v>102.98</v>
+        <v>102.85</v>
       </c>
       <c r="F241" s="7" t="inlineStr"/>
     </row>
@@ -5583,13 +5583,13 @@
         <v>103.39</v>
       </c>
       <c r="C242" s="5" t="n">
-        <v>113.37</v>
+        <v>113.21</v>
       </c>
       <c r="D242" s="5" t="n">
         <v>107.73</v>
       </c>
       <c r="E242" s="5" t="n">
-        <v>118.13</v>
+        <v>117.96</v>
       </c>
       <c r="F242" s="7" t="inlineStr"/>
     </row>
@@ -5603,13 +5603,13 @@
         <v>219.34</v>
       </c>
       <c r="C243" s="5" t="n">
-        <v>327.99</v>
+        <v>327.6</v>
       </c>
       <c r="D243" s="5" t="n">
         <v>227.99</v>
       </c>
       <c r="E243" s="5" t="n">
-        <v>340.92</v>
+        <v>340.51</v>
       </c>
       <c r="F243" s="7" t="inlineStr"/>
     </row>
@@ -5623,13 +5623,13 @@
         <v>117.85</v>
       </c>
       <c r="C244" s="5" t="n">
-        <v>130.45</v>
+        <v>130.22</v>
       </c>
       <c r="D244" s="5" t="n">
         <v>121.96</v>
       </c>
       <c r="E244" s="5" t="n">
-        <v>135</v>
+        <v>134.76</v>
       </c>
       <c r="F244" s="7" t="inlineStr"/>
     </row>
@@ -5643,13 +5643,13 @@
         <v>125.22</v>
       </c>
       <c r="C245" s="5" t="n">
-        <v>133.56</v>
+        <v>133.43</v>
       </c>
       <c r="D245" s="5" t="n">
         <v>129.02</v>
       </c>
       <c r="E245" s="5" t="n">
-        <v>137.61</v>
+        <v>137.48</v>
       </c>
       <c r="F245" s="7" t="inlineStr"/>
     </row>
@@ -5663,13 +5663,13 @@
         <v>28.63</v>
       </c>
       <c r="C246" s="5" t="n">
-        <v>36.24</v>
+        <v>36.13</v>
       </c>
       <c r="D246" s="5" t="n">
         <v>29.37</v>
       </c>
       <c r="E246" s="5" t="n">
-        <v>37.18</v>
+        <v>37.06</v>
       </c>
       <c r="F246" s="7" t="inlineStr"/>
     </row>
@@ -5703,13 +5703,13 @@
         <v>40.51</v>
       </c>
       <c r="C248" s="5" t="n">
-        <v>34.34</v>
+        <v>34.33</v>
       </c>
       <c r="D248" s="5" t="n">
         <v>41.39</v>
       </c>
       <c r="E248" s="5" t="n">
-        <v>35.09</v>
+        <v>35.08</v>
       </c>
       <c r="F248" s="7" t="inlineStr"/>
     </row>
@@ -5723,13 +5723,13 @@
         <v>59.34</v>
       </c>
       <c r="C249" s="5" t="n">
-        <v>55.6</v>
+        <v>55.59</v>
       </c>
       <c r="D249" s="5" t="n">
         <v>60.52</v>
       </c>
       <c r="E249" s="5" t="n">
-        <v>56.7</v>
+        <v>56.69</v>
       </c>
       <c r="F249" s="7" t="inlineStr"/>
     </row>
@@ -5743,13 +5743,13 @@
         <v>100.93</v>
       </c>
       <c r="C250" s="5" t="n">
-        <v>114.88</v>
+        <v>114.92</v>
       </c>
       <c r="D250" s="5" t="n">
         <v>102.46</v>
       </c>
       <c r="E250" s="5" t="n">
-        <v>116.62</v>
+        <v>116.66</v>
       </c>
       <c r="F250" s="7" t="inlineStr"/>
     </row>
@@ -5763,13 +5763,13 @@
         <v>90.28</v>
       </c>
       <c r="C251" s="5" t="n">
-        <v>87.56</v>
+        <v>87.54000000000001</v>
       </c>
       <c r="D251" s="5" t="n">
         <v>91.23</v>
       </c>
       <c r="E251" s="5" t="n">
-        <v>88.48999999999999</v>
+        <v>88.47</v>
       </c>
       <c r="F251" s="7" t="inlineStr"/>
     </row>
@@ -5783,13 +5783,13 @@
         <v>91.04000000000001</v>
       </c>
       <c r="C252" s="5" t="n">
-        <v>90.94</v>
+        <v>90.92</v>
       </c>
       <c r="D252" s="5" t="n">
         <v>91.59</v>
       </c>
       <c r="E252" s="5" t="n">
-        <v>91.48999999999999</v>
+        <v>91.47</v>
       </c>
       <c r="F252" s="7" t="inlineStr"/>
     </row>
@@ -5803,13 +5803,13 @@
         <v>85.23999999999999</v>
       </c>
       <c r="C253" s="5" t="n">
-        <v>87.34</v>
+        <v>87.29000000000001</v>
       </c>
       <c r="D253" s="5" t="n">
         <v>85.58</v>
       </c>
       <c r="E253" s="5" t="n">
-        <v>87.69</v>
+        <v>87.64</v>
       </c>
       <c r="F253" s="7" t="inlineStr"/>
     </row>
@@ -5823,13 +5823,13 @@
         <v>96.14</v>
       </c>
       <c r="C254" s="5" t="n">
-        <v>100.08</v>
+        <v>100.05</v>
       </c>
       <c r="D254" s="5" t="n">
         <v>96.33</v>
       </c>
       <c r="E254" s="5" t="n">
-        <v>100.28</v>
+        <v>100.25</v>
       </c>
       <c r="F254" s="7" t="inlineStr"/>
     </row>
@@ -5843,13 +5843,13 @@
         <v>76.83</v>
       </c>
       <c r="C255" s="5" t="n">
-        <v>81.73</v>
+        <v>81.67</v>
       </c>
       <c r="D255" s="5" t="n">
         <v>76.83</v>
       </c>
       <c r="E255" s="5" t="n">
-        <v>81.73</v>
+        <v>81.67</v>
       </c>
       <c r="F255" s="7" t="inlineStr"/>
     </row>
@@ -5863,13 +5863,13 @@
         <v>71.04000000000001</v>
       </c>
       <c r="C256" s="5" t="n">
-        <v>93.83</v>
+        <v>93.72</v>
       </c>
       <c r="D256" s="5" t="n">
         <v>71.04000000000001</v>
       </c>
       <c r="E256" s="5" t="n">
-        <v>93.83</v>
+        <v>93.72</v>
       </c>
       <c r="F256" s="7" t="inlineStr"/>
     </row>
@@ -5883,13 +5883,13 @@
         <v>57.95</v>
       </c>
       <c r="C257" s="5" t="n">
-        <v>65.81</v>
+        <v>65.73</v>
       </c>
       <c r="D257" s="5" t="n">
         <v>57.95</v>
       </c>
       <c r="E257" s="5" t="n">
-        <v>65.81</v>
+        <v>65.73</v>
       </c>
       <c r="F257" s="7" t="inlineStr"/>
     </row>
@@ -5903,13 +5903,13 @@
         <v>38.86</v>
       </c>
       <c r="C258" s="5" t="n">
-        <v>37.8</v>
+        <v>37.87</v>
       </c>
       <c r="D258" s="5" t="n">
         <v>38.86</v>
       </c>
       <c r="E258" s="5" t="n">
-        <v>37.8</v>
+        <v>37.87</v>
       </c>
       <c r="F258" s="7" t="inlineStr"/>
     </row>
@@ -5971,13 +5971,13 @@
         <v>306.87</v>
       </c>
       <c r="C2" s="5" t="n">
-        <v>392.08</v>
+        <v>361.77</v>
       </c>
       <c r="D2" s="5" t="n">
         <v>548.53</v>
       </c>
       <c r="E2" s="5" t="n">
-        <v>700.84</v>
+        <v>646.66</v>
       </c>
     </row>
     <row r="3">
@@ -6009,13 +6009,13 @@
         <v>112.34</v>
       </c>
       <c r="C4" s="5" t="n">
-        <v>115.44</v>
+        <v>115.77</v>
       </c>
       <c r="D4" s="5" t="n">
         <v>199.75</v>
       </c>
       <c r="E4" s="5" t="n">
-        <v>205.26</v>
+        <v>205.85</v>
       </c>
     </row>
     <row r="5">
@@ -6028,13 +6028,13 @@
         <v>107.2</v>
       </c>
       <c r="C5" s="5" t="n">
-        <v>141.07</v>
+        <v>141.34</v>
       </c>
       <c r="D5" s="5" t="n">
         <v>189.98</v>
       </c>
       <c r="E5" s="5" t="n">
-        <v>250.01</v>
+        <v>250.48</v>
       </c>
     </row>
     <row r="6">
@@ -6047,13 +6047,13 @@
         <v>69.34999999999999</v>
       </c>
       <c r="C6" s="5" t="n">
-        <v>78.06</v>
+        <v>77.7</v>
       </c>
       <c r="D6" s="5" t="n">
         <v>122.5</v>
       </c>
       <c r="E6" s="5" t="n">
-        <v>137.89</v>
+        <v>137.25</v>
       </c>
     </row>
     <row r="7">
@@ -6066,13 +6066,13 @@
         <v>82.38</v>
       </c>
       <c r="C7" s="5" t="n">
-        <v>102.26</v>
+        <v>102.17</v>
       </c>
       <c r="D7" s="5" t="n">
         <v>145.27</v>
       </c>
       <c r="E7" s="5" t="n">
-        <v>180.32</v>
+        <v>180.16</v>
       </c>
     </row>
     <row r="8">
@@ -6085,13 +6085,13 @@
         <v>57.64</v>
       </c>
       <c r="C8" s="5" t="n">
-        <v>59.27</v>
+        <v>59.19</v>
       </c>
       <c r="D8" s="5" t="n">
         <v>101.47</v>
       </c>
       <c r="E8" s="5" t="n">
-        <v>104.33</v>
+        <v>104.19</v>
       </c>
     </row>
     <row r="9">
@@ -6104,13 +6104,13 @@
         <v>42.82</v>
       </c>
       <c r="C9" s="5" t="n">
-        <v>47</v>
+        <v>46.71</v>
       </c>
       <c r="D9" s="5" t="n">
         <v>75.25</v>
       </c>
       <c r="E9" s="5" t="n">
-        <v>82.59</v>
+        <v>82.08</v>
       </c>
     </row>
     <row r="10">
@@ -6123,13 +6123,13 @@
         <v>36.9</v>
       </c>
       <c r="C10" s="5" t="n">
-        <v>40.37</v>
+        <v>40.3</v>
       </c>
       <c r="D10" s="5" t="n">
         <v>64.66</v>
       </c>
       <c r="E10" s="5" t="n">
-        <v>70.73999999999999</v>
+        <v>70.62</v>
       </c>
     </row>
     <row r="11">
@@ -6142,13 +6142,13 @@
         <v>32.44</v>
       </c>
       <c r="C11" s="5" t="n">
-        <v>35.76</v>
+        <v>35.57</v>
       </c>
       <c r="D11" s="5" t="n">
         <v>56.68</v>
       </c>
       <c r="E11" s="5" t="n">
-        <v>62.48</v>
+        <v>62.15</v>
       </c>
     </row>
     <row r="12">
@@ -6161,13 +6161,13 @@
         <v>28.4</v>
       </c>
       <c r="C12" s="5" t="n">
-        <v>32.55</v>
+        <v>32.53</v>
       </c>
       <c r="D12" s="5" t="n">
         <v>49.48</v>
       </c>
       <c r="E12" s="5" t="n">
-        <v>56.71</v>
+        <v>56.68</v>
       </c>
     </row>
     <row r="13">
@@ -6180,13 +6180,13 @@
         <v>33.36</v>
       </c>
       <c r="C13" s="5" t="n">
-        <v>33.84</v>
+        <v>33.75</v>
       </c>
       <c r="D13" s="5" t="n">
         <v>57.82</v>
       </c>
       <c r="E13" s="5" t="n">
-        <v>58.65</v>
+        <v>58.5</v>
       </c>
     </row>
     <row r="14">
@@ -6199,13 +6199,13 @@
         <v>33.76</v>
       </c>
       <c r="C14" s="5" t="n">
-        <v>47.58</v>
+        <v>47.59</v>
       </c>
       <c r="D14" s="5" t="n">
         <v>58.21</v>
       </c>
       <c r="E14" s="5" t="n">
-        <v>82.03</v>
+        <v>82.05</v>
       </c>
     </row>
     <row r="15">
@@ -6218,13 +6218,13 @@
         <v>41.39</v>
       </c>
       <c r="C15" s="5" t="n">
-        <v>51.97</v>
+        <v>52.3</v>
       </c>
       <c r="D15" s="5" t="n">
         <v>70.98999999999999</v>
       </c>
       <c r="E15" s="5" t="n">
-        <v>89.14</v>
+        <v>89.7</v>
       </c>
     </row>
     <row r="16">
@@ -6237,13 +6237,13 @@
         <v>48.24</v>
       </c>
       <c r="C16" s="5" t="n">
-        <v>68.81</v>
+        <v>69.09999999999999</v>
       </c>
       <c r="D16" s="5" t="n">
         <v>82.5</v>
       </c>
       <c r="E16" s="5" t="n">
-        <v>117.67</v>
+        <v>118.17</v>
       </c>
     </row>
     <row r="17">
@@ -6256,13 +6256,13 @@
         <v>35.17</v>
       </c>
       <c r="C17" s="5" t="n">
-        <v>39.83</v>
+        <v>39.9</v>
       </c>
       <c r="D17" s="5" t="n">
         <v>59.97</v>
       </c>
       <c r="E17" s="5" t="n">
-        <v>67.91</v>
+        <v>68.03</v>
       </c>
     </row>
     <row r="18">
@@ -6275,13 +6275,13 @@
         <v>38.25</v>
       </c>
       <c r="C18" s="5" t="n">
-        <v>41.53</v>
+        <v>41.6</v>
       </c>
       <c r="D18" s="5" t="n">
         <v>65.03</v>
       </c>
       <c r="E18" s="5" t="n">
-        <v>70.59999999999999</v>
+        <v>70.72</v>
       </c>
     </row>
     <row r="19">
@@ -6294,13 +6294,13 @@
         <v>34.23</v>
       </c>
       <c r="C19" s="5" t="n">
-        <v>36.83</v>
+        <v>36.71</v>
       </c>
       <c r="D19" s="5" t="n">
         <v>58.22</v>
       </c>
       <c r="E19" s="5" t="n">
-        <v>62.64</v>
+        <v>62.43</v>
       </c>
     </row>
     <row r="20">
@@ -6313,13 +6313,13 @@
         <v>39.8</v>
       </c>
       <c r="C20" s="5" t="n">
-        <v>44.85</v>
+        <v>44.53</v>
       </c>
       <c r="D20" s="5" t="n">
         <v>67.72</v>
       </c>
       <c r="E20" s="5" t="n">
-        <v>76.31</v>
+        <v>75.76000000000001</v>
       </c>
     </row>
     <row r="21">
@@ -6332,13 +6332,13 @@
         <v>35.17</v>
       </c>
       <c r="C21" s="5" t="n">
-        <v>41.08</v>
+        <v>40.79</v>
       </c>
       <c r="D21" s="5" t="n">
         <v>59.86</v>
       </c>
       <c r="E21" s="5" t="n">
-        <v>69.92</v>
+        <v>69.43000000000001</v>
       </c>
     </row>
     <row r="22">
@@ -6351,13 +6351,13 @@
         <v>44.3</v>
       </c>
       <c r="C22" s="5" t="n">
-        <v>47.25</v>
+        <v>47.2</v>
       </c>
       <c r="D22" s="5" t="n">
         <v>75.38</v>
       </c>
       <c r="E22" s="5" t="n">
-        <v>80.40000000000001</v>
+        <v>80.31</v>
       </c>
     </row>
     <row r="23">
@@ -6370,13 +6370,13 @@
         <v>52.95</v>
       </c>
       <c r="C23" s="5" t="n">
-        <v>67.59999999999999</v>
+        <v>67.45</v>
       </c>
       <c r="D23" s="5" t="n">
         <v>90.06999999999999</v>
       </c>
       <c r="E23" s="5" t="n">
-        <v>114.99</v>
+        <v>114.74</v>
       </c>
     </row>
     <row r="24">
@@ -6389,13 +6389,13 @@
         <v>50.75</v>
       </c>
       <c r="C24" s="5" t="n">
-        <v>53.83</v>
+        <v>53.78</v>
       </c>
       <c r="D24" s="5" t="n">
         <v>86.31</v>
       </c>
       <c r="E24" s="5" t="n">
-        <v>91.55</v>
+        <v>91.45999999999999</v>
       </c>
     </row>
     <row r="25">
@@ -6408,13 +6408,13 @@
         <v>73.08</v>
       </c>
       <c r="C25" s="5" t="n">
-        <v>82.19</v>
+        <v>81.98999999999999</v>
       </c>
       <c r="D25" s="5" t="n">
         <v>123.77</v>
       </c>
       <c r="E25" s="5" t="n">
-        <v>139.2</v>
+        <v>138.87</v>
       </c>
     </row>
     <row r="26">
@@ -6427,13 +6427,13 @@
         <v>66.34</v>
       </c>
       <c r="C26" s="5" t="n">
-        <v>72.31</v>
+        <v>72.01000000000001</v>
       </c>
       <c r="D26" s="5" t="n">
         <v>111.9</v>
       </c>
       <c r="E26" s="5" t="n">
-        <v>121.97</v>
+        <v>121.47</v>
       </c>
     </row>
     <row r="27">
@@ -6446,13 +6446,13 @@
         <v>77.81</v>
       </c>
       <c r="C27" s="5" t="n">
-        <v>79.93000000000001</v>
+        <v>79.87</v>
       </c>
       <c r="D27" s="5" t="n">
         <v>130.72</v>
       </c>
       <c r="E27" s="5" t="n">
-        <v>134.28</v>
+        <v>134.18</v>
       </c>
     </row>
     <row r="28">
@@ -6465,13 +6465,13 @@
         <v>99.45</v>
       </c>
       <c r="C28" s="5" t="n">
-        <v>115.5</v>
+        <v>115.14</v>
       </c>
       <c r="D28" s="5" t="n">
         <v>166.69</v>
       </c>
       <c r="E28" s="5" t="n">
-        <v>193.59</v>
+        <v>192.99</v>
       </c>
     </row>
     <row r="29">
@@ -6484,13 +6484,13 @@
         <v>40.7</v>
       </c>
       <c r="C29" s="5" t="n">
-        <v>48.82</v>
+        <v>48.48</v>
       </c>
       <c r="D29" s="5" t="n">
         <v>68.06</v>
       </c>
       <c r="E29" s="5" t="n">
-        <v>81.64</v>
+        <v>81.06999999999999</v>
       </c>
     </row>
     <row r="30">
@@ -6503,13 +6503,13 @@
         <v>47.24</v>
       </c>
       <c r="C30" s="5" t="n">
-        <v>50.3</v>
+        <v>49.1</v>
       </c>
       <c r="D30" s="5" t="n">
         <v>78.81999999999999</v>
       </c>
       <c r="E30" s="5" t="n">
-        <v>83.92</v>
+        <v>81.92</v>
       </c>
     </row>
     <row r="31">
@@ -6522,13 +6522,13 @@
         <v>34.03</v>
       </c>
       <c r="C31" s="5" t="n">
-        <v>38.54</v>
+        <v>32.4</v>
       </c>
       <c r="D31" s="5" t="n">
         <v>56.6</v>
       </c>
       <c r="E31" s="5" t="n">
-        <v>64.09999999999999</v>
+        <v>53.89</v>
       </c>
     </row>
     <row r="32">
@@ -6541,13 +6541,13 @@
         <v>44.74</v>
       </c>
       <c r="C32" s="5" t="n">
-        <v>49.43</v>
+        <v>49.25</v>
       </c>
       <c r="D32" s="5" t="n">
         <v>74.19</v>
       </c>
       <c r="E32" s="5" t="n">
-        <v>81.95999999999999</v>
+        <v>81.67</v>
       </c>
     </row>
     <row r="33">
@@ -6560,13 +6560,13 @@
         <v>50.96</v>
       </c>
       <c r="C33" s="5" t="n">
-        <v>60.54</v>
+        <v>60.6</v>
       </c>
       <c r="D33" s="5" t="n">
         <v>84.23999999999999</v>
       </c>
       <c r="E33" s="5" t="n">
-        <v>100.08</v>
+        <v>100.18</v>
       </c>
     </row>
     <row r="34">
@@ -6579,13 +6579,13 @@
         <v>47.33</v>
       </c>
       <c r="C34" s="5" t="n">
-        <v>59.06</v>
+        <v>59.02</v>
       </c>
       <c r="D34" s="5" t="n">
         <v>77.89</v>
       </c>
       <c r="E34" s="5" t="n">
-        <v>97.2</v>
+        <v>97.13</v>
       </c>
     </row>
     <row r="35">
@@ -6598,13 +6598,13 @@
         <v>56.46</v>
       </c>
       <c r="C35" s="5" t="n">
-        <v>67.75</v>
+        <v>67.68000000000001</v>
       </c>
       <c r="D35" s="5" t="n">
         <v>92.51000000000001</v>
       </c>
       <c r="E35" s="5" t="n">
-        <v>111</v>
+        <v>110.89</v>
       </c>
     </row>
     <row r="36">
@@ -6617,13 +6617,13 @@
         <v>56.17</v>
       </c>
       <c r="C36" s="5" t="n">
-        <v>68.79000000000001</v>
+        <v>68.55</v>
       </c>
       <c r="D36" s="5" t="n">
         <v>91.63</v>
       </c>
       <c r="E36" s="5" t="n">
-        <v>112.21</v>
+        <v>111.82</v>
       </c>
     </row>
     <row r="37">
@@ -6636,13 +6636,13 @@
         <v>54.93</v>
       </c>
       <c r="C37" s="5" t="n">
-        <v>63.84</v>
+        <v>63.43</v>
       </c>
       <c r="D37" s="5" t="n">
         <v>89.17</v>
       </c>
       <c r="E37" s="5" t="n">
-        <v>103.64</v>
+        <v>102.97</v>
       </c>
     </row>
     <row r="38">
@@ -6655,13 +6655,13 @@
         <v>67.73999999999999</v>
       </c>
       <c r="C38" s="5" t="n">
-        <v>69.72</v>
+        <v>69.15000000000001</v>
       </c>
       <c r="D38" s="5" t="n">
         <v>109.44</v>
       </c>
       <c r="E38" s="5" t="n">
-        <v>112.64</v>
+        <v>111.72</v>
       </c>
     </row>
     <row r="39">
@@ -6674,13 +6674,13 @@
         <v>55.96</v>
       </c>
       <c r="C39" s="5" t="n">
-        <v>63.27</v>
+        <v>63.04</v>
       </c>
       <c r="D39" s="5" t="n">
         <v>89.98</v>
       </c>
       <c r="E39" s="5" t="n">
-        <v>101.73</v>
+        <v>101.36</v>
       </c>
     </row>
     <row r="40">
@@ -6693,13 +6693,13 @@
         <v>30.36</v>
       </c>
       <c r="C40" s="5" t="n">
-        <v>30.26</v>
+        <v>31.08</v>
       </c>
       <c r="D40" s="5" t="n">
         <v>48.63</v>
       </c>
       <c r="E40" s="5" t="n">
-        <v>48.47</v>
+        <v>49.78</v>
       </c>
     </row>
     <row r="41">
@@ -6712,13 +6712,13 @@
         <v>54.96</v>
       </c>
       <c r="C41" s="5" t="n">
-        <v>60.94</v>
+        <v>60.78</v>
       </c>
       <c r="D41" s="5" t="n">
         <v>87.69</v>
       </c>
       <c r="E41" s="5" t="n">
-        <v>97.23</v>
+        <v>96.98</v>
       </c>
     </row>
     <row r="42">
@@ -6731,13 +6731,13 @@
         <v>43.94</v>
       </c>
       <c r="C42" s="5" t="n">
-        <v>53.5</v>
+        <v>53.01</v>
       </c>
       <c r="D42" s="5" t="n">
         <v>69.84</v>
       </c>
       <c r="E42" s="5" t="n">
-        <v>85.03</v>
+        <v>84.25</v>
       </c>
     </row>
     <row r="43">
@@ -6750,13 +6750,13 @@
         <v>45.92</v>
       </c>
       <c r="C43" s="5" t="n">
-        <v>56.32</v>
+        <v>55.72</v>
       </c>
       <c r="D43" s="5" t="n">
         <v>73.06</v>
       </c>
       <c r="E43" s="5" t="n">
-        <v>89.61</v>
+        <v>88.66</v>
       </c>
     </row>
     <row r="44">
@@ -6769,13 +6769,13 @@
         <v>50.7</v>
       </c>
       <c r="C44" s="5" t="n">
-        <v>61.31</v>
+        <v>60.73</v>
       </c>
       <c r="D44" s="5" t="n">
         <v>80.76000000000001</v>
       </c>
       <c r="E44" s="5" t="n">
-        <v>97.66</v>
+        <v>96.73</v>
       </c>
     </row>
     <row r="45">
@@ -6788,13 +6788,13 @@
         <v>32.91</v>
       </c>
       <c r="C45" s="5" t="n">
-        <v>38.3</v>
+        <v>38.15</v>
       </c>
       <c r="D45" s="5" t="n">
         <v>52.48</v>
       </c>
       <c r="E45" s="5" t="n">
-        <v>61.07</v>
+        <v>60.83</v>
       </c>
     </row>
     <row r="46">
@@ -6807,13 +6807,13 @@
         <v>78.88</v>
       </c>
       <c r="C46" s="5" t="n">
-        <v>119.63</v>
+        <v>119.54</v>
       </c>
       <c r="D46" s="5" t="n">
         <v>125.74</v>
       </c>
       <c r="E46" s="5" t="n">
-        <v>190.69</v>
+        <v>190.55</v>
       </c>
     </row>
     <row r="47">
@@ -6826,13 +6826,13 @@
         <v>39.08</v>
       </c>
       <c r="C47" s="5" t="n">
-        <v>63.91</v>
+        <v>63.49</v>
       </c>
       <c r="D47" s="5" t="n">
         <v>62.27</v>
       </c>
       <c r="E47" s="5" t="n">
-        <v>101.84</v>
+        <v>101.17</v>
       </c>
     </row>
     <row r="48">
@@ -6845,13 +6845,13 @@
         <v>36.48</v>
       </c>
       <c r="C48" s="5" t="n">
-        <v>43.73</v>
+        <v>43.09</v>
       </c>
       <c r="D48" s="5" t="n">
         <v>58.11</v>
       </c>
       <c r="E48" s="5" t="n">
-        <v>69.66</v>
+        <v>68.64</v>
       </c>
     </row>
     <row r="49">
@@ -6864,13 +6864,13 @@
         <v>69.31</v>
       </c>
       <c r="C49" s="5" t="n">
-        <v>63.23</v>
+        <v>61.35</v>
       </c>
       <c r="D49" s="5" t="n">
         <v>110.22</v>
       </c>
       <c r="E49" s="5" t="n">
-        <v>100.55</v>
+        <v>97.56</v>
       </c>
     </row>
     <row r="50">
@@ -6883,13 +6883,13 @@
         <v>46.84</v>
       </c>
       <c r="C50" s="5" t="n">
-        <v>50.07</v>
+        <v>48.31</v>
       </c>
       <c r="D50" s="5" t="n">
         <v>74.36</v>
       </c>
       <c r="E50" s="5" t="n">
-        <v>79.48999999999999</v>
+        <v>76.7</v>
       </c>
     </row>
     <row r="51">
@@ -6902,13 +6902,13 @@
         <v>173.8</v>
       </c>
       <c r="C51" s="5" t="n">
-        <v>292.02</v>
+        <v>287.29</v>
       </c>
       <c r="D51" s="5" t="n">
         <v>275.47</v>
       </c>
       <c r="E51" s="5" t="n">
-        <v>462.84</v>
+        <v>455.35</v>
       </c>
     </row>
     <row r="52">
@@ -6921,13 +6921,13 @@
         <v>25.89</v>
       </c>
       <c r="C52" s="5" t="n">
-        <v>31.68</v>
+        <v>31.56</v>
       </c>
       <c r="D52" s="5" t="n">
         <v>40.91</v>
       </c>
       <c r="E52" s="5" t="n">
-        <v>50.05</v>
+        <v>49.86</v>
       </c>
     </row>
     <row r="53">
@@ -6940,13 +6940,13 @@
         <v>21.29</v>
       </c>
       <c r="C53" s="5" t="n">
-        <v>28.03</v>
+        <v>27.86</v>
       </c>
       <c r="D53" s="5" t="n">
         <v>33.53</v>
       </c>
       <c r="E53" s="5" t="n">
-        <v>44.15</v>
+        <v>43.88</v>
       </c>
     </row>
     <row r="54">
@@ -6959,13 +6959,13 @@
         <v>21.52</v>
       </c>
       <c r="C54" s="5" t="n">
-        <v>27.51</v>
+        <v>27.5</v>
       </c>
       <c r="D54" s="5" t="n">
         <v>33.79</v>
       </c>
       <c r="E54" s="5" t="n">
-        <v>43.19</v>
+        <v>43.18</v>
       </c>
     </row>
     <row r="55">
@@ -6978,13 +6978,13 @@
         <v>25.78</v>
       </c>
       <c r="C55" s="5" t="n">
-        <v>30.14</v>
+        <v>29.55</v>
       </c>
       <c r="D55" s="5" t="n">
         <v>40.41</v>
       </c>
       <c r="E55" s="5" t="n">
-        <v>47.24</v>
+        <v>46.31</v>
       </c>
     </row>
     <row r="56">
@@ -6997,13 +6997,13 @@
         <v>33.7</v>
       </c>
       <c r="C56" s="5" t="n">
-        <v>38.11</v>
+        <v>37.68</v>
       </c>
       <c r="D56" s="5" t="n">
         <v>52.72</v>
       </c>
       <c r="E56" s="5" t="n">
-        <v>59.62</v>
+        <v>58.95</v>
       </c>
     </row>
     <row r="57">
@@ -7016,13 +7016,13 @@
         <v>31.86</v>
       </c>
       <c r="C57" s="5" t="n">
-        <v>31.86</v>
+        <v>31.42</v>
       </c>
       <c r="D57" s="5" t="n">
         <v>49.76</v>
       </c>
       <c r="E57" s="5" t="n">
-        <v>49.76</v>
+        <v>49.07</v>
       </c>
     </row>
     <row r="58">
@@ -7035,13 +7035,13 @@
         <v>29.23</v>
       </c>
       <c r="C58" s="5" t="n">
-        <v>32.52</v>
+        <v>32.51</v>
       </c>
       <c r="D58" s="5" t="n">
         <v>45.51</v>
       </c>
       <c r="E58" s="5" t="n">
-        <v>50.63</v>
+        <v>50.62</v>
       </c>
     </row>
     <row r="59">
@@ -7054,13 +7054,13 @@
         <v>23.96</v>
       </c>
       <c r="C59" s="5" t="n">
-        <v>20.61</v>
+        <v>20.35</v>
       </c>
       <c r="D59" s="5" t="n">
         <v>37.19</v>
       </c>
       <c r="E59" s="5" t="n">
-        <v>31.99</v>
+        <v>31.59</v>
       </c>
     </row>
     <row r="60">
@@ -7073,13 +7073,13 @@
         <v>26.2</v>
       </c>
       <c r="C60" s="5" t="n">
-        <v>28.67</v>
+        <v>28.45</v>
       </c>
       <c r="D60" s="5" t="n">
         <v>40.54</v>
       </c>
       <c r="E60" s="5" t="n">
-        <v>44.36</v>
+        <v>44.02</v>
       </c>
     </row>
     <row r="61">
@@ -7092,13 +7092,13 @@
         <v>24.42</v>
       </c>
       <c r="C61" s="5" t="n">
-        <v>26.2</v>
+        <v>26.23</v>
       </c>
       <c r="D61" s="5" t="n">
         <v>37.71</v>
       </c>
       <c r="E61" s="5" t="n">
-        <v>40.46</v>
+        <v>40.51</v>
       </c>
     </row>
     <row r="62">
@@ -7111,13 +7111,13 @@
         <v>56.97</v>
       </c>
       <c r="C62" s="5" t="n">
-        <v>40.53</v>
+        <v>36.98</v>
       </c>
       <c r="D62" s="5" t="n">
         <v>87.8</v>
       </c>
       <c r="E62" s="5" t="n">
-        <v>62.46</v>
+        <v>56.99</v>
       </c>
     </row>
     <row r="63">
@@ -7130,13 +7130,13 @@
         <v>30.89</v>
       </c>
       <c r="C63" s="5" t="n">
-        <v>34.48</v>
+        <v>34.53</v>
       </c>
       <c r="D63" s="5" t="n">
         <v>47.51</v>
       </c>
       <c r="E63" s="5" t="n">
-        <v>53.03</v>
+        <v>53.11</v>
       </c>
     </row>
     <row r="64">
@@ -7149,13 +7149,13 @@
         <v>30.2</v>
       </c>
       <c r="C64" s="5" t="n">
-        <v>33.99</v>
+        <v>27.43</v>
       </c>
       <c r="D64" s="5" t="n">
         <v>46.34</v>
       </c>
       <c r="E64" s="5" t="n">
-        <v>52.15</v>
+        <v>42.09</v>
       </c>
     </row>
     <row r="65">
@@ -7168,13 +7168,13 @@
         <v>64.8</v>
       </c>
       <c r="C65" s="5" t="n">
-        <v>27.77</v>
+        <v>27.68</v>
       </c>
       <c r="D65" s="5" t="n">
         <v>99.19</v>
       </c>
       <c r="E65" s="5" t="n">
-        <v>42.51</v>
+        <v>42.37</v>
       </c>
     </row>
     <row r="66">
@@ -7187,13 +7187,13 @@
         <v>20.76</v>
       </c>
       <c r="C66" s="5" t="n">
-        <v>23.94</v>
+        <v>23.49</v>
       </c>
       <c r="D66" s="5" t="n">
         <v>31.7</v>
       </c>
       <c r="E66" s="5" t="n">
-        <v>36.56</v>
+        <v>35.87</v>
       </c>
     </row>
     <row r="67">
@@ -7206,13 +7206,13 @@
         <v>18.14</v>
       </c>
       <c r="C67" s="5" t="n">
-        <v>18.56</v>
+        <v>18.32</v>
       </c>
       <c r="D67" s="5" t="n">
         <v>27.66</v>
       </c>
       <c r="E67" s="5" t="n">
-        <v>28.3</v>
+        <v>27.94</v>
       </c>
     </row>
     <row r="68">
@@ -7225,13 +7225,13 @@
         <v>27.1</v>
       </c>
       <c r="C68" s="5" t="n">
-        <v>38.48</v>
+        <v>19.55</v>
       </c>
       <c r="D68" s="5" t="n">
         <v>41.28</v>
       </c>
       <c r="E68" s="5" t="n">
-        <v>58.61</v>
+        <v>29.78</v>
       </c>
     </row>
     <row r="69">
@@ -7244,13 +7244,13 @@
         <v>16.7</v>
       </c>
       <c r="C69" s="5" t="n">
-        <v>17.8</v>
+        <v>17.67</v>
       </c>
       <c r="D69" s="5" t="n">
         <v>25.4</v>
       </c>
       <c r="E69" s="5" t="n">
-        <v>27.08</v>
+        <v>26.88</v>
       </c>
     </row>
     <row r="70">
@@ -7263,13 +7263,13 @@
         <v>25.95</v>
       </c>
       <c r="C70" s="5" t="n">
-        <v>28.36</v>
+        <v>28.13</v>
       </c>
       <c r="D70" s="5" t="n">
         <v>39.27</v>
       </c>
       <c r="E70" s="5" t="n">
-        <v>42.92</v>
+        <v>42.57</v>
       </c>
     </row>
     <row r="71">
@@ -7282,13 +7282,13 @@
         <v>28.72</v>
       </c>
       <c r="C71" s="5" t="n">
-        <v>31.48</v>
+        <v>31.08</v>
       </c>
       <c r="D71" s="5" t="n">
         <v>43.24</v>
       </c>
       <c r="E71" s="5" t="n">
-        <v>47.4</v>
+        <v>46.79</v>
       </c>
     </row>
     <row r="72">
@@ -7301,13 +7301,13 @@
         <v>25.83</v>
       </c>
       <c r="C72" s="5" t="n">
-        <v>27.22</v>
+        <v>27.04</v>
       </c>
       <c r="D72" s="5" t="n">
         <v>38.69</v>
       </c>
       <c r="E72" s="5" t="n">
-        <v>40.77</v>
+        <v>40.5</v>
       </c>
     </row>
     <row r="73">
@@ -7320,13 +7320,13 @@
         <v>26.8</v>
       </c>
       <c r="C73" s="5" t="n">
-        <v>27.79</v>
+        <v>27.77</v>
       </c>
       <c r="D73" s="5" t="n">
         <v>40.02</v>
       </c>
       <c r="E73" s="5" t="n">
-        <v>41.5</v>
+        <v>41.47</v>
       </c>
     </row>
     <row r="74">
@@ -7339,13 +7339,13 @@
         <v>38.67</v>
       </c>
       <c r="C74" s="5" t="n">
-        <v>40.73</v>
+        <v>40.49</v>
       </c>
       <c r="D74" s="5" t="n">
         <v>57.57</v>
       </c>
       <c r="E74" s="5" t="n">
-        <v>60.64</v>
+        <v>60.28</v>
       </c>
     </row>
     <row r="75">
@@ -7358,13 +7358,13 @@
         <v>29.16</v>
       </c>
       <c r="C75" s="5" t="n">
-        <v>32.31</v>
+        <v>32.23</v>
       </c>
       <c r="D75" s="5" t="n">
         <v>43.28</v>
       </c>
       <c r="E75" s="5" t="n">
-        <v>47.96</v>
+        <v>47.84</v>
       </c>
     </row>
     <row r="76">
@@ -7377,13 +7377,13 @@
         <v>32.59</v>
       </c>
       <c r="C76" s="5" t="n">
-        <v>49.12</v>
+        <v>49.09</v>
       </c>
       <c r="D76" s="5" t="n">
         <v>48.28</v>
       </c>
       <c r="E76" s="5" t="n">
-        <v>72.76000000000001</v>
+        <v>72.72</v>
       </c>
     </row>
     <row r="77">
@@ -7396,13 +7396,13 @@
         <v>27.16</v>
       </c>
       <c r="C77" s="5" t="n">
-        <v>34.69</v>
+        <v>34.57</v>
       </c>
       <c r="D77" s="5" t="n">
         <v>40.15</v>
       </c>
       <c r="E77" s="5" t="n">
-        <v>51.29</v>
+        <v>51.11</v>
       </c>
     </row>
     <row r="78">
@@ -7415,13 +7415,13 @@
         <v>26.4</v>
       </c>
       <c r="C78" s="5" t="n">
-        <v>29.9</v>
+        <v>29.91</v>
       </c>
       <c r="D78" s="5" t="n">
         <v>38.95</v>
       </c>
       <c r="E78" s="5" t="n">
-        <v>44.12</v>
+        <v>44.13</v>
       </c>
     </row>
     <row r="79">
@@ -7434,13 +7434,13 @@
         <v>32.58</v>
       </c>
       <c r="C79" s="5" t="n">
-        <v>31.6</v>
+        <v>31.19</v>
       </c>
       <c r="D79" s="5" t="n">
         <v>48.07</v>
       </c>
       <c r="E79" s="5" t="n">
-        <v>46.63</v>
+        <v>46.02</v>
       </c>
     </row>
     <row r="80">
@@ -7453,13 +7453,13 @@
         <v>30.75</v>
       </c>
       <c r="C80" s="5" t="n">
-        <v>30.44</v>
+        <v>29.77</v>
       </c>
       <c r="D80" s="5" t="n">
         <v>45.37</v>
       </c>
       <c r="E80" s="5" t="n">
-        <v>44.91</v>
+        <v>43.93</v>
       </c>
     </row>
     <row r="81">
@@ -7472,13 +7472,13 @@
         <v>25.85</v>
       </c>
       <c r="C81" s="5" t="n">
-        <v>26.57</v>
+        <v>26.39</v>
       </c>
       <c r="D81" s="5" t="n">
         <v>38.14</v>
       </c>
       <c r="E81" s="5" t="n">
-        <v>39.2</v>
+        <v>38.94</v>
       </c>
     </row>
     <row r="82">
@@ -7491,13 +7491,13 @@
         <v>39.32</v>
       </c>
       <c r="C82" s="5" t="n">
-        <v>34.13</v>
+        <v>34.3</v>
       </c>
       <c r="D82" s="5" t="n">
         <v>58</v>
       </c>
       <c r="E82" s="5" t="n">
-        <v>50.35</v>
+        <v>50.6</v>
       </c>
     </row>
     <row r="83">
@@ -7510,13 +7510,13 @@
         <v>37.37</v>
       </c>
       <c r="C83" s="5" t="n">
-        <v>29.92</v>
+        <v>29.99</v>
       </c>
       <c r="D83" s="5" t="n">
         <v>55.12</v>
       </c>
       <c r="E83" s="5" t="n">
-        <v>44.13</v>
+        <v>44.23</v>
       </c>
     </row>
     <row r="84">
@@ -7529,13 +7529,13 @@
         <v>35.92</v>
       </c>
       <c r="C84" s="5" t="n">
-        <v>29.84</v>
+        <v>29.57</v>
       </c>
       <c r="D84" s="5" t="n">
         <v>52.97</v>
       </c>
       <c r="E84" s="5" t="n">
-        <v>44</v>
+        <v>43.6</v>
       </c>
     </row>
     <row r="85">
@@ -7548,13 +7548,13 @@
         <v>35.96</v>
       </c>
       <c r="C85" s="5" t="n">
-        <v>42.04</v>
+        <v>41.97</v>
       </c>
       <c r="D85" s="5" t="n">
         <v>52.94</v>
       </c>
       <c r="E85" s="5" t="n">
-        <v>61.89</v>
+        <v>61.78</v>
       </c>
     </row>
     <row r="86">
@@ -7567,13 +7567,13 @@
         <v>32.9</v>
       </c>
       <c r="C86" s="5" t="n">
-        <v>29.9</v>
+        <v>29.93</v>
       </c>
       <c r="D86" s="5" t="n">
         <v>48.35</v>
       </c>
       <c r="E86" s="5" t="n">
-        <v>43.94</v>
+        <v>43.98</v>
       </c>
     </row>
     <row r="87">
@@ -7586,13 +7586,13 @@
         <v>34.44</v>
       </c>
       <c r="C87" s="5" t="n">
-        <v>38.55</v>
+        <v>38.35</v>
       </c>
       <c r="D87" s="5" t="n">
         <v>50.52</v>
       </c>
       <c r="E87" s="5" t="n">
-        <v>56.55</v>
+        <v>56.26</v>
       </c>
     </row>
     <row r="88">
@@ -7605,13 +7605,13 @@
         <v>59.23</v>
       </c>
       <c r="C88" s="5" t="n">
-        <v>67.45</v>
+        <v>67.09999999999999</v>
       </c>
       <c r="D88" s="5" t="n">
         <v>86.5</v>
       </c>
       <c r="E88" s="5" t="n">
-        <v>98.5</v>
+        <v>97.98999999999999</v>
       </c>
     </row>
     <row r="89">
@@ -7624,13 +7624,13 @@
         <v>47.22</v>
       </c>
       <c r="C89" s="5" t="n">
-        <v>48.6</v>
+        <v>48.32</v>
       </c>
       <c r="D89" s="5" t="n">
         <v>68.65000000000001</v>
       </c>
       <c r="E89" s="5" t="n">
-        <v>70.66</v>
+        <v>70.25</v>
       </c>
     </row>
     <row r="90">
@@ -7643,13 +7643,13 @@
         <v>39.46</v>
       </c>
       <c r="C90" s="5" t="n">
-        <v>41.42</v>
+        <v>41.39</v>
       </c>
       <c r="D90" s="5" t="n">
         <v>57.11</v>
       </c>
       <c r="E90" s="5" t="n">
-        <v>59.95</v>
+        <v>59.9</v>
       </c>
     </row>
     <row r="91">
@@ -7662,13 +7662,13 @@
         <v>43.62</v>
       </c>
       <c r="C91" s="5" t="n">
-        <v>44.97</v>
+        <v>44.73</v>
       </c>
       <c r="D91" s="5" t="n">
         <v>63.08</v>
       </c>
       <c r="E91" s="5" t="n">
-        <v>65.03</v>
+        <v>64.68000000000001</v>
       </c>
     </row>
     <row r="92">
@@ -7681,13 +7681,13 @@
         <v>50.58</v>
       </c>
       <c r="C92" s="5" t="n">
-        <v>51.39</v>
+        <v>51.23</v>
       </c>
       <c r="D92" s="5" t="n">
         <v>73.08</v>
       </c>
       <c r="E92" s="5" t="n">
-        <v>74.25</v>
+        <v>74.02</v>
       </c>
     </row>
     <row r="93">
@@ -7700,13 +7700,13 @@
         <v>46.7</v>
       </c>
       <c r="C93" s="5" t="n">
-        <v>46.41</v>
+        <v>46.33</v>
       </c>
       <c r="D93" s="5" t="n">
         <v>67.42</v>
       </c>
       <c r="E93" s="5" t="n">
-        <v>67</v>
+        <v>66.88</v>
       </c>
     </row>
     <row r="94">
@@ -7719,13 +7719,13 @@
         <v>56.96</v>
       </c>
       <c r="C94" s="5" t="n">
-        <v>46.53</v>
+        <v>46.27</v>
       </c>
       <c r="D94" s="5" t="n">
         <v>82.14</v>
       </c>
       <c r="E94" s="5" t="n">
-        <v>67.09999999999999</v>
+        <v>66.72</v>
       </c>
     </row>
     <row r="95">
@@ -7738,13 +7738,13 @@
         <v>45.79</v>
       </c>
       <c r="C95" s="5" t="n">
-        <v>46.11</v>
+        <v>45.77</v>
       </c>
       <c r="D95" s="5" t="n">
         <v>65.95</v>
       </c>
       <c r="E95" s="5" t="n">
-        <v>66.42</v>
+        <v>65.93000000000001</v>
       </c>
     </row>
     <row r="96">
@@ -7757,13 +7757,13 @@
         <v>49.81</v>
       </c>
       <c r="C96" s="5" t="n">
-        <v>50.82</v>
+        <v>50.56</v>
       </c>
       <c r="D96" s="5" t="n">
         <v>71.66</v>
       </c>
       <c r="E96" s="5" t="n">
-        <v>73.12</v>
+        <v>72.73999999999999</v>
       </c>
     </row>
     <row r="97">
@@ -7776,13 +7776,13 @@
         <v>45.12</v>
       </c>
       <c r="C97" s="5" t="n">
-        <v>46.73</v>
+        <v>46.49</v>
       </c>
       <c r="D97" s="5" t="n">
         <v>64.83</v>
       </c>
       <c r="E97" s="5" t="n">
-        <v>67.15000000000001</v>
+        <v>66.8</v>
       </c>
     </row>
     <row r="98">
@@ -7795,13 +7795,13 @@
         <v>44.67</v>
       </c>
       <c r="C98" s="5" t="n">
-        <v>49.68</v>
+        <v>49.59</v>
       </c>
       <c r="D98" s="5" t="n">
         <v>64.11</v>
       </c>
       <c r="E98" s="5" t="n">
-        <v>71.3</v>
+        <v>71.17</v>
       </c>
     </row>
     <row r="99">
@@ -7814,13 +7814,13 @@
         <v>49.89</v>
       </c>
       <c r="C99" s="5" t="n">
-        <v>51.77</v>
+        <v>51.48</v>
       </c>
       <c r="D99" s="5" t="n">
         <v>71.51000000000001</v>
       </c>
       <c r="E99" s="5" t="n">
-        <v>74.2</v>
+        <v>73.79000000000001</v>
       </c>
     </row>
     <row r="100">
@@ -7833,13 +7833,13 @@
         <v>51.5</v>
       </c>
       <c r="C100" s="5" t="n">
-        <v>50.69</v>
+        <v>53.74</v>
       </c>
       <c r="D100" s="5" t="n">
         <v>73.52</v>
       </c>
       <c r="E100" s="5" t="n">
-        <v>72.36</v>
+        <v>76.70999999999999</v>
       </c>
     </row>
     <row r="101">
@@ -7852,13 +7852,13 @@
         <v>45.87</v>
       </c>
       <c r="C101" s="5" t="n">
-        <v>49.44</v>
+        <v>49.24</v>
       </c>
       <c r="D101" s="5" t="n">
         <v>65.22</v>
       </c>
       <c r="E101" s="5" t="n">
-        <v>70.29000000000001</v>
+        <v>70.01000000000001</v>
       </c>
     </row>
     <row r="102">
@@ -7871,13 +7871,13 @@
         <v>42.43</v>
       </c>
       <c r="C102" s="5" t="n">
-        <v>44.8</v>
+        <v>44.67</v>
       </c>
       <c r="D102" s="5" t="n">
         <v>60.08</v>
       </c>
       <c r="E102" s="5" t="n">
-        <v>63.44</v>
+        <v>63.26</v>
       </c>
     </row>
     <row r="103">
@@ -7890,13 +7890,13 @@
         <v>38.6</v>
       </c>
       <c r="C103" s="5" t="n">
-        <v>41.47</v>
+        <v>41.23</v>
       </c>
       <c r="D103" s="5" t="n">
         <v>54.53</v>
       </c>
       <c r="E103" s="5" t="n">
-        <v>58.58</v>
+        <v>58.24</v>
       </c>
     </row>
     <row r="104">
@@ -7909,13 +7909,13 @@
         <v>47.09</v>
       </c>
       <c r="C104" s="5" t="n">
-        <v>52.99</v>
+        <v>52.96</v>
       </c>
       <c r="D104" s="5" t="n">
         <v>66.36</v>
       </c>
       <c r="E104" s="5" t="n">
-        <v>74.68000000000001</v>
+        <v>74.64</v>
       </c>
     </row>
     <row r="105">
@@ -7928,13 +7928,13 @@
         <v>37.6</v>
       </c>
       <c r="C105" s="5" t="n">
-        <v>37.58</v>
+        <v>37.37</v>
       </c>
       <c r="D105" s="5" t="n">
         <v>52.86</v>
       </c>
       <c r="E105" s="5" t="n">
-        <v>52.84</v>
+        <v>52.54</v>
       </c>
     </row>
     <row r="106">
@@ -7947,13 +7947,13 @@
         <v>34.88</v>
       </c>
       <c r="C106" s="5" t="n">
-        <v>29.48</v>
+        <v>29.27</v>
       </c>
       <c r="D106" s="5" t="n">
         <v>48.94</v>
       </c>
       <c r="E106" s="5" t="n">
-        <v>41.37</v>
+        <v>41.07</v>
       </c>
     </row>
     <row r="107">
@@ -7966,13 +7966,13 @@
         <v>43.89</v>
       </c>
       <c r="C107" s="5" t="n">
-        <v>43.27</v>
+        <v>42.97</v>
       </c>
       <c r="D107" s="5" t="n">
         <v>61.46</v>
       </c>
       <c r="E107" s="5" t="n">
-        <v>60.6</v>
+        <v>60.18</v>
       </c>
     </row>
     <row r="108">
@@ -7985,13 +7985,13 @@
         <v>44.78</v>
       </c>
       <c r="C108" s="5" t="n">
-        <v>45.47</v>
+        <v>45.1</v>
       </c>
       <c r="D108" s="5" t="n">
         <v>62.59</v>
       </c>
       <c r="E108" s="5" t="n">
-        <v>63.55</v>
+        <v>63.04</v>
       </c>
     </row>
     <row r="109">
@@ -8004,13 +8004,13 @@
         <v>37.68</v>
       </c>
       <c r="C109" s="5" t="n">
-        <v>38.57</v>
+        <v>38.42</v>
       </c>
       <c r="D109" s="5" t="n">
         <v>52.58</v>
       </c>
       <c r="E109" s="5" t="n">
-        <v>53.82</v>
+        <v>53.61</v>
       </c>
     </row>
     <row r="110">
@@ -8023,13 +8023,13 @@
         <v>36.52</v>
       </c>
       <c r="C110" s="5" t="n">
-        <v>40.99</v>
+        <v>40.85</v>
       </c>
       <c r="D110" s="5" t="n">
         <v>50.87</v>
       </c>
       <c r="E110" s="5" t="n">
-        <v>57.1</v>
+        <v>56.9</v>
       </c>
     </row>
     <row r="111">
@@ -8042,13 +8042,13 @@
         <v>43.15</v>
       </c>
       <c r="C111" s="5" t="n">
-        <v>44.06</v>
+        <v>43.96</v>
       </c>
       <c r="D111" s="5" t="n">
         <v>60.01</v>
       </c>
       <c r="E111" s="5" t="n">
-        <v>61.27</v>
+        <v>61.13</v>
       </c>
     </row>
     <row r="112">
@@ -8061,13 +8061,13 @@
         <v>33.83</v>
       </c>
       <c r="C112" s="5" t="n">
-        <v>37.29</v>
+        <v>37.17</v>
       </c>
       <c r="D112" s="5" t="n">
         <v>46.98</v>
       </c>
       <c r="E112" s="5" t="n">
-        <v>51.78</v>
+        <v>51.62</v>
       </c>
     </row>
     <row r="113">
@@ -8080,13 +8080,13 @@
         <v>36.34</v>
       </c>
       <c r="C113" s="5" t="n">
-        <v>41.88</v>
+        <v>41.72</v>
       </c>
       <c r="D113" s="5" t="n">
         <v>50.39</v>
       </c>
       <c r="E113" s="5" t="n">
-        <v>58.08</v>
+        <v>57.86</v>
       </c>
     </row>
     <row r="114">
@@ -8099,13 +8099,13 @@
         <v>37.65</v>
       </c>
       <c r="C114" s="5" t="n">
-        <v>40.3</v>
+        <v>39.82</v>
       </c>
       <c r="D114" s="5" t="n">
         <v>52.14</v>
       </c>
       <c r="E114" s="5" t="n">
-        <v>55.81</v>
+        <v>55.14</v>
       </c>
     </row>
     <row r="115">
@@ -8118,13 +8118,13 @@
         <v>34.91</v>
       </c>
       <c r="C115" s="5" t="n">
-        <v>32.91</v>
+        <v>32.77</v>
       </c>
       <c r="D115" s="5" t="n">
         <v>48.31</v>
       </c>
       <c r="E115" s="5" t="n">
-        <v>45.55</v>
+        <v>45.35</v>
       </c>
     </row>
     <row r="116">
@@ -8137,13 +8137,13 @@
         <v>39.94</v>
       </c>
       <c r="C116" s="5" t="n">
-        <v>37.03</v>
+        <v>37.02</v>
       </c>
       <c r="D116" s="5" t="n">
         <v>55.24</v>
       </c>
       <c r="E116" s="5" t="n">
-        <v>51.21</v>
+        <v>51.2</v>
       </c>
     </row>
     <row r="117">
@@ -8156,13 +8156,13 @@
         <v>45.26</v>
       </c>
       <c r="C117" s="5" t="n">
-        <v>44.4</v>
+        <v>44.27</v>
       </c>
       <c r="D117" s="5" t="n">
         <v>62.56</v>
       </c>
       <c r="E117" s="5" t="n">
-        <v>61.37</v>
+        <v>61.19</v>
       </c>
     </row>
     <row r="118">
@@ -8175,13 +8175,13 @@
         <v>35.08</v>
       </c>
       <c r="C118" s="5" t="n">
-        <v>36.8</v>
+        <v>36.59</v>
       </c>
       <c r="D118" s="5" t="n">
         <v>48.46</v>
       </c>
       <c r="E118" s="5" t="n">
-        <v>50.83</v>
+        <v>50.54</v>
       </c>
     </row>
     <row r="119">
@@ -8194,13 +8194,13 @@
         <v>42.54</v>
       </c>
       <c r="C119" s="5" t="n">
-        <v>41.1</v>
+        <v>40.89</v>
       </c>
       <c r="D119" s="5" t="n">
         <v>58.72</v>
       </c>
       <c r="E119" s="5" t="n">
-        <v>56.74</v>
+        <v>56.45</v>
       </c>
     </row>
     <row r="120">
@@ -8213,13 +8213,13 @@
         <v>39.77</v>
       </c>
       <c r="C120" s="5" t="n">
-        <v>39.98</v>
+        <v>39.56</v>
       </c>
       <c r="D120" s="5" t="n">
         <v>54.87</v>
       </c>
       <c r="E120" s="5" t="n">
-        <v>55.16</v>
+        <v>54.58</v>
       </c>
     </row>
     <row r="121">
@@ -8232,13 +8232,13 @@
         <v>40.64</v>
       </c>
       <c r="C121" s="5" t="n">
-        <v>38.37</v>
+        <v>38.06</v>
       </c>
       <c r="D121" s="5" t="n">
         <v>55.93</v>
       </c>
       <c r="E121" s="5" t="n">
-        <v>52.81</v>
+        <v>52.38</v>
       </c>
     </row>
     <row r="122">
@@ -8251,13 +8251,13 @@
         <v>28.3</v>
       </c>
       <c r="C122" s="5" t="n">
-        <v>37.02</v>
+        <v>33.76</v>
       </c>
       <c r="D122" s="5" t="n">
         <v>38.86</v>
       </c>
       <c r="E122" s="5" t="n">
-        <v>50.83</v>
+        <v>46.35</v>
       </c>
     </row>
     <row r="123">
@@ -8270,13 +8270,13 @@
         <v>32.25</v>
       </c>
       <c r="C123" s="5" t="n">
-        <v>37.68</v>
+        <v>37.17</v>
       </c>
       <c r="D123" s="5" t="n">
         <v>44.18</v>
       </c>
       <c r="E123" s="5" t="n">
-        <v>51.61</v>
+        <v>50.92</v>
       </c>
     </row>
     <row r="124">
@@ -8289,13 +8289,13 @@
         <v>34.9</v>
       </c>
       <c r="C124" s="5" t="n">
-        <v>39.11</v>
+        <v>38.8</v>
       </c>
       <c r="D124" s="5" t="n">
         <v>47.74</v>
       </c>
       <c r="E124" s="5" t="n">
-        <v>53.5</v>
+        <v>53.08</v>
       </c>
     </row>
     <row r="125">
@@ -8308,13 +8308,13 @@
         <v>31.89</v>
       </c>
       <c r="C125" s="5" t="n">
-        <v>38.28</v>
+        <v>37.69</v>
       </c>
       <c r="D125" s="5" t="n">
         <v>43.57</v>
       </c>
       <c r="E125" s="5" t="n">
-        <v>52.3</v>
+        <v>51.49</v>
       </c>
     </row>
     <row r="126">
@@ -8327,13 +8327,13 @@
         <v>46.02</v>
       </c>
       <c r="C126" s="5" t="n">
-        <v>48.78</v>
+        <v>48.67</v>
       </c>
       <c r="D126" s="5" t="n">
         <v>62.79</v>
       </c>
       <c r="E126" s="5" t="n">
-        <v>66.56</v>
+        <v>66.41</v>
       </c>
     </row>
     <row r="127">
@@ -8346,13 +8346,13 @@
         <v>59.22</v>
       </c>
       <c r="C127" s="5" t="n">
-        <v>60.34</v>
+        <v>60.05</v>
       </c>
       <c r="D127" s="5" t="n">
         <v>80.7</v>
       </c>
       <c r="E127" s="5" t="n">
-        <v>82.23</v>
+        <v>81.83</v>
       </c>
     </row>
     <row r="128">
@@ -8365,13 +8365,13 @@
         <v>83.73</v>
       </c>
       <c r="C128" s="5" t="n">
-        <v>85.88</v>
+        <v>85.7</v>
       </c>
       <c r="D128" s="5" t="n">
         <v>113.96</v>
       </c>
       <c r="E128" s="5" t="n">
-        <v>116.88</v>
+        <v>116.64</v>
       </c>
     </row>
     <row r="129">
@@ -8384,13 +8384,13 @@
         <v>96.09999999999999</v>
       </c>
       <c r="C129" s="5" t="n">
-        <v>97.17</v>
+        <v>96.81999999999999</v>
       </c>
       <c r="D129" s="5" t="n">
         <v>130.62</v>
       </c>
       <c r="E129" s="5" t="n">
-        <v>132.08</v>
+        <v>131.6</v>
       </c>
     </row>
     <row r="130">
@@ -8403,13 +8403,13 @@
         <v>112.73</v>
       </c>
       <c r="C130" s="5" t="n">
-        <v>114.3</v>
+        <v>112.56</v>
       </c>
       <c r="D130" s="5" t="n">
         <v>153.33</v>
       </c>
       <c r="E130" s="5" t="n">
-        <v>155.46</v>
+        <v>153.1</v>
       </c>
     </row>
     <row r="131">
@@ -8422,13 +8422,13 @@
         <v>165.67</v>
       </c>
       <c r="C131" s="5" t="n">
-        <v>164</v>
+        <v>163.47</v>
       </c>
       <c r="D131" s="5" t="n">
         <v>225.48</v>
       </c>
       <c r="E131" s="5" t="n">
-        <v>223.21</v>
+        <v>222.49</v>
       </c>
     </row>
     <row r="132">
@@ -8441,13 +8441,13 @@
         <v>252.37</v>
       </c>
       <c r="C132" s="5" t="n">
-        <v>256.22</v>
+        <v>255.9</v>
       </c>
       <c r="D132" s="5" t="n">
         <v>343.72</v>
       </c>
       <c r="E132" s="5" t="n">
-        <v>348.96</v>
+        <v>348.52</v>
       </c>
     </row>
     <row r="133">
@@ -8460,13 +8460,13 @@
         <v>236.85</v>
       </c>
       <c r="C133" s="5" t="n">
-        <v>236.68</v>
+        <v>227.53</v>
       </c>
       <c r="D133" s="5" t="n">
         <v>322.11</v>
       </c>
       <c r="E133" s="5" t="n">
-        <v>321.88</v>
+        <v>309.43</v>
       </c>
     </row>
     <row r="134">
@@ -8479,13 +8479,13 @@
         <v>45.45</v>
       </c>
       <c r="C134" s="5" t="n">
-        <v>57.34</v>
+        <v>57</v>
       </c>
       <c r="D134" s="5" t="n">
         <v>61.72</v>
       </c>
       <c r="E134" s="5" t="n">
-        <v>77.87</v>
+        <v>77.40000000000001</v>
       </c>
     </row>
     <row r="135">
@@ -8498,13 +8498,13 @@
         <v>72.5</v>
       </c>
       <c r="C135" s="5" t="n">
-        <v>100.06</v>
+        <v>98.19</v>
       </c>
       <c r="D135" s="5" t="n">
         <v>98.31</v>
       </c>
       <c r="E135" s="5" t="n">
-        <v>135.68</v>
+        <v>133.15</v>
       </c>
     </row>
     <row r="136">
@@ -8517,13 +8517,13 @@
         <v>67.92</v>
       </c>
       <c r="C136" s="5" t="n">
-        <v>97.12</v>
+        <v>95.26000000000001</v>
       </c>
       <c r="D136" s="5" t="n">
         <v>91.88</v>
       </c>
       <c r="E136" s="5" t="n">
-        <v>131.39</v>
+        <v>128.87</v>
       </c>
     </row>
     <row r="137">
@@ -8536,13 +8536,13 @@
         <v>43.68</v>
       </c>
       <c r="C137" s="5" t="n">
-        <v>58.34</v>
+        <v>56.46</v>
       </c>
       <c r="D137" s="5" t="n">
         <v>58.95</v>
       </c>
       <c r="E137" s="5" t="n">
-        <v>78.73999999999999</v>
+        <v>76.2</v>
       </c>
     </row>
     <row r="138">
@@ -8555,13 +8555,13 @@
         <v>46.18</v>
       </c>
       <c r="C138" s="5" t="n">
-        <v>52.77</v>
+        <v>52.02</v>
       </c>
       <c r="D138" s="5" t="n">
         <v>62.18</v>
       </c>
       <c r="E138" s="5" t="n">
-        <v>71.06</v>
+        <v>70.05</v>
       </c>
     </row>
     <row r="139">
@@ -8574,13 +8574,13 @@
         <v>33.22</v>
       </c>
       <c r="C139" s="5" t="n">
-        <v>42.16</v>
+        <v>39.37</v>
       </c>
       <c r="D139" s="5" t="n">
         <v>44.65</v>
       </c>
       <c r="E139" s="5" t="n">
-        <v>56.67</v>
+        <v>52.92</v>
       </c>
     </row>
     <row r="140">
@@ -8593,13 +8593,13 @@
         <v>37.58</v>
       </c>
       <c r="C140" s="5" t="n">
-        <v>52.68</v>
+        <v>50.91</v>
       </c>
       <c r="D140" s="5" t="n">
         <v>50.43</v>
       </c>
       <c r="E140" s="5" t="n">
-        <v>70.69</v>
+        <v>68.31</v>
       </c>
     </row>
     <row r="141">
@@ -8612,13 +8612,13 @@
         <v>41.3</v>
       </c>
       <c r="C141" s="5" t="n">
-        <v>46.61</v>
+        <v>45.93</v>
       </c>
       <c r="D141" s="5" t="n">
         <v>55.32</v>
       </c>
       <c r="E141" s="5" t="n">
-        <v>62.43</v>
+        <v>61.52</v>
       </c>
     </row>
     <row r="142">
@@ -8631,13 +8631,13 @@
         <v>86.11</v>
       </c>
       <c r="C142" s="5" t="n">
-        <v>91.34999999999999</v>
+        <v>90.94</v>
       </c>
       <c r="D142" s="5" t="n">
         <v>115.17</v>
       </c>
       <c r="E142" s="5" t="n">
-        <v>122.18</v>
+        <v>121.63</v>
       </c>
     </row>
     <row r="143">
@@ -8650,13 +8650,13 @@
         <v>94.38</v>
       </c>
       <c r="C143" s="5" t="n">
-        <v>104.02</v>
+        <v>102.31</v>
       </c>
       <c r="D143" s="5" t="n">
         <v>126.04</v>
       </c>
       <c r="E143" s="5" t="n">
-        <v>138.91</v>
+        <v>136.63</v>
       </c>
     </row>
     <row r="144">
@@ -8669,13 +8669,13 @@
         <v>113.81</v>
       </c>
       <c r="C144" s="5" t="n">
-        <v>117.62</v>
+        <v>116.54</v>
       </c>
       <c r="D144" s="5" t="n">
         <v>151.75</v>
       </c>
       <c r="E144" s="5" t="n">
-        <v>156.83</v>
+        <v>155.39</v>
       </c>
     </row>
     <row r="145">
@@ -8688,13 +8688,13 @@
         <v>131.25</v>
       </c>
       <c r="C145" s="5" t="n">
-        <v>128.93</v>
+        <v>127.22</v>
       </c>
       <c r="D145" s="5" t="n">
         <v>174.89</v>
       </c>
       <c r="E145" s="5" t="n">
-        <v>171.8</v>
+        <v>169.52</v>
       </c>
     </row>
     <row r="146">
@@ -8707,13 +8707,13 @@
         <v>107.94</v>
       </c>
       <c r="C146" s="5" t="n">
-        <v>118.62</v>
+        <v>117.37</v>
       </c>
       <c r="D146" s="5" t="n">
         <v>143.74</v>
       </c>
       <c r="E146" s="5" t="n">
-        <v>157.96</v>
+        <v>156.29</v>
       </c>
     </row>
     <row r="147">
@@ -8726,13 +8726,13 @@
         <v>103.84</v>
       </c>
       <c r="C147" s="5" t="n">
-        <v>109.77</v>
+        <v>109.28</v>
       </c>
       <c r="D147" s="5" t="n">
         <v>138.19</v>
       </c>
       <c r="E147" s="5" t="n">
-        <v>146.08</v>
+        <v>145.43</v>
       </c>
     </row>
     <row r="148">
@@ -8745,13 +8745,13 @@
         <v>116.03</v>
       </c>
       <c r="C148" s="5" t="n">
-        <v>126.14</v>
+        <v>125.08</v>
       </c>
       <c r="D148" s="5" t="n">
         <v>154.1</v>
       </c>
       <c r="E148" s="5" t="n">
-        <v>167.52</v>
+        <v>166.11</v>
       </c>
     </row>
     <row r="149">
@@ -8764,13 +8764,13 @@
         <v>97.20999999999999</v>
       </c>
       <c r="C149" s="5" t="n">
-        <v>110.94</v>
+        <v>109.03</v>
       </c>
       <c r="D149" s="5" t="n">
         <v>128.84</v>
       </c>
       <c r="E149" s="5" t="n">
-        <v>147.04</v>
+        <v>144.51</v>
       </c>
     </row>
     <row r="150">
@@ -8783,13 +8783,13 @@
         <v>73.58</v>
       </c>
       <c r="C150" s="5" t="n">
-        <v>82.05</v>
+        <v>81.7</v>
       </c>
       <c r="D150" s="5" t="n">
         <v>97.31999999999999</v>
       </c>
       <c r="E150" s="5" t="n">
-        <v>108.53</v>
+        <v>108.06</v>
       </c>
     </row>
     <row r="151">
@@ -8802,13 +8802,13 @@
         <v>68.66</v>
       </c>
       <c r="C151" s="5" t="n">
-        <v>75.56</v>
+        <v>75.29000000000001</v>
       </c>
       <c r="D151" s="5" t="n">
         <v>90.61</v>
       </c>
       <c r="E151" s="5" t="n">
-        <v>99.72</v>
+        <v>99.36</v>
       </c>
     </row>
     <row r="152">
@@ -8821,13 +8821,13 @@
         <v>94.03</v>
       </c>
       <c r="C152" s="5" t="n">
-        <v>105.59</v>
+        <v>105.28</v>
       </c>
       <c r="D152" s="5" t="n">
         <v>123.82</v>
       </c>
       <c r="E152" s="5" t="n">
-        <v>139.04</v>
+        <v>138.63</v>
       </c>
     </row>
     <row r="153">
@@ -8840,13 +8840,13 @@
         <v>90.95999999999999</v>
       </c>
       <c r="C153" s="5" t="n">
-        <v>106.82</v>
+        <v>106.8</v>
       </c>
       <c r="D153" s="5" t="n">
         <v>119.51</v>
       </c>
       <c r="E153" s="5" t="n">
-        <v>140.35</v>
+        <v>140.32</v>
       </c>
     </row>
     <row r="154">
@@ -8859,13 +8859,13 @@
         <v>98.97</v>
       </c>
       <c r="C154" s="5" t="n">
-        <v>95.51000000000001</v>
+        <v>96.02</v>
       </c>
       <c r="D154" s="5" t="n">
         <v>129.84</v>
       </c>
       <c r="E154" s="5" t="n">
-        <v>125.3</v>
+        <v>125.97</v>
       </c>
     </row>
     <row r="155">
@@ -8878,13 +8878,13 @@
         <v>89.27</v>
       </c>
       <c r="C155" s="5" t="n">
-        <v>89.34999999999999</v>
+        <v>89.25</v>
       </c>
       <c r="D155" s="5" t="n">
         <v>116.95</v>
       </c>
       <c r="E155" s="5" t="n">
-        <v>117.05</v>
+        <v>116.92</v>
       </c>
     </row>
     <row r="156">
@@ -8897,13 +8897,13 @@
         <v>83.52</v>
       </c>
       <c r="C156" s="5" t="n">
-        <v>86.02</v>
+        <v>85.43000000000001</v>
       </c>
       <c r="D156" s="5" t="n">
         <v>109.26</v>
       </c>
       <c r="E156" s="5" t="n">
-        <v>112.53</v>
+        <v>111.75</v>
       </c>
     </row>
     <row r="157">
@@ -8916,13 +8916,13 @@
         <v>80.70999999999999</v>
       </c>
       <c r="C157" s="5" t="n">
-        <v>80.12</v>
+        <v>80.17</v>
       </c>
       <c r="D157" s="5" t="n">
         <v>105.45</v>
       </c>
       <c r="E157" s="5" t="n">
-        <v>104.68</v>
+        <v>104.75</v>
       </c>
     </row>
     <row r="158">
@@ -8935,13 +8935,13 @@
         <v>76.56</v>
       </c>
       <c r="C158" s="5" t="n">
-        <v>79.66</v>
+        <v>79.65000000000001</v>
       </c>
       <c r="D158" s="5" t="n">
         <v>99.91</v>
       </c>
       <c r="E158" s="5" t="n">
-        <v>103.96</v>
+        <v>103.95</v>
       </c>
     </row>
     <row r="159">
@@ -8954,13 +8954,13 @@
         <v>73.59</v>
       </c>
       <c r="C159" s="5" t="n">
-        <v>81.06</v>
+        <v>80.17</v>
       </c>
       <c r="D159" s="5" t="n">
         <v>95.92</v>
       </c>
       <c r="E159" s="5" t="n">
-        <v>105.66</v>
+        <v>104.5</v>
       </c>
     </row>
     <row r="160">
@@ -8973,13 +8973,13 @@
         <v>44.85</v>
       </c>
       <c r="C160" s="5" t="n">
-        <v>50.01</v>
+        <v>49.51</v>
       </c>
       <c r="D160" s="5" t="n">
         <v>58.38</v>
       </c>
       <c r="E160" s="5" t="n">
-        <v>65.09</v>
+        <v>64.44</v>
       </c>
     </row>
     <row r="161">
@@ -8992,13 +8992,13 @@
         <v>25.03</v>
       </c>
       <c r="C161" s="5" t="n">
-        <v>31.66</v>
+        <v>31.23</v>
       </c>
       <c r="D161" s="5" t="n">
         <v>32.53</v>
       </c>
       <c r="E161" s="5" t="n">
-        <v>41.15</v>
+        <v>40.59</v>
       </c>
     </row>
     <row r="162">
@@ -9011,13 +9011,13 @@
         <v>60.86</v>
       </c>
       <c r="C162" s="5" t="n">
-        <v>75.48</v>
+        <v>70.7</v>
       </c>
       <c r="D162" s="5" t="n">
         <v>78.98999999999999</v>
       </c>
       <c r="E162" s="5" t="n">
-        <v>97.95999999999999</v>
+        <v>91.76000000000001</v>
       </c>
     </row>
     <row r="163">
@@ -9030,13 +9030,13 @@
         <v>95.37</v>
       </c>
       <c r="C163" s="5" t="n">
-        <v>102.32</v>
+        <v>101.45</v>
       </c>
       <c r="D163" s="5" t="n">
         <v>123.56</v>
       </c>
       <c r="E163" s="5" t="n">
-        <v>132.57</v>
+        <v>131.44</v>
       </c>
     </row>
     <row r="164">
@@ -9049,13 +9049,13 @@
         <v>85.59999999999999</v>
       </c>
       <c r="C164" s="5" t="n">
-        <v>88.54000000000001</v>
+        <v>88.25</v>
       </c>
       <c r="D164" s="5" t="n">
         <v>110.71</v>
       </c>
       <c r="E164" s="5" t="n">
-        <v>114.52</v>
+        <v>114.14</v>
       </c>
     </row>
     <row r="165">
@@ -9068,13 +9068,13 @@
         <v>72.13</v>
       </c>
       <c r="C165" s="5" t="n">
-        <v>71.18000000000001</v>
+        <v>70.48</v>
       </c>
       <c r="D165" s="5" t="n">
         <v>93.13</v>
       </c>
       <c r="E165" s="5" t="n">
-        <v>91.90000000000001</v>
+        <v>91</v>
       </c>
     </row>
     <row r="166">
@@ -9087,13 +9087,13 @@
         <v>147.91</v>
       </c>
       <c r="C166" s="5" t="n">
-        <v>163.88</v>
+        <v>163</v>
       </c>
       <c r="D166" s="5" t="n">
         <v>190.98</v>
       </c>
       <c r="E166" s="5" t="n">
-        <v>211.6</v>
+        <v>210.46</v>
       </c>
     </row>
     <row r="167">
@@ -9106,13 +9106,13 @@
         <v>134.79</v>
       </c>
       <c r="C167" s="5" t="n">
-        <v>133.69</v>
+        <v>133.08</v>
       </c>
       <c r="D167" s="5" t="n">
         <v>174.05</v>
       </c>
       <c r="E167" s="5" t="n">
-        <v>172.63</v>
+        <v>171.84</v>
       </c>
     </row>
     <row r="168">
@@ -9125,13 +9125,13 @@
         <v>123.43</v>
       </c>
       <c r="C168" s="5" t="n">
-        <v>115.58</v>
+        <v>114.79</v>
       </c>
       <c r="D168" s="5" t="n">
         <v>159.39</v>
       </c>
       <c r="E168" s="5" t="n">
-        <v>149.25</v>
+        <v>148.23</v>
       </c>
     </row>
     <row r="169">
@@ -9144,13 +9144,13 @@
         <v>104.72</v>
       </c>
       <c r="C169" s="5" t="n">
-        <v>109.29</v>
+        <v>108.07</v>
       </c>
       <c r="D169" s="5" t="n">
         <v>134.96</v>
       </c>
       <c r="E169" s="5" t="n">
-        <v>140.85</v>
+        <v>139.28</v>
       </c>
     </row>
     <row r="170">
@@ -9163,13 +9163,13 @@
         <v>92.55</v>
       </c>
       <c r="C170" s="5" t="n">
-        <v>102.33</v>
+        <v>101.97</v>
       </c>
       <c r="D170" s="5" t="n">
         <v>119.04</v>
       </c>
       <c r="E170" s="5" t="n">
-        <v>131.62</v>
+        <v>131.16</v>
       </c>
     </row>
     <row r="171">
@@ -9182,13 +9182,13 @@
         <v>96.8</v>
       </c>
       <c r="C171" s="5" t="n">
-        <v>109.49</v>
+        <v>108.62</v>
       </c>
       <c r="D171" s="5" t="n">
         <v>124.26</v>
       </c>
       <c r="E171" s="5" t="n">
-        <v>140.55</v>
+        <v>139.43</v>
       </c>
     </row>
     <row r="172">
@@ -9201,13 +9201,13 @@
         <v>74.77</v>
       </c>
       <c r="C172" s="5" t="n">
-        <v>89.78</v>
+        <v>89.16</v>
       </c>
       <c r="D172" s="5" t="n">
         <v>95.8</v>
       </c>
       <c r="E172" s="5" t="n">
-        <v>115.03</v>
+        <v>114.24</v>
       </c>
     </row>
     <row r="173">
@@ -9220,13 +9220,13 @@
         <v>70.04000000000001</v>
       </c>
       <c r="C173" s="5" t="n">
-        <v>81.81</v>
+        <v>80.14</v>
       </c>
       <c r="D173" s="5" t="n">
         <v>89.56999999999999</v>
       </c>
       <c r="E173" s="5" t="n">
-        <v>104.62</v>
+        <v>102.49</v>
       </c>
     </row>
     <row r="174">
@@ -9239,13 +9239,13 @@
         <v>57.62</v>
       </c>
       <c r="C174" s="5" t="n">
-        <v>63.98</v>
+        <v>63.58</v>
       </c>
       <c r="D174" s="5" t="n">
         <v>73.55</v>
       </c>
       <c r="E174" s="5" t="n">
-        <v>81.67</v>
+        <v>81.16</v>
       </c>
     </row>
     <row r="175">
@@ -9258,13 +9258,13 @@
         <v>107.68</v>
       </c>
       <c r="C175" s="5" t="n">
-        <v>106.88</v>
+        <v>105.77</v>
       </c>
       <c r="D175" s="5" t="n">
         <v>137.14</v>
       </c>
       <c r="E175" s="5" t="n">
-        <v>136.12</v>
+        <v>134.71</v>
       </c>
     </row>
     <row r="176">
@@ -9277,13 +9277,13 @@
         <v>68.29000000000001</v>
       </c>
       <c r="C176" s="5" t="n">
-        <v>77.56</v>
+        <v>76.48</v>
       </c>
       <c r="D176" s="5" t="n">
         <v>86.77</v>
       </c>
       <c r="E176" s="5" t="n">
-        <v>98.55</v>
+        <v>97.18000000000001</v>
       </c>
     </row>
     <row r="177">
@@ -9296,13 +9296,13 @@
         <v>52.18</v>
       </c>
       <c r="C177" s="5" t="n">
-        <v>50.23</v>
+        <v>49.82</v>
       </c>
       <c r="D177" s="5" t="n">
         <v>66.15000000000001</v>
       </c>
       <c r="E177" s="5" t="n">
-        <v>63.68</v>
+        <v>63.16</v>
       </c>
     </row>
     <row r="178">
@@ -9315,13 +9315,13 @@
         <v>56.84</v>
       </c>
       <c r="C178" s="5" t="n">
-        <v>49.85</v>
+        <v>49.53</v>
       </c>
       <c r="D178" s="5" t="n">
         <v>71.97</v>
       </c>
       <c r="E178" s="5" t="n">
-        <v>63.12</v>
+        <v>62.72</v>
       </c>
     </row>
     <row r="179">
@@ -9334,13 +9334,13 @@
         <v>39.1</v>
       </c>
       <c r="C179" s="5" t="n">
-        <v>38.9</v>
+        <v>38.95</v>
       </c>
       <c r="D179" s="5" t="n">
         <v>49.45</v>
       </c>
       <c r="E179" s="5" t="n">
-        <v>49.19</v>
+        <v>49.26</v>
       </c>
     </row>
     <row r="180">
@@ -9353,13 +9353,13 @@
         <v>37.37</v>
       </c>
       <c r="C180" s="5" t="n">
-        <v>35.52</v>
+        <v>34.97</v>
       </c>
       <c r="D180" s="5" t="n">
         <v>47.2</v>
       </c>
       <c r="E180" s="5" t="n">
-        <v>44.86</v>
+        <v>44.17</v>
       </c>
     </row>
     <row r="181">
@@ -9372,13 +9372,13 @@
         <v>23.37</v>
       </c>
       <c r="C181" s="5" t="n">
-        <v>24.48</v>
+        <v>24.19</v>
       </c>
       <c r="D181" s="5" t="n">
         <v>29.71</v>
       </c>
       <c r="E181" s="5" t="n">
-        <v>31.12</v>
+        <v>30.75</v>
       </c>
     </row>
     <row r="182">
@@ -9391,13 +9391,13 @@
         <v>34.77</v>
       </c>
       <c r="C182" s="5" t="n">
-        <v>41.19</v>
+        <v>40.61</v>
       </c>
       <c r="D182" s="5" t="n">
         <v>44.49</v>
       </c>
       <c r="E182" s="5" t="n">
-        <v>52.7</v>
+        <v>51.96</v>
       </c>
     </row>
     <row r="183">
@@ -9410,13 +9410,13 @@
         <v>36.41</v>
       </c>
       <c r="C183" s="5" t="n">
-        <v>39.42</v>
+        <v>39.02</v>
       </c>
       <c r="D183" s="5" t="n">
         <v>46.89</v>
       </c>
       <c r="E183" s="5" t="n">
-        <v>50.77</v>
+        <v>50.25</v>
       </c>
     </row>
     <row r="184">
@@ -9429,13 +9429,13 @@
         <v>56.6</v>
       </c>
       <c r="C184" s="5" t="n">
-        <v>57.55</v>
+        <v>57.29</v>
       </c>
       <c r="D184" s="5" t="n">
         <v>72.52</v>
       </c>
       <c r="E184" s="5" t="n">
-        <v>73.73999999999999</v>
+        <v>73.40000000000001</v>
       </c>
     </row>
     <row r="185">
@@ -9448,13 +9448,13 @@
         <v>55.75</v>
       </c>
       <c r="C185" s="5" t="n">
-        <v>56.78</v>
+        <v>56.57</v>
       </c>
       <c r="D185" s="5" t="n">
         <v>71.06999999999999</v>
       </c>
       <c r="E185" s="5" t="n">
-        <v>72.38</v>
+        <v>72.11</v>
       </c>
     </row>
     <row r="186">
@@ -9467,13 +9467,13 @@
         <v>37.52</v>
       </c>
       <c r="C186" s="5" t="n">
-        <v>39.19</v>
+        <v>38.94</v>
       </c>
       <c r="D186" s="5" t="n">
         <v>47.58</v>
       </c>
       <c r="E186" s="5" t="n">
-        <v>49.7</v>
+        <v>49.39</v>
       </c>
     </row>
     <row r="187">
@@ -9486,13 +9486,13 @@
         <v>41.51</v>
       </c>
       <c r="C187" s="5" t="n">
-        <v>42.32</v>
+        <v>37.37</v>
       </c>
       <c r="D187" s="5" t="n">
         <v>52.49</v>
       </c>
       <c r="E187" s="5" t="n">
-        <v>53.51</v>
+        <v>47.25</v>
       </c>
     </row>
     <row r="188">
@@ -9505,13 +9505,13 @@
         <v>59.37</v>
       </c>
       <c r="C188" s="5" t="n">
-        <v>57.44</v>
+        <v>57.08</v>
       </c>
       <c r="D188" s="5" t="n">
         <v>74.84</v>
       </c>
       <c r="E188" s="5" t="n">
-        <v>72.41</v>
+        <v>71.95999999999999</v>
       </c>
     </row>
     <row r="189">
@@ -9524,13 +9524,13 @@
         <v>36.86</v>
       </c>
       <c r="C189" s="5" t="n">
-        <v>43.49</v>
+        <v>43.26</v>
       </c>
       <c r="D189" s="5" t="n">
         <v>46.33</v>
       </c>
       <c r="E189" s="5" t="n">
-        <v>54.66</v>
+        <v>54.37</v>
       </c>
     </row>
     <row r="190">
@@ -9543,13 +9543,13 @@
         <v>37.81</v>
       </c>
       <c r="C190" s="5" t="n">
-        <v>40.16</v>
+        <v>40.03</v>
       </c>
       <c r="D190" s="5" t="n">
         <v>47.43</v>
       </c>
       <c r="E190" s="5" t="n">
-        <v>50.38</v>
+        <v>50.22</v>
       </c>
     </row>
     <row r="191">
@@ -9562,13 +9562,13 @@
         <v>31.99</v>
       </c>
       <c r="C191" s="5" t="n">
-        <v>36.94</v>
+        <v>36.7</v>
       </c>
       <c r="D191" s="5" t="n">
         <v>40.05</v>
       </c>
       <c r="E191" s="5" t="n">
-        <v>46.25</v>
+        <v>45.95</v>
       </c>
     </row>
     <row r="192">
@@ -9581,13 +9581,13 @@
         <v>30.78</v>
       </c>
       <c r="C192" s="5" t="n">
-        <v>31.99</v>
+        <v>31.5</v>
       </c>
       <c r="D192" s="5" t="n">
         <v>38.46</v>
       </c>
       <c r="E192" s="5" t="n">
-        <v>39.98</v>
+        <v>39.36</v>
       </c>
     </row>
     <row r="193">
@@ -9600,13 +9600,13 @@
         <v>25.34</v>
       </c>
       <c r="C193" s="5" t="n">
-        <v>28.96</v>
+        <v>28.45</v>
       </c>
       <c r="D193" s="5" t="n">
         <v>31.59</v>
       </c>
       <c r="E193" s="5" t="n">
-        <v>36.1</v>
+        <v>35.47</v>
       </c>
     </row>
     <row r="194">
@@ -9619,13 +9619,13 @@
         <v>41.25</v>
       </c>
       <c r="C194" s="5" t="n">
-        <v>45.01</v>
+        <v>44.32</v>
       </c>
       <c r="D194" s="5" t="n">
         <v>51.3</v>
       </c>
       <c r="E194" s="5" t="n">
-        <v>55.97</v>
+        <v>55.12</v>
       </c>
     </row>
     <row r="195">
@@ -9638,13 +9638,13 @@
         <v>68.88</v>
       </c>
       <c r="C195" s="5" t="n">
-        <v>77.88</v>
+        <v>77.62</v>
       </c>
       <c r="D195" s="5" t="n">
         <v>85.45</v>
       </c>
       <c r="E195" s="5" t="n">
-        <v>96.62</v>
+        <v>96.29000000000001</v>
       </c>
     </row>
     <row r="196">
@@ -9657,13 +9657,13 @@
         <v>38.15</v>
       </c>
       <c r="C196" s="5" t="n">
-        <v>43.06</v>
+        <v>42.75</v>
       </c>
       <c r="D196" s="5" t="n">
         <v>47.19</v>
       </c>
       <c r="E196" s="5" t="n">
-        <v>53.27</v>
+        <v>52.88</v>
       </c>
     </row>
     <row r="197">
@@ -9676,13 +9676,13 @@
         <v>21.46</v>
       </c>
       <c r="C197" s="5" t="n">
-        <v>25.45</v>
+        <v>24.96</v>
       </c>
       <c r="D197" s="5" t="n">
         <v>26.47</v>
       </c>
       <c r="E197" s="5" t="n">
-        <v>31.39</v>
+        <v>30.79</v>
       </c>
     </row>
     <row r="198">
@@ -9695,13 +9695,13 @@
         <v>16.52</v>
       </c>
       <c r="C198" s="5" t="n">
-        <v>22.15</v>
+        <v>21.88</v>
       </c>
       <c r="D198" s="5" t="n">
         <v>20.32</v>
       </c>
       <c r="E198" s="5" t="n">
-        <v>27.25</v>
+        <v>26.92</v>
       </c>
     </row>
     <row r="199">
@@ -9714,13 +9714,13 @@
         <v>9.380000000000001</v>
       </c>
       <c r="C199" s="5" t="n">
-        <v>9.77</v>
+        <v>9.68</v>
       </c>
       <c r="D199" s="5" t="n">
         <v>11.49</v>
       </c>
       <c r="E199" s="5" t="n">
-        <v>11.97</v>
+        <v>11.86</v>
       </c>
     </row>
     <row r="200">
@@ -9733,13 +9733,13 @@
         <v>31.76</v>
       </c>
       <c r="C200" s="5" t="n">
-        <v>33.57</v>
+        <v>33.48</v>
       </c>
       <c r="D200" s="5" t="n">
         <v>38.74</v>
       </c>
       <c r="E200" s="5" t="n">
-        <v>40.95</v>
+        <v>40.84</v>
       </c>
     </row>
     <row r="201">
@@ -9752,13 +9752,13 @@
         <v>49.85</v>
       </c>
       <c r="C201" s="5" t="n">
-        <v>50.76</v>
+        <v>50.7</v>
       </c>
       <c r="D201" s="5" t="n">
         <v>60.55</v>
       </c>
       <c r="E201" s="5" t="n">
-        <v>61.66</v>
+        <v>61.58</v>
       </c>
     </row>
     <row r="202">
@@ -9771,13 +9771,13 @@
         <v>62.54</v>
       </c>
       <c r="C202" s="5" t="n">
-        <v>66.84999999999999</v>
+        <v>66.73999999999999</v>
       </c>
       <c r="D202" s="5" t="n">
         <v>75.42</v>
       </c>
       <c r="E202" s="5" t="n">
-        <v>80.62</v>
+        <v>80.48999999999999</v>
       </c>
     </row>
     <row r="203">
@@ -9790,13 +9790,13 @@
         <v>72.20999999999999</v>
       </c>
       <c r="C203" s="5" t="n">
-        <v>78.13</v>
+        <v>78.06999999999999</v>
       </c>
       <c r="D203" s="5" t="n">
         <v>86.45999999999999</v>
       </c>
       <c r="E203" s="5" t="n">
-        <v>93.55</v>
+        <v>93.48</v>
       </c>
     </row>
     <row r="204">
@@ -9809,13 +9809,13 @@
         <v>74.83</v>
       </c>
       <c r="C204" s="5" t="n">
-        <v>78.79000000000001</v>
+        <v>78.65000000000001</v>
       </c>
       <c r="D204" s="5" t="n">
         <v>88.97</v>
       </c>
       <c r="E204" s="5" t="n">
-        <v>93.68000000000001</v>
+        <v>93.51000000000001</v>
       </c>
     </row>
     <row r="205">
@@ -9828,13 +9828,13 @@
         <v>141.27</v>
       </c>
       <c r="C205" s="5" t="n">
-        <v>165</v>
+        <v>164.79</v>
       </c>
       <c r="D205" s="5" t="n">
         <v>166.97</v>
       </c>
       <c r="E205" s="5" t="n">
-        <v>195.02</v>
+        <v>194.77</v>
       </c>
     </row>
     <row r="206">
@@ -9847,13 +9847,13 @@
         <v>217.19</v>
       </c>
       <c r="C206" s="5" t="n">
-        <v>241.96</v>
+        <v>241.85</v>
       </c>
       <c r="D206" s="5" t="n">
         <v>255.19</v>
       </c>
       <c r="E206" s="5" t="n">
-        <v>284.29</v>
+        <v>284.16</v>
       </c>
     </row>
     <row r="207">
@@ -9866,13 +9866,13 @@
         <v>286.75</v>
       </c>
       <c r="C207" s="5" t="n">
-        <v>382.49</v>
+        <v>382.13</v>
       </c>
       <c r="D207" s="5" t="n">
         <v>334.94</v>
       </c>
       <c r="E207" s="5" t="n">
-        <v>446.77</v>
+        <v>446.35</v>
       </c>
     </row>
     <row r="208">
@@ -9885,13 +9885,13 @@
         <v>322.84</v>
       </c>
       <c r="C208" s="5" t="n">
-        <v>366.3</v>
+        <v>366</v>
       </c>
       <c r="D208" s="5" t="n">
         <v>374.8</v>
       </c>
       <c r="E208" s="5" t="n">
-        <v>425.25</v>
+        <v>424.9</v>
       </c>
     </row>
     <row r="209">
@@ -9904,13 +9904,13 @@
         <v>149.51</v>
       </c>
       <c r="C209" s="5" t="n">
-        <v>169.69</v>
+        <v>169.02</v>
       </c>
       <c r="D209" s="5" t="n">
         <v>172.52</v>
       </c>
       <c r="E209" s="5" t="n">
-        <v>195.81</v>
+        <v>195.03</v>
       </c>
     </row>
     <row r="210">
@@ -9923,13 +9923,13 @@
         <v>132.74</v>
       </c>
       <c r="C210" s="5" t="n">
-        <v>150.78</v>
+        <v>150.51</v>
       </c>
       <c r="D210" s="5" t="n">
         <v>152.25</v>
       </c>
       <c r="E210" s="5" t="n">
-        <v>172.94</v>
+        <v>172.63</v>
       </c>
     </row>
     <row r="211">
@@ -9942,13 +9942,13 @@
         <v>122</v>
       </c>
       <c r="C211" s="5" t="n">
-        <v>126.75</v>
+        <v>126.49</v>
       </c>
       <c r="D211" s="5" t="n">
         <v>139.07</v>
       </c>
       <c r="E211" s="5" t="n">
-        <v>144.49</v>
+        <v>144.19</v>
       </c>
     </row>
     <row r="212">
@@ -9961,13 +9961,13 @@
         <v>100.98</v>
       </c>
       <c r="C212" s="5" t="n">
-        <v>114.81</v>
+        <v>112.35</v>
       </c>
       <c r="D212" s="5" t="n">
         <v>114.41</v>
       </c>
       <c r="E212" s="5" t="n">
-        <v>130.08</v>
+        <v>127.29</v>
       </c>
     </row>
     <row r="213">
@@ -9999,13 +9999,13 @@
         <v>86.86</v>
       </c>
       <c r="C214" s="5" t="n">
-        <v>81.12</v>
+        <v>81.09</v>
       </c>
       <c r="D214" s="5" t="n">
         <v>97.38</v>
       </c>
       <c r="E214" s="5" t="n">
-        <v>90.94</v>
+        <v>90.91</v>
       </c>
     </row>
     <row r="215">
@@ -10018,13 +10018,13 @@
         <v>81.53</v>
       </c>
       <c r="C215" s="5" t="n">
-        <v>76.66</v>
+        <v>76.56999999999999</v>
       </c>
       <c r="D215" s="5" t="n">
         <v>90.98999999999999</v>
       </c>
       <c r="E215" s="5" t="n">
-        <v>85.56</v>
+        <v>85.45999999999999</v>
       </c>
     </row>
     <row r="216">
@@ -10037,13 +10037,13 @@
         <v>72.34999999999999</v>
       </c>
       <c r="C216" s="5" t="n">
-        <v>68.13</v>
+        <v>68.09999999999999</v>
       </c>
       <c r="D216" s="5" t="n">
         <v>80.39</v>
       </c>
       <c r="E216" s="5" t="n">
-        <v>75.7</v>
+        <v>75.67</v>
       </c>
     </row>
     <row r="217">
@@ -10056,13 +10056,13 @@
         <v>70.03</v>
       </c>
       <c r="C217" s="5" t="n">
-        <v>70.95</v>
+        <v>70.91</v>
       </c>
       <c r="D217" s="5" t="n">
         <v>77.59</v>
       </c>
       <c r="E217" s="5" t="n">
-        <v>78.61</v>
+        <v>78.56</v>
       </c>
     </row>
     <row r="218">
@@ -10075,13 +10075,13 @@
         <v>84.16</v>
       </c>
       <c r="C218" s="5" t="n">
-        <v>86.54000000000001</v>
+        <v>86.34999999999999</v>
       </c>
       <c r="D218" s="5" t="n">
         <v>92.98</v>
       </c>
       <c r="E218" s="5" t="n">
-        <v>95.61</v>
+        <v>95.40000000000001</v>
       </c>
     </row>
     <row r="219">
@@ -10094,13 +10094,13 @@
         <v>38.04</v>
       </c>
       <c r="C219" s="5" t="n">
-        <v>52.33</v>
+        <v>52.09</v>
       </c>
       <c r="D219" s="5" t="n">
         <v>41.91</v>
       </c>
       <c r="E219" s="5" t="n">
-        <v>57.65</v>
+        <v>57.38</v>
       </c>
     </row>
     <row r="220">
@@ -10113,13 +10113,13 @@
         <v>23.32</v>
       </c>
       <c r="C220" s="5" t="n">
-        <v>32.72</v>
+        <v>32.62</v>
       </c>
       <c r="D220" s="5" t="n">
         <v>25.59</v>
       </c>
       <c r="E220" s="5" t="n">
-        <v>35.91</v>
+        <v>35.8</v>
       </c>
     </row>
     <row r="221">
@@ -10132,13 +10132,13 @@
         <v>37.65</v>
       </c>
       <c r="C221" s="5" t="n">
-        <v>37.93</v>
+        <v>37.77</v>
       </c>
       <c r="D221" s="5" t="n">
         <v>41.16</v>
       </c>
       <c r="E221" s="5" t="n">
-        <v>41.47</v>
+        <v>41.29</v>
       </c>
     </row>
     <row r="222">
@@ -10151,13 +10151,13 @@
         <v>26.71</v>
       </c>
       <c r="C222" s="5" t="n">
-        <v>24.88</v>
+        <v>24.86</v>
       </c>
       <c r="D222" s="5" t="n">
         <v>29.09</v>
       </c>
       <c r="E222" s="5" t="n">
-        <v>27.1</v>
+        <v>27.08</v>
       </c>
     </row>
     <row r="223">
@@ -10189,13 +10189,13 @@
         <v>59.97</v>
       </c>
       <c r="C224" s="5" t="n">
-        <v>57.48</v>
+        <v>57.49</v>
       </c>
       <c r="D224" s="5" t="n">
         <v>65.04000000000001</v>
       </c>
       <c r="E224" s="5" t="n">
-        <v>62.34</v>
+        <v>62.35</v>
       </c>
     </row>
     <row r="225">
@@ -10208,13 +10208,13 @@
         <v>52.09</v>
       </c>
       <c r="C225" s="5" t="n">
-        <v>49.05</v>
+        <v>49.09</v>
       </c>
       <c r="D225" s="5" t="n">
         <v>56.38</v>
       </c>
       <c r="E225" s="5" t="n">
-        <v>53.09</v>
+        <v>53.13</v>
       </c>
     </row>
     <row r="226">
@@ -10227,13 +10227,13 @@
         <v>50.12</v>
       </c>
       <c r="C226" s="5" t="n">
-        <v>49.55</v>
+        <v>49.62</v>
       </c>
       <c r="D226" s="5" t="n">
         <v>54.08</v>
       </c>
       <c r="E226" s="5" t="n">
-        <v>53.46</v>
+        <v>53.54</v>
       </c>
     </row>
     <row r="227">
@@ -10246,13 +10246,13 @@
         <v>81.86</v>
       </c>
       <c r="C227" s="5" t="n">
-        <v>110.19</v>
+        <v>110.18</v>
       </c>
       <c r="D227" s="5" t="n">
         <v>88.05</v>
       </c>
       <c r="E227" s="5" t="n">
-        <v>118.52</v>
+        <v>118.51</v>
       </c>
     </row>
     <row r="228">
@@ -10265,13 +10265,13 @@
         <v>69.65000000000001</v>
       </c>
       <c r="C228" s="5" t="n">
-        <v>67.51000000000001</v>
+        <v>67.43000000000001</v>
       </c>
       <c r="D228" s="5" t="n">
         <v>74.69</v>
       </c>
       <c r="E228" s="5" t="n">
-        <v>72.39</v>
+        <v>72.31</v>
       </c>
     </row>
     <row r="229">
@@ -10284,13 +10284,13 @@
         <v>73.34999999999999</v>
       </c>
       <c r="C229" s="5" t="n">
-        <v>70.58</v>
+        <v>70.53</v>
       </c>
       <c r="D229" s="5" t="n">
         <v>78.38</v>
       </c>
       <c r="E229" s="5" t="n">
-        <v>75.42</v>
+        <v>75.37</v>
       </c>
     </row>
     <row r="230">
@@ -10303,13 +10303,13 @@
         <v>141.03</v>
       </c>
       <c r="C230" s="5" t="n">
-        <v>145.64</v>
+        <v>145.36</v>
       </c>
       <c r="D230" s="5" t="n">
         <v>150.18</v>
       </c>
       <c r="E230" s="5" t="n">
-        <v>155.09</v>
+        <v>154.79</v>
       </c>
     </row>
     <row r="231">
@@ -10322,13 +10322,13 @@
         <v>178.25</v>
       </c>
       <c r="C231" s="5" t="n">
-        <v>212.93</v>
+        <v>212.7</v>
       </c>
       <c r="D231" s="5" t="n">
         <v>189.16</v>
       </c>
       <c r="E231" s="5" t="n">
-        <v>225.96</v>
+        <v>225.72</v>
       </c>
     </row>
     <row r="232">
@@ -10341,13 +10341,13 @@
         <v>180.76</v>
       </c>
       <c r="C232" s="5" t="n">
-        <v>215.63</v>
+        <v>215.33</v>
       </c>
       <c r="D232" s="5" t="n">
         <v>191.68</v>
       </c>
       <c r="E232" s="5" t="n">
-        <v>228.66</v>
+        <v>228.34</v>
       </c>
     </row>
     <row r="233">
@@ -10360,13 +10360,13 @@
         <v>128.69</v>
       </c>
       <c r="C233" s="5" t="n">
-        <v>156.24</v>
+        <v>155.78</v>
       </c>
       <c r="D233" s="5" t="n">
         <v>136.37</v>
       </c>
       <c r="E233" s="5" t="n">
-        <v>165.56</v>
+        <v>165.07</v>
       </c>
     </row>
     <row r="234">
@@ -10379,13 +10379,13 @@
         <v>22.51</v>
       </c>
       <c r="C234" s="5" t="n">
-        <v>31.25</v>
+        <v>31.21</v>
       </c>
       <c r="D234" s="5" t="n">
         <v>23.84</v>
       </c>
       <c r="E234" s="5" t="n">
-        <v>33.09</v>
+        <v>33.05</v>
       </c>
     </row>
     <row r="235">
@@ -10398,13 +10398,13 @@
         <v>49.8</v>
       </c>
       <c r="C235" s="5" t="n">
-        <v>52.52</v>
+        <v>52.54</v>
       </c>
       <c r="D235" s="5" t="n">
         <v>52.7</v>
       </c>
       <c r="E235" s="5" t="n">
-        <v>55.58</v>
+        <v>55.6</v>
       </c>
     </row>
     <row r="236">
@@ -10417,13 +10417,13 @@
         <v>95.86</v>
       </c>
       <c r="C236" s="5" t="n">
-        <v>96.58</v>
+        <v>96.67</v>
       </c>
       <c r="D236" s="5" t="n">
         <v>101.37</v>
       </c>
       <c r="E236" s="5" t="n">
-        <v>102.13</v>
+        <v>102.23</v>
       </c>
     </row>
     <row r="237">
@@ -10436,13 +10436,13 @@
         <v>76.11</v>
       </c>
       <c r="C237" s="5" t="n">
-        <v>68.48</v>
+        <v>68.69</v>
       </c>
       <c r="D237" s="5" t="n">
         <v>80.43000000000001</v>
       </c>
       <c r="E237" s="5" t="n">
-        <v>72.37</v>
+        <v>72.59</v>
       </c>
     </row>
     <row r="238">
@@ -10455,13 +10455,13 @@
         <v>113.63</v>
       </c>
       <c r="C238" s="5" t="n">
-        <v>109.08</v>
+        <v>109.16</v>
       </c>
       <c r="D238" s="5" t="n">
         <v>119.72</v>
       </c>
       <c r="E238" s="5" t="n">
-        <v>114.92</v>
+        <v>115.01</v>
       </c>
     </row>
     <row r="239">
@@ -10474,13 +10474,13 @@
         <v>121.69</v>
       </c>
       <c r="C239" s="5" t="n">
-        <v>125.01</v>
+        <v>124.99</v>
       </c>
       <c r="D239" s="5" t="n">
         <v>127.82</v>
       </c>
       <c r="E239" s="5" t="n">
-        <v>131.31</v>
+        <v>131.29</v>
       </c>
     </row>
     <row r="240">
@@ -10493,13 +10493,13 @@
         <v>100.04</v>
       </c>
       <c r="C240" s="5" t="n">
-        <v>100.83</v>
+        <v>100.72</v>
       </c>
       <c r="D240" s="5" t="n">
         <v>104.76</v>
       </c>
       <c r="E240" s="5" t="n">
-        <v>105.59</v>
+        <v>105.47</v>
       </c>
     </row>
     <row r="241">
@@ -10512,13 +10512,13 @@
         <v>100.53</v>
       </c>
       <c r="C241" s="5" t="n">
-        <v>98.58</v>
+        <v>98.45999999999999</v>
       </c>
       <c r="D241" s="5" t="n">
         <v>105.01</v>
       </c>
       <c r="E241" s="5" t="n">
-        <v>102.98</v>
+        <v>102.85</v>
       </c>
     </row>
     <row r="242">
@@ -10531,13 +10531,13 @@
         <v>103.39</v>
       </c>
       <c r="C242" s="5" t="n">
-        <v>113.37</v>
+        <v>113.21</v>
       </c>
       <c r="D242" s="5" t="n">
         <v>107.73</v>
       </c>
       <c r="E242" s="5" t="n">
-        <v>118.13</v>
+        <v>117.96</v>
       </c>
     </row>
     <row r="243">
@@ -10550,13 +10550,13 @@
         <v>219.34</v>
       </c>
       <c r="C243" s="5" t="n">
-        <v>327.99</v>
+        <v>327.6</v>
       </c>
       <c r="D243" s="5" t="n">
         <v>227.99</v>
       </c>
       <c r="E243" s="5" t="n">
-        <v>340.92</v>
+        <v>340.51</v>
       </c>
     </row>
     <row r="244">
@@ -10569,13 +10569,13 @@
         <v>117.85</v>
       </c>
       <c r="C244" s="5" t="n">
-        <v>130.45</v>
+        <v>130.22</v>
       </c>
       <c r="D244" s="5" t="n">
         <v>121.96</v>
       </c>
       <c r="E244" s="5" t="n">
-        <v>135</v>
+        <v>134.76</v>
       </c>
     </row>
     <row r="245">
@@ -10588,13 +10588,13 @@
         <v>125.22</v>
       </c>
       <c r="C245" s="5" t="n">
-        <v>133.56</v>
+        <v>133.43</v>
       </c>
       <c r="D245" s="5" t="n">
         <v>129.02</v>
       </c>
       <c r="E245" s="5" t="n">
-        <v>137.61</v>
+        <v>137.48</v>
       </c>
     </row>
     <row r="246">
@@ -10607,13 +10607,13 @@
         <v>28.63</v>
       </c>
       <c r="C246" s="5" t="n">
-        <v>36.24</v>
+        <v>36.13</v>
       </c>
       <c r="D246" s="5" t="n">
         <v>29.37</v>
       </c>
       <c r="E246" s="5" t="n">
-        <v>37.18</v>
+        <v>37.06</v>
       </c>
     </row>
     <row r="247">
@@ -10645,13 +10645,13 @@
         <v>40.51</v>
       </c>
       <c r="C248" s="5" t="n">
-        <v>34.34</v>
+        <v>34.33</v>
       </c>
       <c r="D248" s="5" t="n">
         <v>41.39</v>
       </c>
       <c r="E248" s="5" t="n">
-        <v>35.09</v>
+        <v>35.08</v>
       </c>
     </row>
     <row r="249">
@@ -10664,13 +10664,13 @@
         <v>59.34</v>
       </c>
       <c r="C249" s="5" t="n">
-        <v>55.6</v>
+        <v>55.59</v>
       </c>
       <c r="D249" s="5" t="n">
         <v>60.52</v>
       </c>
       <c r="E249" s="5" t="n">
-        <v>56.7</v>
+        <v>56.69</v>
       </c>
     </row>
     <row r="250">
@@ -10683,13 +10683,13 @@
         <v>100.93</v>
       </c>
       <c r="C250" s="5" t="n">
-        <v>114.88</v>
+        <v>114.92</v>
       </c>
       <c r="D250" s="5" t="n">
         <v>102.46</v>
       </c>
       <c r="E250" s="5" t="n">
-        <v>116.62</v>
+        <v>116.66</v>
       </c>
     </row>
     <row r="251">
@@ -10702,13 +10702,13 @@
         <v>90.28</v>
       </c>
       <c r="C251" s="5" t="n">
-        <v>87.56</v>
+        <v>87.54000000000001</v>
       </c>
       <c r="D251" s="5" t="n">
         <v>91.23</v>
       </c>
       <c r="E251" s="5" t="n">
-        <v>88.48999999999999</v>
+        <v>88.47</v>
       </c>
     </row>
     <row r="252">
@@ -10721,13 +10721,13 @@
         <v>91.04000000000001</v>
       </c>
       <c r="C252" s="5" t="n">
-        <v>90.94</v>
+        <v>90.92</v>
       </c>
       <c r="D252" s="5" t="n">
         <v>91.59</v>
       </c>
       <c r="E252" s="5" t="n">
-        <v>91.48999999999999</v>
+        <v>91.47</v>
       </c>
     </row>
     <row r="253">
@@ -10740,13 +10740,13 @@
         <v>85.23999999999999</v>
       </c>
       <c r="C253" s="5" t="n">
-        <v>87.34</v>
+        <v>87.29000000000001</v>
       </c>
       <c r="D253" s="5" t="n">
         <v>85.58</v>
       </c>
       <c r="E253" s="5" t="n">
-        <v>87.69</v>
+        <v>87.64</v>
       </c>
     </row>
     <row r="254">
@@ -10759,13 +10759,13 @@
         <v>96.14</v>
       </c>
       <c r="C254" s="5" t="n">
-        <v>100.08</v>
+        <v>100.05</v>
       </c>
       <c r="D254" s="5" t="n">
         <v>96.33</v>
       </c>
       <c r="E254" s="5" t="n">
-        <v>100.28</v>
+        <v>100.25</v>
       </c>
     </row>
     <row r="255">
@@ -10778,13 +10778,13 @@
         <v>76.83</v>
       </c>
       <c r="C255" s="5" t="n">
-        <v>81.73</v>
+        <v>81.67</v>
       </c>
       <c r="D255" s="5" t="n">
         <v>76.83</v>
       </c>
       <c r="E255" s="5" t="n">
-        <v>81.73</v>
+        <v>81.67</v>
       </c>
     </row>
     <row r="256">
@@ -10797,13 +10797,13 @@
         <v>71.04000000000001</v>
       </c>
       <c r="C256" s="5" t="n">
-        <v>93.83</v>
+        <v>93.72</v>
       </c>
       <c r="D256" s="5" t="n">
         <v>71.04000000000001</v>
       </c>
       <c r="E256" s="5" t="n">
-        <v>93.83</v>
+        <v>93.72</v>
       </c>
     </row>
     <row r="257">
@@ -10816,13 +10816,13 @@
         <v>57.95</v>
       </c>
       <c r="C257" s="5" t="n">
-        <v>65.81</v>
+        <v>65.73</v>
       </c>
       <c r="D257" s="5" t="n">
         <v>57.95</v>
       </c>
       <c r="E257" s="5" t="n">
-        <v>65.81</v>
+        <v>65.73</v>
       </c>
     </row>
     <row r="258">
@@ -10835,13 +10835,13 @@
         <v>38.86</v>
       </c>
       <c r="C258" s="5" t="n">
-        <v>37.8</v>
+        <v>37.87</v>
       </c>
       <c r="D258" s="5" t="n">
         <v>38.86</v>
       </c>
       <c r="E258" s="5" t="n">
-        <v>37.8</v>
+        <v>37.87</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/TAS_historical_prices.xlsx
+++ b/outputs/TAS_historical_prices.xlsx
@@ -534,10 +534,10 @@
         <v>73.04000000000001</v>
       </c>
       <c r="D5" s="5" t="n">
-        <v>69.91</v>
+        <v>70.70999999999999</v>
       </c>
       <c r="E5" s="5" t="n">
-        <v>73.56</v>
+        <v>74.40000000000001</v>
       </c>
     </row>
     <row r="6">
@@ -553,10 +553,10 @@
         <v>94.51000000000001</v>
       </c>
       <c r="D6" s="5" t="n">
-        <v>89.45</v>
+        <v>90.56</v>
       </c>
       <c r="E6" s="5" t="n">
-        <v>97.31999999999999</v>
+        <v>98.52</v>
       </c>
     </row>
     <row r="7">
@@ -572,10 +572,10 @@
         <v>96.36</v>
       </c>
       <c r="D7" s="5" t="n">
-        <v>91.54000000000001</v>
+        <v>92.7</v>
       </c>
       <c r="E7" s="5" t="n">
-        <v>100.47</v>
+        <v>101.74</v>
       </c>
     </row>
     <row r="8">
@@ -591,10 +591,10 @@
         <v>101.62</v>
       </c>
       <c r="D8" s="5" t="n">
-        <v>100.51</v>
+        <v>101.79</v>
       </c>
       <c r="E8" s="5" t="n">
-        <v>110.86</v>
+        <v>112.27</v>
       </c>
     </row>
     <row r="9">
@@ -610,10 +610,10 @@
         <v>87.36</v>
       </c>
       <c r="D9" s="5" t="n">
-        <v>94.95</v>
+        <v>96.17</v>
       </c>
       <c r="E9" s="5" t="n">
-        <v>102.84</v>
+        <v>104.17</v>
       </c>
     </row>
     <row r="10">
@@ -629,10 +629,10 @@
         <v>76.83</v>
       </c>
       <c r="D10" s="5" t="n">
-        <v>88.34999999999999</v>
+        <v>89.48999999999999</v>
       </c>
       <c r="E10" s="5" t="n">
-        <v>94.48</v>
+        <v>95.7</v>
       </c>
     </row>
     <row r="11">
@@ -648,10 +648,10 @@
         <v>70.08</v>
       </c>
       <c r="D11" s="5" t="n">
-        <v>83.8</v>
+        <v>84.89</v>
       </c>
       <c r="E11" s="5" t="n">
-        <v>90.88</v>
+        <v>92.05</v>
       </c>
     </row>
     <row r="13">
@@ -664,7 +664,7 @@
     <row r="14">
       <c r="A14" s="6" t="inlineStr">
         <is>
-          <t>Real prices are in Jun 2026 dollars (latest published CPI quarter). The latest 3 month(s) have no CPI yet, so real = nominal there (flagged in Monthly Data).</t>
+          <t>Real prices are in Sep 2026 dollars (latest published CPI quarter).</t>
         </is>
       </c>
     </row>
@@ -741,10 +741,10 @@
         <v>86.38</v>
       </c>
       <c r="D2" s="5" t="n">
-        <v>140.27</v>
+        <v>142.1</v>
       </c>
       <c r="E2" s="5" t="n">
-        <v>154.1</v>
+        <v>156.1</v>
       </c>
       <c r="F2" s="7" t="inlineStr"/>
       <c r="G2" s="7" t="inlineStr"/>
@@ -762,10 +762,10 @@
         <v>115.77</v>
       </c>
       <c r="D3" s="5" t="n">
-        <v>199.75</v>
+        <v>202.34</v>
       </c>
       <c r="E3" s="5" t="n">
-        <v>205.85</v>
+        <v>208.52</v>
       </c>
       <c r="F3" s="7" t="inlineStr"/>
       <c r="G3" s="7" t="inlineStr"/>
@@ -783,10 +783,10 @@
         <v>141.34</v>
       </c>
       <c r="D4" s="5" t="n">
-        <v>189.98</v>
+        <v>192.45</v>
       </c>
       <c r="E4" s="5" t="n">
-        <v>250.48</v>
+        <v>253.74</v>
       </c>
       <c r="F4" s="7" t="inlineStr"/>
       <c r="G4" s="7" t="inlineStr"/>
@@ -804,10 +804,10 @@
         <v>77.7</v>
       </c>
       <c r="D5" s="5" t="n">
-        <v>122.5</v>
+        <v>124.09</v>
       </c>
       <c r="E5" s="5" t="n">
-        <v>137.25</v>
+        <v>139.03</v>
       </c>
       <c r="F5" s="7" t="inlineStr"/>
       <c r="G5" s="7" t="inlineStr"/>
@@ -825,10 +825,10 @@
         <v>102.17</v>
       </c>
       <c r="D6" s="5" t="n">
-        <v>145.27</v>
+        <v>147.15</v>
       </c>
       <c r="E6" s="5" t="n">
-        <v>180.16</v>
+        <v>182.5</v>
       </c>
       <c r="F6" s="7" t="inlineStr"/>
       <c r="G6" s="7" t="inlineStr"/>
@@ -846,10 +846,10 @@
         <v>59.19</v>
       </c>
       <c r="D7" s="5" t="n">
-        <v>101.47</v>
+        <v>102.78</v>
       </c>
       <c r="E7" s="5" t="n">
-        <v>104.19</v>
+        <v>105.55</v>
       </c>
       <c r="F7" s="7" t="inlineStr"/>
       <c r="G7" s="7" t="inlineStr"/>
@@ -867,10 +867,10 @@
         <v>46.71</v>
       </c>
       <c r="D8" s="5" t="n">
-        <v>75.25</v>
+        <v>76.23</v>
       </c>
       <c r="E8" s="5" t="n">
-        <v>82.08</v>
+        <v>83.15000000000001</v>
       </c>
       <c r="F8" s="7" t="inlineStr"/>
       <c r="G8" s="7" t="inlineStr"/>
@@ -888,10 +888,10 @@
         <v>40.3</v>
       </c>
       <c r="D9" s="5" t="n">
-        <v>64.66</v>
+        <v>65.5</v>
       </c>
       <c r="E9" s="5" t="n">
-        <v>70.62</v>
+        <v>71.54000000000001</v>
       </c>
       <c r="F9" s="7" t="inlineStr"/>
       <c r="G9" s="7" t="inlineStr"/>
@@ -909,10 +909,10 @@
         <v>35.57</v>
       </c>
       <c r="D10" s="5" t="n">
-        <v>56.68</v>
+        <v>57.42</v>
       </c>
       <c r="E10" s="5" t="n">
-        <v>62.15</v>
+        <v>62.96</v>
       </c>
       <c r="F10" s="7" t="inlineStr"/>
       <c r="G10" s="7" t="inlineStr"/>
@@ -930,10 +930,10 @@
         <v>32.53</v>
       </c>
       <c r="D11" s="5" t="n">
-        <v>49.48</v>
+        <v>50.13</v>
       </c>
       <c r="E11" s="5" t="n">
-        <v>56.68</v>
+        <v>57.42</v>
       </c>
       <c r="F11" s="7" t="inlineStr"/>
       <c r="G11" s="7" t="inlineStr"/>
@@ -951,10 +951,10 @@
         <v>33.75</v>
       </c>
       <c r="D12" s="5" t="n">
-        <v>57.82</v>
+        <v>58.57</v>
       </c>
       <c r="E12" s="5" t="n">
-        <v>58.5</v>
+        <v>59.26</v>
       </c>
       <c r="F12" s="7" t="inlineStr"/>
       <c r="G12" s="7" t="inlineStr"/>
@@ -972,10 +972,10 @@
         <v>47.59</v>
       </c>
       <c r="D13" s="5" t="n">
-        <v>58.21</v>
+        <v>58.96</v>
       </c>
       <c r="E13" s="5" t="n">
-        <v>82.05</v>
+        <v>83.12</v>
       </c>
       <c r="F13" s="7" t="inlineStr"/>
       <c r="G13" s="7" t="inlineStr"/>
@@ -993,10 +993,10 @@
         <v>52.3</v>
       </c>
       <c r="D14" s="5" t="n">
-        <v>70.98999999999999</v>
+        <v>71.91</v>
       </c>
       <c r="E14" s="5" t="n">
-        <v>89.7</v>
+        <v>90.87</v>
       </c>
       <c r="F14" s="7" t="inlineStr"/>
       <c r="G14" s="7" t="inlineStr"/>
@@ -1014,10 +1014,10 @@
         <v>69.09999999999999</v>
       </c>
       <c r="D15" s="5" t="n">
-        <v>82.5</v>
+        <v>83.56999999999999</v>
       </c>
       <c r="E15" s="5" t="n">
-        <v>118.17</v>
+        <v>119.7</v>
       </c>
       <c r="F15" s="7" t="inlineStr"/>
       <c r="G15" s="7" t="inlineStr"/>
@@ -1035,10 +1035,10 @@
         <v>39.9</v>
       </c>
       <c r="D16" s="5" t="n">
-        <v>59.97</v>
+        <v>60.75</v>
       </c>
       <c r="E16" s="5" t="n">
-        <v>68.03</v>
+        <v>68.92</v>
       </c>
       <c r="F16" s="7" t="inlineStr"/>
       <c r="G16" s="7" t="inlineStr"/>
@@ -1056,10 +1056,10 @@
         <v>41.6</v>
       </c>
       <c r="D17" s="5" t="n">
-        <v>65.03</v>
+        <v>65.87</v>
       </c>
       <c r="E17" s="5" t="n">
-        <v>70.72</v>
+        <v>71.64</v>
       </c>
       <c r="F17" s="7" t="inlineStr"/>
       <c r="G17" s="7" t="inlineStr"/>
@@ -1077,10 +1077,10 @@
         <v>36.71</v>
       </c>
       <c r="D18" s="5" t="n">
-        <v>58.22</v>
+        <v>58.97</v>
       </c>
       <c r="E18" s="5" t="n">
-        <v>62.43</v>
+        <v>63.25</v>
       </c>
       <c r="F18" s="7" t="inlineStr"/>
       <c r="G18" s="7" t="inlineStr"/>
@@ -1098,10 +1098,10 @@
         <v>44.53</v>
       </c>
       <c r="D19" s="5" t="n">
-        <v>67.72</v>
+        <v>68.59999999999999</v>
       </c>
       <c r="E19" s="5" t="n">
-        <v>75.76000000000001</v>
+        <v>76.75</v>
       </c>
       <c r="F19" s="7" t="inlineStr"/>
       <c r="G19" s="7" t="inlineStr"/>
@@ -1119,10 +1119,10 @@
         <v>40.79</v>
       </c>
       <c r="D20" s="5" t="n">
-        <v>59.86</v>
+        <v>60.64</v>
       </c>
       <c r="E20" s="5" t="n">
-        <v>69.43000000000001</v>
+        <v>70.33</v>
       </c>
       <c r="F20" s="7" t="inlineStr"/>
       <c r="G20" s="7" t="inlineStr"/>
@@ -1140,10 +1140,10 @@
         <v>47.2</v>
       </c>
       <c r="D21" s="5" t="n">
-        <v>75.38</v>
+        <v>76.36</v>
       </c>
       <c r="E21" s="5" t="n">
-        <v>80.31</v>
+        <v>81.36</v>
       </c>
       <c r="F21" s="7" t="inlineStr"/>
       <c r="G21" s="7" t="inlineStr"/>
@@ -1161,10 +1161,10 @@
         <v>67.45</v>
       </c>
       <c r="D22" s="5" t="n">
-        <v>90.06999999999999</v>
+        <v>91.23999999999999</v>
       </c>
       <c r="E22" s="5" t="n">
-        <v>114.74</v>
+        <v>116.23</v>
       </c>
       <c r="F22" s="7" t="inlineStr"/>
       <c r="G22" s="7" t="inlineStr"/>
@@ -1182,10 +1182,10 @@
         <v>53.78</v>
       </c>
       <c r="D23" s="5" t="n">
-        <v>86.31</v>
+        <v>87.43000000000001</v>
       </c>
       <c r="E23" s="5" t="n">
-        <v>91.45999999999999</v>
+        <v>92.65000000000001</v>
       </c>
       <c r="F23" s="7" t="inlineStr"/>
       <c r="G23" s="7" t="inlineStr"/>
@@ -1203,10 +1203,10 @@
         <v>81.98999999999999</v>
       </c>
       <c r="D24" s="5" t="n">
-        <v>123.77</v>
+        <v>125.38</v>
       </c>
       <c r="E24" s="5" t="n">
-        <v>138.87</v>
+        <v>140.67</v>
       </c>
       <c r="F24" s="7" t="inlineStr"/>
       <c r="G24" s="7" t="inlineStr"/>
@@ -1224,10 +1224,10 @@
         <v>72.01000000000001</v>
       </c>
       <c r="D25" s="5" t="n">
-        <v>111.9</v>
+        <v>113.36</v>
       </c>
       <c r="E25" s="5" t="n">
-        <v>121.47</v>
+        <v>123.05</v>
       </c>
       <c r="F25" s="7" t="inlineStr"/>
       <c r="G25" s="7" t="inlineStr"/>
@@ -1245,10 +1245,10 @@
         <v>79.87</v>
       </c>
       <c r="D26" s="5" t="n">
-        <v>130.72</v>
+        <v>132.42</v>
       </c>
       <c r="E26" s="5" t="n">
-        <v>134.18</v>
+        <v>135.92</v>
       </c>
       <c r="F26" s="7" t="inlineStr"/>
       <c r="G26" s="7" t="inlineStr"/>
@@ -1266,10 +1266,10 @@
         <v>115.14</v>
       </c>
       <c r="D27" s="5" t="n">
-        <v>166.69</v>
+        <v>168.86</v>
       </c>
       <c r="E27" s="5" t="n">
-        <v>192.99</v>
+        <v>195.5</v>
       </c>
       <c r="F27" s="7" t="inlineStr"/>
       <c r="G27" s="7" t="inlineStr"/>
@@ -1287,10 +1287,10 @@
         <v>48.48</v>
       </c>
       <c r="D28" s="5" t="n">
-        <v>68.06</v>
+        <v>68.95</v>
       </c>
       <c r="E28" s="5" t="n">
-        <v>81.06999999999999</v>
+        <v>82.13</v>
       </c>
       <c r="F28" s="7" t="inlineStr"/>
       <c r="G28" s="7" t="inlineStr"/>
@@ -1308,10 +1308,10 @@
         <v>49.1</v>
       </c>
       <c r="D29" s="5" t="n">
-        <v>78.81999999999999</v>
+        <v>79.84</v>
       </c>
       <c r="E29" s="5" t="n">
-        <v>81.92</v>
+        <v>82.98999999999999</v>
       </c>
       <c r="F29" s="7" t="inlineStr"/>
       <c r="G29" s="7" t="inlineStr"/>
@@ -1329,10 +1329,10 @@
         <v>32.4</v>
       </c>
       <c r="D30" s="5" t="n">
-        <v>56.6</v>
+        <v>57.34</v>
       </c>
       <c r="E30" s="5" t="n">
-        <v>53.89</v>
+        <v>54.59</v>
       </c>
       <c r="F30" s="7" t="inlineStr"/>
       <c r="G30" s="7" t="inlineStr"/>
@@ -1350,10 +1350,10 @@
         <v>49.25</v>
       </c>
       <c r="D31" s="5" t="n">
-        <v>74.19</v>
+        <v>75.15000000000001</v>
       </c>
       <c r="E31" s="5" t="n">
-        <v>81.67</v>
+        <v>82.73</v>
       </c>
       <c r="F31" s="7" t="inlineStr"/>
       <c r="G31" s="7" t="inlineStr"/>
@@ -1371,10 +1371,10 @@
         <v>60.6</v>
       </c>
       <c r="D32" s="5" t="n">
-        <v>84.23999999999999</v>
+        <v>85.34</v>
       </c>
       <c r="E32" s="5" t="n">
-        <v>100.18</v>
+        <v>101.48</v>
       </c>
       <c r="F32" s="7" t="inlineStr"/>
       <c r="G32" s="7" t="inlineStr"/>
@@ -1392,10 +1392,10 @@
         <v>59.02</v>
       </c>
       <c r="D33" s="5" t="n">
-        <v>77.89</v>
+        <v>78.91</v>
       </c>
       <c r="E33" s="5" t="n">
-        <v>97.13</v>
+        <v>98.39</v>
       </c>
       <c r="F33" s="7" t="inlineStr"/>
       <c r="G33" s="7" t="inlineStr"/>
@@ -1413,10 +1413,10 @@
         <v>67.68000000000001</v>
       </c>
       <c r="D34" s="5" t="n">
-        <v>92.51000000000001</v>
+        <v>93.70999999999999</v>
       </c>
       <c r="E34" s="5" t="n">
-        <v>110.89</v>
+        <v>112.33</v>
       </c>
       <c r="F34" s="7" t="inlineStr"/>
       <c r="G34" s="7" t="inlineStr"/>
@@ -1434,10 +1434,10 @@
         <v>68.55</v>
       </c>
       <c r="D35" s="5" t="n">
-        <v>91.63</v>
+        <v>92.81999999999999</v>
       </c>
       <c r="E35" s="5" t="n">
-        <v>111.82</v>
+        <v>113.27</v>
       </c>
       <c r="F35" s="7" t="inlineStr"/>
       <c r="G35" s="7" t="inlineStr"/>
@@ -1455,10 +1455,10 @@
         <v>63.43</v>
       </c>
       <c r="D36" s="5" t="n">
-        <v>89.17</v>
+        <v>90.33</v>
       </c>
       <c r="E36" s="5" t="n">
-        <v>102.97</v>
+        <v>104.31</v>
       </c>
       <c r="F36" s="7" t="inlineStr"/>
       <c r="G36" s="7" t="inlineStr"/>
@@ -1476,10 +1476,10 @@
         <v>69.15000000000001</v>
       </c>
       <c r="D37" s="5" t="n">
-        <v>109.44</v>
+        <v>110.86</v>
       </c>
       <c r="E37" s="5" t="n">
-        <v>111.72</v>
+        <v>113.17</v>
       </c>
       <c r="F37" s="7" t="inlineStr"/>
       <c r="G37" s="7" t="inlineStr"/>
@@ -1497,10 +1497,10 @@
         <v>63.04</v>
       </c>
       <c r="D38" s="5" t="n">
-        <v>89.98</v>
+        <v>91.15000000000001</v>
       </c>
       <c r="E38" s="5" t="n">
-        <v>101.36</v>
+        <v>102.68</v>
       </c>
       <c r="F38" s="7" t="inlineStr"/>
       <c r="G38" s="7" t="inlineStr"/>
@@ -1518,10 +1518,10 @@
         <v>31.08</v>
       </c>
       <c r="D39" s="5" t="n">
-        <v>48.63</v>
+        <v>49.26</v>
       </c>
       <c r="E39" s="5" t="n">
-        <v>49.78</v>
+        <v>50.43</v>
       </c>
       <c r="F39" s="7" t="inlineStr"/>
       <c r="G39" s="7" t="inlineStr"/>
@@ -1539,10 +1539,10 @@
         <v>60.78</v>
       </c>
       <c r="D40" s="5" t="n">
-        <v>87.69</v>
+        <v>88.83</v>
       </c>
       <c r="E40" s="5" t="n">
-        <v>96.98</v>
+        <v>98.23999999999999</v>
       </c>
       <c r="F40" s="7" t="inlineStr"/>
       <c r="G40" s="7" t="inlineStr"/>
@@ -1560,10 +1560,10 @@
         <v>53.01</v>
       </c>
       <c r="D41" s="5" t="n">
-        <v>69.84</v>
+        <v>70.75</v>
       </c>
       <c r="E41" s="5" t="n">
-        <v>84.25</v>
+        <v>85.34999999999999</v>
       </c>
       <c r="F41" s="7" t="inlineStr"/>
       <c r="G41" s="7" t="inlineStr"/>
@@ -1581,10 +1581,10 @@
         <v>55.72</v>
       </c>
       <c r="D42" s="5" t="n">
-        <v>73.06</v>
+        <v>74.01000000000001</v>
       </c>
       <c r="E42" s="5" t="n">
-        <v>88.66</v>
+        <v>89.81</v>
       </c>
       <c r="F42" s="7" t="inlineStr"/>
       <c r="G42" s="7" t="inlineStr"/>
@@ -1602,10 +1602,10 @@
         <v>60.73</v>
       </c>
       <c r="D43" s="5" t="n">
-        <v>80.76000000000001</v>
+        <v>81.81</v>
       </c>
       <c r="E43" s="5" t="n">
-        <v>96.73</v>
+        <v>97.98999999999999</v>
       </c>
       <c r="F43" s="7" t="inlineStr"/>
       <c r="G43" s="7" t="inlineStr"/>
@@ -1623,10 +1623,10 @@
         <v>38.15</v>
       </c>
       <c r="D44" s="5" t="n">
-        <v>52.48</v>
+        <v>53.16</v>
       </c>
       <c r="E44" s="5" t="n">
-        <v>60.83</v>
+        <v>61.63</v>
       </c>
       <c r="F44" s="7" t="inlineStr"/>
       <c r="G44" s="7" t="inlineStr"/>
@@ -1644,10 +1644,10 @@
         <v>119.54</v>
       </c>
       <c r="D45" s="5" t="n">
-        <v>125.74</v>
+        <v>127.37</v>
       </c>
       <c r="E45" s="5" t="n">
-        <v>190.55</v>
+        <v>193.03</v>
       </c>
       <c r="F45" s="7" t="inlineStr"/>
       <c r="G45" s="7" t="inlineStr"/>
@@ -1665,10 +1665,10 @@
         <v>63.49</v>
       </c>
       <c r="D46" s="5" t="n">
-        <v>62.27</v>
+        <v>63.08</v>
       </c>
       <c r="E46" s="5" t="n">
-        <v>101.17</v>
+        <v>102.48</v>
       </c>
       <c r="F46" s="7" t="inlineStr"/>
       <c r="G46" s="7" t="inlineStr"/>
@@ -1686,10 +1686,10 @@
         <v>43.09</v>
       </c>
       <c r="D47" s="5" t="n">
-        <v>58.11</v>
+        <v>58.86</v>
       </c>
       <c r="E47" s="5" t="n">
-        <v>68.64</v>
+        <v>69.53</v>
       </c>
       <c r="F47" s="7" t="inlineStr"/>
       <c r="G47" s="7" t="inlineStr"/>
@@ -1707,10 +1707,10 @@
         <v>61.35</v>
       </c>
       <c r="D48" s="5" t="n">
-        <v>110.22</v>
+        <v>111.65</v>
       </c>
       <c r="E48" s="5" t="n">
-        <v>97.56</v>
+        <v>98.83</v>
       </c>
       <c r="F48" s="7" t="inlineStr"/>
       <c r="G48" s="7" t="inlineStr"/>
@@ -1728,10 +1728,10 @@
         <v>48.31</v>
       </c>
       <c r="D49" s="5" t="n">
-        <v>74.36</v>
+        <v>75.33</v>
       </c>
       <c r="E49" s="5" t="n">
-        <v>76.7</v>
+        <v>77.69</v>
       </c>
       <c r="F49" s="7" t="inlineStr"/>
       <c r="G49" s="7" t="inlineStr"/>
@@ -1749,10 +1749,10 @@
         <v>287.29</v>
       </c>
       <c r="D50" s="5" t="n">
-        <v>275.47</v>
+        <v>279.05</v>
       </c>
       <c r="E50" s="5" t="n">
-        <v>455.35</v>
+        <v>461.27</v>
       </c>
       <c r="F50" s="7" t="inlineStr"/>
       <c r="G50" s="7" t="inlineStr"/>
@@ -1770,10 +1770,10 @@
         <v>31.56</v>
       </c>
       <c r="D51" s="5" t="n">
-        <v>40.91</v>
+        <v>41.44</v>
       </c>
       <c r="E51" s="5" t="n">
-        <v>49.86</v>
+        <v>50.51</v>
       </c>
       <c r="F51" s="7" t="inlineStr"/>
       <c r="G51" s="7" t="inlineStr"/>
@@ -1791,10 +1791,10 @@
         <v>27.86</v>
       </c>
       <c r="D52" s="5" t="n">
-        <v>33.53</v>
+        <v>33.97</v>
       </c>
       <c r="E52" s="5" t="n">
-        <v>43.88</v>
+        <v>44.45</v>
       </c>
       <c r="F52" s="7" t="inlineStr"/>
       <c r="G52" s="7" t="inlineStr"/>
@@ -1812,10 +1812,10 @@
         <v>27.5</v>
       </c>
       <c r="D53" s="5" t="n">
-        <v>33.79</v>
+        <v>34.23</v>
       </c>
       <c r="E53" s="5" t="n">
-        <v>43.18</v>
+        <v>43.74</v>
       </c>
       <c r="F53" s="7" t="inlineStr"/>
       <c r="G53" s="7" t="inlineStr"/>
@@ -1833,10 +1833,10 @@
         <v>29.55</v>
       </c>
       <c r="D54" s="5" t="n">
-        <v>40.41</v>
+        <v>40.93</v>
       </c>
       <c r="E54" s="5" t="n">
-        <v>46.31</v>
+        <v>46.92</v>
       </c>
       <c r="F54" s="7" t="inlineStr"/>
       <c r="G54" s="7" t="inlineStr"/>
@@ -1854,10 +1854,10 @@
         <v>37.68</v>
       </c>
       <c r="D55" s="5" t="n">
-        <v>52.72</v>
+        <v>53.41</v>
       </c>
       <c r="E55" s="5" t="n">
-        <v>58.95</v>
+        <v>59.72</v>
       </c>
       <c r="F55" s="7" t="inlineStr"/>
       <c r="G55" s="7" t="inlineStr"/>
@@ -1875,10 +1875,10 @@
         <v>31.42</v>
       </c>
       <c r="D56" s="5" t="n">
-        <v>49.76</v>
+        <v>50.4</v>
       </c>
       <c r="E56" s="5" t="n">
-        <v>49.07</v>
+        <v>49.71</v>
       </c>
       <c r="F56" s="7" t="inlineStr"/>
       <c r="G56" s="7" t="inlineStr"/>
@@ -1896,10 +1896,10 @@
         <v>32.51</v>
       </c>
       <c r="D57" s="5" t="n">
-        <v>45.51</v>
+        <v>46.1</v>
       </c>
       <c r="E57" s="5" t="n">
-        <v>50.62</v>
+        <v>51.27</v>
       </c>
       <c r="F57" s="7" t="inlineStr"/>
       <c r="G57" s="7" t="inlineStr"/>
@@ -1917,10 +1917,10 @@
         <v>20.35</v>
       </c>
       <c r="D58" s="5" t="n">
-        <v>37.19</v>
+        <v>37.67</v>
       </c>
       <c r="E58" s="5" t="n">
-        <v>31.59</v>
+        <v>32</v>
       </c>
       <c r="F58" s="7" t="inlineStr"/>
       <c r="G58" s="7" t="inlineStr"/>
@@ -1938,10 +1938,10 @@
         <v>28.45</v>
       </c>
       <c r="D59" s="5" t="n">
-        <v>40.54</v>
+        <v>41.07</v>
       </c>
       <c r="E59" s="5" t="n">
-        <v>44.02</v>
+        <v>44.59</v>
       </c>
       <c r="F59" s="7" t="inlineStr"/>
       <c r="G59" s="7" t="inlineStr"/>
@@ -1959,10 +1959,10 @@
         <v>26.23</v>
       </c>
       <c r="D60" s="5" t="n">
-        <v>37.71</v>
+        <v>38.2</v>
       </c>
       <c r="E60" s="5" t="n">
-        <v>40.51</v>
+        <v>41.03</v>
       </c>
       <c r="F60" s="7" t="inlineStr"/>
       <c r="G60" s="7" t="inlineStr"/>
@@ -1980,10 +1980,10 @@
         <v>36.98</v>
       </c>
       <c r="D61" s="5" t="n">
-        <v>87.8</v>
+        <v>88.94</v>
       </c>
       <c r="E61" s="5" t="n">
-        <v>56.99</v>
+        <v>57.73</v>
       </c>
       <c r="F61" s="7" t="inlineStr"/>
       <c r="G61" s="7" t="inlineStr"/>
@@ -2001,10 +2001,10 @@
         <v>34.53</v>
       </c>
       <c r="D62" s="5" t="n">
-        <v>47.51</v>
+        <v>48.13</v>
       </c>
       <c r="E62" s="5" t="n">
-        <v>53.11</v>
+        <v>53.8</v>
       </c>
       <c r="F62" s="7" t="inlineStr"/>
       <c r="G62" s="7" t="inlineStr"/>
@@ -2022,10 +2022,10 @@
         <v>27.43</v>
       </c>
       <c r="D63" s="5" t="n">
-        <v>46.34</v>
+        <v>46.94</v>
       </c>
       <c r="E63" s="5" t="n">
-        <v>42.09</v>
+        <v>42.63</v>
       </c>
       <c r="F63" s="7" t="inlineStr"/>
       <c r="G63" s="7" t="inlineStr"/>
@@ -2043,10 +2043,10 @@
         <v>27.68</v>
       </c>
       <c r="D64" s="5" t="n">
-        <v>99.19</v>
+        <v>100.48</v>
       </c>
       <c r="E64" s="5" t="n">
-        <v>42.37</v>
+        <v>42.92</v>
       </c>
       <c r="F64" s="7" t="inlineStr"/>
       <c r="G64" s="7" t="inlineStr"/>
@@ -2064,10 +2064,10 @@
         <v>23.49</v>
       </c>
       <c r="D65" s="5" t="n">
-        <v>31.7</v>
+        <v>32.11</v>
       </c>
       <c r="E65" s="5" t="n">
-        <v>35.87</v>
+        <v>36.34</v>
       </c>
       <c r="F65" s="7" t="inlineStr"/>
       <c r="G65" s="7" t="inlineStr"/>
@@ -2085,10 +2085,10 @@
         <v>18.32</v>
       </c>
       <c r="D66" s="5" t="n">
-        <v>27.66</v>
+        <v>28.02</v>
       </c>
       <c r="E66" s="5" t="n">
-        <v>27.94</v>
+        <v>28.3</v>
       </c>
       <c r="F66" s="7" t="inlineStr"/>
       <c r="G66" s="7" t="inlineStr"/>
@@ -2106,10 +2106,10 @@
         <v>19.55</v>
       </c>
       <c r="D67" s="5" t="n">
-        <v>41.28</v>
+        <v>41.81</v>
       </c>
       <c r="E67" s="5" t="n">
-        <v>29.78</v>
+        <v>30.16</v>
       </c>
       <c r="F67" s="7" t="inlineStr"/>
       <c r="G67" s="7" t="inlineStr"/>
@@ -2127,10 +2127,10 @@
         <v>17.67</v>
       </c>
       <c r="D68" s="5" t="n">
-        <v>25.4</v>
+        <v>25.73</v>
       </c>
       <c r="E68" s="5" t="n">
-        <v>26.88</v>
+        <v>27.23</v>
       </c>
       <c r="F68" s="7" t="inlineStr"/>
       <c r="G68" s="7" t="inlineStr"/>
@@ -2148,10 +2148,10 @@
         <v>28.13</v>
       </c>
       <c r="D69" s="5" t="n">
-        <v>39.27</v>
+        <v>39.78</v>
       </c>
       <c r="E69" s="5" t="n">
-        <v>42.57</v>
+        <v>43.12</v>
       </c>
       <c r="F69" s="7" t="inlineStr"/>
       <c r="G69" s="7" t="inlineStr"/>
@@ -2169,10 +2169,10 @@
         <v>31.08</v>
       </c>
       <c r="D70" s="5" t="n">
-        <v>43.24</v>
+        <v>43.8</v>
       </c>
       <c r="E70" s="5" t="n">
-        <v>46.79</v>
+        <v>47.4</v>
       </c>
       <c r="F70" s="7" t="inlineStr"/>
       <c r="G70" s="7" t="inlineStr"/>
@@ -2190,10 +2190,10 @@
         <v>27.04</v>
       </c>
       <c r="D71" s="5" t="n">
-        <v>38.69</v>
+        <v>39.2</v>
       </c>
       <c r="E71" s="5" t="n">
-        <v>40.5</v>
+        <v>41.03</v>
       </c>
       <c r="F71" s="7" t="inlineStr"/>
       <c r="G71" s="7" t="inlineStr"/>
@@ -2211,10 +2211,10 @@
         <v>27.77</v>
       </c>
       <c r="D72" s="5" t="n">
-        <v>40.02</v>
+        <v>40.54</v>
       </c>
       <c r="E72" s="5" t="n">
-        <v>41.47</v>
+        <v>42.01</v>
       </c>
       <c r="F72" s="7" t="inlineStr"/>
       <c r="G72" s="7" t="inlineStr"/>
@@ -2232,10 +2232,10 @@
         <v>40.49</v>
       </c>
       <c r="D73" s="5" t="n">
-        <v>57.57</v>
+        <v>58.32</v>
       </c>
       <c r="E73" s="5" t="n">
-        <v>60.28</v>
+        <v>61.06</v>
       </c>
       <c r="F73" s="7" t="inlineStr"/>
       <c r="G73" s="7" t="inlineStr"/>
@@ -2253,10 +2253,10 @@
         <v>32.23</v>
       </c>
       <c r="D74" s="5" t="n">
-        <v>43.28</v>
+        <v>43.84</v>
       </c>
       <c r="E74" s="5" t="n">
-        <v>47.84</v>
+        <v>48.46</v>
       </c>
       <c r="F74" s="7" t="inlineStr"/>
       <c r="G74" s="7" t="inlineStr"/>
@@ -2274,10 +2274,10 @@
         <v>49.09</v>
       </c>
       <c r="D75" s="5" t="n">
-        <v>48.28</v>
+        <v>48.9</v>
       </c>
       <c r="E75" s="5" t="n">
-        <v>72.72</v>
+        <v>73.66</v>
       </c>
       <c r="F75" s="7" t="inlineStr"/>
       <c r="G75" s="7" t="inlineStr"/>
@@ -2295,10 +2295,10 @@
         <v>34.57</v>
       </c>
       <c r="D76" s="5" t="n">
-        <v>40.15</v>
+        <v>40.68</v>
       </c>
       <c r="E76" s="5" t="n">
-        <v>51.11</v>
+        <v>51.77</v>
       </c>
       <c r="F76" s="7" t="inlineStr"/>
       <c r="G76" s="7" t="inlineStr"/>
@@ -2316,10 +2316,10 @@
         <v>29.91</v>
       </c>
       <c r="D77" s="5" t="n">
-        <v>38.95</v>
+        <v>39.46</v>
       </c>
       <c r="E77" s="5" t="n">
-        <v>44.13</v>
+        <v>44.71</v>
       </c>
       <c r="F77" s="7" t="inlineStr"/>
       <c r="G77" s="7" t="inlineStr"/>
@@ -2337,10 +2337,10 @@
         <v>31.19</v>
       </c>
       <c r="D78" s="5" t="n">
-        <v>48.07</v>
+        <v>48.7</v>
       </c>
       <c r="E78" s="5" t="n">
-        <v>46.02</v>
+        <v>46.62</v>
       </c>
       <c r="F78" s="7" t="inlineStr"/>
       <c r="G78" s="7" t="inlineStr"/>
@@ -2358,10 +2358,10 @@
         <v>29.77</v>
       </c>
       <c r="D79" s="5" t="n">
-        <v>45.37</v>
+        <v>45.96</v>
       </c>
       <c r="E79" s="5" t="n">
-        <v>43.93</v>
+        <v>44.5</v>
       </c>
       <c r="F79" s="7" t="inlineStr"/>
       <c r="G79" s="7" t="inlineStr"/>
@@ -2379,10 +2379,10 @@
         <v>26.39</v>
       </c>
       <c r="D80" s="5" t="n">
-        <v>38.14</v>
+        <v>38.64</v>
       </c>
       <c r="E80" s="5" t="n">
-        <v>38.94</v>
+        <v>39.44</v>
       </c>
       <c r="F80" s="7" t="inlineStr"/>
       <c r="G80" s="7" t="inlineStr"/>
@@ -2400,10 +2400,10 @@
         <v>34.3</v>
       </c>
       <c r="D81" s="5" t="n">
-        <v>58</v>
+        <v>58.76</v>
       </c>
       <c r="E81" s="5" t="n">
-        <v>50.6</v>
+        <v>51.26</v>
       </c>
       <c r="F81" s="7" t="inlineStr"/>
       <c r="G81" s="7" t="inlineStr"/>
@@ -2421,10 +2421,10 @@
         <v>29.99</v>
       </c>
       <c r="D82" s="5" t="n">
-        <v>55.12</v>
+        <v>55.83</v>
       </c>
       <c r="E82" s="5" t="n">
-        <v>44.23</v>
+        <v>44.81</v>
       </c>
       <c r="F82" s="7" t="inlineStr"/>
       <c r="G82" s="7" t="inlineStr"/>
@@ -2442,10 +2442,10 @@
         <v>29.57</v>
       </c>
       <c r="D83" s="5" t="n">
-        <v>52.97</v>
+        <v>53.66</v>
       </c>
       <c r="E83" s="5" t="n">
-        <v>43.6</v>
+        <v>44.17</v>
       </c>
       <c r="F83" s="7" t="inlineStr"/>
       <c r="G83" s="7" t="inlineStr"/>
@@ -2463,10 +2463,10 @@
         <v>41.97</v>
       </c>
       <c r="D84" s="5" t="n">
-        <v>52.94</v>
+        <v>53.62</v>
       </c>
       <c r="E84" s="5" t="n">
-        <v>61.78</v>
+        <v>62.59</v>
       </c>
       <c r="F84" s="7" t="inlineStr"/>
       <c r="G84" s="7" t="inlineStr"/>
@@ -2484,10 +2484,10 @@
         <v>29.93</v>
       </c>
       <c r="D85" s="5" t="n">
-        <v>48.35</v>
+        <v>48.98</v>
       </c>
       <c r="E85" s="5" t="n">
-        <v>43.98</v>
+        <v>44.56</v>
       </c>
       <c r="F85" s="7" t="inlineStr"/>
       <c r="G85" s="7" t="inlineStr"/>
@@ -2505,10 +2505,10 @@
         <v>38.35</v>
       </c>
       <c r="D86" s="5" t="n">
-        <v>50.52</v>
+        <v>51.18</v>
       </c>
       <c r="E86" s="5" t="n">
-        <v>56.26</v>
+        <v>56.99</v>
       </c>
       <c r="F86" s="7" t="inlineStr"/>
       <c r="G86" s="7" t="inlineStr"/>
@@ -2526,10 +2526,10 @@
         <v>67.09999999999999</v>
       </c>
       <c r="D87" s="9" t="n">
-        <v>86.5</v>
+        <v>87.62</v>
       </c>
       <c r="E87" s="9" t="n">
-        <v>97.98999999999999</v>
+        <v>99.27</v>
       </c>
       <c r="F87" s="10" t="inlineStr">
         <is>
@@ -2551,10 +2551,10 @@
         <v>48.32</v>
       </c>
       <c r="D88" s="9" t="n">
-        <v>68.65000000000001</v>
+        <v>69.54000000000001</v>
       </c>
       <c r="E88" s="9" t="n">
-        <v>70.25</v>
+        <v>71.16</v>
       </c>
       <c r="F88" s="10" t="inlineStr">
         <is>
@@ -2576,10 +2576,10 @@
         <v>41.39</v>
       </c>
       <c r="D89" s="9" t="n">
-        <v>57.11</v>
+        <v>57.85</v>
       </c>
       <c r="E89" s="9" t="n">
-        <v>59.9</v>
+        <v>60.68</v>
       </c>
       <c r="F89" s="10" t="inlineStr">
         <is>
@@ -2601,10 +2601,10 @@
         <v>44.73</v>
       </c>
       <c r="D90" s="9" t="n">
-        <v>63.08</v>
+        <v>63.9</v>
       </c>
       <c r="E90" s="9" t="n">
-        <v>64.68000000000001</v>
+        <v>65.52</v>
       </c>
       <c r="F90" s="10" t="inlineStr">
         <is>
@@ -2626,10 +2626,10 @@
         <v>51.23</v>
       </c>
       <c r="D91" s="9" t="n">
-        <v>73.08</v>
+        <v>74.03</v>
       </c>
       <c r="E91" s="9" t="n">
-        <v>74.02</v>
+        <v>74.98</v>
       </c>
       <c r="F91" s="10" t="inlineStr">
         <is>
@@ -2651,10 +2651,10 @@
         <v>46.33</v>
       </c>
       <c r="D92" s="9" t="n">
-        <v>67.42</v>
+        <v>68.29000000000001</v>
       </c>
       <c r="E92" s="9" t="n">
-        <v>66.88</v>
+        <v>67.75</v>
       </c>
       <c r="F92" s="10" t="inlineStr">
         <is>
@@ -2676,10 +2676,10 @@
         <v>46.27</v>
       </c>
       <c r="D93" s="9" t="n">
-        <v>82.14</v>
+        <v>83.2</v>
       </c>
       <c r="E93" s="9" t="n">
-        <v>66.72</v>
+        <v>67.59</v>
       </c>
       <c r="F93" s="10" t="inlineStr">
         <is>
@@ -2701,10 +2701,10 @@
         <v>45.77</v>
       </c>
       <c r="D94" s="9" t="n">
-        <v>65.95</v>
+        <v>66.81</v>
       </c>
       <c r="E94" s="9" t="n">
-        <v>65.93000000000001</v>
+        <v>66.78</v>
       </c>
       <c r="F94" s="10" t="inlineStr">
         <is>
@@ -2726,10 +2726,10 @@
         <v>50.56</v>
       </c>
       <c r="D95" s="9" t="n">
-        <v>71.66</v>
+        <v>72.59999999999999</v>
       </c>
       <c r="E95" s="9" t="n">
-        <v>72.73999999999999</v>
+        <v>73.69</v>
       </c>
       <c r="F95" s="10" t="inlineStr">
         <is>
@@ -2751,10 +2751,10 @@
         <v>46.49</v>
       </c>
       <c r="D96" s="9" t="n">
-        <v>64.83</v>
+        <v>65.68000000000001</v>
       </c>
       <c r="E96" s="9" t="n">
-        <v>66.8</v>
+        <v>67.67</v>
       </c>
       <c r="F96" s="10" t="inlineStr">
         <is>
@@ -2776,10 +2776,10 @@
         <v>49.59</v>
       </c>
       <c r="D97" s="9" t="n">
-        <v>64.11</v>
+        <v>64.94</v>
       </c>
       <c r="E97" s="9" t="n">
-        <v>71.17</v>
+        <v>72.09</v>
       </c>
       <c r="F97" s="10" t="inlineStr">
         <is>
@@ -2801,10 +2801,10 @@
         <v>51.48</v>
       </c>
       <c r="D98" s="9" t="n">
-        <v>71.51000000000001</v>
+        <v>72.44</v>
       </c>
       <c r="E98" s="9" t="n">
-        <v>73.79000000000001</v>
+        <v>74.75</v>
       </c>
       <c r="F98" s="10" t="inlineStr">
         <is>
@@ -2826,10 +2826,10 @@
         <v>53.74</v>
       </c>
       <c r="D99" s="9" t="n">
-        <v>73.52</v>
+        <v>74.47</v>
       </c>
       <c r="E99" s="9" t="n">
-        <v>76.70999999999999</v>
+        <v>77.70999999999999</v>
       </c>
       <c r="F99" s="10" t="inlineStr">
         <is>
@@ -2851,10 +2851,10 @@
         <v>49.24</v>
       </c>
       <c r="D100" s="9" t="n">
-        <v>65.22</v>
+        <v>66.06</v>
       </c>
       <c r="E100" s="9" t="n">
-        <v>70.01000000000001</v>
+        <v>70.92</v>
       </c>
       <c r="F100" s="10" t="inlineStr">
         <is>
@@ -2876,10 +2876,10 @@
         <v>44.67</v>
       </c>
       <c r="D101" s="9" t="n">
-        <v>60.08</v>
+        <v>60.86</v>
       </c>
       <c r="E101" s="9" t="n">
-        <v>63.26</v>
+        <v>64.08</v>
       </c>
       <c r="F101" s="10" t="inlineStr">
         <is>
@@ -2901,10 +2901,10 @@
         <v>41.23</v>
       </c>
       <c r="D102" s="9" t="n">
-        <v>54.53</v>
+        <v>55.24</v>
       </c>
       <c r="E102" s="9" t="n">
-        <v>58.24</v>
+        <v>59</v>
       </c>
       <c r="F102" s="10" t="inlineStr">
         <is>
@@ -2926,10 +2926,10 @@
         <v>52.96</v>
       </c>
       <c r="D103" s="9" t="n">
-        <v>66.36</v>
+        <v>67.23</v>
       </c>
       <c r="E103" s="9" t="n">
-        <v>74.64</v>
+        <v>75.61</v>
       </c>
       <c r="F103" s="10" t="inlineStr">
         <is>
@@ -2951,10 +2951,10 @@
         <v>37.37</v>
       </c>
       <c r="D104" s="9" t="n">
-        <v>52.86</v>
+        <v>53.55</v>
       </c>
       <c r="E104" s="9" t="n">
-        <v>52.54</v>
+        <v>53.22</v>
       </c>
       <c r="F104" s="10" t="inlineStr">
         <is>
@@ -2976,10 +2976,10 @@
         <v>29.27</v>
       </c>
       <c r="D105" s="9" t="n">
-        <v>48.94</v>
+        <v>49.58</v>
       </c>
       <c r="E105" s="9" t="n">
-        <v>41.07</v>
+        <v>41.6</v>
       </c>
       <c r="F105" s="10" t="inlineStr">
         <is>
@@ -3001,10 +3001,10 @@
         <v>42.97</v>
       </c>
       <c r="D106" s="9" t="n">
-        <v>61.46</v>
+        <v>62.26</v>
       </c>
       <c r="E106" s="9" t="n">
-        <v>60.18</v>
+        <v>60.96</v>
       </c>
       <c r="F106" s="10" t="inlineStr">
         <is>
@@ -3026,10 +3026,10 @@
         <v>45.1</v>
       </c>
       <c r="D107" s="9" t="n">
-        <v>62.59</v>
+        <v>63.4</v>
       </c>
       <c r="E107" s="9" t="n">
-        <v>63.04</v>
+        <v>63.85</v>
       </c>
       <c r="F107" s="10" t="inlineStr">
         <is>
@@ -3051,10 +3051,10 @@
         <v>38.42</v>
       </c>
       <c r="D108" s="9" t="n">
-        <v>52.58</v>
+        <v>53.26</v>
       </c>
       <c r="E108" s="9" t="n">
-        <v>53.61</v>
+        <v>54.31</v>
       </c>
       <c r="F108" s="10" t="inlineStr">
         <is>
@@ -3076,10 +3076,10 @@
         <v>40.85</v>
       </c>
       <c r="D109" s="9" t="n">
-        <v>50.87</v>
+        <v>51.53</v>
       </c>
       <c r="E109" s="9" t="n">
-        <v>56.9</v>
+        <v>57.64</v>
       </c>
       <c r="F109" s="10" t="inlineStr">
         <is>
@@ -3101,10 +3101,10 @@
         <v>43.96</v>
       </c>
       <c r="D110" s="9" t="n">
-        <v>60.01</v>
+        <v>60.79</v>
       </c>
       <c r="E110" s="9" t="n">
-        <v>61.13</v>
+        <v>61.93</v>
       </c>
       <c r="F110" s="10" t="inlineStr">
         <is>
@@ -3126,10 +3126,10 @@
         <v>37.17</v>
       </c>
       <c r="D111" s="5" t="n">
-        <v>46.98</v>
+        <v>47.59</v>
       </c>
       <c r="E111" s="5" t="n">
-        <v>51.62</v>
+        <v>52.29</v>
       </c>
       <c r="F111" s="7" t="inlineStr"/>
       <c r="G111" s="7" t="inlineStr"/>
@@ -3147,10 +3147,10 @@
         <v>41.72</v>
       </c>
       <c r="D112" s="5" t="n">
-        <v>50.39</v>
+        <v>51.05</v>
       </c>
       <c r="E112" s="5" t="n">
-        <v>57.86</v>
+        <v>58.61</v>
       </c>
       <c r="F112" s="7" t="inlineStr"/>
       <c r="G112" s="7" t="inlineStr"/>
@@ -3168,10 +3168,10 @@
         <v>39.82</v>
       </c>
       <c r="D113" s="5" t="n">
-        <v>52.14</v>
+        <v>52.82</v>
       </c>
       <c r="E113" s="5" t="n">
-        <v>55.14</v>
+        <v>55.86</v>
       </c>
       <c r="F113" s="7" t="inlineStr"/>
       <c r="G113" s="7" t="inlineStr"/>
@@ -3189,10 +3189,10 @@
         <v>32.77</v>
       </c>
       <c r="D114" s="5" t="n">
-        <v>48.31</v>
+        <v>48.94</v>
       </c>
       <c r="E114" s="5" t="n">
-        <v>45.35</v>
+        <v>45.94</v>
       </c>
       <c r="F114" s="7" t="inlineStr"/>
       <c r="G114" s="7" t="inlineStr"/>
@@ -3210,10 +3210,10 @@
         <v>37.02</v>
       </c>
       <c r="D115" s="5" t="n">
-        <v>55.24</v>
+        <v>55.96</v>
       </c>
       <c r="E115" s="5" t="n">
-        <v>51.2</v>
+        <v>51.87</v>
       </c>
       <c r="F115" s="7" t="inlineStr"/>
       <c r="G115" s="7" t="inlineStr"/>
@@ -3231,10 +3231,10 @@
         <v>44.27</v>
       </c>
       <c r="D116" s="5" t="n">
-        <v>62.56</v>
+        <v>63.37</v>
       </c>
       <c r="E116" s="5" t="n">
-        <v>61.19</v>
+        <v>61.99</v>
       </c>
       <c r="F116" s="7" t="inlineStr"/>
       <c r="G116" s="7" t="inlineStr"/>
@@ -3252,10 +3252,10 @@
         <v>36.59</v>
       </c>
       <c r="D117" s="5" t="n">
-        <v>48.46</v>
+        <v>49.09</v>
       </c>
       <c r="E117" s="5" t="n">
-        <v>50.54</v>
+        <v>51.2</v>
       </c>
       <c r="F117" s="7" t="inlineStr"/>
       <c r="G117" s="7" t="inlineStr"/>
@@ -3273,10 +3273,10 @@
         <v>40.89</v>
       </c>
       <c r="D118" s="5" t="n">
-        <v>58.72</v>
+        <v>59.49</v>
       </c>
       <c r="E118" s="5" t="n">
-        <v>56.45</v>
+        <v>57.18</v>
       </c>
       <c r="F118" s="7" t="inlineStr"/>
       <c r="G118" s="7" t="inlineStr"/>
@@ -3294,10 +3294,10 @@
         <v>39.56</v>
       </c>
       <c r="D119" s="5" t="n">
-        <v>54.87</v>
+        <v>55.58</v>
       </c>
       <c r="E119" s="5" t="n">
-        <v>54.58</v>
+        <v>55.29</v>
       </c>
       <c r="F119" s="7" t="inlineStr"/>
       <c r="G119" s="7" t="inlineStr"/>
@@ -3315,10 +3315,10 @@
         <v>38.06</v>
       </c>
       <c r="D120" s="5" t="n">
-        <v>55.93</v>
+        <v>56.66</v>
       </c>
       <c r="E120" s="5" t="n">
-        <v>52.38</v>
+        <v>53.06</v>
       </c>
       <c r="F120" s="7" t="inlineStr"/>
       <c r="G120" s="7" t="inlineStr"/>
@@ -3336,10 +3336,10 @@
         <v>33.76</v>
       </c>
       <c r="D121" s="5" t="n">
-        <v>38.86</v>
+        <v>39.36</v>
       </c>
       <c r="E121" s="5" t="n">
-        <v>46.35</v>
+        <v>46.96</v>
       </c>
       <c r="F121" s="7" t="inlineStr"/>
       <c r="G121" s="7" t="inlineStr"/>
@@ -3357,10 +3357,10 @@
         <v>37.17</v>
       </c>
       <c r="D122" s="5" t="n">
-        <v>44.18</v>
+        <v>44.75</v>
       </c>
       <c r="E122" s="5" t="n">
-        <v>50.92</v>
+        <v>51.58</v>
       </c>
       <c r="F122" s="7" t="inlineStr"/>
       <c r="G122" s="7" t="inlineStr"/>
@@ -3378,10 +3378,10 @@
         <v>38.8</v>
       </c>
       <c r="D123" s="5" t="n">
-        <v>47.74</v>
+        <v>48.36</v>
       </c>
       <c r="E123" s="5" t="n">
-        <v>53.08</v>
+        <v>53.77</v>
       </c>
       <c r="F123" s="7" t="inlineStr"/>
       <c r="G123" s="7" t="inlineStr"/>
@@ -3399,10 +3399,10 @@
         <v>37.69</v>
       </c>
       <c r="D124" s="5" t="n">
-        <v>43.57</v>
+        <v>44.14</v>
       </c>
       <c r="E124" s="5" t="n">
-        <v>51.49</v>
+        <v>52.16</v>
       </c>
       <c r="F124" s="7" t="inlineStr"/>
       <c r="G124" s="7" t="inlineStr"/>
@@ -3420,10 +3420,10 @@
         <v>48.67</v>
       </c>
       <c r="D125" s="5" t="n">
-        <v>62.79</v>
+        <v>63.61</v>
       </c>
       <c r="E125" s="5" t="n">
-        <v>66.41</v>
+        <v>67.27</v>
       </c>
       <c r="F125" s="7" t="inlineStr"/>
       <c r="G125" s="7" t="inlineStr"/>
@@ -3441,10 +3441,10 @@
         <v>60.05</v>
       </c>
       <c r="D126" s="5" t="n">
-        <v>80.7</v>
+        <v>81.75</v>
       </c>
       <c r="E126" s="5" t="n">
-        <v>81.83</v>
+        <v>82.90000000000001</v>
       </c>
       <c r="F126" s="7" t="inlineStr"/>
       <c r="G126" s="7" t="inlineStr"/>
@@ -3462,10 +3462,10 @@
         <v>85.7</v>
       </c>
       <c r="D127" s="5" t="n">
-        <v>113.96</v>
+        <v>115.44</v>
       </c>
       <c r="E127" s="5" t="n">
-        <v>116.64</v>
+        <v>118.15</v>
       </c>
       <c r="F127" s="7" t="inlineStr"/>
       <c r="G127" s="7" t="inlineStr"/>
@@ -3483,10 +3483,10 @@
         <v>96.81999999999999</v>
       </c>
       <c r="D128" s="5" t="n">
-        <v>130.62</v>
+        <v>132.32</v>
       </c>
       <c r="E128" s="5" t="n">
-        <v>131.6</v>
+        <v>133.31</v>
       </c>
       <c r="F128" s="7" t="inlineStr"/>
       <c r="G128" s="7" t="inlineStr"/>
@@ -3504,10 +3504,10 @@
         <v>112.56</v>
       </c>
       <c r="D129" s="5" t="n">
-        <v>153.33</v>
+        <v>155.32</v>
       </c>
       <c r="E129" s="5" t="n">
-        <v>153.1</v>
+        <v>155.09</v>
       </c>
       <c r="F129" s="7" t="inlineStr"/>
       <c r="G129" s="7" t="inlineStr"/>
@@ -3525,10 +3525,10 @@
         <v>163.47</v>
       </c>
       <c r="D130" s="5" t="n">
-        <v>225.48</v>
+        <v>228.42</v>
       </c>
       <c r="E130" s="5" t="n">
-        <v>222.49</v>
+        <v>225.38</v>
       </c>
       <c r="F130" s="7" t="inlineStr"/>
       <c r="G130" s="7" t="inlineStr"/>
@@ -3546,10 +3546,10 @@
         <v>255.9</v>
       </c>
       <c r="D131" s="5" t="n">
-        <v>343.72</v>
+        <v>348.18</v>
       </c>
       <c r="E131" s="5" t="n">
-        <v>348.52</v>
+        <v>353.05</v>
       </c>
       <c r="F131" s="7" t="inlineStr"/>
       <c r="G131" s="7" t="inlineStr"/>
@@ -3567,10 +3567,10 @@
         <v>227.53</v>
       </c>
       <c r="D132" s="5" t="n">
-        <v>322.11</v>
+        <v>326.29</v>
       </c>
       <c r="E132" s="5" t="n">
-        <v>309.43</v>
+        <v>313.45</v>
       </c>
       <c r="F132" s="7" t="inlineStr"/>
       <c r="G132" s="7" t="inlineStr"/>
@@ -3588,10 +3588,10 @@
         <v>57</v>
       </c>
       <c r="D133" s="5" t="n">
-        <v>61.72</v>
+        <v>62.52</v>
       </c>
       <c r="E133" s="5" t="n">
-        <v>77.40000000000001</v>
+        <v>78.41</v>
       </c>
       <c r="F133" s="7" t="inlineStr"/>
       <c r="G133" s="7" t="inlineStr"/>
@@ -3609,10 +3609,10 @@
         <v>98.19</v>
       </c>
       <c r="D134" s="5" t="n">
-        <v>98.31</v>
+        <v>99.59</v>
       </c>
       <c r="E134" s="5" t="n">
-        <v>133.15</v>
+        <v>134.88</v>
       </c>
       <c r="F134" s="7" t="inlineStr"/>
       <c r="G134" s="7" t="inlineStr"/>
@@ -3630,10 +3630,10 @@
         <v>95.26000000000001</v>
       </c>
       <c r="D135" s="5" t="n">
-        <v>91.88</v>
+        <v>93.08</v>
       </c>
       <c r="E135" s="5" t="n">
-        <v>128.87</v>
+        <v>130.55</v>
       </c>
       <c r="F135" s="7" t="inlineStr"/>
       <c r="G135" s="7" t="inlineStr"/>
@@ -3651,10 +3651,10 @@
         <v>56.46</v>
       </c>
       <c r="D136" s="5" t="n">
-        <v>58.95</v>
+        <v>59.72</v>
       </c>
       <c r="E136" s="5" t="n">
-        <v>76.2</v>
+        <v>77.19</v>
       </c>
       <c r="F136" s="7" t="inlineStr"/>
       <c r="G136" s="7" t="inlineStr"/>
@@ -3672,10 +3672,10 @@
         <v>52.02</v>
       </c>
       <c r="D137" s="5" t="n">
-        <v>62.18</v>
+        <v>62.99</v>
       </c>
       <c r="E137" s="5" t="n">
-        <v>70.05</v>
+        <v>70.95999999999999</v>
       </c>
       <c r="F137" s="7" t="inlineStr"/>
       <c r="G137" s="7" t="inlineStr"/>
@@ -3693,10 +3693,10 @@
         <v>39.37</v>
       </c>
       <c r="D138" s="5" t="n">
-        <v>44.65</v>
+        <v>45.23</v>
       </c>
       <c r="E138" s="5" t="n">
-        <v>52.92</v>
+        <v>53.61</v>
       </c>
       <c r="F138" s="7" t="inlineStr"/>
       <c r="G138" s="7" t="inlineStr"/>
@@ -3714,10 +3714,10 @@
         <v>50.91</v>
       </c>
       <c r="D139" s="5" t="n">
-        <v>50.43</v>
+        <v>51.08</v>
       </c>
       <c r="E139" s="5" t="n">
-        <v>68.31</v>
+        <v>69.2</v>
       </c>
       <c r="F139" s="7" t="inlineStr"/>
       <c r="G139" s="7" t="inlineStr"/>
@@ -3735,10 +3735,10 @@
         <v>45.93</v>
       </c>
       <c r="D140" s="5" t="n">
-        <v>55.32</v>
+        <v>56.04</v>
       </c>
       <c r="E140" s="5" t="n">
-        <v>61.52</v>
+        <v>62.32</v>
       </c>
       <c r="F140" s="7" t="inlineStr"/>
       <c r="G140" s="7" t="inlineStr"/>
@@ -3756,10 +3756,10 @@
         <v>90.94</v>
       </c>
       <c r="D141" s="5" t="n">
-        <v>115.17</v>
+        <v>116.66</v>
       </c>
       <c r="E141" s="5" t="n">
-        <v>121.63</v>
+        <v>123.21</v>
       </c>
       <c r="F141" s="7" t="inlineStr"/>
       <c r="G141" s="7" t="inlineStr"/>
@@ -3777,10 +3777,10 @@
         <v>102.31</v>
       </c>
       <c r="D142" s="5" t="n">
-        <v>126.04</v>
+        <v>127.67</v>
       </c>
       <c r="E142" s="5" t="n">
-        <v>136.63</v>
+        <v>138.4</v>
       </c>
       <c r="F142" s="7" t="inlineStr"/>
       <c r="G142" s="7" t="inlineStr"/>
@@ -3798,10 +3798,10 @@
         <v>116.54</v>
       </c>
       <c r="D143" s="5" t="n">
-        <v>151.75</v>
+        <v>153.72</v>
       </c>
       <c r="E143" s="5" t="n">
-        <v>155.39</v>
+        <v>157.41</v>
       </c>
       <c r="F143" s="7" t="inlineStr"/>
       <c r="G143" s="7" t="inlineStr"/>
@@ -3819,10 +3819,10 @@
         <v>127.22</v>
       </c>
       <c r="D144" s="5" t="n">
-        <v>174.89</v>
+        <v>177.17</v>
       </c>
       <c r="E144" s="5" t="n">
-        <v>169.52</v>
+        <v>171.73</v>
       </c>
       <c r="F144" s="7" t="inlineStr"/>
       <c r="G144" s="7" t="inlineStr"/>
@@ -3840,10 +3840,10 @@
         <v>117.37</v>
       </c>
       <c r="D145" s="5" t="n">
-        <v>143.74</v>
+        <v>145.61</v>
       </c>
       <c r="E145" s="5" t="n">
-        <v>156.29</v>
+        <v>158.33</v>
       </c>
       <c r="F145" s="7" t="inlineStr"/>
       <c r="G145" s="7" t="inlineStr"/>
@@ -3861,10 +3861,10 @@
         <v>109.28</v>
       </c>
       <c r="D146" s="5" t="n">
-        <v>138.19</v>
+        <v>139.98</v>
       </c>
       <c r="E146" s="5" t="n">
-        <v>145.43</v>
+        <v>147.32</v>
       </c>
       <c r="F146" s="7" t="inlineStr"/>
       <c r="G146" s="7" t="inlineStr"/>
@@ -3882,10 +3882,10 @@
         <v>125.08</v>
       </c>
       <c r="D147" s="5" t="n">
-        <v>154.1</v>
+        <v>156.1</v>
       </c>
       <c r="E147" s="5" t="n">
-        <v>166.11</v>
+        <v>168.27</v>
       </c>
       <c r="F147" s="7" t="inlineStr"/>
       <c r="G147" s="7" t="inlineStr"/>
@@ -3903,10 +3903,10 @@
         <v>109.03</v>
       </c>
       <c r="D148" s="5" t="n">
-        <v>128.84</v>
+        <v>130.51</v>
       </c>
       <c r="E148" s="5" t="n">
-        <v>144.51</v>
+        <v>146.38</v>
       </c>
       <c r="F148" s="7" t="inlineStr"/>
       <c r="G148" s="7" t="inlineStr"/>
@@ -3924,10 +3924,10 @@
         <v>81.7</v>
       </c>
       <c r="D149" s="5" t="n">
-        <v>97.31999999999999</v>
+        <v>98.59</v>
       </c>
       <c r="E149" s="5" t="n">
-        <v>108.06</v>
+        <v>109.47</v>
       </c>
       <c r="F149" s="7" t="inlineStr"/>
       <c r="G149" s="7" t="inlineStr"/>
@@ -3945,10 +3945,10 @@
         <v>75.29000000000001</v>
       </c>
       <c r="D150" s="5" t="n">
-        <v>90.61</v>
+        <v>91.79000000000001</v>
       </c>
       <c r="E150" s="5" t="n">
-        <v>99.36</v>
+        <v>100.65</v>
       </c>
       <c r="F150" s="7" t="inlineStr"/>
       <c r="G150" s="7" t="inlineStr"/>
@@ -3966,10 +3966,10 @@
         <v>105.28</v>
       </c>
       <c r="D151" s="5" t="n">
-        <v>123.82</v>
+        <v>125.43</v>
       </c>
       <c r="E151" s="5" t="n">
-        <v>138.63</v>
+        <v>140.43</v>
       </c>
       <c r="F151" s="7" t="inlineStr"/>
       <c r="G151" s="7" t="inlineStr"/>
@@ -3987,10 +3987,10 @@
         <v>106.8</v>
       </c>
       <c r="D152" s="5" t="n">
-        <v>119.51</v>
+        <v>121.06</v>
       </c>
       <c r="E152" s="5" t="n">
-        <v>140.32</v>
+        <v>142.14</v>
       </c>
       <c r="F152" s="7" t="inlineStr"/>
       <c r="G152" s="7" t="inlineStr"/>
@@ -4008,10 +4008,10 @@
         <v>96.02</v>
       </c>
       <c r="D153" s="5" t="n">
-        <v>129.84</v>
+        <v>131.53</v>
       </c>
       <c r="E153" s="5" t="n">
-        <v>125.97</v>
+        <v>127.61</v>
       </c>
       <c r="F153" s="7" t="inlineStr"/>
       <c r="G153" s="7" t="inlineStr"/>
@@ -4029,10 +4029,10 @@
         <v>89.25</v>
       </c>
       <c r="D154" s="5" t="n">
-        <v>116.95</v>
+        <v>118.47</v>
       </c>
       <c r="E154" s="5" t="n">
-        <v>116.92</v>
+        <v>118.44</v>
       </c>
       <c r="F154" s="7" t="inlineStr"/>
       <c r="G154" s="7" t="inlineStr"/>
@@ -4050,10 +4050,10 @@
         <v>85.43000000000001</v>
       </c>
       <c r="D155" s="5" t="n">
-        <v>109.26</v>
+        <v>110.68</v>
       </c>
       <c r="E155" s="5" t="n">
-        <v>111.75</v>
+        <v>113.21</v>
       </c>
       <c r="F155" s="7" t="inlineStr"/>
       <c r="G155" s="7" t="inlineStr"/>
@@ -4071,10 +4071,10 @@
         <v>80.17</v>
       </c>
       <c r="D156" s="5" t="n">
-        <v>105.45</v>
+        <v>106.83</v>
       </c>
       <c r="E156" s="5" t="n">
-        <v>104.75</v>
+        <v>106.11</v>
       </c>
       <c r="F156" s="7" t="inlineStr"/>
       <c r="G156" s="7" t="inlineStr"/>
@@ -4092,10 +4092,10 @@
         <v>79.65000000000001</v>
       </c>
       <c r="D157" s="5" t="n">
-        <v>99.91</v>
+        <v>101.21</v>
       </c>
       <c r="E157" s="5" t="n">
-        <v>103.95</v>
+        <v>105.3</v>
       </c>
       <c r="F157" s="7" t="inlineStr"/>
       <c r="G157" s="7" t="inlineStr"/>
@@ -4113,10 +4113,10 @@
         <v>80.17</v>
       </c>
       <c r="D158" s="5" t="n">
-        <v>95.92</v>
+        <v>97.17</v>
       </c>
       <c r="E158" s="5" t="n">
-        <v>104.5</v>
+        <v>105.86</v>
       </c>
       <c r="F158" s="7" t="inlineStr"/>
       <c r="G158" s="7" t="inlineStr"/>
@@ -4134,10 +4134,10 @@
         <v>49.51</v>
       </c>
       <c r="D159" s="5" t="n">
-        <v>58.38</v>
+        <v>59.14</v>
       </c>
       <c r="E159" s="5" t="n">
-        <v>64.44</v>
+        <v>65.28</v>
       </c>
       <c r="F159" s="7" t="inlineStr"/>
       <c r="G159" s="7" t="inlineStr"/>
@@ -4155,10 +4155,10 @@
         <v>31.23</v>
       </c>
       <c r="D160" s="5" t="n">
-        <v>32.53</v>
+        <v>32.96</v>
       </c>
       <c r="E160" s="5" t="n">
-        <v>40.59</v>
+        <v>41.12</v>
       </c>
       <c r="F160" s="7" t="inlineStr"/>
       <c r="G160" s="7" t="inlineStr"/>
@@ -4176,10 +4176,10 @@
         <v>70.7</v>
       </c>
       <c r="D161" s="5" t="n">
-        <v>78.98999999999999</v>
+        <v>80.01000000000001</v>
       </c>
       <c r="E161" s="5" t="n">
-        <v>91.76000000000001</v>
+        <v>92.95</v>
       </c>
       <c r="F161" s="7" t="inlineStr"/>
       <c r="G161" s="7" t="inlineStr"/>
@@ -4197,10 +4197,10 @@
         <v>101.45</v>
       </c>
       <c r="D162" s="5" t="n">
-        <v>123.56</v>
+        <v>125.17</v>
       </c>
       <c r="E162" s="5" t="n">
-        <v>131.44</v>
+        <v>133.15</v>
       </c>
       <c r="F162" s="7" t="inlineStr"/>
       <c r="G162" s="7" t="inlineStr"/>
@@ -4218,10 +4218,10 @@
         <v>88.25</v>
       </c>
       <c r="D163" s="5" t="n">
-        <v>110.71</v>
+        <v>112.15</v>
       </c>
       <c r="E163" s="5" t="n">
-        <v>114.14</v>
+        <v>115.62</v>
       </c>
       <c r="F163" s="7" t="inlineStr"/>
       <c r="G163" s="7" t="inlineStr"/>
@@ -4239,10 +4239,10 @@
         <v>70.48</v>
       </c>
       <c r="D164" s="5" t="n">
-        <v>93.13</v>
+        <v>94.34</v>
       </c>
       <c r="E164" s="5" t="n">
-        <v>91</v>
+        <v>92.18000000000001</v>
       </c>
       <c r="F164" s="7" t="inlineStr"/>
       <c r="G164" s="7" t="inlineStr"/>
@@ -4260,10 +4260,10 @@
         <v>163</v>
       </c>
       <c r="D165" s="5" t="n">
-        <v>190.98</v>
+        <v>193.46</v>
       </c>
       <c r="E165" s="5" t="n">
-        <v>210.46</v>
+        <v>213.2</v>
       </c>
       <c r="F165" s="7" t="inlineStr"/>
       <c r="G165" s="7" t="inlineStr"/>
@@ -4281,10 +4281,10 @@
         <v>133.08</v>
       </c>
       <c r="D166" s="5" t="n">
-        <v>174.05</v>
+        <v>176.31</v>
       </c>
       <c r="E166" s="5" t="n">
-        <v>171.84</v>
+        <v>174.07</v>
       </c>
       <c r="F166" s="7" t="inlineStr"/>
       <c r="G166" s="7" t="inlineStr"/>
@@ -4302,10 +4302,10 @@
         <v>114.79</v>
       </c>
       <c r="D167" s="5" t="n">
-        <v>159.39</v>
+        <v>161.46</v>
       </c>
       <c r="E167" s="5" t="n">
-        <v>148.23</v>
+        <v>150.16</v>
       </c>
       <c r="F167" s="7" t="inlineStr"/>
       <c r="G167" s="7" t="inlineStr"/>
@@ -4323,10 +4323,10 @@
         <v>108.07</v>
       </c>
       <c r="D168" s="5" t="n">
-        <v>134.96</v>
+        <v>136.71</v>
       </c>
       <c r="E168" s="5" t="n">
-        <v>139.28</v>
+        <v>141.09</v>
       </c>
       <c r="F168" s="7" t="inlineStr"/>
       <c r="G168" s="7" t="inlineStr"/>
@@ -4344,10 +4344,10 @@
         <v>101.97</v>
       </c>
       <c r="D169" s="5" t="n">
-        <v>119.04</v>
+        <v>120.59</v>
       </c>
       <c r="E169" s="5" t="n">
-        <v>131.16</v>
+        <v>132.86</v>
       </c>
       <c r="F169" s="7" t="inlineStr"/>
       <c r="G169" s="7" t="inlineStr"/>
@@ -4365,10 +4365,10 @@
         <v>108.62</v>
       </c>
       <c r="D170" s="5" t="n">
-        <v>124.26</v>
+        <v>125.88</v>
       </c>
       <c r="E170" s="5" t="n">
-        <v>139.43</v>
+        <v>141.25</v>
       </c>
       <c r="F170" s="7" t="inlineStr"/>
       <c r="G170" s="7" t="inlineStr"/>
@@ -4386,10 +4386,10 @@
         <v>89.16</v>
       </c>
       <c r="D171" s="5" t="n">
-        <v>95.8</v>
+        <v>97.05</v>
       </c>
       <c r="E171" s="5" t="n">
-        <v>114.24</v>
+        <v>115.72</v>
       </c>
       <c r="F171" s="7" t="inlineStr"/>
       <c r="G171" s="7" t="inlineStr"/>
@@ -4407,10 +4407,10 @@
         <v>80.14</v>
       </c>
       <c r="D172" s="5" t="n">
-        <v>89.56999999999999</v>
+        <v>90.73999999999999</v>
       </c>
       <c r="E172" s="5" t="n">
-        <v>102.49</v>
+        <v>103.82</v>
       </c>
       <c r="F172" s="7" t="inlineStr"/>
       <c r="G172" s="7" t="inlineStr"/>
@@ -4428,10 +4428,10 @@
         <v>63.58</v>
       </c>
       <c r="D173" s="5" t="n">
-        <v>73.55</v>
+        <v>74.51000000000001</v>
       </c>
       <c r="E173" s="5" t="n">
-        <v>81.16</v>
+        <v>82.20999999999999</v>
       </c>
       <c r="F173" s="7" t="inlineStr"/>
       <c r="G173" s="7" t="inlineStr"/>
@@ -4449,10 +4449,10 @@
         <v>105.77</v>
       </c>
       <c r="D174" s="5" t="n">
-        <v>137.14</v>
+        <v>138.92</v>
       </c>
       <c r="E174" s="5" t="n">
-        <v>134.71</v>
+        <v>136.46</v>
       </c>
       <c r="F174" s="7" t="inlineStr"/>
       <c r="G174" s="7" t="inlineStr"/>
@@ -4470,10 +4470,10 @@
         <v>76.48</v>
       </c>
       <c r="D175" s="5" t="n">
-        <v>86.77</v>
+        <v>87.90000000000001</v>
       </c>
       <c r="E175" s="5" t="n">
-        <v>97.18000000000001</v>
+        <v>98.44</v>
       </c>
       <c r="F175" s="7" t="inlineStr"/>
       <c r="G175" s="7" t="inlineStr"/>
@@ -4491,10 +4491,10 @@
         <v>49.82</v>
       </c>
       <c r="D176" s="5" t="n">
-        <v>66.15000000000001</v>
+        <v>67.01000000000001</v>
       </c>
       <c r="E176" s="5" t="n">
-        <v>63.16</v>
+        <v>63.98</v>
       </c>
       <c r="F176" s="7" t="inlineStr"/>
       <c r="G176" s="7" t="inlineStr"/>
@@ -4512,10 +4512,10 @@
         <v>49.53</v>
       </c>
       <c r="D177" s="5" t="n">
-        <v>71.97</v>
+        <v>72.91</v>
       </c>
       <c r="E177" s="5" t="n">
-        <v>62.72</v>
+        <v>63.53</v>
       </c>
       <c r="F177" s="7" t="inlineStr"/>
       <c r="G177" s="7" t="inlineStr"/>
@@ -4533,10 +4533,10 @@
         <v>38.95</v>
       </c>
       <c r="D178" s="5" t="n">
-        <v>49.45</v>
+        <v>50.09</v>
       </c>
       <c r="E178" s="5" t="n">
-        <v>49.26</v>
+        <v>49.9</v>
       </c>
       <c r="F178" s="7" t="inlineStr"/>
       <c r="G178" s="7" t="inlineStr"/>
@@ -4554,10 +4554,10 @@
         <v>34.97</v>
       </c>
       <c r="D179" s="5" t="n">
-        <v>47.2</v>
+        <v>47.82</v>
       </c>
       <c r="E179" s="5" t="n">
-        <v>44.17</v>
+        <v>44.74</v>
       </c>
       <c r="F179" s="7" t="inlineStr"/>
       <c r="G179" s="7" t="inlineStr"/>
@@ -4575,10 +4575,10 @@
         <v>24.19</v>
       </c>
       <c r="D180" s="5" t="n">
-        <v>29.71</v>
+        <v>30.1</v>
       </c>
       <c r="E180" s="5" t="n">
-        <v>30.75</v>
+        <v>31.15</v>
       </c>
       <c r="F180" s="7" t="inlineStr"/>
       <c r="G180" s="7" t="inlineStr"/>
@@ -4596,10 +4596,10 @@
         <v>40.61</v>
       </c>
       <c r="D181" s="5" t="n">
-        <v>44.49</v>
+        <v>45.07</v>
       </c>
       <c r="E181" s="5" t="n">
-        <v>51.96</v>
+        <v>52.64</v>
       </c>
       <c r="F181" s="7" t="inlineStr"/>
       <c r="G181" s="7" t="inlineStr"/>
@@ -4617,10 +4617,10 @@
         <v>39.02</v>
       </c>
       <c r="D182" s="5" t="n">
-        <v>46.89</v>
+        <v>47.5</v>
       </c>
       <c r="E182" s="5" t="n">
-        <v>50.25</v>
+        <v>50.91</v>
       </c>
       <c r="F182" s="7" t="inlineStr"/>
       <c r="G182" s="7" t="inlineStr"/>
@@ -4638,10 +4638,10 @@
         <v>57.29</v>
       </c>
       <c r="D183" s="5" t="n">
-        <v>72.52</v>
+        <v>73.45999999999999</v>
       </c>
       <c r="E183" s="5" t="n">
-        <v>73.40000000000001</v>
+        <v>74.36</v>
       </c>
       <c r="F183" s="7" t="inlineStr"/>
       <c r="G183" s="7" t="inlineStr"/>
@@ -4659,10 +4659,10 @@
         <v>56.57</v>
       </c>
       <c r="D184" s="5" t="n">
-        <v>71.06999999999999</v>
+        <v>71.98999999999999</v>
       </c>
       <c r="E184" s="5" t="n">
-        <v>72.11</v>
+        <v>73.05</v>
       </c>
       <c r="F184" s="7" t="inlineStr"/>
       <c r="G184" s="7" t="inlineStr"/>
@@ -4680,10 +4680,10 @@
         <v>38.94</v>
       </c>
       <c r="D185" s="5" t="n">
-        <v>47.58</v>
+        <v>48.2</v>
       </c>
       <c r="E185" s="5" t="n">
-        <v>49.39</v>
+        <v>50.03</v>
       </c>
       <c r="F185" s="7" t="inlineStr"/>
       <c r="G185" s="7" t="inlineStr"/>
@@ -4701,10 +4701,10 @@
         <v>37.37</v>
       </c>
       <c r="D186" s="5" t="n">
-        <v>52.49</v>
+        <v>53.17</v>
       </c>
       <c r="E186" s="5" t="n">
-        <v>47.25</v>
+        <v>47.87</v>
       </c>
       <c r="F186" s="7" t="inlineStr"/>
       <c r="G186" s="7" t="inlineStr"/>
@@ -4722,10 +4722,10 @@
         <v>57.08</v>
       </c>
       <c r="D187" s="5" t="n">
-        <v>74.84</v>
+        <v>75.81999999999999</v>
       </c>
       <c r="E187" s="5" t="n">
-        <v>71.95999999999999</v>
+        <v>72.89</v>
       </c>
       <c r="F187" s="7" t="inlineStr"/>
       <c r="G187" s="7" t="inlineStr"/>
@@ -4743,10 +4743,10 @@
         <v>43.26</v>
       </c>
       <c r="D188" s="5" t="n">
-        <v>46.33</v>
+        <v>46.93</v>
       </c>
       <c r="E188" s="5" t="n">
-        <v>54.37</v>
+        <v>55.08</v>
       </c>
       <c r="F188" s="7" t="inlineStr"/>
       <c r="G188" s="7" t="inlineStr"/>
@@ -4764,10 +4764,10 @@
         <v>40.03</v>
       </c>
       <c r="D189" s="5" t="n">
-        <v>47.43</v>
+        <v>48.05</v>
       </c>
       <c r="E189" s="5" t="n">
-        <v>50.22</v>
+        <v>50.87</v>
       </c>
       <c r="F189" s="7" t="inlineStr"/>
       <c r="G189" s="7" t="inlineStr"/>
@@ -4785,10 +4785,10 @@
         <v>36.7</v>
       </c>
       <c r="D190" s="5" t="n">
-        <v>40.05</v>
+        <v>40.57</v>
       </c>
       <c r="E190" s="5" t="n">
-        <v>45.95</v>
+        <v>46.55</v>
       </c>
       <c r="F190" s="7" t="inlineStr"/>
       <c r="G190" s="7" t="inlineStr"/>
@@ -4806,10 +4806,10 @@
         <v>31.5</v>
       </c>
       <c r="D191" s="5" t="n">
-        <v>38.46</v>
+        <v>38.96</v>
       </c>
       <c r="E191" s="5" t="n">
-        <v>39.36</v>
+        <v>39.88</v>
       </c>
       <c r="F191" s="7" t="inlineStr"/>
       <c r="G191" s="7" t="inlineStr"/>
@@ -4827,10 +4827,10 @@
         <v>28.45</v>
       </c>
       <c r="D192" s="5" t="n">
-        <v>31.59</v>
+        <v>32</v>
       </c>
       <c r="E192" s="5" t="n">
-        <v>35.47</v>
+        <v>35.93</v>
       </c>
       <c r="F192" s="7" t="inlineStr"/>
       <c r="G192" s="7" t="inlineStr"/>
@@ -4848,10 +4848,10 @@
         <v>44.32</v>
       </c>
       <c r="D193" s="5" t="n">
-        <v>51.3</v>
+        <v>51.96</v>
       </c>
       <c r="E193" s="5" t="n">
-        <v>55.12</v>
+        <v>55.83</v>
       </c>
       <c r="F193" s="7" t="inlineStr"/>
       <c r="G193" s="7" t="inlineStr"/>
@@ -4869,10 +4869,10 @@
         <v>77.62</v>
       </c>
       <c r="D194" s="5" t="n">
-        <v>85.45</v>
+        <v>86.56</v>
       </c>
       <c r="E194" s="5" t="n">
-        <v>96.29000000000001</v>
+        <v>97.55</v>
       </c>
       <c r="F194" s="7" t="inlineStr"/>
       <c r="G194" s="7" t="inlineStr"/>
@@ -4890,10 +4890,10 @@
         <v>42.75</v>
       </c>
       <c r="D195" s="5" t="n">
-        <v>47.19</v>
+        <v>47.81</v>
       </c>
       <c r="E195" s="5" t="n">
-        <v>52.88</v>
+        <v>53.57</v>
       </c>
       <c r="F195" s="7" t="inlineStr"/>
       <c r="G195" s="7" t="inlineStr"/>
@@ -4911,10 +4911,10 @@
         <v>24.96</v>
       </c>
       <c r="D196" s="5" t="n">
-        <v>26.47</v>
+        <v>26.82</v>
       </c>
       <c r="E196" s="5" t="n">
-        <v>30.79</v>
+        <v>31.19</v>
       </c>
       <c r="F196" s="7" t="inlineStr"/>
       <c r="G196" s="7" t="inlineStr"/>
@@ -4932,10 +4932,10 @@
         <v>21.88</v>
       </c>
       <c r="D197" s="5" t="n">
-        <v>20.32</v>
+        <v>20.59</v>
       </c>
       <c r="E197" s="5" t="n">
-        <v>26.92</v>
+        <v>27.27</v>
       </c>
       <c r="F197" s="7" t="inlineStr"/>
       <c r="G197" s="7" t="inlineStr"/>
@@ -4953,10 +4953,10 @@
         <v>9.68</v>
       </c>
       <c r="D198" s="5" t="n">
-        <v>11.49</v>
+        <v>11.64</v>
       </c>
       <c r="E198" s="5" t="n">
-        <v>11.86</v>
+        <v>12.01</v>
       </c>
       <c r="F198" s="7" t="inlineStr"/>
       <c r="G198" s="7" t="inlineStr"/>
@@ -4974,10 +4974,10 @@
         <v>33.48</v>
       </c>
       <c r="D199" s="5" t="n">
-        <v>38.74</v>
+        <v>39.24</v>
       </c>
       <c r="E199" s="5" t="n">
-        <v>40.84</v>
+        <v>41.37</v>
       </c>
       <c r="F199" s="7" t="inlineStr"/>
       <c r="G199" s="7" t="inlineStr"/>
@@ -4995,10 +4995,10 @@
         <v>50.7</v>
       </c>
       <c r="D200" s="5" t="n">
-        <v>60.55</v>
+        <v>61.34</v>
       </c>
       <c r="E200" s="5" t="n">
-        <v>61.58</v>
+        <v>62.38</v>
       </c>
       <c r="F200" s="7" t="inlineStr"/>
       <c r="G200" s="7" t="inlineStr"/>
@@ -5016,10 +5016,10 @@
         <v>66.73999999999999</v>
       </c>
       <c r="D201" s="5" t="n">
-        <v>75.42</v>
+        <v>76.40000000000001</v>
       </c>
       <c r="E201" s="5" t="n">
-        <v>80.48999999999999</v>
+        <v>81.53</v>
       </c>
       <c r="F201" s="7" t="inlineStr"/>
       <c r="G201" s="7" t="inlineStr"/>
@@ -5037,10 +5037,10 @@
         <v>78.06999999999999</v>
       </c>
       <c r="D202" s="5" t="n">
-        <v>86.45999999999999</v>
+        <v>87.59</v>
       </c>
       <c r="E202" s="5" t="n">
-        <v>93.48</v>
+        <v>94.7</v>
       </c>
       <c r="F202" s="7" t="inlineStr"/>
       <c r="G202" s="7" t="inlineStr"/>
@@ -5058,10 +5058,10 @@
         <v>78.65000000000001</v>
       </c>
       <c r="D203" s="5" t="n">
-        <v>88.97</v>
+        <v>90.13</v>
       </c>
       <c r="E203" s="5" t="n">
-        <v>93.51000000000001</v>
+        <v>94.73</v>
       </c>
       <c r="F203" s="7" t="inlineStr"/>
       <c r="G203" s="7" t="inlineStr"/>
@@ -5079,10 +5079,10 @@
         <v>164.79</v>
       </c>
       <c r="D204" s="5" t="n">
-        <v>166.97</v>
+        <v>169.14</v>
       </c>
       <c r="E204" s="5" t="n">
-        <v>194.77</v>
+        <v>197.3</v>
       </c>
       <c r="F204" s="7" t="inlineStr"/>
       <c r="G204" s="7" t="inlineStr"/>
@@ -5100,10 +5100,10 @@
         <v>241.85</v>
       </c>
       <c r="D205" s="5" t="n">
-        <v>255.19</v>
+        <v>258.5</v>
       </c>
       <c r="E205" s="5" t="n">
-        <v>284.16</v>
+        <v>287.85</v>
       </c>
       <c r="F205" s="7" t="inlineStr"/>
       <c r="G205" s="7" t="inlineStr"/>
@@ -5121,10 +5121,10 @@
         <v>382.13</v>
       </c>
       <c r="D206" s="5" t="n">
-        <v>334.94</v>
+        <v>339.29</v>
       </c>
       <c r="E206" s="5" t="n">
-        <v>446.35</v>
+        <v>452.15</v>
       </c>
       <c r="F206" s="7" t="inlineStr"/>
       <c r="G206" s="7" t="inlineStr"/>
@@ -5142,10 +5142,10 @@
         <v>366</v>
       </c>
       <c r="D207" s="5" t="n">
-        <v>374.8</v>
+        <v>379.67</v>
       </c>
       <c r="E207" s="5" t="n">
-        <v>424.9</v>
+        <v>430.43</v>
       </c>
       <c r="F207" s="7" t="inlineStr"/>
       <c r="G207" s="7" t="inlineStr"/>
@@ -5163,10 +5163,10 @@
         <v>169.02</v>
       </c>
       <c r="D208" s="5" t="n">
-        <v>172.52</v>
+        <v>174.76</v>
       </c>
       <c r="E208" s="5" t="n">
-        <v>195.03</v>
+        <v>197.57</v>
       </c>
       <c r="F208" s="7" t="inlineStr"/>
       <c r="G208" s="7" t="inlineStr"/>
@@ -5184,10 +5184,10 @@
         <v>150.51</v>
       </c>
       <c r="D209" s="5" t="n">
-        <v>152.25</v>
+        <v>154.23</v>
       </c>
       <c r="E209" s="5" t="n">
-        <v>172.63</v>
+        <v>174.88</v>
       </c>
       <c r="F209" s="7" t="inlineStr"/>
       <c r="G209" s="7" t="inlineStr"/>
@@ -5205,10 +5205,10 @@
         <v>126.49</v>
       </c>
       <c r="D210" s="5" t="n">
-        <v>139.07</v>
+        <v>140.88</v>
       </c>
       <c r="E210" s="5" t="n">
-        <v>144.19</v>
+        <v>146.07</v>
       </c>
       <c r="F210" s="7" t="inlineStr"/>
       <c r="G210" s="7" t="inlineStr"/>
@@ -5226,10 +5226,10 @@
         <v>112.35</v>
       </c>
       <c r="D211" s="5" t="n">
-        <v>114.41</v>
+        <v>115.9</v>
       </c>
       <c r="E211" s="5" t="n">
-        <v>127.29</v>
+        <v>128.95</v>
       </c>
       <c r="F211" s="7" t="inlineStr"/>
       <c r="G211" s="7" t="inlineStr"/>
@@ -5247,10 +5247,10 @@
         <v>67.38</v>
       </c>
       <c r="D212" s="5" t="n">
-        <v>85.98999999999999</v>
+        <v>87.11</v>
       </c>
       <c r="E212" s="5" t="n">
-        <v>75.88</v>
+        <v>76.87</v>
       </c>
       <c r="F212" s="7" t="inlineStr"/>
       <c r="G212" s="7" t="inlineStr"/>
@@ -5268,10 +5268,10 @@
         <v>81.09</v>
       </c>
       <c r="D213" s="5" t="n">
-        <v>97.38</v>
+        <v>98.64</v>
       </c>
       <c r="E213" s="5" t="n">
-        <v>90.91</v>
+        <v>92.09</v>
       </c>
       <c r="F213" s="7" t="inlineStr"/>
       <c r="G213" s="7" t="inlineStr"/>
@@ -5289,10 +5289,10 @@
         <v>76.56999999999999</v>
       </c>
       <c r="D214" s="5" t="n">
-        <v>90.98999999999999</v>
+        <v>92.18000000000001</v>
       </c>
       <c r="E214" s="5" t="n">
-        <v>85.45999999999999</v>
+        <v>86.56999999999999</v>
       </c>
       <c r="F214" s="7" t="inlineStr"/>
       <c r="G214" s="7" t="inlineStr"/>
@@ -5310,10 +5310,10 @@
         <v>68.09999999999999</v>
       </c>
       <c r="D215" s="5" t="n">
-        <v>80.39</v>
+        <v>81.43000000000001</v>
       </c>
       <c r="E215" s="5" t="n">
-        <v>75.67</v>
+        <v>76.65000000000001</v>
       </c>
       <c r="F215" s="7" t="inlineStr"/>
       <c r="G215" s="7" t="inlineStr"/>
@@ -5331,10 +5331,10 @@
         <v>70.91</v>
       </c>
       <c r="D216" s="5" t="n">
-        <v>77.59</v>
+        <v>78.59999999999999</v>
       </c>
       <c r="E216" s="5" t="n">
-        <v>78.56</v>
+        <v>79.58</v>
       </c>
       <c r="F216" s="7" t="inlineStr"/>
       <c r="G216" s="7" t="inlineStr"/>
@@ -5352,10 +5352,10 @@
         <v>86.34999999999999</v>
       </c>
       <c r="D217" s="5" t="n">
-        <v>92.98</v>
+        <v>94.19</v>
       </c>
       <c r="E217" s="5" t="n">
-        <v>95.40000000000001</v>
+        <v>96.64</v>
       </c>
       <c r="F217" s="7" t="inlineStr"/>
       <c r="G217" s="7" t="inlineStr"/>
@@ -5373,10 +5373,10 @@
         <v>52.09</v>
       </c>
       <c r="D218" s="5" t="n">
-        <v>41.91</v>
+        <v>42.45</v>
       </c>
       <c r="E218" s="5" t="n">
-        <v>57.38</v>
+        <v>58.13</v>
       </c>
       <c r="F218" s="7" t="inlineStr"/>
       <c r="G218" s="7" t="inlineStr"/>
@@ -5394,10 +5394,10 @@
         <v>32.62</v>
       </c>
       <c r="D219" s="5" t="n">
-        <v>25.59</v>
+        <v>25.92</v>
       </c>
       <c r="E219" s="5" t="n">
-        <v>35.8</v>
+        <v>36.26</v>
       </c>
       <c r="F219" s="7" t="inlineStr"/>
       <c r="G219" s="7" t="inlineStr"/>
@@ -5415,10 +5415,10 @@
         <v>37.77</v>
       </c>
       <c r="D220" s="5" t="n">
-        <v>41.16</v>
+        <v>41.7</v>
       </c>
       <c r="E220" s="5" t="n">
-        <v>41.29</v>
+        <v>41.83</v>
       </c>
       <c r="F220" s="7" t="inlineStr"/>
       <c r="G220" s="7" t="inlineStr"/>
@@ -5436,10 +5436,10 @@
         <v>24.86</v>
       </c>
       <c r="D221" s="5" t="n">
-        <v>29.09</v>
+        <v>29.47</v>
       </c>
       <c r="E221" s="5" t="n">
-        <v>27.08</v>
+        <v>27.43</v>
       </c>
       <c r="F221" s="7" t="inlineStr"/>
       <c r="G221" s="7" t="inlineStr"/>
@@ -5457,10 +5457,10 @@
         <v>36.02</v>
       </c>
       <c r="D222" s="5" t="n">
-        <v>40.93</v>
+        <v>41.46</v>
       </c>
       <c r="E222" s="5" t="n">
-        <v>39.15</v>
+        <v>39.66</v>
       </c>
       <c r="F222" s="7" t="inlineStr"/>
       <c r="G222" s="7" t="inlineStr"/>
@@ -5478,10 +5478,10 @@
         <v>57.49</v>
       </c>
       <c r="D223" s="5" t="n">
-        <v>65.04000000000001</v>
+        <v>65.89</v>
       </c>
       <c r="E223" s="5" t="n">
-        <v>62.35</v>
+        <v>63.16</v>
       </c>
       <c r="F223" s="7" t="inlineStr"/>
       <c r="G223" s="7" t="inlineStr"/>
@@ -5499,10 +5499,10 @@
         <v>49.09</v>
       </c>
       <c r="D224" s="5" t="n">
-        <v>56.38</v>
+        <v>57.11</v>
       </c>
       <c r="E224" s="5" t="n">
-        <v>53.13</v>
+        <v>53.82</v>
       </c>
       <c r="F224" s="7" t="inlineStr"/>
       <c r="G224" s="7" t="inlineStr"/>
@@ -5520,10 +5520,10 @@
         <v>49.62</v>
       </c>
       <c r="D225" s="5" t="n">
-        <v>54.08</v>
+        <v>54.78</v>
       </c>
       <c r="E225" s="5" t="n">
-        <v>53.54</v>
+        <v>54.23</v>
       </c>
       <c r="F225" s="7" t="inlineStr"/>
       <c r="G225" s="7" t="inlineStr"/>
@@ -5541,10 +5541,10 @@
         <v>110.18</v>
       </c>
       <c r="D226" s="5" t="n">
-        <v>88.05</v>
+        <v>89.2</v>
       </c>
       <c r="E226" s="5" t="n">
-        <v>118.51</v>
+        <v>120.05</v>
       </c>
       <c r="F226" s="7" t="inlineStr"/>
       <c r="G226" s="7" t="inlineStr"/>
@@ -5562,10 +5562,10 @@
         <v>67.43000000000001</v>
       </c>
       <c r="D227" s="5" t="n">
-        <v>74.69</v>
+        <v>75.66</v>
       </c>
       <c r="E227" s="5" t="n">
-        <v>72.31</v>
+        <v>73.25</v>
       </c>
       <c r="F227" s="7" t="inlineStr"/>
       <c r="G227" s="7" t="inlineStr"/>
@@ -5583,10 +5583,10 @@
         <v>70.53</v>
       </c>
       <c r="D228" s="5" t="n">
-        <v>78.38</v>
+        <v>79.40000000000001</v>
       </c>
       <c r="E228" s="5" t="n">
-        <v>75.37</v>
+        <v>76.34999999999999</v>
       </c>
       <c r="F228" s="7" t="inlineStr"/>
       <c r="G228" s="7" t="inlineStr"/>
@@ -5604,10 +5604,10 @@
         <v>145.36</v>
       </c>
       <c r="D229" s="5" t="n">
-        <v>150.18</v>
+        <v>152.13</v>
       </c>
       <c r="E229" s="5" t="n">
-        <v>154.79</v>
+        <v>156.8</v>
       </c>
       <c r="F229" s="7" t="inlineStr"/>
       <c r="G229" s="7" t="inlineStr"/>
@@ -5625,10 +5625,10 @@
         <v>212.7</v>
       </c>
       <c r="D230" s="5" t="n">
-        <v>189.16</v>
+        <v>191.62</v>
       </c>
       <c r="E230" s="5" t="n">
-        <v>225.72</v>
+        <v>228.65</v>
       </c>
       <c r="F230" s="7" t="inlineStr"/>
       <c r="G230" s="7" t="inlineStr"/>
@@ -5646,10 +5646,10 @@
         <v>215.33</v>
       </c>
       <c r="D231" s="5" t="n">
-        <v>191.68</v>
+        <v>194.17</v>
       </c>
       <c r="E231" s="5" t="n">
-        <v>228.34</v>
+        <v>231.31</v>
       </c>
       <c r="F231" s="7" t="inlineStr"/>
       <c r="G231" s="7" t="inlineStr"/>
@@ -5667,10 +5667,10 @@
         <v>155.78</v>
       </c>
       <c r="D232" s="5" t="n">
-        <v>136.37</v>
+        <v>138.14</v>
       </c>
       <c r="E232" s="5" t="n">
-        <v>165.07</v>
+        <v>167.22</v>
       </c>
       <c r="F232" s="7" t="inlineStr"/>
       <c r="G232" s="7" t="inlineStr"/>
@@ -5688,10 +5688,10 @@
         <v>31.21</v>
       </c>
       <c r="D233" s="5" t="n">
-        <v>23.84</v>
+        <v>24.15</v>
       </c>
       <c r="E233" s="5" t="n">
-        <v>33.05</v>
+        <v>33.48</v>
       </c>
       <c r="F233" s="7" t="inlineStr"/>
       <c r="G233" s="7" t="inlineStr"/>
@@ -5709,10 +5709,10 @@
         <v>52.54</v>
       </c>
       <c r="D234" s="5" t="n">
-        <v>52.7</v>
+        <v>53.38</v>
       </c>
       <c r="E234" s="5" t="n">
-        <v>55.6</v>
+        <v>56.32</v>
       </c>
       <c r="F234" s="7" t="inlineStr"/>
       <c r="G234" s="7" t="inlineStr"/>
@@ -5730,10 +5730,10 @@
         <v>96.67</v>
       </c>
       <c r="D235" s="5" t="n">
-        <v>101.37</v>
+        <v>102.69</v>
       </c>
       <c r="E235" s="5" t="n">
-        <v>102.23</v>
+        <v>103.56</v>
       </c>
       <c r="F235" s="7" t="inlineStr"/>
       <c r="G235" s="7" t="inlineStr"/>
@@ -5751,10 +5751,10 @@
         <v>68.69</v>
       </c>
       <c r="D236" s="5" t="n">
-        <v>80.43000000000001</v>
+        <v>81.48</v>
       </c>
       <c r="E236" s="5" t="n">
-        <v>72.59</v>
+        <v>73.54000000000001</v>
       </c>
       <c r="F236" s="7" t="inlineStr"/>
       <c r="G236" s="7" t="inlineStr"/>
@@ -5772,10 +5772,10 @@
         <v>109.16</v>
       </c>
       <c r="D237" s="5" t="n">
-        <v>119.72</v>
+        <v>121.28</v>
       </c>
       <c r="E237" s="5" t="n">
-        <v>115.01</v>
+        <v>116.5</v>
       </c>
       <c r="F237" s="7" t="inlineStr"/>
       <c r="G237" s="7" t="inlineStr"/>
@@ -5793,10 +5793,10 @@
         <v>124.99</v>
       </c>
       <c r="D238" s="5" t="n">
-        <v>127.82</v>
+        <v>129.48</v>
       </c>
       <c r="E238" s="5" t="n">
-        <v>131.29</v>
+        <v>132.99</v>
       </c>
       <c r="F238" s="7" t="inlineStr"/>
       <c r="G238" s="7" t="inlineStr"/>
@@ -5814,10 +5814,10 @@
         <v>100.72</v>
       </c>
       <c r="D239" s="5" t="n">
-        <v>104.76</v>
+        <v>106.12</v>
       </c>
       <c r="E239" s="5" t="n">
-        <v>105.47</v>
+        <v>106.84</v>
       </c>
       <c r="F239" s="7" t="inlineStr"/>
       <c r="G239" s="7" t="inlineStr"/>
@@ -5835,10 +5835,10 @@
         <v>98.45999999999999</v>
       </c>
       <c r="D240" s="5" t="n">
-        <v>105.01</v>
+        <v>106.38</v>
       </c>
       <c r="E240" s="5" t="n">
-        <v>102.85</v>
+        <v>104.19</v>
       </c>
       <c r="F240" s="7" t="inlineStr"/>
       <c r="G240" s="7" t="inlineStr"/>
@@ -5856,10 +5856,10 @@
         <v>113.21</v>
       </c>
       <c r="D241" s="5" t="n">
-        <v>107.73</v>
+        <v>109.13</v>
       </c>
       <c r="E241" s="5" t="n">
-        <v>117.96</v>
+        <v>119.5</v>
       </c>
       <c r="F241" s="7" t="inlineStr"/>
       <c r="G241" s="7" t="inlineStr"/>
@@ -5877,10 +5877,10 @@
         <v>327.6</v>
       </c>
       <c r="D242" s="5" t="n">
-        <v>227.99</v>
+        <v>230.95</v>
       </c>
       <c r="E242" s="5" t="n">
-        <v>340.51</v>
+        <v>344.94</v>
       </c>
       <c r="F242" s="7" t="inlineStr"/>
       <c r="G242" s="7" t="inlineStr"/>
@@ -5898,10 +5898,10 @@
         <v>130.22</v>
       </c>
       <c r="D243" s="5" t="n">
-        <v>121.96</v>
+        <v>123.54</v>
       </c>
       <c r="E243" s="5" t="n">
-        <v>134.76</v>
+        <v>136.51</v>
       </c>
       <c r="F243" s="7" t="inlineStr"/>
       <c r="G243" s="7" t="inlineStr"/>
@@ -5919,10 +5919,10 @@
         <v>133.43</v>
       </c>
       <c r="D244" s="5" t="n">
-        <v>129.02</v>
+        <v>130.7</v>
       </c>
       <c r="E244" s="5" t="n">
-        <v>137.48</v>
+        <v>139.27</v>
       </c>
       <c r="F244" s="7" t="inlineStr"/>
       <c r="G244" s="7" t="inlineStr"/>
@@ -5940,10 +5940,10 @@
         <v>36.13</v>
       </c>
       <c r="D245" s="5" t="n">
-        <v>29.37</v>
+        <v>29.75</v>
       </c>
       <c r="E245" s="5" t="n">
-        <v>37.06</v>
+        <v>37.55</v>
       </c>
       <c r="F245" s="7" t="inlineStr"/>
       <c r="G245" s="7" t="inlineStr"/>
@@ -5961,10 +5961,10 @@
         <v>26.88</v>
       </c>
       <c r="D246" s="5" t="n">
-        <v>25.14</v>
+        <v>25.46</v>
       </c>
       <c r="E246" s="5" t="n">
-        <v>27.52</v>
+        <v>27.88</v>
       </c>
       <c r="F246" s="7" t="inlineStr"/>
       <c r="G246" s="7" t="inlineStr"/>
@@ -5982,10 +5982,10 @@
         <v>34.33</v>
       </c>
       <c r="D247" s="5" t="n">
-        <v>41.39</v>
+        <v>41.93</v>
       </c>
       <c r="E247" s="5" t="n">
-        <v>35.08</v>
+        <v>35.54</v>
       </c>
       <c r="F247" s="7" t="inlineStr"/>
       <c r="G247" s="7" t="inlineStr"/>
@@ -6003,10 +6003,10 @@
         <v>55.59</v>
       </c>
       <c r="D248" s="5" t="n">
-        <v>60.52</v>
+        <v>61.3</v>
       </c>
       <c r="E248" s="5" t="n">
-        <v>56.69</v>
+        <v>57.43</v>
       </c>
       <c r="F248" s="7" t="inlineStr"/>
       <c r="G248" s="7" t="inlineStr"/>
@@ -6024,10 +6024,10 @@
         <v>114.92</v>
       </c>
       <c r="D249" s="5" t="n">
-        <v>102.46</v>
+        <v>103.79</v>
       </c>
       <c r="E249" s="5" t="n">
-        <v>116.66</v>
+        <v>118.18</v>
       </c>
       <c r="F249" s="7" t="inlineStr"/>
       <c r="G249" s="7" t="inlineStr"/>
@@ -6045,10 +6045,10 @@
         <v>87.54000000000001</v>
       </c>
       <c r="D250" s="5" t="n">
-        <v>91.23</v>
+        <v>92.42</v>
       </c>
       <c r="E250" s="5" t="n">
-        <v>88.47</v>
+        <v>89.62</v>
       </c>
       <c r="F250" s="7" t="inlineStr"/>
       <c r="G250" s="7" t="inlineStr"/>
@@ -6066,10 +6066,10 @@
         <v>90.92</v>
       </c>
       <c r="D251" s="5" t="n">
-        <v>91.59</v>
+        <v>92.78</v>
       </c>
       <c r="E251" s="5" t="n">
-        <v>91.47</v>
+        <v>92.65000000000001</v>
       </c>
       <c r="F251" s="7" t="inlineStr"/>
       <c r="G251" s="7" t="inlineStr"/>
@@ -6087,10 +6087,10 @@
         <v>87.29000000000001</v>
       </c>
       <c r="D252" s="5" t="n">
-        <v>85.58</v>
+        <v>86.69</v>
       </c>
       <c r="E252" s="5" t="n">
-        <v>87.64</v>
+        <v>88.78</v>
       </c>
       <c r="F252" s="7" t="inlineStr"/>
       <c r="G252" s="7" t="inlineStr"/>
@@ -6108,10 +6108,10 @@
         <v>100.05</v>
       </c>
       <c r="D253" s="5" t="n">
-        <v>96.33</v>
+        <v>97.58</v>
       </c>
       <c r="E253" s="5" t="n">
-        <v>100.25</v>
+        <v>101.55</v>
       </c>
       <c r="F253" s="7" t="inlineStr"/>
       <c r="G253" s="7" t="inlineStr"/>
@@ -6129,10 +6129,10 @@
         <v>81.67</v>
       </c>
       <c r="D254" s="5" t="n">
-        <v>76.83</v>
+        <v>77.83</v>
       </c>
       <c r="E254" s="5" t="n">
-        <v>81.67</v>
+        <v>82.73</v>
       </c>
       <c r="F254" s="7" t="inlineStr"/>
       <c r="G254" s="7" t="inlineStr"/>
@@ -6150,17 +6150,13 @@
         <v>93.72</v>
       </c>
       <c r="D255" s="5" t="n">
-        <v>71.04000000000001</v>
+        <v>71.65000000000001</v>
       </c>
       <c r="E255" s="5" t="n">
-        <v>93.72</v>
+        <v>94.53</v>
       </c>
       <c r="F255" s="7" t="inlineStr"/>
-      <c r="G255" s="7" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
+      <c r="G255" s="7" t="inlineStr"/>
     </row>
     <row r="256">
       <c r="A256" s="4" t="inlineStr">
@@ -6175,17 +6171,13 @@
         <v>65.73</v>
       </c>
       <c r="D256" s="5" t="n">
-        <v>57.95</v>
+        <v>58.2</v>
       </c>
       <c r="E256" s="5" t="n">
-        <v>65.73</v>
+        <v>66.01000000000001</v>
       </c>
       <c r="F256" s="7" t="inlineStr"/>
-      <c r="G256" s="7" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
+      <c r="G256" s="7" t="inlineStr"/>
     </row>
     <row r="257">
       <c r="A257" s="4" t="inlineStr">
@@ -6206,11 +6198,7 @@
         <v>37.87</v>
       </c>
       <c r="F257" s="7" t="inlineStr"/>
-      <c r="G257" s="7" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
+      <c r="G257" s="7" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -6273,10 +6261,10 @@
         <v>86.38</v>
       </c>
       <c r="D2" s="5" t="n">
-        <v>140.27</v>
+        <v>142.1</v>
       </c>
       <c r="E2" s="5" t="n">
-        <v>154.1</v>
+        <v>156.1</v>
       </c>
     </row>
     <row r="3">
@@ -6292,10 +6280,10 @@
         <v>115.77</v>
       </c>
       <c r="D3" s="5" t="n">
-        <v>199.75</v>
+        <v>202.34</v>
       </c>
       <c r="E3" s="5" t="n">
-        <v>205.85</v>
+        <v>208.52</v>
       </c>
     </row>
     <row r="4">
@@ -6311,10 +6299,10 @@
         <v>141.34</v>
       </c>
       <c r="D4" s="5" t="n">
-        <v>189.98</v>
+        <v>192.45</v>
       </c>
       <c r="E4" s="5" t="n">
-        <v>250.48</v>
+        <v>253.74</v>
       </c>
     </row>
     <row r="5">
@@ -6330,10 +6318,10 @@
         <v>77.7</v>
       </c>
       <c r="D5" s="5" t="n">
-        <v>122.5</v>
+        <v>124.09</v>
       </c>
       <c r="E5" s="5" t="n">
-        <v>137.25</v>
+        <v>139.03</v>
       </c>
     </row>
     <row r="6">
@@ -6349,10 +6337,10 @@
         <v>102.17</v>
       </c>
       <c r="D6" s="5" t="n">
-        <v>145.27</v>
+        <v>147.15</v>
       </c>
       <c r="E6" s="5" t="n">
-        <v>180.16</v>
+        <v>182.5</v>
       </c>
     </row>
     <row r="7">
@@ -6368,10 +6356,10 @@
         <v>59.19</v>
       </c>
       <c r="D7" s="5" t="n">
-        <v>101.47</v>
+        <v>102.78</v>
       </c>
       <c r="E7" s="5" t="n">
-        <v>104.19</v>
+        <v>105.55</v>
       </c>
     </row>
     <row r="8">
@@ -6387,10 +6375,10 @@
         <v>46.71</v>
       </c>
       <c r="D8" s="5" t="n">
-        <v>75.25</v>
+        <v>76.23</v>
       </c>
       <c r="E8" s="5" t="n">
-        <v>82.08</v>
+        <v>83.15000000000001</v>
       </c>
     </row>
     <row r="9">
@@ -6406,10 +6394,10 @@
         <v>40.3</v>
       </c>
       <c r="D9" s="5" t="n">
-        <v>64.66</v>
+        <v>65.5</v>
       </c>
       <c r="E9" s="5" t="n">
-        <v>70.62</v>
+        <v>71.54000000000001</v>
       </c>
     </row>
     <row r="10">
@@ -6425,10 +6413,10 @@
         <v>35.57</v>
       </c>
       <c r="D10" s="5" t="n">
-        <v>56.68</v>
+        <v>57.42</v>
       </c>
       <c r="E10" s="5" t="n">
-        <v>62.15</v>
+        <v>62.96</v>
       </c>
     </row>
     <row r="11">
@@ -6444,10 +6432,10 @@
         <v>32.53</v>
       </c>
       <c r="D11" s="5" t="n">
-        <v>49.48</v>
+        <v>50.13</v>
       </c>
       <c r="E11" s="5" t="n">
-        <v>56.68</v>
+        <v>57.42</v>
       </c>
     </row>
     <row r="12">
@@ -6463,10 +6451,10 @@
         <v>33.75</v>
       </c>
       <c r="D12" s="5" t="n">
-        <v>57.82</v>
+        <v>58.57</v>
       </c>
       <c r="E12" s="5" t="n">
-        <v>58.5</v>
+        <v>59.26</v>
       </c>
     </row>
     <row r="13">
@@ -6482,10 +6470,10 @@
         <v>47.59</v>
       </c>
       <c r="D13" s="5" t="n">
-        <v>58.21</v>
+        <v>58.96</v>
       </c>
       <c r="E13" s="5" t="n">
-        <v>82.05</v>
+        <v>83.12</v>
       </c>
     </row>
     <row r="14">
@@ -6501,10 +6489,10 @@
         <v>52.3</v>
       </c>
       <c r="D14" s="5" t="n">
-        <v>70.98999999999999</v>
+        <v>71.91</v>
       </c>
       <c r="E14" s="5" t="n">
-        <v>89.7</v>
+        <v>90.87</v>
       </c>
     </row>
     <row r="15">
@@ -6520,10 +6508,10 @@
         <v>69.09999999999999</v>
       </c>
       <c r="D15" s="5" t="n">
-        <v>82.5</v>
+        <v>83.56999999999999</v>
       </c>
       <c r="E15" s="5" t="n">
-        <v>118.17</v>
+        <v>119.7</v>
       </c>
     </row>
     <row r="16">
@@ -6539,10 +6527,10 @@
         <v>39.9</v>
       </c>
       <c r="D16" s="5" t="n">
-        <v>59.97</v>
+        <v>60.75</v>
       </c>
       <c r="E16" s="5" t="n">
-        <v>68.03</v>
+        <v>68.92</v>
       </c>
     </row>
     <row r="17">
@@ -6558,10 +6546,10 @@
         <v>41.6</v>
       </c>
       <c r="D17" s="5" t="n">
-        <v>65.03</v>
+        <v>65.87</v>
       </c>
       <c r="E17" s="5" t="n">
-        <v>70.72</v>
+        <v>71.64</v>
       </c>
     </row>
     <row r="18">
@@ -6577,10 +6565,10 @@
         <v>36.71</v>
       </c>
       <c r="D18" s="5" t="n">
-        <v>58.22</v>
+        <v>58.97</v>
       </c>
       <c r="E18" s="5" t="n">
-        <v>62.43</v>
+        <v>63.25</v>
       </c>
     </row>
     <row r="19">
@@ -6596,10 +6584,10 @@
         <v>44.53</v>
       </c>
       <c r="D19" s="5" t="n">
-        <v>67.72</v>
+        <v>68.59999999999999</v>
       </c>
       <c r="E19" s="5" t="n">
-        <v>75.76000000000001</v>
+        <v>76.75</v>
       </c>
     </row>
     <row r="20">
@@ -6615,10 +6603,10 @@
         <v>40.79</v>
       </c>
       <c r="D20" s="5" t="n">
-        <v>59.86</v>
+        <v>60.64</v>
       </c>
       <c r="E20" s="5" t="n">
-        <v>69.43000000000001</v>
+        <v>70.33</v>
       </c>
     </row>
     <row r="21">
@@ -6634,10 +6622,10 @@
         <v>47.2</v>
       </c>
       <c r="D21" s="5" t="n">
-        <v>75.38</v>
+        <v>76.36</v>
       </c>
       <c r="E21" s="5" t="n">
-        <v>80.31</v>
+        <v>81.36</v>
       </c>
     </row>
     <row r="22">
@@ -6653,10 +6641,10 @@
         <v>67.45</v>
       </c>
       <c r="D22" s="5" t="n">
-        <v>90.06999999999999</v>
+        <v>91.23999999999999</v>
       </c>
       <c r="E22" s="5" t="n">
-        <v>114.74</v>
+        <v>116.23</v>
       </c>
     </row>
     <row r="23">
@@ -6672,10 +6660,10 @@
         <v>53.78</v>
       </c>
       <c r="D23" s="5" t="n">
-        <v>86.31</v>
+        <v>87.43000000000001</v>
       </c>
       <c r="E23" s="5" t="n">
-        <v>91.45999999999999</v>
+        <v>92.65000000000001</v>
       </c>
     </row>
     <row r="24">
@@ -6691,10 +6679,10 @@
         <v>81.98999999999999</v>
       </c>
       <c r="D24" s="5" t="n">
-        <v>123.77</v>
+        <v>125.38</v>
       </c>
       <c r="E24" s="5" t="n">
-        <v>138.87</v>
+        <v>140.67</v>
       </c>
     </row>
     <row r="25">
@@ -6710,10 +6698,10 @@
         <v>72.01000000000001</v>
       </c>
       <c r="D25" s="5" t="n">
-        <v>111.9</v>
+        <v>113.36</v>
       </c>
       <c r="E25" s="5" t="n">
-        <v>121.47</v>
+        <v>123.05</v>
       </c>
     </row>
     <row r="26">
@@ -6729,10 +6717,10 @@
         <v>79.87</v>
       </c>
       <c r="D26" s="5" t="n">
-        <v>130.72</v>
+        <v>132.42</v>
       </c>
       <c r="E26" s="5" t="n">
-        <v>134.18</v>
+        <v>135.92</v>
       </c>
     </row>
     <row r="27">
@@ -6748,10 +6736,10 @@
         <v>115.14</v>
       </c>
       <c r="D27" s="5" t="n">
-        <v>166.69</v>
+        <v>168.86</v>
       </c>
       <c r="E27" s="5" t="n">
-        <v>192.99</v>
+        <v>195.5</v>
       </c>
     </row>
     <row r="28">
@@ -6767,10 +6755,10 @@
         <v>48.48</v>
       </c>
       <c r="D28" s="5" t="n">
-        <v>68.06</v>
+        <v>68.95</v>
       </c>
       <c r="E28" s="5" t="n">
-        <v>81.06999999999999</v>
+        <v>82.13</v>
       </c>
     </row>
     <row r="29">
@@ -6786,10 +6774,10 @@
         <v>49.1</v>
       </c>
       <c r="D29" s="5" t="n">
-        <v>78.81999999999999</v>
+        <v>79.84</v>
       </c>
       <c r="E29" s="5" t="n">
-        <v>81.92</v>
+        <v>82.98999999999999</v>
       </c>
     </row>
     <row r="30">
@@ -6805,10 +6793,10 @@
         <v>32.4</v>
       </c>
       <c r="D30" s="5" t="n">
-        <v>56.6</v>
+        <v>57.34</v>
       </c>
       <c r="E30" s="5" t="n">
-        <v>53.89</v>
+        <v>54.59</v>
       </c>
     </row>
     <row r="31">
@@ -6824,10 +6812,10 @@
         <v>49.25</v>
       </c>
       <c r="D31" s="5" t="n">
-        <v>74.19</v>
+        <v>75.15000000000001</v>
       </c>
       <c r="E31" s="5" t="n">
-        <v>81.67</v>
+        <v>82.73</v>
       </c>
     </row>
     <row r="32">
@@ -6843,10 +6831,10 @@
         <v>60.6</v>
       </c>
       <c r="D32" s="5" t="n">
-        <v>84.23999999999999</v>
+        <v>85.34</v>
       </c>
       <c r="E32" s="5" t="n">
-        <v>100.18</v>
+        <v>101.48</v>
       </c>
     </row>
     <row r="33">
@@ -6862,10 +6850,10 @@
         <v>59.02</v>
       </c>
       <c r="D33" s="5" t="n">
-        <v>77.89</v>
+        <v>78.91</v>
       </c>
       <c r="E33" s="5" t="n">
-        <v>97.13</v>
+        <v>98.39</v>
       </c>
     </row>
     <row r="34">
@@ -6881,10 +6869,10 @@
         <v>67.68000000000001</v>
       </c>
       <c r="D34" s="5" t="n">
-        <v>92.51000000000001</v>
+        <v>93.70999999999999</v>
       </c>
       <c r="E34" s="5" t="n">
-        <v>110.89</v>
+        <v>112.33</v>
       </c>
     </row>
     <row r="35">
@@ -6900,10 +6888,10 @@
         <v>68.55</v>
       </c>
       <c r="D35" s="5" t="n">
-        <v>91.63</v>
+        <v>92.81999999999999</v>
       </c>
       <c r="E35" s="5" t="n">
-        <v>111.82</v>
+        <v>113.27</v>
       </c>
     </row>
     <row r="36">
@@ -6919,10 +6907,10 @@
         <v>63.43</v>
       </c>
       <c r="D36" s="5" t="n">
-        <v>89.17</v>
+        <v>90.33</v>
       </c>
       <c r="E36" s="5" t="n">
-        <v>102.97</v>
+        <v>104.31</v>
       </c>
     </row>
     <row r="37">
@@ -6938,10 +6926,10 @@
         <v>69.15000000000001</v>
       </c>
       <c r="D37" s="5" t="n">
-        <v>109.44</v>
+        <v>110.86</v>
       </c>
       <c r="E37" s="5" t="n">
-        <v>111.72</v>
+        <v>113.17</v>
       </c>
     </row>
     <row r="38">
@@ -6957,10 +6945,10 @@
         <v>63.04</v>
       </c>
       <c r="D38" s="5" t="n">
-        <v>89.98</v>
+        <v>91.15000000000001</v>
       </c>
       <c r="E38" s="5" t="n">
-        <v>101.36</v>
+        <v>102.68</v>
       </c>
     </row>
     <row r="39">
@@ -6976,10 +6964,10 @@
         <v>31.08</v>
       </c>
       <c r="D39" s="5" t="n">
-        <v>48.63</v>
+        <v>49.26</v>
       </c>
       <c r="E39" s="5" t="n">
-        <v>49.78</v>
+        <v>50.43</v>
       </c>
     </row>
     <row r="40">
@@ -6995,10 +6983,10 @@
         <v>60.78</v>
       </c>
       <c r="D40" s="5" t="n">
-        <v>87.69</v>
+        <v>88.83</v>
       </c>
       <c r="E40" s="5" t="n">
-        <v>96.98</v>
+        <v>98.23999999999999</v>
       </c>
     </row>
     <row r="41">
@@ -7014,10 +7002,10 @@
         <v>53.01</v>
       </c>
       <c r="D41" s="5" t="n">
-        <v>69.84</v>
+        <v>70.75</v>
       </c>
       <c r="E41" s="5" t="n">
-        <v>84.25</v>
+        <v>85.34999999999999</v>
       </c>
     </row>
     <row r="42">
@@ -7033,10 +7021,10 @@
         <v>55.72</v>
       </c>
       <c r="D42" s="5" t="n">
-        <v>73.06</v>
+        <v>74.01000000000001</v>
       </c>
       <c r="E42" s="5" t="n">
-        <v>88.66</v>
+        <v>89.81</v>
       </c>
     </row>
     <row r="43">
@@ -7052,10 +7040,10 @@
         <v>60.73</v>
       </c>
       <c r="D43" s="5" t="n">
-        <v>80.76000000000001</v>
+        <v>81.81</v>
       </c>
       <c r="E43" s="5" t="n">
-        <v>96.73</v>
+        <v>97.98999999999999</v>
       </c>
     </row>
     <row r="44">
@@ -7071,10 +7059,10 @@
         <v>38.15</v>
       </c>
       <c r="D44" s="5" t="n">
-        <v>52.48</v>
+        <v>53.16</v>
       </c>
       <c r="E44" s="5" t="n">
-        <v>60.83</v>
+        <v>61.63</v>
       </c>
     </row>
     <row r="45">
@@ -7090,10 +7078,10 @@
         <v>119.54</v>
       </c>
       <c r="D45" s="5" t="n">
-        <v>125.74</v>
+        <v>127.37</v>
       </c>
       <c r="E45" s="5" t="n">
-        <v>190.55</v>
+        <v>193.03</v>
       </c>
     </row>
     <row r="46">
@@ -7109,10 +7097,10 @@
         <v>63.49</v>
       </c>
       <c r="D46" s="5" t="n">
-        <v>62.27</v>
+        <v>63.08</v>
       </c>
       <c r="E46" s="5" t="n">
-        <v>101.17</v>
+        <v>102.48</v>
       </c>
     </row>
     <row r="47">
@@ -7128,10 +7116,10 @@
         <v>43.09</v>
       </c>
       <c r="D47" s="5" t="n">
-        <v>58.11</v>
+        <v>58.86</v>
       </c>
       <c r="E47" s="5" t="n">
-        <v>68.64</v>
+        <v>69.53</v>
       </c>
     </row>
     <row r="48">
@@ -7147,10 +7135,10 @@
         <v>61.35</v>
       </c>
       <c r="D48" s="5" t="n">
-        <v>110.22</v>
+        <v>111.65</v>
       </c>
       <c r="E48" s="5" t="n">
-        <v>97.56</v>
+        <v>98.83</v>
       </c>
     </row>
     <row r="49">
@@ -7166,10 +7154,10 @@
         <v>48.31</v>
       </c>
       <c r="D49" s="5" t="n">
-        <v>74.36</v>
+        <v>75.33</v>
       </c>
       <c r="E49" s="5" t="n">
-        <v>76.7</v>
+        <v>77.69</v>
       </c>
     </row>
     <row r="50">
@@ -7185,10 +7173,10 @@
         <v>287.29</v>
       </c>
       <c r="D50" s="5" t="n">
-        <v>275.47</v>
+        <v>279.05</v>
       </c>
       <c r="E50" s="5" t="n">
-        <v>455.35</v>
+        <v>461.27</v>
       </c>
     </row>
     <row r="51">
@@ -7204,10 +7192,10 @@
         <v>31.56</v>
       </c>
       <c r="D51" s="5" t="n">
-        <v>40.91</v>
+        <v>41.44</v>
       </c>
       <c r="E51" s="5" t="n">
-        <v>49.86</v>
+        <v>50.51</v>
       </c>
     </row>
     <row r="52">
@@ -7223,10 +7211,10 @@
         <v>27.86</v>
       </c>
       <c r="D52" s="5" t="n">
-        <v>33.53</v>
+        <v>33.97</v>
       </c>
       <c r="E52" s="5" t="n">
-        <v>43.88</v>
+        <v>44.45</v>
       </c>
     </row>
     <row r="53">
@@ -7242,10 +7230,10 @@
         <v>27.5</v>
       </c>
       <c r="D53" s="5" t="n">
-        <v>33.79</v>
+        <v>34.23</v>
       </c>
       <c r="E53" s="5" t="n">
-        <v>43.18</v>
+        <v>43.74</v>
       </c>
     </row>
     <row r="54">
@@ -7261,10 +7249,10 @@
         <v>29.55</v>
       </c>
       <c r="D54" s="5" t="n">
-        <v>40.41</v>
+        <v>40.93</v>
       </c>
       <c r="E54" s="5" t="n">
-        <v>46.31</v>
+        <v>46.92</v>
       </c>
     </row>
     <row r="55">
@@ -7280,10 +7268,10 @@
         <v>37.68</v>
       </c>
       <c r="D55" s="5" t="n">
-        <v>52.72</v>
+        <v>53.41</v>
       </c>
       <c r="E55" s="5" t="n">
-        <v>58.95</v>
+        <v>59.72</v>
       </c>
     </row>
     <row r="56">
@@ -7299,10 +7287,10 @@
         <v>31.42</v>
       </c>
       <c r="D56" s="5" t="n">
-        <v>49.76</v>
+        <v>50.4</v>
       </c>
       <c r="E56" s="5" t="n">
-        <v>49.07</v>
+        <v>49.71</v>
       </c>
     </row>
     <row r="57">
@@ -7318,10 +7306,10 @@
         <v>32.51</v>
       </c>
       <c r="D57" s="5" t="n">
-        <v>45.51</v>
+        <v>46.1</v>
       </c>
       <c r="E57" s="5" t="n">
-        <v>50.62</v>
+        <v>51.27</v>
       </c>
     </row>
     <row r="58">
@@ -7337,10 +7325,10 @@
         <v>20.35</v>
       </c>
       <c r="D58" s="5" t="n">
-        <v>37.19</v>
+        <v>37.67</v>
       </c>
       <c r="E58" s="5" t="n">
-        <v>31.59</v>
+        <v>32</v>
       </c>
     </row>
     <row r="59">
@@ -7356,10 +7344,10 @@
         <v>28.45</v>
       </c>
       <c r="D59" s="5" t="n">
-        <v>40.54</v>
+        <v>41.07</v>
       </c>
       <c r="E59" s="5" t="n">
-        <v>44.02</v>
+        <v>44.59</v>
       </c>
     </row>
     <row r="60">
@@ -7375,10 +7363,10 @@
         <v>26.23</v>
       </c>
       <c r="D60" s="5" t="n">
-        <v>37.71</v>
+        <v>38.2</v>
       </c>
       <c r="E60" s="5" t="n">
-        <v>40.51</v>
+        <v>41.03</v>
       </c>
     </row>
     <row r="61">
@@ -7394,10 +7382,10 @@
         <v>36.98</v>
       </c>
       <c r="D61" s="5" t="n">
-        <v>87.8</v>
+        <v>88.94</v>
       </c>
       <c r="E61" s="5" t="n">
-        <v>56.99</v>
+        <v>57.73</v>
       </c>
     </row>
     <row r="62">
@@ -7413,10 +7401,10 @@
         <v>34.53</v>
       </c>
       <c r="D62" s="5" t="n">
-        <v>47.51</v>
+        <v>48.13</v>
       </c>
       <c r="E62" s="5" t="n">
-        <v>53.11</v>
+        <v>53.8</v>
       </c>
     </row>
     <row r="63">
@@ -7432,10 +7420,10 @@
         <v>27.43</v>
       </c>
       <c r="D63" s="5" t="n">
-        <v>46.34</v>
+        <v>46.94</v>
       </c>
       <c r="E63" s="5" t="n">
-        <v>42.09</v>
+        <v>42.63</v>
       </c>
     </row>
     <row r="64">
@@ -7451,10 +7439,10 @@
         <v>27.68</v>
       </c>
       <c r="D64" s="5" t="n">
-        <v>99.19</v>
+        <v>100.48</v>
       </c>
       <c r="E64" s="5" t="n">
-        <v>42.37</v>
+        <v>42.92</v>
       </c>
     </row>
     <row r="65">
@@ -7470,10 +7458,10 @@
         <v>23.49</v>
       </c>
       <c r="D65" s="5" t="n">
-        <v>31.7</v>
+        <v>32.11</v>
       </c>
       <c r="E65" s="5" t="n">
-        <v>35.87</v>
+        <v>36.34</v>
       </c>
     </row>
     <row r="66">
@@ -7489,10 +7477,10 @@
         <v>18.32</v>
       </c>
       <c r="D66" s="5" t="n">
-        <v>27.66</v>
+        <v>28.02</v>
       </c>
       <c r="E66" s="5" t="n">
-        <v>27.94</v>
+        <v>28.3</v>
       </c>
     </row>
     <row r="67">
@@ -7508,10 +7496,10 @@
         <v>19.55</v>
       </c>
       <c r="D67" s="5" t="n">
-        <v>41.28</v>
+        <v>41.81</v>
       </c>
       <c r="E67" s="5" t="n">
-        <v>29.78</v>
+        <v>30.16</v>
       </c>
     </row>
     <row r="68">
@@ -7527,10 +7515,10 @@
         <v>17.67</v>
       </c>
       <c r="D68" s="5" t="n">
-        <v>25.4</v>
+        <v>25.73</v>
       </c>
       <c r="E68" s="5" t="n">
-        <v>26.88</v>
+        <v>27.23</v>
       </c>
     </row>
     <row r="69">
@@ -7546,10 +7534,10 @@
         <v>28.13</v>
       </c>
       <c r="D69" s="5" t="n">
-        <v>39.27</v>
+        <v>39.78</v>
       </c>
       <c r="E69" s="5" t="n">
-        <v>42.57</v>
+        <v>43.12</v>
       </c>
     </row>
     <row r="70">
@@ -7565,10 +7553,10 @@
         <v>31.08</v>
       </c>
       <c r="D70" s="5" t="n">
-        <v>43.24</v>
+        <v>43.8</v>
       </c>
       <c r="E70" s="5" t="n">
-        <v>46.79</v>
+        <v>47.4</v>
       </c>
     </row>
     <row r="71">
@@ -7584,10 +7572,10 @@
         <v>27.04</v>
       </c>
       <c r="D71" s="5" t="n">
-        <v>38.69</v>
+        <v>39.2</v>
       </c>
       <c r="E71" s="5" t="n">
-        <v>40.5</v>
+        <v>41.03</v>
       </c>
     </row>
     <row r="72">
@@ -7603,10 +7591,10 @@
         <v>27.77</v>
       </c>
       <c r="D72" s="5" t="n">
-        <v>40.02</v>
+        <v>40.54</v>
       </c>
       <c r="E72" s="5" t="n">
-        <v>41.47</v>
+        <v>42.01</v>
       </c>
     </row>
     <row r="73">
@@ -7622,10 +7610,10 @@
         <v>40.49</v>
       </c>
       <c r="D73" s="5" t="n">
-        <v>57.57</v>
+        <v>58.32</v>
       </c>
       <c r="E73" s="5" t="n">
-        <v>60.28</v>
+        <v>61.06</v>
       </c>
     </row>
     <row r="74">
@@ -7641,10 +7629,10 @@
         <v>32.23</v>
       </c>
       <c r="D74" s="5" t="n">
-        <v>43.28</v>
+        <v>43.84</v>
       </c>
       <c r="E74" s="5" t="n">
-        <v>47.84</v>
+        <v>48.46</v>
       </c>
     </row>
     <row r="75">
@@ -7660,10 +7648,10 @@
         <v>49.09</v>
       </c>
       <c r="D75" s="5" t="n">
-        <v>48.28</v>
+        <v>48.9</v>
       </c>
       <c r="E75" s="5" t="n">
-        <v>72.72</v>
+        <v>73.66</v>
       </c>
     </row>
     <row r="76">
@@ -7679,10 +7667,10 @@
         <v>34.57</v>
       </c>
       <c r="D76" s="5" t="n">
-        <v>40.15</v>
+        <v>40.68</v>
       </c>
       <c r="E76" s="5" t="n">
-        <v>51.11</v>
+        <v>51.77</v>
       </c>
     </row>
     <row r="77">
@@ -7698,10 +7686,10 @@
         <v>29.91</v>
       </c>
       <c r="D77" s="5" t="n">
-        <v>38.95</v>
+        <v>39.46</v>
       </c>
       <c r="E77" s="5" t="n">
-        <v>44.13</v>
+        <v>44.71</v>
       </c>
     </row>
     <row r="78">
@@ -7717,10 +7705,10 @@
         <v>31.19</v>
       </c>
       <c r="D78" s="5" t="n">
-        <v>48.07</v>
+        <v>48.7</v>
       </c>
       <c r="E78" s="5" t="n">
-        <v>46.02</v>
+        <v>46.62</v>
       </c>
     </row>
     <row r="79">
@@ -7736,10 +7724,10 @@
         <v>29.77</v>
       </c>
       <c r="D79" s="5" t="n">
-        <v>45.37</v>
+        <v>45.96</v>
       </c>
       <c r="E79" s="5" t="n">
-        <v>43.93</v>
+        <v>44.5</v>
       </c>
     </row>
     <row r="80">
@@ -7755,10 +7743,10 @@
         <v>26.39</v>
       </c>
       <c r="D80" s="5" t="n">
-        <v>38.14</v>
+        <v>38.64</v>
       </c>
       <c r="E80" s="5" t="n">
-        <v>38.94</v>
+        <v>39.44</v>
       </c>
     </row>
     <row r="81">
@@ -7774,10 +7762,10 @@
         <v>34.3</v>
       </c>
       <c r="D81" s="5" t="n">
-        <v>58</v>
+        <v>58.76</v>
       </c>
       <c r="E81" s="5" t="n">
-        <v>50.6</v>
+        <v>51.26</v>
       </c>
     </row>
     <row r="82">
@@ -7793,10 +7781,10 @@
         <v>29.99</v>
       </c>
       <c r="D82" s="5" t="n">
-        <v>55.12</v>
+        <v>55.83</v>
       </c>
       <c r="E82" s="5" t="n">
-        <v>44.23</v>
+        <v>44.81</v>
       </c>
     </row>
     <row r="83">
@@ -7812,10 +7800,10 @@
         <v>29.57</v>
       </c>
       <c r="D83" s="5" t="n">
-        <v>52.97</v>
+        <v>53.66</v>
       </c>
       <c r="E83" s="5" t="n">
-        <v>43.6</v>
+        <v>44.17</v>
       </c>
     </row>
     <row r="84">
@@ -7831,10 +7819,10 @@
         <v>41.97</v>
       </c>
       <c r="D84" s="5" t="n">
-        <v>52.94</v>
+        <v>53.62</v>
       </c>
       <c r="E84" s="5" t="n">
-        <v>61.78</v>
+        <v>62.59</v>
       </c>
     </row>
     <row r="85">
@@ -7850,10 +7838,10 @@
         <v>29.93</v>
       </c>
       <c r="D85" s="5" t="n">
-        <v>48.35</v>
+        <v>48.98</v>
       </c>
       <c r="E85" s="5" t="n">
-        <v>43.98</v>
+        <v>44.56</v>
       </c>
     </row>
     <row r="86">
@@ -7869,10 +7857,10 @@
         <v>38.35</v>
       </c>
       <c r="D86" s="5" t="n">
-        <v>50.52</v>
+        <v>51.18</v>
       </c>
       <c r="E86" s="5" t="n">
-        <v>56.26</v>
+        <v>56.99</v>
       </c>
     </row>
     <row r="87">
@@ -7888,10 +7876,10 @@
         <v>67.09999999999999</v>
       </c>
       <c r="D87" s="5" t="n">
-        <v>86.5</v>
+        <v>87.62</v>
       </c>
       <c r="E87" s="5" t="n">
-        <v>97.98999999999999</v>
+        <v>99.27</v>
       </c>
     </row>
     <row r="88">
@@ -7907,10 +7895,10 @@
         <v>48.32</v>
       </c>
       <c r="D88" s="5" t="n">
-        <v>68.65000000000001</v>
+        <v>69.54000000000001</v>
       </c>
       <c r="E88" s="5" t="n">
-        <v>70.25</v>
+        <v>71.16</v>
       </c>
     </row>
     <row r="89">
@@ -7926,10 +7914,10 @@
         <v>41.39</v>
       </c>
       <c r="D89" s="5" t="n">
-        <v>57.11</v>
+        <v>57.85</v>
       </c>
       <c r="E89" s="5" t="n">
-        <v>59.9</v>
+        <v>60.68</v>
       </c>
     </row>
     <row r="90">
@@ -7945,10 +7933,10 @@
         <v>44.73</v>
       </c>
       <c r="D90" s="5" t="n">
-        <v>63.08</v>
+        <v>63.9</v>
       </c>
       <c r="E90" s="5" t="n">
-        <v>64.68000000000001</v>
+        <v>65.52</v>
       </c>
     </row>
     <row r="91">
@@ -7964,10 +7952,10 @@
         <v>51.23</v>
       </c>
       <c r="D91" s="5" t="n">
-        <v>73.08</v>
+        <v>74.03</v>
       </c>
       <c r="E91" s="5" t="n">
-        <v>74.02</v>
+        <v>74.98</v>
       </c>
     </row>
     <row r="92">
@@ -7983,10 +7971,10 @@
         <v>46.33</v>
       </c>
       <c r="D92" s="5" t="n">
-        <v>67.42</v>
+        <v>68.29000000000001</v>
       </c>
       <c r="E92" s="5" t="n">
-        <v>66.88</v>
+        <v>67.75</v>
       </c>
     </row>
     <row r="93">
@@ -8002,10 +7990,10 @@
         <v>46.27</v>
       </c>
       <c r="D93" s="5" t="n">
-        <v>82.14</v>
+        <v>83.2</v>
       </c>
       <c r="E93" s="5" t="n">
-        <v>66.72</v>
+        <v>67.59</v>
       </c>
     </row>
     <row r="94">
@@ -8021,10 +8009,10 @@
         <v>45.77</v>
       </c>
       <c r="D94" s="5" t="n">
-        <v>65.95</v>
+        <v>66.81</v>
       </c>
       <c r="E94" s="5" t="n">
-        <v>65.93000000000001</v>
+        <v>66.78</v>
       </c>
     </row>
     <row r="95">
@@ -8040,10 +8028,10 @@
         <v>50.56</v>
       </c>
       <c r="D95" s="5" t="n">
-        <v>71.66</v>
+        <v>72.59999999999999</v>
       </c>
       <c r="E95" s="5" t="n">
-        <v>72.73999999999999</v>
+        <v>73.69</v>
       </c>
     </row>
     <row r="96">
@@ -8059,10 +8047,10 @@
         <v>46.49</v>
       </c>
       <c r="D96" s="5" t="n">
-        <v>64.83</v>
+        <v>65.68000000000001</v>
       </c>
       <c r="E96" s="5" t="n">
-        <v>66.8</v>
+        <v>67.67</v>
       </c>
     </row>
     <row r="97">
@@ -8078,10 +8066,10 @@
         <v>49.59</v>
       </c>
       <c r="D97" s="5" t="n">
-        <v>64.11</v>
+        <v>64.94</v>
       </c>
       <c r="E97" s="5" t="n">
-        <v>71.17</v>
+        <v>72.09</v>
       </c>
     </row>
     <row r="98">
@@ -8097,10 +8085,10 @@
         <v>51.48</v>
       </c>
       <c r="D98" s="5" t="n">
-        <v>71.51000000000001</v>
+        <v>72.44</v>
       </c>
       <c r="E98" s="5" t="n">
-        <v>73.79000000000001</v>
+        <v>74.75</v>
       </c>
     </row>
     <row r="99">
@@ -8116,10 +8104,10 @@
         <v>53.74</v>
       </c>
       <c r="D99" s="5" t="n">
-        <v>73.52</v>
+        <v>74.47</v>
       </c>
       <c r="E99" s="5" t="n">
-        <v>76.70999999999999</v>
+        <v>77.70999999999999</v>
       </c>
     </row>
     <row r="100">
@@ -8135,10 +8123,10 @@
         <v>49.24</v>
       </c>
       <c r="D100" s="5" t="n">
-        <v>65.22</v>
+        <v>66.06</v>
       </c>
       <c r="E100" s="5" t="n">
-        <v>70.01000000000001</v>
+        <v>70.92</v>
       </c>
     </row>
     <row r="101">
@@ -8154,10 +8142,10 @@
         <v>44.67</v>
       </c>
       <c r="D101" s="5" t="n">
-        <v>60.08</v>
+        <v>60.86</v>
       </c>
       <c r="E101" s="5" t="n">
-        <v>63.26</v>
+        <v>64.08</v>
       </c>
     </row>
     <row r="102">
@@ -8173,10 +8161,10 @@
         <v>41.23</v>
       </c>
       <c r="D102" s="5" t="n">
-        <v>54.53</v>
+        <v>55.24</v>
       </c>
       <c r="E102" s="5" t="n">
-        <v>58.24</v>
+        <v>59</v>
       </c>
     </row>
     <row r="103">
@@ -8192,10 +8180,10 @@
         <v>52.96</v>
       </c>
       <c r="D103" s="5" t="n">
-        <v>66.36</v>
+        <v>67.23</v>
       </c>
       <c r="E103" s="5" t="n">
-        <v>74.64</v>
+        <v>75.61</v>
       </c>
     </row>
     <row r="104">
@@ -8211,10 +8199,10 @@
         <v>37.37</v>
       </c>
       <c r="D104" s="5" t="n">
-        <v>52.86</v>
+        <v>53.55</v>
       </c>
       <c r="E104" s="5" t="n">
-        <v>52.54</v>
+        <v>53.22</v>
       </c>
     </row>
     <row r="105">
@@ -8230,10 +8218,10 @@
         <v>29.27</v>
       </c>
       <c r="D105" s="5" t="n">
-        <v>48.94</v>
+        <v>49.58</v>
       </c>
       <c r="E105" s="5" t="n">
-        <v>41.07</v>
+        <v>41.6</v>
       </c>
     </row>
     <row r="106">
@@ -8249,10 +8237,10 @@
         <v>42.97</v>
       </c>
       <c r="D106" s="5" t="n">
-        <v>61.46</v>
+        <v>62.26</v>
       </c>
       <c r="E106" s="5" t="n">
-        <v>60.18</v>
+        <v>60.96</v>
       </c>
     </row>
     <row r="107">
@@ -8268,10 +8256,10 @@
         <v>45.1</v>
       </c>
       <c r="D107" s="5" t="n">
-        <v>62.59</v>
+        <v>63.4</v>
       </c>
       <c r="E107" s="5" t="n">
-        <v>63.04</v>
+        <v>63.85</v>
       </c>
     </row>
     <row r="108">
@@ -8287,10 +8275,10 @@
         <v>38.42</v>
       </c>
       <c r="D108" s="5" t="n">
-        <v>52.58</v>
+        <v>53.26</v>
       </c>
       <c r="E108" s="5" t="n">
-        <v>53.61</v>
+        <v>54.31</v>
       </c>
     </row>
     <row r="109">
@@ -8306,10 +8294,10 @@
         <v>40.85</v>
       </c>
       <c r="D109" s="5" t="n">
-        <v>50.87</v>
+        <v>51.53</v>
       </c>
       <c r="E109" s="5" t="n">
-        <v>56.9</v>
+        <v>57.64</v>
       </c>
     </row>
     <row r="110">
@@ -8325,10 +8313,10 @@
         <v>43.96</v>
       </c>
       <c r="D110" s="5" t="n">
-        <v>60.01</v>
+        <v>60.79</v>
       </c>
       <c r="E110" s="5" t="n">
-        <v>61.13</v>
+        <v>61.93</v>
       </c>
     </row>
     <row r="111">
@@ -8344,10 +8332,10 @@
         <v>37.17</v>
       </c>
       <c r="D111" s="5" t="n">
-        <v>46.98</v>
+        <v>47.59</v>
       </c>
       <c r="E111" s="5" t="n">
-        <v>51.62</v>
+        <v>52.29</v>
       </c>
     </row>
     <row r="112">
@@ -8363,10 +8351,10 @@
         <v>41.72</v>
       </c>
       <c r="D112" s="5" t="n">
-        <v>50.39</v>
+        <v>51.05</v>
       </c>
       <c r="E112" s="5" t="n">
-        <v>57.86</v>
+        <v>58.61</v>
       </c>
     </row>
     <row r="113">
@@ -8382,10 +8370,10 @@
         <v>39.82</v>
       </c>
       <c r="D113" s="5" t="n">
-        <v>52.14</v>
+        <v>52.82</v>
       </c>
       <c r="E113" s="5" t="n">
-        <v>55.14</v>
+        <v>55.86</v>
       </c>
     </row>
     <row r="114">
@@ -8401,10 +8389,10 @@
         <v>32.77</v>
       </c>
       <c r="D114" s="5" t="n">
-        <v>48.31</v>
+        <v>48.94</v>
       </c>
       <c r="E114" s="5" t="n">
-        <v>45.35</v>
+        <v>45.94</v>
       </c>
     </row>
     <row r="115">
@@ -8420,10 +8408,10 @@
         <v>37.02</v>
       </c>
       <c r="D115" s="5" t="n">
-        <v>55.24</v>
+        <v>55.96</v>
       </c>
       <c r="E115" s="5" t="n">
-        <v>51.2</v>
+        <v>51.87</v>
       </c>
     </row>
     <row r="116">
@@ -8439,10 +8427,10 @@
         <v>44.27</v>
       </c>
       <c r="D116" s="5" t="n">
-        <v>62.56</v>
+        <v>63.37</v>
       </c>
       <c r="E116" s="5" t="n">
-        <v>61.19</v>
+        <v>61.99</v>
       </c>
     </row>
     <row r="117">
@@ -8458,10 +8446,10 @@
         <v>36.59</v>
       </c>
       <c r="D117" s="5" t="n">
-        <v>48.46</v>
+        <v>49.09</v>
       </c>
       <c r="E117" s="5" t="n">
-        <v>50.54</v>
+        <v>51.2</v>
       </c>
     </row>
     <row r="118">
@@ -8477,10 +8465,10 @@
         <v>40.89</v>
       </c>
       <c r="D118" s="5" t="n">
-        <v>58.72</v>
+        <v>59.49</v>
       </c>
       <c r="E118" s="5" t="n">
-        <v>56.45</v>
+        <v>57.18</v>
       </c>
     </row>
     <row r="119">
@@ -8496,10 +8484,10 @@
         <v>39.56</v>
       </c>
       <c r="D119" s="5" t="n">
-        <v>54.87</v>
+        <v>55.58</v>
       </c>
       <c r="E119" s="5" t="n">
-        <v>54.58</v>
+        <v>55.29</v>
       </c>
     </row>
     <row r="120">
@@ -8515,10 +8503,10 @@
         <v>38.06</v>
       </c>
       <c r="D120" s="5" t="n">
-        <v>55.93</v>
+        <v>56.66</v>
       </c>
       <c r="E120" s="5" t="n">
-        <v>52.38</v>
+        <v>53.06</v>
       </c>
     </row>
     <row r="121">
@@ -8534,10 +8522,10 @@
         <v>33.76</v>
       </c>
       <c r="D121" s="5" t="n">
-        <v>38.86</v>
+        <v>39.36</v>
       </c>
       <c r="E121" s="5" t="n">
-        <v>46.35</v>
+        <v>46.96</v>
       </c>
     </row>
     <row r="122">
@@ -8553,10 +8541,10 @@
         <v>37.17</v>
       </c>
       <c r="D122" s="5" t="n">
-        <v>44.18</v>
+        <v>44.75</v>
       </c>
       <c r="E122" s="5" t="n">
-        <v>50.92</v>
+        <v>51.58</v>
       </c>
     </row>
     <row r="123">
@@ -8572,10 +8560,10 @@
         <v>38.8</v>
       </c>
       <c r="D123" s="5" t="n">
-        <v>47.74</v>
+        <v>48.36</v>
       </c>
       <c r="E123" s="5" t="n">
-        <v>53.08</v>
+        <v>53.77</v>
       </c>
     </row>
     <row r="124">
@@ -8591,10 +8579,10 @@
         <v>37.69</v>
       </c>
       <c r="D124" s="5" t="n">
-        <v>43.57</v>
+        <v>44.14</v>
       </c>
       <c r="E124" s="5" t="n">
-        <v>51.49</v>
+        <v>52.16</v>
       </c>
     </row>
     <row r="125">
@@ -8610,10 +8598,10 @@
         <v>48.67</v>
       </c>
       <c r="D125" s="5" t="n">
-        <v>62.79</v>
+        <v>63.61</v>
       </c>
       <c r="E125" s="5" t="n">
-        <v>66.41</v>
+        <v>67.27</v>
       </c>
     </row>
     <row r="126">
@@ -8629,10 +8617,10 @@
         <v>60.05</v>
       </c>
       <c r="D126" s="5" t="n">
-        <v>80.7</v>
+        <v>81.75</v>
       </c>
       <c r="E126" s="5" t="n">
-        <v>81.83</v>
+        <v>82.90000000000001</v>
       </c>
     </row>
     <row r="127">
@@ -8648,10 +8636,10 @@
         <v>85.7</v>
       </c>
       <c r="D127" s="5" t="n">
-        <v>113.96</v>
+        <v>115.44</v>
       </c>
       <c r="E127" s="5" t="n">
-        <v>116.64</v>
+        <v>118.15</v>
       </c>
     </row>
     <row r="128">
@@ -8667,10 +8655,10 @@
         <v>96.81999999999999</v>
       </c>
       <c r="D128" s="5" t="n">
-        <v>130.62</v>
+        <v>132.32</v>
       </c>
       <c r="E128" s="5" t="n">
-        <v>131.6</v>
+        <v>133.31</v>
       </c>
     </row>
     <row r="129">
@@ -8686,10 +8674,10 @@
         <v>112.56</v>
       </c>
       <c r="D129" s="5" t="n">
-        <v>153.33</v>
+        <v>155.32</v>
       </c>
       <c r="E129" s="5" t="n">
-        <v>153.1</v>
+        <v>155.09</v>
       </c>
     </row>
     <row r="130">
@@ -8705,10 +8693,10 @@
         <v>163.47</v>
       </c>
       <c r="D130" s="5" t="n">
-        <v>225.48</v>
+        <v>228.42</v>
       </c>
       <c r="E130" s="5" t="n">
-        <v>222.49</v>
+        <v>225.38</v>
       </c>
     </row>
     <row r="131">
@@ -8724,10 +8712,10 @@
         <v>255.9</v>
       </c>
       <c r="D131" s="5" t="n">
-        <v>343.72</v>
+        <v>348.18</v>
       </c>
       <c r="E131" s="5" t="n">
-        <v>348.52</v>
+        <v>353.05</v>
       </c>
     </row>
     <row r="132">
@@ -8743,10 +8731,10 @@
         <v>227.53</v>
       </c>
       <c r="D132" s="5" t="n">
-        <v>322.11</v>
+        <v>326.29</v>
       </c>
       <c r="E132" s="5" t="n">
-        <v>309.43</v>
+        <v>313.45</v>
       </c>
     </row>
     <row r="133">
@@ -8762,10 +8750,10 @@
         <v>57</v>
       </c>
       <c r="D133" s="5" t="n">
-        <v>61.72</v>
+        <v>62.52</v>
       </c>
       <c r="E133" s="5" t="n">
-        <v>77.40000000000001</v>
+        <v>78.41</v>
       </c>
     </row>
     <row r="134">
@@ -8781,10 +8769,10 @@
         <v>98.19</v>
       </c>
       <c r="D134" s="5" t="n">
-        <v>98.31</v>
+        <v>99.59</v>
       </c>
       <c r="E134" s="5" t="n">
-        <v>133.15</v>
+        <v>134.88</v>
       </c>
     </row>
     <row r="135">
@@ -8800,10 +8788,10 @@
         <v>95.26000000000001</v>
       </c>
       <c r="D135" s="5" t="n">
-        <v>91.88</v>
+        <v>93.08</v>
       </c>
       <c r="E135" s="5" t="n">
-        <v>128.87</v>
+        <v>130.55</v>
       </c>
     </row>
     <row r="136">
@@ -8819,10 +8807,10 @@
         <v>56.46</v>
       </c>
       <c r="D136" s="5" t="n">
-        <v>58.95</v>
+        <v>59.72</v>
       </c>
       <c r="E136" s="5" t="n">
-        <v>76.2</v>
+        <v>77.19</v>
       </c>
     </row>
     <row r="137">
@@ -8838,10 +8826,10 @@
         <v>52.02</v>
       </c>
       <c r="D137" s="5" t="n">
-        <v>62.18</v>
+        <v>62.99</v>
       </c>
       <c r="E137" s="5" t="n">
-        <v>70.05</v>
+        <v>70.95999999999999</v>
       </c>
     </row>
     <row r="138">
@@ -8857,10 +8845,10 @@
         <v>39.37</v>
       </c>
       <c r="D138" s="5" t="n">
-        <v>44.65</v>
+        <v>45.23</v>
       </c>
       <c r="E138" s="5" t="n">
-        <v>52.92</v>
+        <v>53.61</v>
       </c>
     </row>
     <row r="139">
@@ -8876,10 +8864,10 @@
         <v>50.91</v>
       </c>
       <c r="D139" s="5" t="n">
-        <v>50.43</v>
+        <v>51.08</v>
       </c>
       <c r="E139" s="5" t="n">
-        <v>68.31</v>
+        <v>69.2</v>
       </c>
     </row>
     <row r="140">
@@ -8895,10 +8883,10 @@
         <v>45.93</v>
       </c>
       <c r="D140" s="5" t="n">
-        <v>55.32</v>
+        <v>56.04</v>
       </c>
       <c r="E140" s="5" t="n">
-        <v>61.52</v>
+        <v>62.32</v>
       </c>
     </row>
     <row r="141">
@@ -8914,10 +8902,10 @@
         <v>90.94</v>
       </c>
       <c r="D141" s="5" t="n">
-        <v>115.17</v>
+        <v>116.66</v>
       </c>
       <c r="E141" s="5" t="n">
-        <v>121.63</v>
+        <v>123.21</v>
       </c>
     </row>
     <row r="142">
@@ -8933,10 +8921,10 @@
         <v>102.31</v>
       </c>
       <c r="D142" s="5" t="n">
-        <v>126.04</v>
+        <v>127.67</v>
       </c>
       <c r="E142" s="5" t="n">
-        <v>136.63</v>
+        <v>138.4</v>
       </c>
     </row>
     <row r="143">
@@ -8952,10 +8940,10 @@
         <v>116.54</v>
       </c>
       <c r="D143" s="5" t="n">
-        <v>151.75</v>
+        <v>153.72</v>
       </c>
       <c r="E143" s="5" t="n">
-        <v>155.39</v>
+        <v>157.41</v>
       </c>
     </row>
     <row r="144">
@@ -8971,10 +8959,10 @@
         <v>127.22</v>
       </c>
       <c r="D144" s="5" t="n">
-        <v>174.89</v>
+        <v>177.17</v>
       </c>
       <c r="E144" s="5" t="n">
-        <v>169.52</v>
+        <v>171.73</v>
       </c>
     </row>
     <row r="145">
@@ -8990,10 +8978,10 @@
         <v>117.37</v>
       </c>
       <c r="D145" s="5" t="n">
-        <v>143.74</v>
+        <v>145.61</v>
       </c>
       <c r="E145" s="5" t="n">
-        <v>156.29</v>
+        <v>158.33</v>
       </c>
     </row>
     <row r="146">
@@ -9009,10 +8997,10 @@
         <v>109.28</v>
       </c>
       <c r="D146" s="5" t="n">
-        <v>138.19</v>
+        <v>139.98</v>
       </c>
       <c r="E146" s="5" t="n">
-        <v>145.43</v>
+        <v>147.32</v>
       </c>
     </row>
     <row r="147">
@@ -9028,10 +9016,10 @@
         <v>125.08</v>
       </c>
       <c r="D147" s="5" t="n">
-        <v>154.1</v>
+        <v>156.1</v>
       </c>
       <c r="E147" s="5" t="n">
-        <v>166.11</v>
+        <v>168.27</v>
       </c>
     </row>
     <row r="148">
@@ -9047,10 +9035,10 @@
         <v>109.03</v>
       </c>
       <c r="D148" s="5" t="n">
-        <v>128.84</v>
+        <v>130.51</v>
       </c>
       <c r="E148" s="5" t="n">
-        <v>144.51</v>
+        <v>146.38</v>
       </c>
     </row>
     <row r="149">
@@ -9066,10 +9054,10 @@
         <v>81.7</v>
       </c>
       <c r="D149" s="5" t="n">
-        <v>97.31999999999999</v>
+        <v>98.59</v>
       </c>
       <c r="E149" s="5" t="n">
-        <v>108.06</v>
+        <v>109.47</v>
       </c>
     </row>
     <row r="150">
@@ -9085,10 +9073,10 @@
         <v>75.29000000000001</v>
       </c>
       <c r="D150" s="5" t="n">
-        <v>90.61</v>
+        <v>91.79000000000001</v>
       </c>
       <c r="E150" s="5" t="n">
-        <v>99.36</v>
+        <v>100.65</v>
       </c>
     </row>
     <row r="151">
@@ -9104,10 +9092,10 @@
         <v>105.28</v>
       </c>
       <c r="D151" s="5" t="n">
-        <v>123.82</v>
+        <v>125.43</v>
       </c>
       <c r="E151" s="5" t="n">
-        <v>138.63</v>
+        <v>140.43</v>
       </c>
     </row>
     <row r="152">
@@ -9123,10 +9111,10 @@
         <v>106.8</v>
       </c>
       <c r="D152" s="5" t="n">
-        <v>119.51</v>
+        <v>121.06</v>
       </c>
       <c r="E152" s="5" t="n">
-        <v>140.32</v>
+        <v>142.14</v>
       </c>
     </row>
     <row r="153">
@@ -9142,10 +9130,10 @@
         <v>96.02</v>
       </c>
       <c r="D153" s="5" t="n">
-        <v>129.84</v>
+        <v>131.53</v>
       </c>
       <c r="E153" s="5" t="n">
-        <v>125.97</v>
+        <v>127.61</v>
       </c>
     </row>
     <row r="154">
@@ -9161,10 +9149,10 @@
         <v>89.25</v>
       </c>
       <c r="D154" s="5" t="n">
-        <v>116.95</v>
+        <v>118.47</v>
       </c>
       <c r="E154" s="5" t="n">
-        <v>116.92</v>
+        <v>118.44</v>
       </c>
     </row>
     <row r="155">
@@ -9180,10 +9168,10 @@
         <v>85.43000000000001</v>
       </c>
       <c r="D155" s="5" t="n">
-        <v>109.26</v>
+        <v>110.68</v>
       </c>
       <c r="E155" s="5" t="n">
-        <v>111.75</v>
+        <v>113.21</v>
       </c>
     </row>
     <row r="156">
@@ -9199,10 +9187,10 @@
         <v>80.17</v>
       </c>
       <c r="D156" s="5" t="n">
-        <v>105.45</v>
+        <v>106.83</v>
       </c>
       <c r="E156" s="5" t="n">
-        <v>104.75</v>
+        <v>106.11</v>
       </c>
     </row>
     <row r="157">
@@ -9218,10 +9206,10 @@
         <v>79.65000000000001</v>
       </c>
       <c r="D157" s="5" t="n">
-        <v>99.91</v>
+        <v>101.21</v>
       </c>
       <c r="E157" s="5" t="n">
-        <v>103.95</v>
+        <v>105.3</v>
       </c>
     </row>
     <row r="158">
@@ -9237,10 +9225,10 @@
         <v>80.17</v>
       </c>
       <c r="D158" s="5" t="n">
-        <v>95.92</v>
+        <v>97.17</v>
       </c>
       <c r="E158" s="5" t="n">
-        <v>104.5</v>
+        <v>105.86</v>
       </c>
     </row>
     <row r="159">
@@ -9256,10 +9244,10 @@
         <v>49.51</v>
       </c>
       <c r="D159" s="5" t="n">
-        <v>58.38</v>
+        <v>59.14</v>
       </c>
       <c r="E159" s="5" t="n">
-        <v>64.44</v>
+        <v>65.28</v>
       </c>
     </row>
     <row r="160">
@@ -9275,10 +9263,10 @@
         <v>31.23</v>
       </c>
       <c r="D160" s="5" t="n">
-        <v>32.53</v>
+        <v>32.96</v>
       </c>
       <c r="E160" s="5" t="n">
-        <v>40.59</v>
+        <v>41.12</v>
       </c>
     </row>
     <row r="161">
@@ -9294,10 +9282,10 @@
         <v>70.7</v>
       </c>
       <c r="D161" s="5" t="n">
-        <v>78.98999999999999</v>
+        <v>80.01000000000001</v>
       </c>
       <c r="E161" s="5" t="n">
-        <v>91.76000000000001</v>
+        <v>92.95</v>
       </c>
     </row>
     <row r="162">
@@ -9313,10 +9301,10 @@
         <v>101.45</v>
       </c>
       <c r="D162" s="5" t="n">
-        <v>123.56</v>
+        <v>125.17</v>
       </c>
       <c r="E162" s="5" t="n">
-        <v>131.44</v>
+        <v>133.15</v>
       </c>
     </row>
     <row r="163">
@@ -9332,10 +9320,10 @@
         <v>88.25</v>
       </c>
       <c r="D163" s="5" t="n">
-        <v>110.71</v>
+        <v>112.15</v>
       </c>
       <c r="E163" s="5" t="n">
-        <v>114.14</v>
+        <v>115.62</v>
       </c>
     </row>
     <row r="164">
@@ -9351,10 +9339,10 @@
         <v>70.48</v>
       </c>
       <c r="D164" s="5" t="n">
-        <v>93.13</v>
+        <v>94.34</v>
       </c>
       <c r="E164" s="5" t="n">
-        <v>91</v>
+        <v>92.18000000000001</v>
       </c>
     </row>
     <row r="165">
@@ -9370,10 +9358,10 @@
         <v>163</v>
       </c>
       <c r="D165" s="5" t="n">
-        <v>190.98</v>
+        <v>193.46</v>
       </c>
       <c r="E165" s="5" t="n">
-        <v>210.46</v>
+        <v>213.2</v>
       </c>
     </row>
     <row r="166">
@@ -9389,10 +9377,10 @@
         <v>133.08</v>
       </c>
       <c r="D166" s="5" t="n">
-        <v>174.05</v>
+        <v>176.31</v>
       </c>
       <c r="E166" s="5" t="n">
-        <v>171.84</v>
+        <v>174.07</v>
       </c>
     </row>
     <row r="167">
@@ -9408,10 +9396,10 @@
         <v>114.79</v>
       </c>
       <c r="D167" s="5" t="n">
-        <v>159.39</v>
+        <v>161.46</v>
       </c>
       <c r="E167" s="5" t="n">
-        <v>148.23</v>
+        <v>150.16</v>
       </c>
     </row>
     <row r="168">
@@ -9427,10 +9415,10 @@
         <v>108.07</v>
       </c>
       <c r="D168" s="5" t="n">
-        <v>134.96</v>
+        <v>136.71</v>
       </c>
       <c r="E168" s="5" t="n">
-        <v>139.28</v>
+        <v>141.09</v>
       </c>
     </row>
     <row r="169">
@@ -9446,10 +9434,10 @@
         <v>101.97</v>
       </c>
       <c r="D169" s="5" t="n">
-        <v>119.04</v>
+        <v>120.59</v>
       </c>
       <c r="E169" s="5" t="n">
-        <v>131.16</v>
+        <v>132.86</v>
       </c>
     </row>
     <row r="170">
@@ -9465,10 +9453,10 @@
         <v>108.62</v>
       </c>
       <c r="D170" s="5" t="n">
-        <v>124.26</v>
+        <v>125.88</v>
       </c>
       <c r="E170" s="5" t="n">
-        <v>139.43</v>
+        <v>141.25</v>
       </c>
     </row>
     <row r="171">
@@ -9484,10 +9472,10 @@
         <v>89.16</v>
       </c>
       <c r="D171" s="5" t="n">
-        <v>95.8</v>
+        <v>97.05</v>
       </c>
       <c r="E171" s="5" t="n">
-        <v>114.24</v>
+        <v>115.72</v>
       </c>
     </row>
     <row r="172">
@@ -9503,10 +9491,10 @@
         <v>80.14</v>
       </c>
       <c r="D172" s="5" t="n">
-        <v>89.56999999999999</v>
+        <v>90.73999999999999</v>
       </c>
       <c r="E172" s="5" t="n">
-        <v>102.49</v>
+        <v>103.82</v>
       </c>
     </row>
     <row r="173">
@@ -9522,10 +9510,10 @@
         <v>63.58</v>
       </c>
       <c r="D173" s="5" t="n">
-        <v>73.55</v>
+        <v>74.51000000000001</v>
       </c>
       <c r="E173" s="5" t="n">
-        <v>81.16</v>
+        <v>82.20999999999999</v>
       </c>
     </row>
     <row r="174">
@@ -9541,10 +9529,10 @@
         <v>105.77</v>
       </c>
       <c r="D174" s="5" t="n">
-        <v>137.14</v>
+        <v>138.92</v>
       </c>
       <c r="E174" s="5" t="n">
-        <v>134.71</v>
+        <v>136.46</v>
       </c>
     </row>
     <row r="175">
@@ -9560,10 +9548,10 @@
         <v>76.48</v>
       </c>
       <c r="D175" s="5" t="n">
-        <v>86.77</v>
+        <v>87.90000000000001</v>
       </c>
       <c r="E175" s="5" t="n">
-        <v>97.18000000000001</v>
+        <v>98.44</v>
       </c>
     </row>
     <row r="176">
@@ -9579,10 +9567,10 @@
         <v>49.82</v>
       </c>
       <c r="D176" s="5" t="n">
-        <v>66.15000000000001</v>
+        <v>67.01000000000001</v>
       </c>
       <c r="E176" s="5" t="n">
-        <v>63.16</v>
+        <v>63.98</v>
       </c>
     </row>
     <row r="177">
@@ -9598,10 +9586,10 @@
         <v>49.53</v>
       </c>
       <c r="D177" s="5" t="n">
-        <v>71.97</v>
+        <v>72.91</v>
       </c>
       <c r="E177" s="5" t="n">
-        <v>62.72</v>
+        <v>63.53</v>
       </c>
     </row>
     <row r="178">
@@ -9617,10 +9605,10 @@
         <v>38.95</v>
       </c>
       <c r="D178" s="5" t="n">
-        <v>49.45</v>
+        <v>50.09</v>
       </c>
       <c r="E178" s="5" t="n">
-        <v>49.26</v>
+        <v>49.9</v>
       </c>
     </row>
     <row r="179">
@@ -9636,10 +9624,10 @@
         <v>34.97</v>
       </c>
       <c r="D179" s="5" t="n">
-        <v>47.2</v>
+        <v>47.82</v>
       </c>
       <c r="E179" s="5" t="n">
-        <v>44.17</v>
+        <v>44.74</v>
       </c>
     </row>
     <row r="180">
@@ -9655,10 +9643,10 @@
         <v>24.19</v>
       </c>
       <c r="D180" s="5" t="n">
-        <v>29.71</v>
+        <v>30.1</v>
       </c>
       <c r="E180" s="5" t="n">
-        <v>30.75</v>
+        <v>31.15</v>
       </c>
     </row>
     <row r="181">
@@ -9674,10 +9662,10 @@
         <v>40.61</v>
       </c>
       <c r="D181" s="5" t="n">
-        <v>44.49</v>
+        <v>45.07</v>
       </c>
       <c r="E181" s="5" t="n">
-        <v>51.96</v>
+        <v>52.64</v>
       </c>
     </row>
     <row r="182">
@@ -9693,10 +9681,10 @@
         <v>39.02</v>
       </c>
       <c r="D182" s="5" t="n">
-        <v>46.89</v>
+        <v>47.5</v>
       </c>
       <c r="E182" s="5" t="n">
-        <v>50.25</v>
+        <v>50.91</v>
       </c>
     </row>
     <row r="183">
@@ -9712,10 +9700,10 @@
         <v>57.29</v>
       </c>
       <c r="D183" s="5" t="n">
-        <v>72.52</v>
+        <v>73.45999999999999</v>
       </c>
       <c r="E183" s="5" t="n">
-        <v>73.40000000000001</v>
+        <v>74.36</v>
       </c>
     </row>
     <row r="184">
@@ -9731,10 +9719,10 @@
         <v>56.57</v>
       </c>
       <c r="D184" s="5" t="n">
-        <v>71.06999999999999</v>
+        <v>71.98999999999999</v>
       </c>
       <c r="E184" s="5" t="n">
-        <v>72.11</v>
+        <v>73.05</v>
       </c>
     </row>
     <row r="185">
@@ -9750,10 +9738,10 @@
         <v>38.94</v>
       </c>
       <c r="D185" s="5" t="n">
-        <v>47.58</v>
+        <v>48.2</v>
       </c>
       <c r="E185" s="5" t="n">
-        <v>49.39</v>
+        <v>50.03</v>
       </c>
     </row>
     <row r="186">
@@ -9769,10 +9757,10 @@
         <v>37.37</v>
       </c>
       <c r="D186" s="5" t="n">
-        <v>52.49</v>
+        <v>53.17</v>
       </c>
       <c r="E186" s="5" t="n">
-        <v>47.25</v>
+        <v>47.87</v>
       </c>
     </row>
     <row r="187">
@@ -9788,10 +9776,10 @@
         <v>57.08</v>
       </c>
       <c r="D187" s="5" t="n">
-        <v>74.84</v>
+        <v>75.81999999999999</v>
       </c>
       <c r="E187" s="5" t="n">
-        <v>71.95999999999999</v>
+        <v>72.89</v>
       </c>
     </row>
     <row r="188">
@@ -9807,10 +9795,10 @@
         <v>43.26</v>
       </c>
       <c r="D188" s="5" t="n">
-        <v>46.33</v>
+        <v>46.93</v>
       </c>
       <c r="E188" s="5" t="n">
-        <v>54.37</v>
+        <v>55.08</v>
       </c>
     </row>
     <row r="189">
@@ -9826,10 +9814,10 @@
         <v>40.03</v>
       </c>
       <c r="D189" s="5" t="n">
-        <v>47.43</v>
+        <v>48.05</v>
       </c>
       <c r="E189" s="5" t="n">
-        <v>50.22</v>
+        <v>50.87</v>
       </c>
     </row>
     <row r="190">
@@ -9845,10 +9833,10 @@
         <v>36.7</v>
       </c>
       <c r="D190" s="5" t="n">
-        <v>40.05</v>
+        <v>40.57</v>
       </c>
       <c r="E190" s="5" t="n">
-        <v>45.95</v>
+        <v>46.55</v>
       </c>
     </row>
     <row r="191">
@@ -9864,10 +9852,10 @@
         <v>31.5</v>
       </c>
       <c r="D191" s="5" t="n">
-        <v>38.46</v>
+        <v>38.96</v>
       </c>
       <c r="E191" s="5" t="n">
-        <v>39.36</v>
+        <v>39.88</v>
       </c>
     </row>
     <row r="192">
@@ -9883,10 +9871,10 @@
         <v>28.45</v>
       </c>
       <c r="D192" s="5" t="n">
-        <v>31.59</v>
+        <v>32</v>
       </c>
       <c r="E192" s="5" t="n">
-        <v>35.47</v>
+        <v>35.93</v>
       </c>
     </row>
     <row r="193">
@@ -9902,10 +9890,10 @@
         <v>44.32</v>
       </c>
       <c r="D193" s="5" t="n">
-        <v>51.3</v>
+        <v>51.96</v>
       </c>
       <c r="E193" s="5" t="n">
-        <v>55.12</v>
+        <v>55.83</v>
       </c>
     </row>
     <row r="194">
@@ -9921,10 +9909,10 @@
         <v>77.62</v>
       </c>
       <c r="D194" s="5" t="n">
-        <v>85.45</v>
+        <v>86.56</v>
       </c>
       <c r="E194" s="5" t="n">
-        <v>96.29000000000001</v>
+        <v>97.55</v>
       </c>
     </row>
     <row r="195">
@@ -9940,10 +9928,10 @@
         <v>42.75</v>
       </c>
       <c r="D195" s="5" t="n">
-        <v>47.19</v>
+        <v>47.81</v>
       </c>
       <c r="E195" s="5" t="n">
-        <v>52.88</v>
+        <v>53.57</v>
       </c>
     </row>
     <row r="196">
@@ -9959,10 +9947,10 @@
         <v>24.96</v>
       </c>
       <c r="D196" s="5" t="n">
-        <v>26.47</v>
+        <v>26.82</v>
       </c>
       <c r="E196" s="5" t="n">
-        <v>30.79</v>
+        <v>31.19</v>
       </c>
     </row>
     <row r="197">
@@ -9978,10 +9966,10 @@
         <v>21.88</v>
       </c>
       <c r="D197" s="5" t="n">
-        <v>20.32</v>
+        <v>20.59</v>
       </c>
       <c r="E197" s="5" t="n">
-        <v>26.92</v>
+        <v>27.27</v>
       </c>
     </row>
     <row r="198">
@@ -9997,10 +9985,10 @@
         <v>9.68</v>
       </c>
       <c r="D198" s="5" t="n">
-        <v>11.49</v>
+        <v>11.64</v>
       </c>
       <c r="E198" s="5" t="n">
-        <v>11.86</v>
+        <v>12.01</v>
       </c>
     </row>
     <row r="199">
@@ -10016,10 +10004,10 @@
         <v>33.48</v>
       </c>
       <c r="D199" s="5" t="n">
-        <v>38.74</v>
+        <v>39.24</v>
       </c>
       <c r="E199" s="5" t="n">
-        <v>40.84</v>
+        <v>41.37</v>
       </c>
     </row>
     <row r="200">
@@ -10035,10 +10023,10 @@
         <v>50.7</v>
       </c>
       <c r="D200" s="5" t="n">
-        <v>60.55</v>
+        <v>61.34</v>
       </c>
       <c r="E200" s="5" t="n">
-        <v>61.58</v>
+        <v>62.38</v>
       </c>
     </row>
     <row r="201">
@@ -10054,10 +10042,10 @@
         <v>66.73999999999999</v>
       </c>
       <c r="D201" s="5" t="n">
-        <v>75.42</v>
+        <v>76.40000000000001</v>
       </c>
       <c r="E201" s="5" t="n">
-        <v>80.48999999999999</v>
+        <v>81.53</v>
       </c>
     </row>
     <row r="202">
@@ -10073,10 +10061,10 @@
         <v>78.06999999999999</v>
       </c>
       <c r="D202" s="5" t="n">
-        <v>86.45999999999999</v>
+        <v>87.59</v>
       </c>
       <c r="E202" s="5" t="n">
-        <v>93.48</v>
+        <v>94.7</v>
       </c>
     </row>
     <row r="203">
@@ -10092,10 +10080,10 @@
         <v>78.65000000000001</v>
       </c>
       <c r="D203" s="5" t="n">
-        <v>88.97</v>
+        <v>90.13</v>
       </c>
       <c r="E203" s="5" t="n">
-        <v>93.51000000000001</v>
+        <v>94.73</v>
       </c>
     </row>
     <row r="204">
@@ -10111,10 +10099,10 @@
         <v>164.79</v>
       </c>
       <c r="D204" s="5" t="n">
-        <v>166.97</v>
+        <v>169.14</v>
       </c>
       <c r="E204" s="5" t="n">
-        <v>194.77</v>
+        <v>197.3</v>
       </c>
     </row>
     <row r="205">
@@ -10130,10 +10118,10 @@
         <v>241.85</v>
       </c>
       <c r="D205" s="5" t="n">
-        <v>255.19</v>
+        <v>258.5</v>
       </c>
       <c r="E205" s="5" t="n">
-        <v>284.16</v>
+        <v>287.85</v>
       </c>
     </row>
     <row r="206">
@@ -10149,10 +10137,10 @@
         <v>382.13</v>
       </c>
       <c r="D206" s="5" t="n">
-        <v>334.94</v>
+        <v>339.29</v>
       </c>
       <c r="E206" s="5" t="n">
-        <v>446.35</v>
+        <v>452.15</v>
       </c>
     </row>
     <row r="207">
@@ -10168,10 +10156,10 @@
         <v>366</v>
       </c>
       <c r="D207" s="5" t="n">
-        <v>374.8</v>
+        <v>379.67</v>
       </c>
       <c r="E207" s="5" t="n">
-        <v>424.9</v>
+        <v>430.43</v>
       </c>
     </row>
     <row r="208">
@@ -10187,10 +10175,10 @@
         <v>169.02</v>
       </c>
       <c r="D208" s="5" t="n">
-        <v>172.52</v>
+        <v>174.76</v>
       </c>
       <c r="E208" s="5" t="n">
-        <v>195.03</v>
+        <v>197.57</v>
       </c>
     </row>
     <row r="209">
@@ -10206,10 +10194,10 @@
         <v>150.51</v>
       </c>
       <c r="D209" s="5" t="n">
-        <v>152.25</v>
+        <v>154.23</v>
       </c>
       <c r="E209" s="5" t="n">
-        <v>172.63</v>
+        <v>174.88</v>
       </c>
     </row>
     <row r="210">
@@ -10225,10 +10213,10 @@
         <v>126.49</v>
       </c>
       <c r="D210" s="5" t="n">
-        <v>139.07</v>
+        <v>140.88</v>
       </c>
       <c r="E210" s="5" t="n">
-        <v>144.19</v>
+        <v>146.07</v>
       </c>
     </row>
     <row r="211">
@@ -10244,10 +10232,10 @@
         <v>112.35</v>
       </c>
       <c r="D211" s="5" t="n">
-        <v>114.41</v>
+        <v>115.9</v>
       </c>
       <c r="E211" s="5" t="n">
-        <v>127.29</v>
+        <v>128.95</v>
       </c>
     </row>
     <row r="212">
@@ -10263,10 +10251,10 @@
         <v>67.38</v>
       </c>
       <c r="D212" s="5" t="n">
-        <v>85.98999999999999</v>
+        <v>87.11</v>
       </c>
       <c r="E212" s="5" t="n">
-        <v>75.88</v>
+        <v>76.87</v>
       </c>
     </row>
     <row r="213">
@@ -10282,10 +10270,10 @@
         <v>81.09</v>
       </c>
       <c r="D213" s="5" t="n">
-        <v>97.38</v>
+        <v>98.64</v>
       </c>
       <c r="E213" s="5" t="n">
-        <v>90.91</v>
+        <v>92.09</v>
       </c>
     </row>
     <row r="214">
@@ -10301,10 +10289,10 @@
         <v>76.56999999999999</v>
       </c>
       <c r="D214" s="5" t="n">
-        <v>90.98999999999999</v>
+        <v>92.18000000000001</v>
       </c>
       <c r="E214" s="5" t="n">
-        <v>85.45999999999999</v>
+        <v>86.56999999999999</v>
       </c>
     </row>
     <row r="215">
@@ -10320,10 +10308,10 @@
         <v>68.09999999999999</v>
       </c>
       <c r="D215" s="5" t="n">
-        <v>80.39</v>
+        <v>81.43000000000001</v>
       </c>
       <c r="E215" s="5" t="n">
-        <v>75.67</v>
+        <v>76.65000000000001</v>
       </c>
     </row>
     <row r="216">
@@ -10339,10 +10327,10 @@
         <v>70.91</v>
       </c>
       <c r="D216" s="5" t="n">
-        <v>77.59</v>
+        <v>78.59999999999999</v>
       </c>
       <c r="E216" s="5" t="n">
-        <v>78.56</v>
+        <v>79.58</v>
       </c>
     </row>
     <row r="217">
@@ -10358,10 +10346,10 @@
         <v>86.34999999999999</v>
       </c>
       <c r="D217" s="5" t="n">
-        <v>92.98</v>
+        <v>94.19</v>
       </c>
       <c r="E217" s="5" t="n">
-        <v>95.40000000000001</v>
+        <v>96.64</v>
       </c>
     </row>
     <row r="218">
@@ -10377,10 +10365,10 @@
         <v>52.09</v>
       </c>
       <c r="D218" s="5" t="n">
-        <v>41.91</v>
+        <v>42.45</v>
       </c>
       <c r="E218" s="5" t="n">
-        <v>57.38</v>
+        <v>58.13</v>
       </c>
     </row>
     <row r="219">
@@ -10396,10 +10384,10 @@
         <v>32.62</v>
       </c>
       <c r="D219" s="5" t="n">
-        <v>25.59</v>
+        <v>25.92</v>
       </c>
       <c r="E219" s="5" t="n">
-        <v>35.8</v>
+        <v>36.26</v>
       </c>
     </row>
     <row r="220">
@@ -10415,10 +10403,10 @@
         <v>37.77</v>
       </c>
       <c r="D220" s="5" t="n">
-        <v>41.16</v>
+        <v>41.7</v>
       </c>
       <c r="E220" s="5" t="n">
-        <v>41.29</v>
+        <v>41.83</v>
       </c>
     </row>
     <row r="221">
@@ -10434,10 +10422,10 @@
         <v>24.86</v>
       </c>
       <c r="D221" s="5" t="n">
-        <v>29.09</v>
+        <v>29.47</v>
       </c>
       <c r="E221" s="5" t="n">
-        <v>27.08</v>
+        <v>27.43</v>
       </c>
     </row>
     <row r="222">
@@ -10453,10 +10441,10 @@
         <v>36.02</v>
       </c>
       <c r="D222" s="5" t="n">
-        <v>40.93</v>
+        <v>41.46</v>
       </c>
       <c r="E222" s="5" t="n">
-        <v>39.15</v>
+        <v>39.66</v>
       </c>
     </row>
     <row r="223">
@@ -10472,10 +10460,10 @@
         <v>57.49</v>
       </c>
       <c r="D223" s="5" t="n">
-        <v>65.04000000000001</v>
+        <v>65.89</v>
       </c>
       <c r="E223" s="5" t="n">
-        <v>62.35</v>
+        <v>63.16</v>
       </c>
     </row>
     <row r="224">
@@ -10491,10 +10479,10 @@
         <v>49.09</v>
       </c>
       <c r="D224" s="5" t="n">
-        <v>56.38</v>
+        <v>57.11</v>
       </c>
       <c r="E224" s="5" t="n">
-        <v>53.13</v>
+        <v>53.82</v>
       </c>
     </row>
     <row r="225">
@@ -10510,10 +10498,10 @@
         <v>49.62</v>
       </c>
       <c r="D225" s="5" t="n">
-        <v>54.08</v>
+        <v>54.78</v>
       </c>
       <c r="E225" s="5" t="n">
-        <v>53.54</v>
+        <v>54.23</v>
       </c>
     </row>
     <row r="226">
@@ -10529,10 +10517,10 @@
         <v>110.18</v>
       </c>
       <c r="D226" s="5" t="n">
-        <v>88.05</v>
+        <v>89.2</v>
       </c>
       <c r="E226" s="5" t="n">
-        <v>118.51</v>
+        <v>120.05</v>
       </c>
     </row>
     <row r="227">
@@ -10548,10 +10536,10 @@
         <v>67.43000000000001</v>
       </c>
       <c r="D227" s="5" t="n">
-        <v>74.69</v>
+        <v>75.66</v>
       </c>
       <c r="E227" s="5" t="n">
-        <v>72.31</v>
+        <v>73.25</v>
       </c>
     </row>
     <row r="228">
@@ -10567,10 +10555,10 @@
         <v>70.53</v>
       </c>
       <c r="D228" s="5" t="n">
-        <v>78.38</v>
+        <v>79.40000000000001</v>
       </c>
       <c r="E228" s="5" t="n">
-        <v>75.37</v>
+        <v>76.34999999999999</v>
       </c>
     </row>
     <row r="229">
@@ -10586,10 +10574,10 @@
         <v>145.36</v>
       </c>
       <c r="D229" s="5" t="n">
-        <v>150.18</v>
+        <v>152.13</v>
       </c>
       <c r="E229" s="5" t="n">
-        <v>154.79</v>
+        <v>156.8</v>
       </c>
     </row>
     <row r="230">
@@ -10605,10 +10593,10 @@
         <v>212.7</v>
       </c>
       <c r="D230" s="5" t="n">
-        <v>189.16</v>
+        <v>191.62</v>
       </c>
       <c r="E230" s="5" t="n">
-        <v>225.72</v>
+        <v>228.65</v>
       </c>
     </row>
     <row r="231">
@@ -10624,10 +10612,10 @@
         <v>215.33</v>
       </c>
       <c r="D231" s="5" t="n">
-        <v>191.68</v>
+        <v>194.17</v>
       </c>
       <c r="E231" s="5" t="n">
-        <v>228.34</v>
+        <v>231.31</v>
       </c>
     </row>
     <row r="232">
@@ -10643,10 +10631,10 @@
         <v>155.78</v>
       </c>
       <c r="D232" s="5" t="n">
-        <v>136.37</v>
+        <v>138.14</v>
       </c>
       <c r="E232" s="5" t="n">
-        <v>165.07</v>
+        <v>167.22</v>
       </c>
     </row>
     <row r="233">
@@ -10662,10 +10650,10 @@
         <v>31.21</v>
       </c>
       <c r="D233" s="5" t="n">
-        <v>23.84</v>
+        <v>24.15</v>
       </c>
       <c r="E233" s="5" t="n">
-        <v>33.05</v>
+        <v>33.48</v>
       </c>
     </row>
     <row r="234">
@@ -10681,10 +10669,10 @@
         <v>52.54</v>
       </c>
       <c r="D234" s="5" t="n">
-        <v>52.7</v>
+        <v>53.38</v>
       </c>
       <c r="E234" s="5" t="n">
-        <v>55.6</v>
+        <v>56.32</v>
       </c>
     </row>
     <row r="235">
@@ -10700,10 +10688,10 @@
         <v>96.67</v>
       </c>
       <c r="D235" s="5" t="n">
-        <v>101.37</v>
+        <v>102.69</v>
       </c>
       <c r="E235" s="5" t="n">
-        <v>102.23</v>
+        <v>103.56</v>
       </c>
     </row>
     <row r="236">
@@ -10719,10 +10707,10 @@
         <v>68.69</v>
       </c>
       <c r="D236" s="5" t="n">
-        <v>80.43000000000001</v>
+        <v>81.48</v>
       </c>
       <c r="E236" s="5" t="n">
-        <v>72.59</v>
+        <v>73.54000000000001</v>
       </c>
     </row>
     <row r="237">
@@ -10738,10 +10726,10 @@
         <v>109.16</v>
       </c>
       <c r="D237" s="5" t="n">
-        <v>119.72</v>
+        <v>121.28</v>
       </c>
       <c r="E237" s="5" t="n">
-        <v>115.01</v>
+        <v>116.5</v>
       </c>
     </row>
     <row r="238">
@@ -10757,10 +10745,10 @@
         <v>124.99</v>
       </c>
       <c r="D238" s="5" t="n">
-        <v>127.82</v>
+        <v>129.48</v>
       </c>
       <c r="E238" s="5" t="n">
-        <v>131.29</v>
+        <v>132.99</v>
       </c>
     </row>
     <row r="239">
@@ -10776,10 +10764,10 @@
         <v>100.72</v>
       </c>
       <c r="D239" s="5" t="n">
-        <v>104.76</v>
+        <v>106.12</v>
       </c>
       <c r="E239" s="5" t="n">
-        <v>105.47</v>
+        <v>106.84</v>
       </c>
     </row>
     <row r="240">
@@ -10795,10 +10783,10 @@
         <v>98.45999999999999</v>
       </c>
       <c r="D240" s="5" t="n">
-        <v>105.01</v>
+        <v>106.38</v>
       </c>
       <c r="E240" s="5" t="n">
-        <v>102.85</v>
+        <v>104.19</v>
       </c>
     </row>
     <row r="241">
@@ -10814,10 +10802,10 @@
         <v>113.21</v>
       </c>
       <c r="D241" s="5" t="n">
-        <v>107.73</v>
+        <v>109.13</v>
       </c>
       <c r="E241" s="5" t="n">
-        <v>117.96</v>
+        <v>119.5</v>
       </c>
     </row>
     <row r="242">
@@ -10833,10 +10821,10 @@
         <v>327.6</v>
       </c>
       <c r="D242" s="5" t="n">
-        <v>227.99</v>
+        <v>230.95</v>
       </c>
       <c r="E242" s="5" t="n">
-        <v>340.51</v>
+        <v>344.94</v>
       </c>
     </row>
     <row r="243">
@@ -10852,10 +10840,10 @@
         <v>130.22</v>
       </c>
       <c r="D243" s="5" t="n">
-        <v>121.96</v>
+        <v>123.54</v>
       </c>
       <c r="E243" s="5" t="n">
-        <v>134.76</v>
+        <v>136.51</v>
       </c>
     </row>
     <row r="244">
@@ -10871,10 +10859,10 @@
         <v>133.43</v>
       </c>
       <c r="D244" s="5" t="n">
-        <v>129.02</v>
+        <v>130.7</v>
       </c>
       <c r="E244" s="5" t="n">
-        <v>137.48</v>
+        <v>139.27</v>
       </c>
     </row>
     <row r="245">
@@ -10890,10 +10878,10 @@
         <v>36.13</v>
       </c>
       <c r="D245" s="5" t="n">
-        <v>29.37</v>
+        <v>29.75</v>
       </c>
       <c r="E245" s="5" t="n">
-        <v>37.06</v>
+        <v>37.55</v>
       </c>
     </row>
     <row r="246">
@@ -10909,10 +10897,10 @@
         <v>26.88</v>
       </c>
       <c r="D246" s="5" t="n">
-        <v>25.14</v>
+        <v>25.46</v>
       </c>
       <c r="E246" s="5" t="n">
-        <v>27.52</v>
+        <v>27.88</v>
       </c>
     </row>
     <row r="247">
@@ -10928,10 +10916,10 @@
         <v>34.33</v>
       </c>
       <c r="D247" s="5" t="n">
-        <v>41.39</v>
+        <v>41.93</v>
       </c>
       <c r="E247" s="5" t="n">
-        <v>35.08</v>
+        <v>35.54</v>
       </c>
     </row>
     <row r="248">
@@ -10947,10 +10935,10 @@
         <v>55.59</v>
       </c>
       <c r="D248" s="5" t="n">
-        <v>60.52</v>
+        <v>61.3</v>
       </c>
       <c r="E248" s="5" t="n">
-        <v>56.69</v>
+        <v>57.43</v>
       </c>
     </row>
     <row r="249">
@@ -10966,10 +10954,10 @@
         <v>114.92</v>
       </c>
       <c r="D249" s="5" t="n">
-        <v>102.46</v>
+        <v>103.79</v>
       </c>
       <c r="E249" s="5" t="n">
-        <v>116.66</v>
+        <v>118.18</v>
       </c>
     </row>
     <row r="250">
@@ -10985,10 +10973,10 @@
         <v>87.54000000000001</v>
       </c>
       <c r="D250" s="5" t="n">
-        <v>91.23</v>
+        <v>92.42</v>
       </c>
       <c r="E250" s="5" t="n">
-        <v>88.47</v>
+        <v>89.62</v>
       </c>
     </row>
     <row r="251">
@@ -11004,10 +10992,10 @@
         <v>90.92</v>
       </c>
       <c r="D251" s="5" t="n">
-        <v>91.59</v>
+        <v>92.78</v>
       </c>
       <c r="E251" s="5" t="n">
-        <v>91.47</v>
+        <v>92.65000000000001</v>
       </c>
     </row>
     <row r="252">
@@ -11023,10 +11011,10 @@
         <v>87.29000000000001</v>
       </c>
       <c r="D252" s="5" t="n">
-        <v>85.58</v>
+        <v>86.69</v>
       </c>
       <c r="E252" s="5" t="n">
-        <v>87.64</v>
+        <v>88.78</v>
       </c>
     </row>
     <row r="253">
@@ -11042,10 +11030,10 @@
         <v>100.05</v>
       </c>
       <c r="D253" s="5" t="n">
-        <v>96.33</v>
+        <v>97.58</v>
       </c>
       <c r="E253" s="5" t="n">
-        <v>100.25</v>
+        <v>101.55</v>
       </c>
     </row>
     <row r="254">
@@ -11061,10 +11049,10 @@
         <v>81.67</v>
       </c>
       <c r="D254" s="5" t="n">
-        <v>76.83</v>
+        <v>77.83</v>
       </c>
       <c r="E254" s="5" t="n">
-        <v>81.67</v>
+        <v>82.73</v>
       </c>
     </row>
     <row r="255">
@@ -11080,10 +11068,10 @@
         <v>93.72</v>
       </c>
       <c r="D255" s="5" t="n">
-        <v>71.04000000000001</v>
+        <v>71.65000000000001</v>
       </c>
       <c r="E255" s="5" t="n">
-        <v>93.72</v>
+        <v>94.53</v>
       </c>
     </row>
     <row r="256">
@@ -11099,10 +11087,10 @@
         <v>65.73</v>
       </c>
       <c r="D256" s="5" t="n">
-        <v>57.95</v>
+        <v>58.2</v>
       </c>
       <c r="E256" s="5" t="n">
-        <v>65.73</v>
+        <v>66.01000000000001</v>
       </c>
     </row>
     <row r="257">
